--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616E9CC8-9B6A-49D6-8B4C-1FED2B488999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BA6C7-9256-42A2-9AA9-0704DA6D9261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="918">
   <si>
     <t>Recensore</t>
   </si>
@@ -3697,19 +3697,19 @@
       </c>
       <c r="E3" s="7">
         <f>+AH6</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>10</v>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E4" s="10">
         <f>+AI6</f>
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3761,15 +3761,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1958)</f>
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -3874,11 +3874,11 @@
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5487,49 +5487,55 @@
       <c r="AT19" s="13"/>
     </row>
     <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
-        <v>0</v>
-      </c>
-      <c r="B20" s="20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="20">
+      <c r="A20" s="33">
+        <v>0</v>
+      </c>
+      <c r="B20" s="33">
+        <v>1</v>
+      </c>
+      <c r="C20" s="33">
         <v>2</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="20" t="s">
+      <c r="J20" s="33">
+        <v>1</v>
+      </c>
+      <c r="K20" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L20" s="20" t="s">
+      <c r="L20" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="34" t="s">
         <v>732</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="18"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="19"/>
+      <c r="N20" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O20" s="35">
+        <v>1</v>
+      </c>
+      <c r="P20" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="34"/>
       <c r="R20" s="13"/>
       <c r="S20" s="2">
         <f t="shared" si="7"/>
@@ -5574,7 +5580,7 @@
       <c r="AC20" s="2"/>
       <c r="AD20" s="2">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="2">
         <f t="shared" si="18"/>
@@ -5582,7 +5588,7 @@
       </c>
       <c r="AF20" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="2">
         <f t="shared" si="4"/>
@@ -5590,11 +5596,11 @@
       </c>
       <c r="AH20" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="13"/>
       <c r="AK20" s="13"/>
@@ -5731,49 +5737,55 @@
       <c r="AT21" s="13"/>
     </row>
     <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
-        <v>0</v>
-      </c>
-      <c r="B22" s="20">
-        <v>1</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="A22" s="33">
+        <v>0</v>
+      </c>
+      <c r="B22" s="33">
+        <v>1</v>
+      </c>
+      <c r="C22" s="33">
         <v>2</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="J22" s="20">
-        <v>1</v>
-      </c>
-      <c r="K22" s="20" t="s">
+      <c r="J22" s="33">
+        <v>1</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="34" t="s">
         <v>685</v>
       </c>
-      <c r="N22" s="19"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="19"/>
+      <c r="N22" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O22" s="35">
+        <v>1</v>
+      </c>
+      <c r="P22" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="34"/>
       <c r="R22" s="13"/>
       <c r="S22" s="2">
         <f t="shared" si="7"/>
@@ -5818,7 +5830,7 @@
       <c r="AC22" s="2"/>
       <c r="AD22" s="2">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" s="2">
         <f t="shared" si="18"/>
@@ -5826,7 +5838,7 @@
       </c>
       <c r="AF22" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="2">
         <f t="shared" si="4"/>
@@ -5834,11 +5846,11 @@
       </c>
       <c r="AH22" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="13"/>
       <c r="AK22" s="13"/>
@@ -26167,51 +26179,55 @@
       <c r="AT186" s="13"/>
     </row>
     <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="30">
-        <v>0</v>
-      </c>
-      <c r="B187" s="30">
+      <c r="A187" s="33">
+        <v>0</v>
+      </c>
+      <c r="B187" s="33">
         <v>2</v>
       </c>
-      <c r="C187" s="30">
+      <c r="C187" s="33">
         <v>7</v>
       </c>
-      <c r="D187" s="31" t="s">
+      <c r="D187" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E187" s="31" t="s">
+      <c r="E187" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F187" s="31" t="s">
+      <c r="F187" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="G187" s="31" t="s">
+      <c r="G187" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H187" s="31" t="s">
+      <c r="H187" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I187" s="30" t="s">
+      <c r="I187" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="J187" s="30">
+      <c r="J187" s="33">
         <v>2</v>
       </c>
-      <c r="K187" s="30" t="s">
+      <c r="K187" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L187" s="30" t="s">
+      <c r="L187" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="M187" s="31" t="s">
+      <c r="M187" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="N187" s="31"/>
-      <c r="O187" s="32"/>
-      <c r="P187" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q187" s="31"/>
+      <c r="N187" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O187" s="35">
+        <v>1</v>
+      </c>
+      <c r="P187" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q187" s="34"/>
       <c r="R187" s="13"/>
       <c r="S187" s="2">
         <f t="shared" si="51"/>
@@ -26256,7 +26272,7 @@
       <c r="AC187" s="2"/>
       <c r="AD187" s="2">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE187" s="2">
         <f t="shared" si="62"/>
@@ -26264,7 +26280,7 @@
       </c>
       <c r="AF187" s="2">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG187" s="2">
         <f t="shared" si="48"/>
@@ -29265,51 +29281,55 @@
       <c r="AT211" s="13"/>
     </row>
     <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="30">
-        <v>0</v>
-      </c>
-      <c r="B212" s="30">
+      <c r="A212" s="33">
+        <v>0</v>
+      </c>
+      <c r="B212" s="33">
         <v>2</v>
       </c>
-      <c r="C212" s="30">
+      <c r="C212" s="33">
         <v>7</v>
       </c>
-      <c r="D212" s="31" t="s">
+      <c r="D212" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="E212" s="31" t="s">
+      <c r="E212" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F212" s="31" t="s">
+      <c r="F212" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="G212" s="31" t="s">
+      <c r="G212" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H212" s="31" t="s">
+      <c r="H212" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I212" s="30" t="s">
+      <c r="I212" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="J212" s="30">
+      <c r="J212" s="33">
         <v>2</v>
       </c>
-      <c r="K212" s="30" t="s">
+      <c r="K212" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L212" s="30" t="s">
+      <c r="L212" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="M212" s="31" t="s">
+      <c r="M212" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="N212" s="31"/>
-      <c r="O212" s="32"/>
-      <c r="P212" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q212" s="31"/>
+      <c r="N212" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O212" s="35">
+        <v>1</v>
+      </c>
+      <c r="P212" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q212" s="34"/>
       <c r="R212" s="13"/>
       <c r="S212" s="2">
         <f t="shared" ref="S212:S217" si="67">IF(J212=$S$7,1,0)</f>
@@ -29354,7 +29374,7 @@
       <c r="AC212" s="2"/>
       <c r="AD212" s="2">
         <f t="shared" ref="AD212:AD217" si="77">+O212*P212</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE212" s="2">
         <f t="shared" ref="AE212:AE217" si="78">O212*(1-P212)</f>
@@ -29362,7 +29382,7 @@
       </c>
       <c r="AF212" s="2">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG212" s="2">
         <f t="shared" si="64"/>
@@ -29389,51 +29409,55 @@
       <c r="AT212" s="13"/>
     </row>
     <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="30">
-        <v>1</v>
-      </c>
-      <c r="B213" s="30">
+      <c r="A213" s="33">
+        <v>1</v>
+      </c>
+      <c r="B213" s="33">
         <v>2</v>
       </c>
-      <c r="C213" s="30">
+      <c r="C213" s="33">
         <v>7</v>
       </c>
-      <c r="D213" s="31" t="s">
+      <c r="D213" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="E213" s="31" t="s">
+      <c r="E213" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F213" s="31" t="s">
+      <c r="F213" s="34" t="s">
         <v>559</v>
       </c>
-      <c r="G213" s="31" t="s">
+      <c r="G213" s="34" t="s">
         <v>560</v>
       </c>
-      <c r="H213" s="31" t="s">
+      <c r="H213" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I213" s="30" t="s">
+      <c r="I213" s="33" t="s">
         <v>566</v>
       </c>
-      <c r="J213" s="30">
-        <v>1</v>
-      </c>
-      <c r="K213" s="30" t="s">
+      <c r="J213" s="33">
+        <v>1</v>
+      </c>
+      <c r="K213" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L213" s="30" t="s">
+      <c r="L213" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="M213" s="31" t="s">
+      <c r="M213" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="N213" s="31"/>
-      <c r="O213" s="32"/>
-      <c r="P213" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q213" s="31"/>
+      <c r="N213" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O213" s="35">
+        <v>1</v>
+      </c>
+      <c r="P213" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q213" s="34"/>
       <c r="R213" s="13"/>
       <c r="S213" s="2">
         <f t="shared" si="67"/>
@@ -29478,7 +29502,7 @@
       <c r="AC213" s="2"/>
       <c r="AD213" s="2">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE213" s="2">
         <f t="shared" si="78"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064BA6C7-9256-42A2-9AA9-0704DA6D9261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2B893-5296-4654-8C3A-3F40EDAD55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="918">
   <si>
     <t>Recensore</t>
   </si>
@@ -3697,15 +3697,15 @@
       </c>
       <c r="E3" s="7">
         <f>+AH6</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E4" s="10">
         <f>+AI6</f>
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3761,15 +3761,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1958)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -3874,11 +3874,11 @@
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="1"/>
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18036,49 +18036,55 @@
       <c r="AT120" s="13"/>
     </row>
     <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="20">
-        <v>0</v>
-      </c>
-      <c r="B121" s="20">
+      <c r="A121" s="33">
+        <v>0</v>
+      </c>
+      <c r="B121" s="33">
         <v>2</v>
       </c>
-      <c r="C121" s="20">
+      <c r="C121" s="33">
         <v>2</v>
       </c>
-      <c r="D121" s="19" t="s">
+      <c r="D121" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="E121" s="19" t="s">
+      <c r="E121" s="34" t="s">
         <v>410</v>
       </c>
-      <c r="F121" s="19" t="s">
+      <c r="F121" s="34" t="s">
         <v>411</v>
       </c>
-      <c r="G121" s="19" t="s">
+      <c r="G121" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H121" s="19" t="s">
+      <c r="H121" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I121" s="20" t="s">
+      <c r="I121" s="33" t="s">
         <v>412</v>
       </c>
-      <c r="J121" s="20">
-        <v>1</v>
-      </c>
-      <c r="K121" s="20" t="s">
+      <c r="J121" s="33">
+        <v>1</v>
+      </c>
+      <c r="K121" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L121" s="20" t="s">
+      <c r="L121" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="M121" s="19" t="s">
+      <c r="M121" s="34" t="s">
         <v>818</v>
       </c>
-      <c r="N121" s="19"/>
-      <c r="O121" s="18"/>
-      <c r="P121" s="20"/>
-      <c r="Q121" s="19"/>
+      <c r="N121" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O121" s="35">
+        <v>1</v>
+      </c>
+      <c r="P121" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="34"/>
       <c r="R121" s="13"/>
       <c r="S121" s="2">
         <f t="shared" si="23"/>
@@ -18123,7 +18129,7 @@
       <c r="AC121" s="2"/>
       <c r="AD121" s="2">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE121" s="2">
         <f t="shared" si="34"/>
@@ -18131,7 +18137,7 @@
       </c>
       <c r="AF121" s="2">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG121" s="2">
         <f t="shared" si="20"/>
@@ -18139,11 +18145,11 @@
       </c>
       <c r="AH121" s="2">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI121" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ121" s="13"/>
       <c r="AK121" s="13"/>
@@ -29910,50 +29916,57 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="20">
-        <v>0</v>
-      </c>
-      <c r="B217" s="20">
+    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="33">
+        <v>0</v>
+      </c>
+      <c r="B217" s="33">
         <v>2</v>
       </c>
-      <c r="C217" s="20">
+      <c r="C217" s="33">
         <v>7</v>
       </c>
-      <c r="D217" s="19" t="s">
+      <c r="D217" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="E217" s="19" t="s">
+      <c r="E217" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F217" s="19" t="s">
+      <c r="F217" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="G217" s="19" t="s">
+      <c r="G217" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H217" s="19" t="s">
+      <c r="H217" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I217" s="20" t="s">
+      <c r="I217" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="J217" s="20">
-        <v>1</v>
-      </c>
-      <c r="K217" s="20" t="s">
+      <c r="J217" s="33">
+        <v>1</v>
+      </c>
+      <c r="K217" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L217" s="20" t="s">
+      <c r="L217" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M217" s="19" t="s">
+      <c r="M217" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="N217" s="19"/>
-      <c r="O217" s="18"/>
-      <c r="P217" s="20"/>
-      <c r="Q217" s="19"/>
+      <c r="N217" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O217" s="35">
+        <v>1</v>
+      </c>
+      <c r="P217" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q217" s="34"/>
+      <c r="R217" s="13"/>
       <c r="S217" s="2">
         <f t="shared" si="67"/>
         <v>1</v>
@@ -29994,9 +30007,10 @@
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
+      <c r="AC217" s="2"/>
       <c r="AD217" s="2">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE217" s="2">
         <f t="shared" si="78"/>
@@ -30004,7 +30018,7 @@
       </c>
       <c r="AF217" s="2">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG217" s="2">
         <f t="shared" si="64"/>
@@ -30012,22 +30026,23 @@
       </c>
       <c r="AH217" s="2">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI217" s="2">
         <f t="shared" si="66"/>
-        <v>1</v>
-      </c>
-      <c r="AK217" s="3"/>
-      <c r="AL217" s="3"/>
-      <c r="AM217" s="3"/>
-      <c r="AN217" s="3"/>
-      <c r="AO217" s="3"/>
-      <c r="AP217" s="3"/>
-      <c r="AQ217" s="3"/>
-      <c r="AR217" s="3"/>
-      <c r="AS217" s="3"/>
-      <c r="AT217" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ217" s="13"/>
+      <c r="AK217" s="13"/>
+      <c r="AL217" s="13"/>
+      <c r="AM217" s="13"/>
+      <c r="AN217" s="13"/>
+      <c r="AO217" s="13"/>
+      <c r="AP217" s="13"/>
+      <c r="AQ217" s="13"/>
+      <c r="AR217" s="13"/>
+      <c r="AS217" s="13"/>
+      <c r="AT217" s="13"/>
     </row>
     <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E2B893-5296-4654-8C3A-3F40EDAD55F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5314CD3E-E41C-43B3-9C86-83E100360B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="918">
   <si>
     <t>Recensore</t>
   </si>
@@ -3697,15 +3697,15 @@
       </c>
       <c r="E3" s="7">
         <f>+AH6</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E4" s="10">
         <f>+AI6</f>
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3761,15 +3761,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1958)</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -3874,11 +3874,11 @@
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="1"/>
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -21380,49 +21380,55 @@
       <c r="AT147" s="13"/>
     </row>
     <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="20">
-        <v>0</v>
-      </c>
-      <c r="B148" s="20">
+      <c r="A148" s="33">
+        <v>0</v>
+      </c>
+      <c r="B148" s="33">
         <v>2</v>
       </c>
-      <c r="C148" s="20">
+      <c r="C148" s="33">
         <v>4</v>
       </c>
-      <c r="D148" s="19" t="s">
+      <c r="D148" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="E148" s="19" t="s">
+      <c r="E148" s="34" t="s">
         <v>554</v>
       </c>
-      <c r="F148" s="19" t="s">
+      <c r="F148" s="34" t="s">
         <v>557</v>
       </c>
-      <c r="G148" s="19" t="s">
+      <c r="G148" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H148" s="19" t="s">
+      <c r="H148" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I148" s="20" t="s">
+      <c r="I148" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="J148" s="20">
+      <c r="J148" s="33">
         <v>2</v>
       </c>
-      <c r="K148" s="20" t="s">
+      <c r="K148" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L148" s="20" t="s">
+      <c r="L148" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="M148" s="19" t="s">
+      <c r="M148" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="N148" s="19"/>
-      <c r="O148" s="18"/>
-      <c r="P148" s="20"/>
-      <c r="Q148" s="19"/>
+      <c r="N148" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O148" s="35">
+        <v>1</v>
+      </c>
+      <c r="P148" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q148" s="34"/>
       <c r="R148" s="13"/>
       <c r="S148" s="2">
         <f t="shared" si="35"/>
@@ -21467,7 +21473,7 @@
       <c r="AC148" s="2"/>
       <c r="AD148" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE148" s="2">
         <f t="shared" si="46"/>
@@ -21475,7 +21481,7 @@
       </c>
       <c r="AF148" s="2">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG148" s="2">
         <f t="shared" si="48"/>
@@ -21483,11 +21489,11 @@
       </c>
       <c r="AH148" s="2">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI148" s="2">
         <f t="shared" si="50"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ148" s="13"/>
       <c r="AK148" s="13"/>
@@ -25448,49 +25454,55 @@
       <c r="AT180" s="13"/>
     </row>
     <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="20">
-        <v>0</v>
-      </c>
-      <c r="B181" s="20">
+      <c r="A181" s="33">
+        <v>0</v>
+      </c>
+      <c r="B181" s="33">
         <v>2</v>
       </c>
-      <c r="C181" s="20">
+      <c r="C181" s="33">
         <v>7</v>
       </c>
-      <c r="D181" s="19" t="s">
+      <c r="D181" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="E181" s="19" t="s">
+      <c r="E181" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F181" s="19" t="s">
+      <c r="F181" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="G181" s="19" t="s">
+      <c r="G181" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H181" s="19" t="s">
+      <c r="H181" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I181" s="20" t="s">
+      <c r="I181" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="J181" s="20">
+      <c r="J181" s="33">
         <v>3</v>
       </c>
-      <c r="K181" s="20" t="s">
+      <c r="K181" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L181" s="20" t="s">
+      <c r="L181" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M181" s="19" t="s">
+      <c r="M181" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="N181" s="19"/>
-      <c r="O181" s="18"/>
-      <c r="P181" s="20"/>
-      <c r="Q181" s="19"/>
+      <c r="N181" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O181" s="35">
+        <v>1</v>
+      </c>
+      <c r="P181" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q181" s="34"/>
       <c r="R181" s="13"/>
       <c r="S181" s="2">
         <f t="shared" ref="S181:S211" si="51">IF(J181=$S$7,1,0)</f>
@@ -25535,7 +25547,7 @@
       <c r="AC181" s="2"/>
       <c r="AD181" s="2">
         <f t="shared" ref="AD181:AD211" si="61">+O181*P181</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE181" s="2">
         <f t="shared" ref="AE181:AE211" si="62">O181*(1-P181)</f>
@@ -25543,7 +25555,7 @@
       </c>
       <c r="AF181" s="2">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG181" s="2">
         <f t="shared" si="48"/>
@@ -25551,11 +25563,11 @@
       </c>
       <c r="AH181" s="2">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI181" s="2">
         <f t="shared" si="50"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ181" s="13"/>
       <c r="AK181" s="13"/>
@@ -25570,49 +25582,55 @@
       <c r="AT181" s="13"/>
     </row>
     <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="20">
-        <v>1</v>
-      </c>
-      <c r="B182" s="20">
+      <c r="A182" s="33">
+        <v>1</v>
+      </c>
+      <c r="B182" s="33">
         <v>2</v>
       </c>
-      <c r="C182" s="20">
+      <c r="C182" s="33">
         <v>7</v>
       </c>
-      <c r="D182" s="19" t="s">
+      <c r="D182" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="E182" s="19" t="s">
+      <c r="E182" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F182" s="19" t="s">
+      <c r="F182" s="34" t="s">
         <v>365</v>
       </c>
-      <c r="G182" s="19" t="s">
+      <c r="G182" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H182" s="19" t="s">
+      <c r="H182" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I182" s="20" t="s">
+      <c r="I182" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="J182" s="20">
+      <c r="J182" s="33">
         <v>7</v>
       </c>
-      <c r="K182" s="20" t="s">
+      <c r="K182" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L182" s="20" t="s">
+      <c r="L182" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M182" s="19" t="s">
+      <c r="M182" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="N182" s="19"/>
-      <c r="O182" s="18"/>
-      <c r="P182" s="20"/>
-      <c r="Q182" s="19"/>
+      <c r="N182" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O182" s="35">
+        <v>1</v>
+      </c>
+      <c r="P182" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q182" s="34"/>
       <c r="R182" s="13"/>
       <c r="S182" s="2">
         <f t="shared" si="51"/>
@@ -25657,7 +25675,7 @@
       <c r="AC182" s="2"/>
       <c r="AD182" s="2">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE182" s="2">
         <f t="shared" si="62"/>
@@ -27307,49 +27325,55 @@
       <c r="AT195" s="13"/>
     </row>
     <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="20">
-        <v>0</v>
-      </c>
-      <c r="B196" s="20">
+      <c r="A196" s="33">
+        <v>0</v>
+      </c>
+      <c r="B196" s="33">
         <v>2</v>
       </c>
-      <c r="C196" s="20">
+      <c r="C196" s="33">
         <v>7</v>
       </c>
-      <c r="D196" s="19" t="s">
+      <c r="D196" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="E196" s="19" t="s">
+      <c r="E196" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F196" s="19" t="s">
+      <c r="F196" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="G196" s="19" t="s">
+      <c r="G196" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H196" s="19" t="s">
+      <c r="H196" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I196" s="20" t="s">
+      <c r="I196" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="J196" s="20">
+      <c r="J196" s="33">
         <v>3</v>
       </c>
-      <c r="K196" s="20" t="s">
+      <c r="K196" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L196" s="20" t="s">
+      <c r="L196" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="M196" s="19" t="s">
+      <c r="M196" s="34" t="s">
         <v>387</v>
       </c>
-      <c r="N196" s="19"/>
-      <c r="O196" s="18"/>
-      <c r="P196" s="20"/>
-      <c r="Q196" s="19"/>
+      <c r="N196" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O196" s="35">
+        <v>1</v>
+      </c>
+      <c r="P196" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q196" s="34"/>
       <c r="R196" s="13"/>
       <c r="S196" s="2">
         <f t="shared" si="51"/>
@@ -27394,7 +27418,7 @@
       <c r="AC196" s="2"/>
       <c r="AD196" s="2">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE196" s="2">
         <f t="shared" si="62"/>
@@ -27402,7 +27426,7 @@
       </c>
       <c r="AF196" s="2">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG196" s="2">
         <f t="shared" si="48"/>
@@ -27410,11 +27434,11 @@
       </c>
       <c r="AH196" s="2">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI196" s="2">
         <f t="shared" si="50"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ196" s="13"/>
       <c r="AK196" s="13"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5314CD3E-E41C-43B3-9C86-83E100360B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DB5FED-2FD8-4E14-BEA4-9694C07AACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="918">
   <si>
     <t>Recensore</t>
   </si>
@@ -3701,15 +3701,15 @@
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="7">
         <f>+E3-G3</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>10</v>
@@ -3761,15 +3761,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AD6" s="2">
         <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1958)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
@@ -17040,51 +17040,55 @@
       <c r="AT112" s="13"/>
     </row>
     <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="30">
-        <v>0</v>
-      </c>
-      <c r="B113" s="30">
+      <c r="A113" s="33">
+        <v>0</v>
+      </c>
+      <c r="B113" s="33">
         <v>2</v>
       </c>
-      <c r="C113" s="30">
-        <v>1</v>
-      </c>
-      <c r="D113" s="31" t="s">
+      <c r="C113" s="33">
+        <v>1</v>
+      </c>
+      <c r="D113" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="E113" s="31" t="s">
+      <c r="E113" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="31" t="s">
+      <c r="F113" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="G113" s="31" t="s">
+      <c r="G113" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H113" s="31" t="s">
+      <c r="H113" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I113" s="30" t="s">
+      <c r="I113" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="J113" s="30">
+      <c r="J113" s="33">
         <v>4</v>
       </c>
-      <c r="K113" s="30" t="s">
+      <c r="K113" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L113" s="30" t="s">
+      <c r="L113" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M113" s="31" t="s">
+      <c r="M113" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="N113" s="31"/>
-      <c r="O113" s="32"/>
-      <c r="P113" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q113" s="31"/>
+      <c r="N113" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O113" s="35">
+        <v>1</v>
+      </c>
+      <c r="P113" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="34"/>
       <c r="R113" s="13"/>
       <c r="S113" s="2">
         <f t="shared" si="23"/>
@@ -17129,7 +17133,7 @@
       <c r="AC113" s="2"/>
       <c r="AD113" s="2">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE113" s="2">
         <f t="shared" si="34"/>
@@ -17137,7 +17141,7 @@
       </c>
       <c r="AF113" s="2">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG113" s="2">
         <f t="shared" si="20"/>
@@ -17164,51 +17168,55 @@
       <c r="AT113" s="13"/>
     </row>
     <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="30">
-        <v>1</v>
-      </c>
-      <c r="B114" s="30">
+      <c r="A114" s="33">
+        <v>1</v>
+      </c>
+      <c r="B114" s="33">
         <v>2</v>
       </c>
-      <c r="C114" s="30">
-        <v>1</v>
-      </c>
-      <c r="D114" s="31" t="s">
+      <c r="C114" s="33">
+        <v>1</v>
+      </c>
+      <c r="D114" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="E114" s="31" t="s">
+      <c r="E114" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F114" s="31" t="s">
+      <c r="F114" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="G114" s="31" t="s">
+      <c r="G114" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="H114" s="31" t="s">
+      <c r="H114" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I114" s="30" t="s">
+      <c r="I114" s="33" t="s">
         <v>698</v>
       </c>
-      <c r="J114" s="30">
+      <c r="J114" s="33">
         <v>99</v>
       </c>
-      <c r="K114" s="30" t="s">
+      <c r="K114" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L114" s="30" t="s">
+      <c r="L114" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M114" s="31" t="s">
+      <c r="M114" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="N114" s="31"/>
-      <c r="O114" s="32"/>
-      <c r="P114" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q114" s="31"/>
+      <c r="N114" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O114" s="35">
+        <v>1</v>
+      </c>
+      <c r="P114" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="34"/>
       <c r="R114" s="13"/>
       <c r="S114" s="2">
         <f t="shared" si="23"/>
@@ -17253,7 +17261,7 @@
       <c r="AC114" s="2"/>
       <c r="AD114" s="2">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE114" s="2">
         <f t="shared" si="34"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DB5FED-2FD8-4E14-BEA4-9694C07AACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F42381C-C524-45BE-BDCA-134ED4B38D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tavole e pause golose'!$A$7:$AI$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tavole e pause golose'!$A$7:$AI$218</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tavole e pause golose'!$A$7:$K$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -90,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M200" authorId="0" shapeId="0" xr:uid="{CECC870D-5033-4412-AA3F-461504F1AA9D}">
+    <comment ref="M201" authorId="0" shapeId="0" xr:uid="{CECC870D-5033-4412-AA3F-461504F1AA9D}">
       <text>
         <r>
           <rPr>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="920">
   <si>
     <t>Recensore</t>
   </si>
@@ -2873,6 +2873,12 @@
   </si>
   <si>
     <t>45.07605746768362, 7.682089683753758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corso Guglielmo Marconi, 23 </t>
+  </si>
+  <si>
+    <t>011/19502617</t>
   </si>
 </sst>
 </file>
@@ -3628,7 +3634,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AT317"/>
+  <dimension ref="A1:AT318"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -3701,7 +3707,7 @@
       </c>
       <c r="F3" s="7">
         <f>+AD6</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="7">
         <f>+AF6</f>
@@ -3761,7 +3767,7 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
@@ -3778,7 +3784,7 @@
       <c r="K5" s="13"/>
       <c r="R5" s="13"/>
       <c r="S5" s="13">
-        <f t="shared" ref="S5:AB5" si="0">SUM(S8:S1959)</f>
+        <f t="shared" ref="S5:AB5" si="0">SUM(S8:S1960)</f>
         <v>55</v>
       </c>
       <c r="T5" s="13">
@@ -3791,7 +3797,7 @@
       </c>
       <c r="V5" s="13">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W5" s="13">
         <f t="shared" si="0"/>
@@ -3857,8 +3863,8 @@
         <v>15</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1958)</f>
-        <v>52</v>
+        <f t="shared" ref="AD6:AI6" si="1">SUM(AD8:AD1959)</f>
+        <v>53</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
@@ -19268,51 +19274,55 @@
       <c r="AT130" s="13"/>
     </row>
     <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="36">
-        <v>0</v>
-      </c>
-      <c r="B131" s="36">
+      <c r="A131" s="33">
+        <v>0</v>
+      </c>
+      <c r="B131" s="33">
         <v>2</v>
       </c>
-      <c r="C131" s="36">
+      <c r="C131" s="33">
         <v>2</v>
       </c>
-      <c r="D131" s="37" t="s">
-        <v>440</v>
-      </c>
-      <c r="E131" s="37" t="s">
-        <v>487</v>
-      </c>
-      <c r="F131" s="37" t="s">
-        <v>439</v>
-      </c>
-      <c r="G131" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H131" s="37" t="s">
+      <c r="D131" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="E131" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="F131" s="34" t="s">
+        <v>557</v>
+      </c>
+      <c r="G131" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H131" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I131" s="36" t="s">
-        <v>671</v>
-      </c>
-      <c r="J131" s="36">
-        <v>5</v>
-      </c>
-      <c r="K131" s="36" t="s">
+      <c r="I131" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="J131" s="33">
+        <v>2</v>
+      </c>
+      <c r="K131" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L131" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="M131" s="37" t="s">
-        <v>463</v>
-      </c>
-      <c r="N131" s="37" t="s">
-        <v>862</v>
-      </c>
-      <c r="O131" s="38"/>
-      <c r="P131" s="36"/>
-      <c r="Q131" s="37"/>
+      <c r="L131" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="M131" s="34" t="s">
+        <v>599</v>
+      </c>
+      <c r="N131" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O131" s="35">
+        <v>1</v>
+      </c>
+      <c r="P131" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="34"/>
       <c r="R131" s="13"/>
       <c r="S131" s="2">
         <f t="shared" si="35"/>
@@ -19320,7 +19330,7 @@
       </c>
       <c r="T131" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U131" s="2">
         <f t="shared" si="37"/>
@@ -19332,7 +19342,7 @@
       </c>
       <c r="W131" s="2">
         <f t="shared" si="39"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X131" s="2">
         <f t="shared" si="40"/>
@@ -19357,7 +19367,7 @@
       <c r="AC131" s="2"/>
       <c r="AD131" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" s="2">
         <f t="shared" si="46"/>
@@ -19365,7 +19375,7 @@
       </c>
       <c r="AF131" s="2">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG131" s="2">
         <f t="shared" si="20"/>
@@ -19373,11 +19383,11 @@
       </c>
       <c r="AH131" s="2">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI131" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ131" s="13"/>
       <c r="AK131" s="13"/>
@@ -19392,49 +19402,51 @@
       <c r="AT131" s="13"/>
     </row>
     <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="20">
-        <v>0</v>
-      </c>
-      <c r="B132" s="20">
+      <c r="A132" s="36">
+        <v>0</v>
+      </c>
+      <c r="B132" s="36">
         <v>2</v>
       </c>
-      <c r="C132" s="20">
+      <c r="C132" s="36">
         <v>2</v>
       </c>
-      <c r="D132" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="E132" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="F132" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="G132" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="H132" s="19" t="s">
+      <c r="D132" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="E132" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="F132" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="G132" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H132" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="I132" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="J132" s="20">
-        <v>4</v>
-      </c>
-      <c r="K132" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="L132" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="M132" s="19" t="s">
+      <c r="I132" s="36" t="s">
+        <v>671</v>
+      </c>
+      <c r="J132" s="36">
+        <v>5</v>
+      </c>
+      <c r="K132" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="L132" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="M132" s="37" t="s">
         <v>463</v>
       </c>
-      <c r="N132" s="19"/>
-      <c r="O132" s="18"/>
-      <c r="P132" s="20"/>
-      <c r="Q132" s="19"/>
+      <c r="N132" s="37" t="s">
+        <v>862</v>
+      </c>
+      <c r="O132" s="38"/>
+      <c r="P132" s="36"/>
+      <c r="Q132" s="37"/>
       <c r="R132" s="13"/>
       <c r="S132" s="2">
         <f t="shared" si="35"/>
@@ -19450,11 +19462,11 @@
       </c>
       <c r="V132" s="2">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W132" s="2">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="2">
         <f t="shared" si="40"/>
@@ -19514,51 +19526,49 @@
       <c r="AT132" s="13"/>
     </row>
     <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="36">
-        <v>0</v>
-      </c>
-      <c r="B133" s="36">
+      <c r="A133" s="20">
+        <v>0</v>
+      </c>
+      <c r="B133" s="20">
         <v>2</v>
       </c>
-      <c r="C133" s="36">
+      <c r="C133" s="20">
         <v>2</v>
       </c>
-      <c r="D133" s="37" t="s">
-        <v>645</v>
-      </c>
-      <c r="E133" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F133" s="37" t="s">
-        <v>654</v>
-      </c>
-      <c r="G133" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="H133" s="37" t="s">
+      <c r="D133" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="F133" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="G133" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H133" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I133" s="36" t="s">
-        <v>792</v>
-      </c>
-      <c r="J133" s="36">
-        <v>99</v>
-      </c>
-      <c r="K133" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="L133" s="36" t="s">
-        <v>512</v>
-      </c>
-      <c r="M133" s="37" t="s">
-        <v>676</v>
-      </c>
-      <c r="N133" s="37" t="s">
-        <v>862</v>
-      </c>
-      <c r="O133" s="38"/>
-      <c r="P133" s="36"/>
-      <c r="Q133" s="37"/>
+      <c r="I133" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="J133" s="20">
+        <v>4</v>
+      </c>
+      <c r="K133" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="L133" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="M133" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="N133" s="19"/>
+      <c r="O133" s="18"/>
+      <c r="P133" s="20"/>
+      <c r="Q133" s="19"/>
       <c r="R133" s="13"/>
       <c r="S133" s="2">
         <f t="shared" si="35"/>
@@ -19574,7 +19584,7 @@
       </c>
       <c r="V133" s="2">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="2">
         <f t="shared" si="39"/>
@@ -19638,55 +19648,51 @@
       <c r="AT133" s="13"/>
     </row>
     <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="33">
-        <v>0</v>
-      </c>
-      <c r="B134" s="33">
+      <c r="A134" s="36">
+        <v>0</v>
+      </c>
+      <c r="B134" s="36">
         <v>2</v>
       </c>
-      <c r="C134" s="33">
-        <v>3</v>
-      </c>
-      <c r="D134" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E134" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="F134" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="G134" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H134" s="34" t="s">
+      <c r="C134" s="36">
+        <v>2</v>
+      </c>
+      <c r="D134" s="37" t="s">
+        <v>645</v>
+      </c>
+      <c r="E134" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="F134" s="37" t="s">
+        <v>654</v>
+      </c>
+      <c r="G134" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H134" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="I134" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="J134" s="33">
-        <v>2</v>
-      </c>
-      <c r="K134" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="L134" s="33" t="s">
-        <v>797</v>
-      </c>
-      <c r="M134" s="34" t="s">
-        <v>801</v>
-      </c>
-      <c r="N134" s="34" t="s">
-        <v>860</v>
-      </c>
-      <c r="O134" s="35">
-        <v>1</v>
-      </c>
-      <c r="P134" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q134" s="34"/>
+      <c r="I134" s="36" t="s">
+        <v>792</v>
+      </c>
+      <c r="J134" s="36">
+        <v>99</v>
+      </c>
+      <c r="K134" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="L134" s="36" t="s">
+        <v>512</v>
+      </c>
+      <c r="M134" s="37" t="s">
+        <v>676</v>
+      </c>
+      <c r="N134" s="37" t="s">
+        <v>862</v>
+      </c>
+      <c r="O134" s="38"/>
+      <c r="P134" s="36"/>
+      <c r="Q134" s="37"/>
       <c r="R134" s="13"/>
       <c r="S134" s="2">
         <f t="shared" si="35"/>
@@ -19694,7 +19700,7 @@
       </c>
       <c r="T134" s="2">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U134" s="2">
         <f t="shared" si="37"/>
@@ -19731,7 +19737,7 @@
       <c r="AC134" s="2"/>
       <c r="AD134" s="2">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE134" s="2">
         <f t="shared" si="46"/>
@@ -19739,7 +19745,7 @@
       </c>
       <c r="AF134" s="2">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG134" s="2">
         <f t="shared" si="20"/>
@@ -19747,11 +19753,11 @@
       </c>
       <c r="AH134" s="2">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI134" s="2">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ134" s="13"/>
       <c r="AK134" s="13"/>
@@ -19766,59 +19772,63 @@
       <c r="AT134" s="13"/>
     </row>
     <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="30">
-        <v>0</v>
-      </c>
-      <c r="B135" s="30">
+      <c r="A135" s="33">
+        <v>0</v>
+      </c>
+      <c r="B135" s="33">
         <v>2</v>
       </c>
-      <c r="C135" s="30">
+      <c r="C135" s="33">
         <v>3</v>
       </c>
-      <c r="D135" s="31" t="s">
-        <v>550</v>
-      </c>
-      <c r="E135" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="F135" s="31" t="s">
-        <v>541</v>
-      </c>
-      <c r="G135" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="H135" s="31" t="s">
+      <c r="D135" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E135" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F135" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H135" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I135" s="30" t="s">
-        <v>542</v>
-      </c>
-      <c r="J135" s="30">
-        <v>1</v>
-      </c>
-      <c r="K135" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="L135" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="M135" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="N135" s="31"/>
-      <c r="O135" s="32"/>
-      <c r="P135" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q135" s="31"/>
+      <c r="I135" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J135" s="33">
+        <v>2</v>
+      </c>
+      <c r="K135" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="L135" s="33" t="s">
+        <v>797</v>
+      </c>
+      <c r="M135" s="34" t="s">
+        <v>801</v>
+      </c>
+      <c r="N135" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O135" s="35">
+        <v>1</v>
+      </c>
+      <c r="P135" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="34"/>
       <c r="R135" s="13"/>
       <c r="S135" s="2">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T135" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U135" s="2">
         <f t="shared" si="37"/>
@@ -19855,7 +19865,7 @@
       <c r="AC135" s="2"/>
       <c r="AD135" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE135" s="2">
         <f t="shared" si="46"/>
@@ -19863,7 +19873,7 @@
       </c>
       <c r="AF135" s="2">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG135" s="2">
         <f t="shared" si="20"/>
@@ -19890,55 +19900,51 @@
       <c r="AT135" s="13"/>
     </row>
     <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="33">
-        <v>0</v>
-      </c>
-      <c r="B136" s="33">
+      <c r="A136" s="30">
+        <v>0</v>
+      </c>
+      <c r="B136" s="30">
         <v>2</v>
       </c>
-      <c r="C136" s="33">
+      <c r="C136" s="30">
         <v>3</v>
       </c>
-      <c r="D136" s="34" t="s">
-        <v>646</v>
-      </c>
-      <c r="E136" s="34" t="s">
-        <v>643</v>
-      </c>
-      <c r="F136" s="34" t="s">
-        <v>657</v>
-      </c>
-      <c r="G136" s="34" t="s">
-        <v>503</v>
-      </c>
-      <c r="H136" s="34" t="s">
+      <c r="D136" s="31" t="s">
+        <v>550</v>
+      </c>
+      <c r="E136" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="F136" s="31" t="s">
+        <v>541</v>
+      </c>
+      <c r="G136" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="H136" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="I136" s="33" t="s">
-        <v>628</v>
-      </c>
-      <c r="J136" s="33">
-        <v>1</v>
-      </c>
-      <c r="K136" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="L136" s="33" t="s">
+      <c r="I136" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="J136" s="30">
+        <v>1</v>
+      </c>
+      <c r="K136" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="L136" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="M136" s="34" t="s">
+      <c r="M136" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="N136" s="34" t="s">
-        <v>860</v>
-      </c>
-      <c r="O136" s="35">
-        <v>1</v>
-      </c>
-      <c r="P136" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q136" s="34"/>
+      <c r="N136" s="31"/>
+      <c r="O136" s="32"/>
+      <c r="P136" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q136" s="31"/>
       <c r="R136" s="13"/>
       <c r="S136" s="2">
         <f t="shared" si="35"/>
@@ -19983,26 +19989,26 @@
       <c r="AC136" s="2"/>
       <c r="AD136" s="2">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE136" s="2">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AF136" s="2">
-        <f t="shared" ref="AF136:AF199" si="47">+O136*P136*(1-A136)</f>
-        <v>1</v>
+        <f t="shared" ref="AF136:AF200" si="47">+O136*P136*(1-A136)</f>
+        <v>0</v>
       </c>
       <c r="AG136" s="2">
-        <f t="shared" ref="AG136:AG199" si="48">O136*(1-P136)*(1-A136)</f>
+        <f t="shared" ref="AG136:AG200" si="48">O136*(1-P136)*(1-A136)</f>
         <v>0</v>
       </c>
       <c r="AH136" s="2">
-        <f t="shared" ref="AH136:AH199" si="49">+P136*(1-A136)</f>
+        <f t="shared" ref="AH136:AH200" si="49">+P136*(1-A136)</f>
         <v>1</v>
       </c>
       <c r="AI136" s="2">
-        <f t="shared" ref="AI136:AI199" si="50">+(1-A136)*(1-P136)</f>
+        <f t="shared" ref="AI136:AI200" si="50">+(1-A136)*(1-P136)</f>
         <v>0</v>
       </c>
       <c r="AJ136" s="13"/>
@@ -20028,28 +20034,28 @@
         <v>3</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>278</v>
+        <v>646</v>
       </c>
       <c r="E137" s="34" t="s">
-        <v>101</v>
+        <v>643</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>285</v>
+        <v>657</v>
       </c>
       <c r="G137" s="34" t="s">
-        <v>90</v>
+        <v>503</v>
       </c>
       <c r="H137" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I137" s="33" t="s">
-        <v>268</v>
+        <v>628</v>
       </c>
       <c r="J137" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K137" s="33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L137" s="33" t="s">
         <v>105</v>
@@ -20070,11 +20076,11 @@
       <c r="R137" s="13"/>
       <c r="S137" s="2">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="2">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" s="2">
         <f t="shared" si="37"/>
@@ -20156,31 +20162,35 @@
         <v>3</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>890</v>
+        <v>278</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>889</v>
+        <v>101</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>891</v>
+        <v>285</v>
       </c>
       <c r="G138" s="34" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>698</v>
+        <v>268</v>
       </c>
       <c r="J138" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K138" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="L138" s="33"/>
-      <c r="M138" s="34"/>
+        <v>295</v>
+      </c>
+      <c r="L138" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M138" s="34" t="s">
+        <v>105</v>
+      </c>
       <c r="N138" s="34" t="s">
         <v>860</v>
       </c>
@@ -20194,11 +20204,11 @@
       <c r="R138" s="13"/>
       <c r="S138" s="2">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T138" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U138" s="2">
         <f t="shared" si="37"/>
@@ -20280,13 +20290,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="34" t="s">
-        <v>572</v>
+        <v>890</v>
       </c>
       <c r="E139" s="34" t="s">
-        <v>644</v>
+        <v>889</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>574</v>
+        <v>891</v>
       </c>
       <c r="G139" s="34" t="s">
         <v>139</v>
@@ -20295,20 +20305,16 @@
         <v>192</v>
       </c>
       <c r="I139" s="33" t="s">
-        <v>573</v>
+        <v>698</v>
       </c>
       <c r="J139" s="33">
         <v>1</v>
       </c>
       <c r="K139" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="L139" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M139" s="34" t="s">
-        <v>105</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="L139" s="33"/>
+      <c r="M139" s="34"/>
       <c r="N139" s="34" t="s">
         <v>860</v>
       </c>
@@ -20408,34 +20414,34 @@
         <v>3</v>
       </c>
       <c r="D140" s="34" t="s">
-        <v>45</v>
+        <v>572</v>
       </c>
       <c r="E140" s="34" t="s">
-        <v>101</v>
+        <v>644</v>
       </c>
       <c r="F140" s="34" t="s">
-        <v>118</v>
+        <v>574</v>
       </c>
       <c r="G140" s="34" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="H140" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I140" s="33" t="s">
-        <v>46</v>
+        <v>573</v>
       </c>
       <c r="J140" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K140" s="33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L140" s="33" t="s">
-        <v>315</v>
+        <v>105</v>
       </c>
       <c r="M140" s="34" t="s">
-        <v>316</v>
+        <v>105</v>
       </c>
       <c r="N140" s="34" t="s">
         <v>860</v>
@@ -20450,11 +20456,11 @@
       <c r="R140" s="13"/>
       <c r="S140" s="2">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T140" s="2">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U140" s="2">
         <f t="shared" si="37"/>
@@ -20526,51 +20532,55 @@
       <c r="AT140" s="13"/>
     </row>
     <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="30">
-        <v>0</v>
-      </c>
-      <c r="B141" s="30">
+      <c r="A141" s="33">
+        <v>0</v>
+      </c>
+      <c r="B141" s="33">
         <v>2</v>
       </c>
-      <c r="C141" s="30">
+      <c r="C141" s="33">
         <v>3</v>
       </c>
-      <c r="D141" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E141" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="F141" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="G141" s="31" t="s">
+      <c r="D141" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E141" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="F141" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="G141" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H141" s="31" t="s">
+      <c r="H141" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I141" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="J141" s="30">
+      <c r="I141" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J141" s="33">
         <v>2</v>
       </c>
-      <c r="K141" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="L141" s="30" t="s">
+      <c r="K141" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="L141" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="M141" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="N141" s="31"/>
-      <c r="O141" s="32"/>
-      <c r="P141" s="30">
-        <v>1</v>
-      </c>
-      <c r="Q141" s="31"/>
+      <c r="M141" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="N141" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O141" s="35">
+        <v>1</v>
+      </c>
+      <c r="P141" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q141" s="34"/>
       <c r="R141" s="13"/>
       <c r="S141" s="2">
         <f t="shared" si="35"/>
@@ -20615,7 +20625,7 @@
       <c r="AC141" s="2"/>
       <c r="AD141" s="2">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE141" s="2">
         <f t="shared" si="46"/>
@@ -20623,7 +20633,7 @@
       </c>
       <c r="AF141" s="2">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG141" s="2">
         <f t="shared" si="48"/>
@@ -20650,57 +20660,59 @@
       <c r="AT141" s="13"/>
     </row>
     <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="20">
-        <v>0</v>
-      </c>
-      <c r="B142" s="20">
+      <c r="A142" s="30">
+        <v>0</v>
+      </c>
+      <c r="B142" s="30">
         <v>2</v>
       </c>
-      <c r="C142" s="20">
-        <v>4</v>
-      </c>
-      <c r="D142" s="19" t="s">
-        <v>548</v>
-      </c>
-      <c r="E142" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F142" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="G142" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="H142" s="19" t="s">
+      <c r="C142" s="30">
+        <v>3</v>
+      </c>
+      <c r="D142" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E142" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F142" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="G142" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H142" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="I142" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="J142" s="20">
-        <v>1</v>
-      </c>
-      <c r="K142" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="L142" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="M142" s="19" t="s">
-        <v>511</v>
-      </c>
-      <c r="N142" s="19"/>
-      <c r="O142" s="18"/>
-      <c r="P142" s="20"/>
-      <c r="Q142" s="19"/>
+      <c r="I142" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="J142" s="30">
+        <v>2</v>
+      </c>
+      <c r="K142" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="L142" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="M142" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="N142" s="31"/>
+      <c r="O142" s="32"/>
+      <c r="P142" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q142" s="31"/>
       <c r="R142" s="13"/>
       <c r="S142" s="2">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U142" s="2">
         <f t="shared" si="37"/>
@@ -20753,11 +20765,11 @@
       </c>
       <c r="AH142" s="2">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI142" s="2">
         <f t="shared" si="50"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ142" s="13"/>
       <c r="AK142" s="13"/>
@@ -20772,55 +20784,53 @@
       <c r="AT142" s="13"/>
     </row>
     <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="36">
-        <v>0</v>
-      </c>
-      <c r="B143" s="36">
+      <c r="A143" s="20">
+        <v>0</v>
+      </c>
+      <c r="B143" s="20">
         <v>2</v>
       </c>
-      <c r="C143" s="36">
+      <c r="C143" s="20">
         <v>4</v>
       </c>
-      <c r="D143" s="37" t="s">
-        <v>537</v>
-      </c>
-      <c r="E143" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F143" s="37" t="s">
-        <v>658</v>
-      </c>
-      <c r="G143" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H143" s="37" t="s">
+      <c r="D143" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F143" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="G143" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H143" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I143" s="36" t="s">
-        <v>538</v>
-      </c>
-      <c r="J143" s="36">
-        <v>3</v>
-      </c>
-      <c r="K143" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="L143" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="M143" s="37" t="s">
-        <v>677</v>
-      </c>
-      <c r="N143" s="37" t="s">
-        <v>864</v>
-      </c>
-      <c r="O143" s="38"/>
-      <c r="P143" s="36"/>
-      <c r="Q143" s="37"/>
+      <c r="I143" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="J143" s="20">
+        <v>1</v>
+      </c>
+      <c r="K143" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="L143" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="M143" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="N143" s="19"/>
+      <c r="O143" s="18"/>
+      <c r="P143" s="20"/>
+      <c r="Q143" s="19"/>
       <c r="R143" s="13"/>
       <c r="S143" s="2">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="2">
         <f t="shared" si="36"/>
@@ -20828,7 +20838,7 @@
       </c>
       <c r="U143" s="2">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V143" s="2">
         <f t="shared" si="38"/>
@@ -20896,49 +20906,51 @@
       <c r="AT143" s="13"/>
     </row>
     <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="20">
-        <v>0</v>
-      </c>
-      <c r="B144" s="20">
+      <c r="A144" s="36">
+        <v>0</v>
+      </c>
+      <c r="B144" s="36">
         <v>2</v>
       </c>
-      <c r="C144" s="20">
+      <c r="C144" s="36">
         <v>4</v>
       </c>
-      <c r="D144" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="E144" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="F144" s="19" t="s">
-        <v>771</v>
-      </c>
-      <c r="G144" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="H144" s="19" t="s">
+      <c r="D144" s="37" t="s">
+        <v>537</v>
+      </c>
+      <c r="E144" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F144" s="37" t="s">
+        <v>658</v>
+      </c>
+      <c r="G144" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H144" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="I144" s="20" t="s">
-        <v>421</v>
-      </c>
-      <c r="J144" s="20">
-        <v>2</v>
-      </c>
-      <c r="K144" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="L144" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="M144" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="N144" s="19"/>
-      <c r="O144" s="18"/>
-      <c r="P144" s="20"/>
-      <c r="Q144" s="19"/>
+      <c r="I144" s="36" t="s">
+        <v>538</v>
+      </c>
+      <c r="J144" s="36">
+        <v>3</v>
+      </c>
+      <c r="K144" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="L144" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="M144" s="37" t="s">
+        <v>677</v>
+      </c>
+      <c r="N144" s="37" t="s">
+        <v>864</v>
+      </c>
+      <c r="O144" s="38"/>
+      <c r="P144" s="36"/>
+      <c r="Q144" s="37"/>
       <c r="R144" s="13"/>
       <c r="S144" s="2">
         <f t="shared" si="35"/>
@@ -20946,11 +20958,11 @@
       </c>
       <c r="T144" s="2">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U144" s="2">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V144" s="2">
         <f t="shared" si="38"/>
@@ -21028,34 +21040,34 @@
         <v>4</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>413</v>
+        <v>637</v>
       </c>
       <c r="E145" s="19" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F145" s="19" t="s">
-        <v>415</v>
+        <v>771</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="H145" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J145" s="20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K145" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="L145" s="20">
-        <v>8</v>
+        <v>296</v>
+      </c>
+      <c r="L145" s="20" t="s">
+        <v>309</v>
       </c>
       <c r="M145" s="19" t="s">
-        <v>417</v>
+        <v>717</v>
       </c>
       <c r="N145" s="19"/>
       <c r="O145" s="18"/>
@@ -21068,7 +21080,7 @@
       </c>
       <c r="T145" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U145" s="2">
         <f t="shared" si="37"/>
@@ -21084,7 +21096,7 @@
       </c>
       <c r="X145" s="2">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y145" s="2">
         <f t="shared" si="41"/>
@@ -21140,51 +21152,49 @@
       <c r="AT145" s="13"/>
     </row>
     <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="36">
-        <v>0</v>
-      </c>
-      <c r="B146" s="36">
+      <c r="A146" s="20">
+        <v>0</v>
+      </c>
+      <c r="B146" s="20">
         <v>2</v>
       </c>
-      <c r="C146" s="36">
+      <c r="C146" s="20">
         <v>4</v>
       </c>
-      <c r="D146" s="37" t="s">
-        <v>647</v>
-      </c>
-      <c r="E146" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="F146" s="37" t="s">
-        <v>659</v>
-      </c>
-      <c r="G146" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="H146" s="37" t="s">
+      <c r="D146" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E146" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F146" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G146" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H146" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I146" s="36" t="s">
-        <v>605</v>
-      </c>
-      <c r="J146" s="36">
-        <v>3</v>
-      </c>
-      <c r="K146" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="L146" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="M146" s="37" t="s">
-        <v>631</v>
-      </c>
-      <c r="N146" s="37" t="s">
-        <v>862</v>
-      </c>
-      <c r="O146" s="38"/>
-      <c r="P146" s="36"/>
-      <c r="Q146" s="37"/>
+      <c r="I146" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="J146" s="20">
+        <v>6</v>
+      </c>
+      <c r="K146" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="L146" s="20">
+        <v>8</v>
+      </c>
+      <c r="M146" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="N146" s="19"/>
+      <c r="O146" s="18"/>
+      <c r="P146" s="20"/>
+      <c r="Q146" s="19"/>
       <c r="R146" s="13"/>
       <c r="S146" s="2">
         <f t="shared" si="35"/>
@@ -21196,7 +21206,7 @@
       </c>
       <c r="U146" s="2">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V146" s="2">
         <f t="shared" si="38"/>
@@ -21208,7 +21218,7 @@
       </c>
       <c r="X146" s="2">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y146" s="2">
         <f t="shared" si="41"/>
@@ -21274,34 +21284,34 @@
         <v>4</v>
       </c>
       <c r="D147" s="37" t="s">
-        <v>473</v>
+        <v>647</v>
       </c>
       <c r="E147" s="37" t="s">
         <v>418</v>
       </c>
       <c r="F147" s="37" t="s">
-        <v>474</v>
+        <v>659</v>
       </c>
       <c r="G147" s="37" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="H147" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>475</v>
+        <v>605</v>
       </c>
       <c r="J147" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K147" s="36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L147" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M147" s="37" t="s">
-        <v>521</v>
+        <v>631</v>
       </c>
       <c r="N147" s="37" t="s">
         <v>862</v>
@@ -21312,7 +21322,7 @@
       <c r="R147" s="13"/>
       <c r="S147" s="2">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T147" s="2">
         <f t="shared" si="36"/>
@@ -21320,7 +21330,7 @@
       </c>
       <c r="U147" s="2">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V147" s="2">
         <f t="shared" si="38"/>
@@ -21388,63 +21398,59 @@
       <c r="AT147" s="13"/>
     </row>
     <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="33">
-        <v>0</v>
-      </c>
-      <c r="B148" s="33">
+      <c r="A148" s="36">
+        <v>0</v>
+      </c>
+      <c r="B148" s="36">
         <v>2</v>
       </c>
-      <c r="C148" s="33">
+      <c r="C148" s="36">
         <v>4</v>
       </c>
-      <c r="D148" s="34" t="s">
-        <v>551</v>
-      </c>
-      <c r="E148" s="34" t="s">
-        <v>554</v>
-      </c>
-      <c r="F148" s="34" t="s">
-        <v>557</v>
-      </c>
-      <c r="G148" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H148" s="34" t="s">
+      <c r="D148" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="E148" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="F148" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="G148" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H148" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="I148" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="J148" s="33">
-        <v>2</v>
-      </c>
-      <c r="K148" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="L148" s="33" t="s">
+      <c r="I148" s="36" t="s">
+        <v>475</v>
+      </c>
+      <c r="J148" s="36">
+        <v>1</v>
+      </c>
+      <c r="K148" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="L148" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="M148" s="34" t="s">
-        <v>599</v>
-      </c>
-      <c r="N148" s="34" t="s">
-        <v>860</v>
-      </c>
-      <c r="O148" s="35">
-        <v>1</v>
-      </c>
-      <c r="P148" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q148" s="34"/>
+      <c r="M148" s="37" t="s">
+        <v>521</v>
+      </c>
+      <c r="N148" s="37" t="s">
+        <v>862</v>
+      </c>
+      <c r="O148" s="38"/>
+      <c r="P148" s="36"/>
+      <c r="Q148" s="37"/>
       <c r="R148" s="13"/>
       <c r="S148" s="2">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148" s="2">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U148" s="2">
         <f t="shared" si="37"/>
@@ -21481,7 +21487,7 @@
       <c r="AC148" s="2"/>
       <c r="AD148" s="2">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE148" s="2">
         <f t="shared" si="46"/>
@@ -21489,7 +21495,7 @@
       </c>
       <c r="AF148" s="2">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG148" s="2">
         <f t="shared" si="48"/>
@@ -21497,11 +21503,11 @@
       </c>
       <c r="AH148" s="2">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI148" s="2">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ148" s="13"/>
       <c r="AK148" s="13"/>
@@ -25513,52 +25519,52 @@
       <c r="Q181" s="34"/>
       <c r="R181" s="13"/>
       <c r="S181" s="2">
-        <f t="shared" ref="S181:S211" si="51">IF(J181=$S$7,1,0)</f>
+        <f t="shared" ref="S181:S212" si="51">IF(J181=$S$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="T181" s="2">
-        <f t="shared" ref="T181:T211" si="52">IF(J181=$T$7,1,0)</f>
+        <f t="shared" ref="T181:T212" si="52">IF(J181=$T$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="U181" s="2">
-        <f t="shared" ref="U181:U211" si="53">IF(J181=$U$7,1,0)</f>
+        <f t="shared" ref="U181:U212" si="53">IF(J181=$U$7,1,0)</f>
         <v>1</v>
       </c>
       <c r="V181" s="2">
-        <f t="shared" ref="V181:V211" si="54">IF(J181=$V$7,1,0)</f>
+        <f t="shared" ref="V181:V212" si="54">IF(J181=$V$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="W181" s="2">
-        <f t="shared" ref="W181:W211" si="55">IF(J181=$W$7,1,0)</f>
+        <f t="shared" ref="W181:W212" si="55">IF(J181=$W$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="X181" s="2">
-        <f t="shared" ref="X181:X211" si="56">IF(J181=$X$7,1,0)</f>
+        <f t="shared" ref="X181:X212" si="56">IF(J181=$X$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Y181" s="2">
-        <f t="shared" ref="Y181:Y211" si="57">IF(J181=$Y$7,1,0)</f>
+        <f t="shared" ref="Y181:Y212" si="57">IF(J181=$Y$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Z181" s="2">
-        <f t="shared" ref="Z181:Z211" si="58">IF(J181=$Z$7,1,0)</f>
+        <f t="shared" ref="Z181:Z212" si="58">IF(J181=$Z$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AA181" s="2">
-        <f t="shared" ref="AA181:AA211" si="59">IF(J181=$AA$7,1,0)</f>
+        <f t="shared" ref="AA181:AA212" si="59">IF(J181=$AA$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB181" s="2">
-        <f t="shared" ref="AB181:AB211" si="60">IF(J181=$AB$7,1,0)</f>
+        <f t="shared" ref="AB181:AB212" si="60">IF(J181=$AB$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC181" s="2"/>
       <c r="AD181" s="2">
-        <f t="shared" ref="AD181:AD211" si="61">+O181*P181</f>
+        <f t="shared" ref="AD181:AD212" si="61">+O181*P181</f>
         <v>1</v>
       </c>
       <c r="AE181" s="2">
-        <f t="shared" ref="AE181:AE211" si="62">O181*(1-P181)</f>
+        <f t="shared" ref="AE181:AE212" si="62">O181*(1-P181)</f>
         <v>0</v>
       </c>
       <c r="AF181" s="2">
@@ -27461,114 +27467,120 @@
       <c r="AT196" s="13"/>
     </row>
     <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="20">
-        <v>0</v>
-      </c>
-      <c r="B197" s="20">
+      <c r="A197" s="33">
+        <v>1</v>
+      </c>
+      <c r="B197" s="33">
         <v>2</v>
       </c>
-      <c r="C197" s="20">
+      <c r="C197" s="33">
         <v>7</v>
       </c>
-      <c r="D197" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="E197" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F197" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="G197" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="H197" s="19" t="s">
+      <c r="D197" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="E197" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F197" s="34" t="s">
+        <v>918</v>
+      </c>
+      <c r="G197" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H197" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I197" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="J197" s="20">
-        <v>99</v>
-      </c>
-      <c r="K197" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="L197" s="20" t="s">
+      <c r="I197" s="33" t="s">
+        <v>919</v>
+      </c>
+      <c r="J197" s="33">
+        <v>4</v>
+      </c>
+      <c r="K197" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="M197" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="N197" s="19"/>
-      <c r="O197" s="18"/>
-      <c r="P197" s="20"/>
-      <c r="Q197" s="19"/>
+      <c r="L197" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="M197" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="N197" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O197" s="35">
+        <v>1</v>
+      </c>
+      <c r="P197" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q197" s="34"/>
       <c r="R197" s="13"/>
       <c r="S197" s="2">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="S197" si="63">IF(J197=$S$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="T197" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="T197" si="64">IF(J197=$T$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="U197" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="U197" si="65">IF(J197=$U$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="V197" s="2">
-        <f t="shared" si="54"/>
-        <v>0</v>
+        <f t="shared" ref="V197" si="66">IF(J197=$V$7,1,0)</f>
+        <v>1</v>
       </c>
       <c r="W197" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="W197" si="67">IF(J197=$W$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="X197" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="X197" si="68">IF(J197=$X$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Y197" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="Y197" si="69">IF(J197=$Y$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Z197" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="Z197" si="70">IF(J197=$Z$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AA197" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="AA197" si="71">IF(J197=$AA$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB197" s="2">
-        <f t="shared" si="60"/>
+        <f t="shared" ref="AB197" si="72">IF(J197=$AB$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC197" s="2"/>
       <c r="AD197" s="2">
-        <f t="shared" si="61"/>
-        <v>0</v>
+        <f t="shared" ref="AD197" si="73">+O197*P197</f>
+        <v>1</v>
       </c>
       <c r="AE197" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="AE197" si="74">O197*(1-P197)</f>
         <v>0</v>
       </c>
       <c r="AF197" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="AF197" si="75">+O197*P197*(1-A197)</f>
         <v>0</v>
       </c>
       <c r="AG197" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="AG197" si="76">O197*(1-P197)*(1-A197)</f>
         <v>0</v>
       </c>
       <c r="AH197" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" ref="AH197" si="77">+P197*(1-A197)</f>
         <v>0</v>
       </c>
       <c r="AI197" s="2">
-        <f t="shared" si="50"/>
-        <v>1</v>
+        <f t="shared" ref="AI197" si="78">+(1-A197)*(1-P197)</f>
+        <v>0</v>
       </c>
       <c r="AJ197" s="13"/>
       <c r="AK197" s="13"/>
@@ -27584,7 +27596,7 @@
     </row>
     <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B198" s="20">
         <v>2</v>
@@ -27599,19 +27611,19 @@
         <v>38</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G198" s="19" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="H198" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I198" s="20" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="J198" s="20">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="K198" s="20" t="s">
         <v>388</v>
@@ -27653,7 +27665,7 @@
       </c>
       <c r="Y198" s="2">
         <f t="shared" si="57"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z198" s="2">
         <f t="shared" si="58"/>
@@ -27690,7 +27702,7 @@
       </c>
       <c r="AI198" s="2">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ198" s="13"/>
       <c r="AK198" s="13"/>
@@ -27721,19 +27733,19 @@
         <v>38</v>
       </c>
       <c r="F199" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G199" s="19" t="s">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="H199" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I199" s="20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J199" s="20">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="K199" s="20" t="s">
         <v>388</v>
@@ -27775,7 +27787,7 @@
       </c>
       <c r="Y199" s="2">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z199" s="2">
         <f t="shared" si="58"/>
@@ -27828,7 +27840,7 @@
     </row>
     <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B200" s="20">
         <v>2</v>
@@ -27837,34 +27849,34 @@
         <v>7</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>749</v>
+        <v>323</v>
       </c>
       <c r="E200" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F200" s="19" t="s">
-        <v>751</v>
+        <v>326</v>
       </c>
       <c r="G200" s="19" t="s">
-        <v>72</v>
+        <v>328</v>
       </c>
       <c r="H200" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I200" s="20" t="s">
-        <v>752</v>
+        <v>327</v>
       </c>
       <c r="J200" s="20">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="K200" s="20" t="s">
-        <v>296</v>
+        <v>388</v>
       </c>
       <c r="L200" s="20" t="s">
         <v>296</v>
       </c>
       <c r="M200" s="19" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="N200" s="19"/>
       <c r="O200" s="18"/>
@@ -27885,7 +27897,7 @@
       </c>
       <c r="V200" s="2">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W200" s="2">
         <f t="shared" si="55"/>
@@ -27921,20 +27933,20 @@
         <v>0</v>
       </c>
       <c r="AF200" s="2">
-        <f t="shared" ref="AF200:AF217" si="63">+O200*P200*(1-A200)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AG200" s="2">
-        <f t="shared" ref="AG200:AG217" si="64">O200*(1-P200)*(1-A200)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AH200" s="2">
-        <f t="shared" ref="AH200:AH217" si="65">+P200*(1-A200)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AI200" s="2">
-        <f t="shared" ref="AI200:AI217" si="66">+(1-A200)*(1-P200)</f>
-        <v>1</v>
+        <f t="shared" si="50"/>
+        <v>0</v>
       </c>
       <c r="AJ200" s="13"/>
       <c r="AK200" s="13"/>
@@ -27950,7 +27962,7 @@
     </row>
     <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B201" s="20">
         <v>2</v>
@@ -27965,19 +27977,19 @@
         <v>38</v>
       </c>
       <c r="F201" s="19" t="s">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="G201" s="19" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="H201" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I201" s="20" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J201" s="20">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="K201" s="20" t="s">
         <v>296</v>
@@ -28007,7 +28019,7 @@
       </c>
       <c r="V201" s="2">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W201" s="2">
         <f t="shared" si="55"/>
@@ -28043,20 +28055,20 @@
         <v>0</v>
       </c>
       <c r="AF201" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="AF201:AF218" si="79">+O201*P201*(1-A201)</f>
         <v>0</v>
       </c>
       <c r="AG201" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" ref="AG201:AG218" si="80">O201*(1-P201)*(1-A201)</f>
         <v>0</v>
       </c>
       <c r="AH201" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" ref="AH201:AH218" si="81">+P201*(1-A201)</f>
         <v>0</v>
       </c>
       <c r="AI201" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" ref="AI201:AI218" si="82">+(1-A201)*(1-P201)</f>
+        <v>1</v>
       </c>
       <c r="AJ201" s="13"/>
       <c r="AK201" s="13"/>
@@ -28071,57 +28083,53 @@
       <c r="AT201" s="13"/>
     </row>
     <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="33">
-        <v>0</v>
-      </c>
-      <c r="B202" s="33">
+      <c r="A202" s="20">
+        <v>1</v>
+      </c>
+      <c r="B202" s="20">
         <v>2</v>
       </c>
-      <c r="C202" s="33">
+      <c r="C202" s="20">
         <v>7</v>
       </c>
-      <c r="D202" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="E202" s="34" t="s">
+      <c r="D202" s="19" t="s">
+        <v>749</v>
+      </c>
+      <c r="E202" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F202" s="34" t="s">
-        <v>778</v>
-      </c>
-      <c r="G202" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H202" s="34" t="s">
+      <c r="F202" s="19" t="s">
+        <v>777</v>
+      </c>
+      <c r="G202" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H202" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I202" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="J202" s="33">
-        <v>1</v>
-      </c>
-      <c r="K202" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="L202" s="33" t="s">
+      <c r="I202" s="20" t="s">
+        <v>750</v>
+      </c>
+      <c r="J202" s="20">
+        <v>99</v>
+      </c>
+      <c r="K202" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="M202" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="N202" s="34" t="s">
-        <v>869</v>
-      </c>
-      <c r="O202" s="35">
-        <v>1</v>
-      </c>
-      <c r="P202" s="33"/>
-      <c r="Q202" s="34"/>
+      <c r="L202" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="M202" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="N202" s="19"/>
+      <c r="O202" s="18"/>
+      <c r="P202" s="20"/>
+      <c r="Q202" s="19"/>
       <c r="R202" s="13"/>
       <c r="S202" s="2">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T202" s="2">
         <f t="shared" si="52"/>
@@ -28166,23 +28174,23 @@
       </c>
       <c r="AE202" s="2">
         <f t="shared" si="62"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF202" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG202" s="2">
-        <f t="shared" si="64"/>
-        <v>1</v>
+        <f t="shared" si="80"/>
+        <v>0</v>
       </c>
       <c r="AH202" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI202" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="AJ202" s="13"/>
       <c r="AK202" s="13"/>
@@ -28198,7 +28206,7 @@
     </row>
     <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B203" s="33">
         <v>2</v>
@@ -28213,19 +28221,19 @@
         <v>38</v>
       </c>
       <c r="F203" s="34" t="s">
-        <v>106</v>
+        <v>778</v>
       </c>
       <c r="G203" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H203" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I203" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J203" s="33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K203" s="33" t="s">
         <v>295</v>
@@ -28247,7 +28255,7 @@
       <c r="R203" s="13"/>
       <c r="S203" s="2">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T203" s="2">
         <f t="shared" si="52"/>
@@ -28267,7 +28275,7 @@
       </c>
       <c r="X203" s="2">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y203" s="2">
         <f t="shared" si="57"/>
@@ -28295,20 +28303,20 @@
         <v>1</v>
       </c>
       <c r="AF203" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG203" s="2">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="80"/>
+        <v>1</v>
       </c>
       <c r="AH203" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI203" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="82"/>
+        <v>1</v>
       </c>
       <c r="AJ203" s="13"/>
       <c r="AK203" s="13"/>
@@ -28323,49 +28331,53 @@
       <c r="AT203" s="13"/>
     </row>
     <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="20">
-        <v>0</v>
-      </c>
-      <c r="B204" s="20">
+      <c r="A204" s="33">
+        <v>1</v>
+      </c>
+      <c r="B204" s="33">
         <v>2</v>
       </c>
-      <c r="C204" s="20">
+      <c r="C204" s="33">
         <v>7</v>
       </c>
-      <c r="D204" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E204" s="19" t="s">
+      <c r="D204" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E204" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F204" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="G204" s="19" t="s">
+      <c r="F204" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="G204" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="H204" s="19" t="s">
+      <c r="H204" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I204" s="20" t="s">
-        <v>506</v>
-      </c>
-      <c r="J204" s="20">
+      <c r="I204" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="J204" s="33">
         <v>6</v>
       </c>
-      <c r="K204" s="20" t="s">
+      <c r="K204" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="L204" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L204" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="M204" s="19" t="s">
+      <c r="M204" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="N204" s="19"/>
-      <c r="O204" s="18"/>
-      <c r="P204" s="20"/>
-      <c r="Q204" s="19"/>
+      <c r="N204" s="34" t="s">
+        <v>869</v>
+      </c>
+      <c r="O204" s="35">
+        <v>1</v>
+      </c>
+      <c r="P204" s="33"/>
+      <c r="Q204" s="34"/>
       <c r="R204" s="13"/>
       <c r="S204" s="2">
         <f t="shared" si="51"/>
@@ -28414,23 +28426,23 @@
       </c>
       <c r="AE204" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF204" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG204" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH204" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI204" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="AJ204" s="13"/>
       <c r="AK204" s="13"/>
@@ -28446,7 +28458,7 @@
     </row>
     <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B205" s="20">
         <v>2</v>
@@ -28461,19 +28473,19 @@
         <v>38</v>
       </c>
       <c r="F205" s="19" t="s">
-        <v>371</v>
+        <v>183</v>
       </c>
       <c r="G205" s="19" t="s">
-        <v>376</v>
+        <v>85</v>
       </c>
       <c r="H205" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I205" s="20" t="s">
-        <v>788</v>
+        <v>506</v>
       </c>
       <c r="J205" s="20">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="K205" s="20" t="s">
         <v>296</v>
@@ -28511,7 +28523,7 @@
       </c>
       <c r="X205" s="2">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y205" s="2">
         <f t="shared" si="57"/>
@@ -28539,20 +28551,20 @@
         <v>0</v>
       </c>
       <c r="AF205" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG205" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH205" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI205" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="82"/>
+        <v>1</v>
       </c>
       <c r="AJ205" s="13"/>
       <c r="AK205" s="13"/>
@@ -28567,53 +28579,49 @@
       <c r="AT205" s="13"/>
     </row>
     <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="33">
-        <v>0</v>
-      </c>
-      <c r="B206" s="33">
+      <c r="A206" s="20">
+        <v>1</v>
+      </c>
+      <c r="B206" s="20">
         <v>2</v>
       </c>
-      <c r="C206" s="33">
+      <c r="C206" s="20">
         <v>7</v>
       </c>
-      <c r="D206" s="34" t="s">
-        <v>729</v>
-      </c>
-      <c r="E206" s="34" t="s">
+      <c r="D206" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E206" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F206" s="34" t="s">
-        <v>730</v>
-      </c>
-      <c r="G206" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H206" s="34" t="s">
+      <c r="F206" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G206" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="H206" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I206" s="33" t="s">
-        <v>731</v>
-      </c>
-      <c r="J206" s="33">
-        <v>4</v>
-      </c>
-      <c r="K206" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="L206" s="33" t="s">
+      <c r="I206" s="20" t="s">
+        <v>788</v>
+      </c>
+      <c r="J206" s="20">
+        <v>99</v>
+      </c>
+      <c r="K206" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="M206" s="34" t="s">
+      <c r="L206" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="M206" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="N206" s="34" t="s">
-        <v>869</v>
-      </c>
-      <c r="O206" s="35">
-        <v>1</v>
-      </c>
-      <c r="P206" s="33"/>
-      <c r="Q206" s="34"/>
+      <c r="N206" s="19"/>
+      <c r="O206" s="18"/>
+      <c r="P206" s="20"/>
+      <c r="Q206" s="19"/>
       <c r="R206" s="13"/>
       <c r="S206" s="2">
         <f t="shared" si="51"/>
@@ -28629,7 +28637,7 @@
       </c>
       <c r="V206" s="2">
         <f t="shared" si="54"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W206" s="2">
         <f t="shared" si="55"/>
@@ -28662,23 +28670,23 @@
       </c>
       <c r="AE206" s="2">
         <f t="shared" si="62"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF206" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG206" s="2">
-        <f t="shared" si="64"/>
-        <v>1</v>
+        <f t="shared" si="80"/>
+        <v>0</v>
       </c>
       <c r="AH206" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI206" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="AJ206" s="13"/>
       <c r="AK206" s="13"/>
@@ -28694,7 +28702,7 @@
     </row>
     <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B207" s="33">
         <v>2</v>
@@ -28709,19 +28717,19 @@
         <v>38</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>780</v>
+        <v>730</v>
       </c>
       <c r="G207" s="34" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H207" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I207" s="33" t="s">
-        <v>789</v>
+        <v>731</v>
       </c>
       <c r="J207" s="33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K207" s="33" t="s">
         <v>298</v>
@@ -28747,7 +28755,7 @@
       </c>
       <c r="T207" s="2">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U207" s="2">
         <f t="shared" si="53"/>
@@ -28755,7 +28763,7 @@
       </c>
       <c r="V207" s="2">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W207" s="2">
         <f t="shared" si="55"/>
@@ -28791,20 +28799,20 @@
         <v>1</v>
       </c>
       <c r="AF207" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG207" s="2">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="80"/>
+        <v>1</v>
       </c>
       <c r="AH207" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI207" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="82"/>
+        <v>1</v>
       </c>
       <c r="AJ207" s="13"/>
       <c r="AK207" s="13"/>
@@ -28820,7 +28828,7 @@
     </row>
     <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B208" s="33">
         <v>2</v>
@@ -28829,28 +28837,28 @@
         <v>7</v>
       </c>
       <c r="D208" s="34" t="s">
-        <v>160</v>
+        <v>729</v>
       </c>
       <c r="E208" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>723</v>
+        <v>780</v>
       </c>
       <c r="G208" s="34" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H208" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I208" s="33" t="s">
-        <v>161</v>
+        <v>789</v>
       </c>
       <c r="J208" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K208" s="33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L208" s="33" t="s">
         <v>296</v>
@@ -28859,23 +28867,21 @@
         <v>198</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
       </c>
-      <c r="P208" s="33">
-        <v>1</v>
-      </c>
+      <c r="P208" s="33"/>
       <c r="Q208" s="34"/>
       <c r="R208" s="13"/>
       <c r="S208" s="2">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T208" s="2">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U208" s="2">
         <f t="shared" si="53"/>
@@ -28912,26 +28918,26 @@
       <c r="AC208" s="2"/>
       <c r="AD208" s="2">
         <f t="shared" si="61"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE208" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF208" s="2">
-        <f t="shared" si="63"/>
-        <v>1</v>
+        <f t="shared" si="79"/>
+        <v>0</v>
       </c>
       <c r="AG208" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH208" s="2">
-        <f t="shared" si="65"/>
-        <v>1</v>
+        <f t="shared" si="81"/>
+        <v>0</v>
       </c>
       <c r="AI208" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AJ208" s="13"/>
@@ -28957,34 +28963,34 @@
         <v>7</v>
       </c>
       <c r="D209" s="34" t="s">
-        <v>343</v>
+        <v>160</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>372</v>
+        <v>723</v>
       </c>
       <c r="G209" s="34" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H209" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I209" s="33" t="s">
-        <v>384</v>
+        <v>161</v>
       </c>
       <c r="J209" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K209" s="33" t="s">
         <v>295</v>
       </c>
       <c r="L209" s="33" t="s">
-        <v>105</v>
+        <v>296</v>
       </c>
       <c r="M209" s="34" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="N209" s="34" t="s">
         <v>860</v>
@@ -28999,11 +29005,11 @@
       <c r="R209" s="13"/>
       <c r="S209" s="2">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T209" s="2">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U209" s="2">
         <f t="shared" si="53"/>
@@ -29047,19 +29053,19 @@
         <v>0</v>
       </c>
       <c r="AF209" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>1</v>
       </c>
       <c r="AG209" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH209" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
       <c r="AI209" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AJ209" s="13"/>
@@ -29075,57 +29081,63 @@
       <c r="AT209" s="13"/>
     </row>
     <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="20">
-        <v>0</v>
-      </c>
-      <c r="B210" s="20">
+      <c r="A210" s="33">
+        <v>0</v>
+      </c>
+      <c r="B210" s="33">
         <v>2</v>
       </c>
-      <c r="C210" s="20">
+      <c r="C210" s="33">
         <v>7</v>
       </c>
-      <c r="D210" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E210" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F210" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="G210" s="19" t="s">
-        <v>558</v>
-      </c>
-      <c r="H210" s="19" t="s">
+      <c r="D210" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="E210" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="F210" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="G210" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H210" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I210" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="J210" s="20">
-        <v>1</v>
-      </c>
-      <c r="K210" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="L210" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="M210" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="N210" s="19"/>
-      <c r="O210" s="18"/>
-      <c r="P210" s="20"/>
-      <c r="Q210" s="19"/>
+      <c r="I210" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="J210" s="33">
+        <v>2</v>
+      </c>
+      <c r="K210" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="L210" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M210" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="N210" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O210" s="35">
+        <v>1</v>
+      </c>
+      <c r="P210" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q210" s="34"/>
       <c r="R210" s="13"/>
       <c r="S210" s="2">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T210" s="2">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U210" s="2">
         <f t="shared" si="53"/>
@@ -29162,27 +29174,27 @@
       <c r="AC210" s="2"/>
       <c r="AD210" s="2">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE210" s="2">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AF210" s="2">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="79"/>
+        <v>1</v>
       </c>
       <c r="AG210" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH210" s="2">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="81"/>
+        <v>1</v>
       </c>
       <c r="AI210" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="AJ210" s="13"/>
       <c r="AK210" s="13"/>
@@ -29207,28 +29219,28 @@
         <v>7</v>
       </c>
       <c r="D211" s="19" t="s">
-        <v>344</v>
+        <v>435</v>
       </c>
       <c r="E211" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F211" s="19" t="s">
-        <v>143</v>
+        <v>436</v>
       </c>
       <c r="G211" s="19" t="s">
-        <v>182</v>
+        <v>558</v>
       </c>
       <c r="H211" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I211" s="20" t="s">
-        <v>144</v>
+        <v>565</v>
       </c>
       <c r="J211" s="20">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="K211" s="20" t="s">
-        <v>296</v>
+        <v>388</v>
       </c>
       <c r="L211" s="20" t="s">
         <v>296</v>
@@ -29243,7 +29255,7 @@
       <c r="R211" s="13"/>
       <c r="S211" s="2">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T211" s="2">
         <f t="shared" si="52"/>
@@ -29291,19 +29303,19 @@
         <v>0</v>
       </c>
       <c r="AF211" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG211" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH211" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI211" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>1</v>
       </c>
       <c r="AJ211" s="13"/>
@@ -29319,120 +29331,114 @@
       <c r="AT211" s="13"/>
     </row>
     <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="33">
-        <v>0</v>
-      </c>
-      <c r="B212" s="33">
+      <c r="A212" s="20">
+        <v>0</v>
+      </c>
+      <c r="B212" s="20">
         <v>2</v>
       </c>
-      <c r="C212" s="33">
+      <c r="C212" s="20">
         <v>7</v>
       </c>
-      <c r="D212" s="34" t="s">
-        <v>345</v>
-      </c>
-      <c r="E212" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="F212" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="G212" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H212" s="34" t="s">
+      <c r="D212" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="E212" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F212" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="G212" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="H212" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I212" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="J212" s="33">
-        <v>2</v>
-      </c>
-      <c r="K212" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="L212" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M212" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="N212" s="34" t="s">
-        <v>860</v>
-      </c>
-      <c r="O212" s="35">
-        <v>1</v>
-      </c>
-      <c r="P212" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q212" s="34"/>
+      <c r="I212" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="J212" s="20">
+        <v>99</v>
+      </c>
+      <c r="K212" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="L212" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="M212" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="N212" s="19"/>
+      <c r="O212" s="18"/>
+      <c r="P212" s="20"/>
+      <c r="Q212" s="19"/>
       <c r="R212" s="13"/>
       <c r="S212" s="2">
-        <f t="shared" ref="S212:S217" si="67">IF(J212=$S$7,1,0)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="T212" s="2">
-        <f t="shared" ref="T212:T217" si="68">IF(J212=$T$7,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="52"/>
+        <v>0</v>
       </c>
       <c r="U212" s="2">
-        <f t="shared" ref="U212:U217" si="69">IF(J212=$U$7,1,0)</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="V212" s="2">
-        <f t="shared" ref="V212:V217" si="70">IF(J212=$V$7,1,0)</f>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="W212" s="2">
-        <f t="shared" ref="W212:W217" si="71">IF(J212=$W$7,1,0)</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="X212" s="2">
-        <f t="shared" ref="X212:X217" si="72">IF(J212=$X$7,1,0)</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Y212" s="2">
-        <f t="shared" ref="Y212:Y217" si="73">IF(J212=$Y$7,1,0)</f>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="Z212" s="2">
-        <f t="shared" ref="Z212:Z217" si="74">IF(J212=$Z$7,1,0)</f>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AA212" s="2">
-        <f t="shared" ref="AA212:AA217" si="75">IF(J212=$AA$7,1,0)</f>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AB212" s="2">
-        <f t="shared" ref="AB212:AB217" si="76">IF(J212=$AB$7,1,0)</f>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AC212" s="2"/>
       <c r="AD212" s="2">
-        <f t="shared" ref="AD212:AD217" si="77">+O212*P212</f>
-        <v>1</v>
+        <f t="shared" si="61"/>
+        <v>0</v>
       </c>
       <c r="AE212" s="2">
-        <f t="shared" ref="AE212:AE217" si="78">O212*(1-P212)</f>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AF212" s="2">
-        <f t="shared" si="63"/>
-        <v>1</v>
+        <f t="shared" si="79"/>
+        <v>0</v>
       </c>
       <c r="AG212" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH212" s="2">
-        <f t="shared" si="65"/>
-        <v>1</v>
+        <f t="shared" si="81"/>
+        <v>0</v>
       </c>
       <c r="AI212" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="82"/>
+        <v>1</v>
       </c>
       <c r="AJ212" s="13"/>
       <c r="AK212" s="13"/>
@@ -29448,7 +29454,7 @@
     </row>
     <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B213" s="33">
         <v>2</v>
@@ -29463,19 +29469,19 @@
         <v>55</v>
       </c>
       <c r="F213" s="34" t="s">
-        <v>559</v>
+        <v>373</v>
       </c>
       <c r="G213" s="34" t="s">
-        <v>560</v>
+        <v>90</v>
       </c>
       <c r="H213" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I213" s="33" t="s">
-        <v>566</v>
+        <v>56</v>
       </c>
       <c r="J213" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K213" s="33" t="s">
         <v>298</v>
@@ -29498,68 +29504,68 @@
       <c r="Q213" s="34"/>
       <c r="R213" s="13"/>
       <c r="S213" s="2">
-        <f t="shared" si="67"/>
-        <v>1</v>
+        <f t="shared" ref="S213:S218" si="83">IF(J213=$S$7,1,0)</f>
+        <v>0</v>
       </c>
       <c r="T213" s="2">
-        <f t="shared" si="68"/>
-        <v>0</v>
+        <f t="shared" ref="T213:T218" si="84">IF(J213=$T$7,1,0)</f>
+        <v>1</v>
       </c>
       <c r="U213" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" ref="U213:U218" si="85">IF(J213=$U$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="V213" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="V213:V218" si="86">IF(J213=$V$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="W213" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" ref="W213:W218" si="87">IF(J213=$W$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="X213" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="X213:X218" si="88">IF(J213=$X$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Y213" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="Y213:Y218" si="89">IF(J213=$Y$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Z213" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" ref="Z213:Z218" si="90">IF(J213=$Z$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AA213" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" ref="AA213:AA218" si="91">IF(J213=$AA$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB213" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="AB213:AB218" si="92">IF(J213=$AB$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC213" s="2"/>
       <c r="AD213" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" ref="AD213:AD218" si="93">+O213*P213</f>
         <v>1</v>
       </c>
       <c r="AE213" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" ref="AE213:AE218" si="94">O213*(1-P213)</f>
         <v>0</v>
       </c>
       <c r="AF213" s="2">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="79"/>
+        <v>1</v>
       </c>
       <c r="AG213" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH213" s="2">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="81"/>
+        <v>1</v>
       </c>
       <c r="AI213" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AJ213" s="13"/>
@@ -29576,7 +29582,7 @@
     </row>
     <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B214" s="33">
         <v>2</v>
@@ -29585,22 +29591,22 @@
         <v>7</v>
       </c>
       <c r="D214" s="34" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="E214" s="34" t="s">
         <v>55</v>
       </c>
       <c r="F214" s="34" t="s">
-        <v>479</v>
+        <v>559</v>
       </c>
       <c r="G214" s="34" t="s">
-        <v>503</v>
+        <v>560</v>
       </c>
       <c r="H214" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I214" s="33" t="s">
-        <v>480</v>
+        <v>566</v>
       </c>
       <c r="J214" s="33">
         <v>1</v>
@@ -29626,68 +29632,68 @@
       <c r="Q214" s="34"/>
       <c r="R214" s="13"/>
       <c r="S214" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="83"/>
         <v>1</v>
       </c>
       <c r="T214" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U214" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="V214" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="W214" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="X214" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="Y214" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Z214" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="AA214" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AB214" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AC214" s="2"/>
       <c r="AD214" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
       <c r="AE214" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AF214" s="2">
-        <f t="shared" si="63"/>
-        <v>1</v>
+        <f t="shared" si="79"/>
+        <v>0</v>
       </c>
       <c r="AG214" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH214" s="2">
-        <f t="shared" si="65"/>
-        <v>1</v>
+        <f t="shared" si="81"/>
+        <v>0</v>
       </c>
       <c r="AI214" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="AJ214" s="13"/>
@@ -29702,9 +29708,9 @@
       <c r="AS214" s="13"/>
       <c r="AT214" s="13"/>
     </row>
-    <row r="215" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B215" s="33">
         <v>2</v>
@@ -29719,19 +29725,19 @@
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>905</v>
+        <v>479</v>
       </c>
       <c r="G215" s="34" t="s">
-        <v>147</v>
+        <v>503</v>
       </c>
       <c r="H215" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I215" s="33" t="s">
-        <v>790</v>
+        <v>480</v>
       </c>
       <c r="J215" s="33">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="K215" s="33" t="s">
         <v>298</v>
@@ -29752,190 +29758,197 @@
         <v>1</v>
       </c>
       <c r="Q215" s="34"/>
+      <c r="R215" s="13"/>
       <c r="S215" s="2">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <f t="shared" si="83"/>
+        <v>1</v>
       </c>
       <c r="T215" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U215" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="V215" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="W215" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="X215" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="Y215" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Z215" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="AA215" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AB215" s="2">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="AC215" s="2"/>
       <c r="AD215" s="2">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
       <c r="AE215" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AF215" s="2">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="79"/>
+        <v>1</v>
       </c>
       <c r="AG215" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH215" s="2">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="81"/>
+        <v>1</v>
       </c>
       <c r="AI215" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AK215" s="3"/>
-      <c r="AL215" s="3"/>
-      <c r="AM215" s="3"/>
-      <c r="AN215" s="3"/>
-      <c r="AO215" s="3"/>
-      <c r="AP215" s="3"/>
-      <c r="AQ215" s="3"/>
-      <c r="AR215" s="3"/>
-      <c r="AS215" s="3"/>
-      <c r="AT215" s="3"/>
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="AJ215" s="13"/>
+      <c r="AK215" s="13"/>
+      <c r="AL215" s="13"/>
+      <c r="AM215" s="13"/>
+      <c r="AN215" s="13"/>
+      <c r="AO215" s="13"/>
+      <c r="AP215" s="13"/>
+      <c r="AQ215" s="13"/>
+      <c r="AR215" s="13"/>
+      <c r="AS215" s="13"/>
+      <c r="AT215" s="13"/>
     </row>
     <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="36">
-        <v>0</v>
-      </c>
-      <c r="B216" s="36">
+      <c r="A216" s="33">
+        <v>1</v>
+      </c>
+      <c r="B216" s="33">
         <v>2</v>
       </c>
-      <c r="C216" s="36">
+      <c r="C216" s="33">
         <v>7</v>
       </c>
-      <c r="D216" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="E216" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="F216" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="G216" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H216" s="37" t="s">
+      <c r="D216" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="E216" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F216" s="34" t="s">
+        <v>905</v>
+      </c>
+      <c r="G216" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="H216" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I216" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="J216" s="36">
-        <v>1</v>
-      </c>
-      <c r="K216" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="L216" s="36" t="s">
-        <v>312</v>
-      </c>
-      <c r="M216" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="N216" s="37" t="s">
-        <v>895</v>
-      </c>
-      <c r="O216" s="38"/>
-      <c r="P216" s="36"/>
-      <c r="Q216" s="37"/>
+      <c r="I216" s="33" t="s">
+        <v>790</v>
+      </c>
+      <c r="J216" s="33">
+        <v>99</v>
+      </c>
+      <c r="K216" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="L216" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M216" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="N216" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O216" s="35">
+        <v>1</v>
+      </c>
+      <c r="P216" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q216" s="34"/>
       <c r="S216" s="2">
-        <f t="shared" si="67"/>
-        <v>1</v>
+        <f t="shared" si="83"/>
+        <v>0</v>
       </c>
       <c r="T216" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U216" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="V216" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="W216" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="X216" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="Y216" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Z216" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="AA216" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AB216" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AD216" s="2">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="93"/>
+        <v>1</v>
       </c>
       <c r="AE216" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AF216" s="2">
-        <f t="shared" si="63"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AG216" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH216" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI216" s="2">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="AK216" s="3"/>
       <c r="AL216" s="3"/>
@@ -29948,170 +29961,243 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="33">
-        <v>0</v>
-      </c>
-      <c r="B217" s="33">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="36">
+        <v>0</v>
+      </c>
+      <c r="B217" s="36">
         <v>2</v>
       </c>
-      <c r="C217" s="33">
+      <c r="C217" s="36">
         <v>7</v>
       </c>
-      <c r="D217" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="E217" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="F217" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="G217" s="34" t="s">
+      <c r="D217" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E217" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="F217" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="G217" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="H217" s="34" t="s">
+      <c r="H217" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="I217" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="J217" s="33">
-        <v>1</v>
-      </c>
-      <c r="K217" s="33" t="s">
+      <c r="I217" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="J217" s="36">
+        <v>1</v>
+      </c>
+      <c r="K217" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="L217" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="M217" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="N217" s="34" t="s">
-        <v>860</v>
-      </c>
-      <c r="O217" s="35">
-        <v>1</v>
-      </c>
-      <c r="P217" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q217" s="34"/>
-      <c r="R217" s="13"/>
+      <c r="L217" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="M217" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="N217" s="37" t="s">
+        <v>895</v>
+      </c>
+      <c r="O217" s="38"/>
+      <c r="P217" s="36"/>
+      <c r="Q217" s="37"/>
       <c r="S217" s="2">
-        <f t="shared" si="67"/>
+        <f t="shared" si="83"/>
         <v>1</v>
       </c>
       <c r="T217" s="2">
-        <f t="shared" si="68"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U217" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="V217" s="2">
-        <f t="shared" si="70"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="W217" s="2">
-        <f t="shared" si="71"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="X217" s="2">
-        <f t="shared" si="72"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="Y217" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="Z217" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="AA217" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AB217" s="2">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AC217" s="2"/>
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
       <c r="AD217" s="2">
-        <f t="shared" si="77"/>
-        <v>1</v>
+        <f t="shared" si="93"/>
+        <v>0</v>
       </c>
       <c r="AE217" s="2">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="AF217" s="2">
-        <f t="shared" si="63"/>
-        <v>1</v>
+        <f t="shared" si="79"/>
+        <v>0</v>
       </c>
       <c r="AG217" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH217" s="2">
-        <f t="shared" si="65"/>
-        <v>1</v>
+        <f t="shared" si="81"/>
+        <v>0</v>
       </c>
       <c r="AI217" s="2">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AJ217" s="13"/>
-      <c r="AK217" s="13"/>
-      <c r="AL217" s="13"/>
-      <c r="AM217" s="13"/>
-      <c r="AN217" s="13"/>
-      <c r="AO217" s="13"/>
-      <c r="AP217" s="13"/>
-      <c r="AQ217" s="13"/>
-      <c r="AR217" s="13"/>
-      <c r="AS217" s="13"/>
-      <c r="AT217" s="13"/>
+        <f t="shared" si="82"/>
+        <v>1</v>
+      </c>
+      <c r="AK217" s="3"/>
+      <c r="AL217" s="3"/>
+      <c r="AM217" s="3"/>
+      <c r="AN217" s="3"/>
+      <c r="AO217" s="3"/>
+      <c r="AP217" s="3"/>
+      <c r="AQ217" s="3"/>
+      <c r="AR217" s="3"/>
+      <c r="AS217" s="3"/>
+      <c r="AT217" s="3"/>
     </row>
     <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="20"/>
-      <c r="B218" s="20"/>
-      <c r="C218" s="20"/>
-      <c r="D218" s="19"/>
-      <c r="E218" s="19"/>
-      <c r="F218" s="19"/>
-      <c r="G218" s="19"/>
-      <c r="H218" s="19"/>
-      <c r="I218" s="20"/>
-      <c r="J218" s="20"/>
-      <c r="K218" s="20"/>
-      <c r="L218" s="20"/>
-      <c r="M218" s="19"/>
-      <c r="N218" s="19"/>
-      <c r="O218" s="18"/>
-      <c r="P218" s="20"/>
-      <c r="Q218" s="19"/>
+      <c r="A218" s="33">
+        <v>0</v>
+      </c>
+      <c r="B218" s="33">
+        <v>2</v>
+      </c>
+      <c r="C218" s="33">
+        <v>7</v>
+      </c>
+      <c r="D218" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E218" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F218" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G218" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H218" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I218" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="J218" s="33">
+        <v>1</v>
+      </c>
+      <c r="K218" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="L218" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="M218" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="N218" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="O218" s="35">
+        <v>1</v>
+      </c>
+      <c r="P218" s="33">
+        <v>1</v>
+      </c>
+      <c r="Q218" s="34"/>
       <c r="R218" s="13"/>
-      <c r="S218" s="2"/>
-      <c r="T218" s="2"/>
-      <c r="U218" s="2"/>
-      <c r="V218" s="2"/>
-      <c r="W218" s="2"/>
-      <c r="X218" s="2"/>
-      <c r="Y218" s="2"/>
-      <c r="Z218" s="2"/>
-      <c r="AA218" s="2"/>
-      <c r="AB218" s="2"/>
+      <c r="S218" s="2">
+        <f t="shared" si="83"/>
+        <v>1</v>
+      </c>
+      <c r="T218" s="2">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="U218" s="2">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="V218" s="2">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="W218" s="2">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="X218" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Y218" s="2">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Z218" s="2">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="AA218" s="2">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="AB218" s="2">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
       <c r="AC218" s="2"/>
-      <c r="AD218" s="2"/>
-      <c r="AE218" s="2"/>
-      <c r="AF218" s="2"/>
-      <c r="AG218" s="2"/>
-      <c r="AH218" s="2"/>
-      <c r="AI218" s="2"/>
+      <c r="AD218" s="2">
+        <f t="shared" si="93"/>
+        <v>1</v>
+      </c>
+      <c r="AE218" s="2">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="AF218" s="2">
+        <f t="shared" si="79"/>
+        <v>1</v>
+      </c>
+      <c r="AG218" s="2">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AH218" s="2">
+        <f t="shared" si="81"/>
+        <v>1</v>
+      </c>
+      <c r="AI218" s="2">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
       <c r="AJ218" s="13"/>
       <c r="AK218" s="13"/>
       <c r="AL218" s="13"/>
@@ -34876,17 +34962,65 @@
       <c r="AS317" s="13"/>
       <c r="AT317" s="13"/>
     </row>
+    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="20"/>
+      <c r="B318" s="20"/>
+      <c r="C318" s="20"/>
+      <c r="D318" s="19"/>
+      <c r="E318" s="19"/>
+      <c r="F318" s="19"/>
+      <c r="G318" s="19"/>
+      <c r="H318" s="19"/>
+      <c r="I318" s="20"/>
+      <c r="J318" s="20"/>
+      <c r="K318" s="20"/>
+      <c r="L318" s="20"/>
+      <c r="M318" s="19"/>
+      <c r="N318" s="19"/>
+      <c r="O318" s="18"/>
+      <c r="P318" s="20"/>
+      <c r="Q318" s="19"/>
+      <c r="R318" s="13"/>
+      <c r="S318" s="2"/>
+      <c r="T318" s="2"/>
+      <c r="U318" s="2"/>
+      <c r="V318" s="2"/>
+      <c r="W318" s="2"/>
+      <c r="X318" s="2"/>
+      <c r="Y318" s="2"/>
+      <c r="Z318" s="2"/>
+      <c r="AA318" s="2"/>
+      <c r="AB318" s="2"/>
+      <c r="AC318" s="2"/>
+      <c r="AD318" s="2"/>
+      <c r="AE318" s="2"/>
+      <c r="AF318" s="2"/>
+      <c r="AG318" s="2"/>
+      <c r="AH318" s="2"/>
+      <c r="AI318" s="2"/>
+      <c r="AJ318" s="13"/>
+      <c r="AK318" s="13"/>
+      <c r="AL318" s="13"/>
+      <c r="AM318" s="13"/>
+      <c r="AN318" s="13"/>
+      <c r="AO318" s="13"/>
+      <c r="AP318" s="13"/>
+      <c r="AQ318" s="13"/>
+      <c r="AR318" s="13"/>
+      <c r="AS318" s="13"/>
+      <c r="AT318" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:AI217" xr:uid="{CEB868F8-3E33-4B67-A7A2-E08A38673519}">
+  <autoFilter ref="A7:AI218" xr:uid="{CEB868F8-3E33-4B67-A7A2-E08A38673519}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:DK183">
       <sortCondition ref="J7:J162"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:P217">
-    <sortCondition ref="B8:B217"/>
-    <sortCondition ref="C8:C217"/>
-    <sortCondition ref="D8:D217"/>
-    <sortCondition ref="A8:A217"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:Q218">
+    <sortCondition ref="B8:B218"/>
+    <sortCondition ref="C8:C218"/>
+    <sortCondition ref="D8:D218"/>
+    <sortCondition ref="A8:A218"/>
   </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.35433070866141736" right="0.35433070866141736" top="0.55118110236220474" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.19685039370078741"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C29166B-6F9D-4FBD-8EC2-53A9EB9B3379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D492D5-694C-47D7-972E-F7C733CB055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -9085,51 +9085,53 @@
       <c r="AT48" s="13"/>
     </row>
     <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="36">
-        <v>0</v>
-      </c>
-      <c r="B49" s="36">
-        <v>1</v>
-      </c>
-      <c r="C49" s="36">
+      <c r="A49" s="33">
+        <v>0</v>
+      </c>
+      <c r="B49" s="33">
+        <v>1</v>
+      </c>
+      <c r="C49" s="33">
         <v>3</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="E49" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="G49" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H49" s="37" t="s">
+      <c r="H49" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I49" s="36" t="s">
+      <c r="I49" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="J49" s="36">
-        <v>1</v>
-      </c>
-      <c r="K49" s="36" t="s">
+      <c r="J49" s="33">
+        <v>1</v>
+      </c>
+      <c r="K49" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="L49" s="36" t="s">
+      <c r="L49" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M49" s="37" t="s">
+      <c r="M49" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="N49" s="37" t="s">
-        <v>861</v>
-      </c>
-      <c r="O49" s="38"/>
-      <c r="P49" s="36"/>
-      <c r="Q49" s="37"/>
+      <c r="N49" s="34" t="s">
+        <v>869</v>
+      </c>
+      <c r="O49" s="35">
+        <v>1</v>
+      </c>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="34"/>
       <c r="R49" s="13"/>
       <c r="S49" s="2">
         <f t="shared" si="7"/>
@@ -9178,7 +9180,7 @@
       </c>
       <c r="AE49" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" s="2">
         <f t="shared" si="3"/>
@@ -9186,7 +9188,7 @@
       </c>
       <c r="AG49" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH49" s="2">
         <f t="shared" si="5"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D492D5-694C-47D7-972E-F7C733CB055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2083CFC0-C743-48F6-9EAF-CDB9EDD184A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>624</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -17935,51 +17935,53 @@
       <c r="AT119" s="13"/>
     </row>
     <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="36">
-        <v>0</v>
-      </c>
-      <c r="B120" s="36">
+      <c r="A120" s="33">
+        <v>0</v>
+      </c>
+      <c r="B120" s="33">
         <v>2</v>
       </c>
-      <c r="C120" s="36">
+      <c r="C120" s="33">
         <v>2</v>
       </c>
-      <c r="D120" s="37" t="s">
+      <c r="D120" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="E120" s="37" t="s">
+      <c r="E120" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F120" s="37" t="s">
+      <c r="F120" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="G120" s="37" t="s">
+      <c r="G120" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H120" s="37" t="s">
+      <c r="H120" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I120" s="36" t="s">
+      <c r="I120" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="J120" s="36">
+      <c r="J120" s="33">
         <v>4</v>
       </c>
-      <c r="K120" s="36" t="s">
+      <c r="K120" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="L120" s="36" t="s">
+      <c r="L120" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M120" s="37" t="s">
+      <c r="M120" s="34" t="s">
         <v>716</v>
       </c>
-      <c r="N120" s="37" t="s">
-        <v>861</v>
-      </c>
-      <c r="O120" s="38"/>
-      <c r="P120" s="36"/>
-      <c r="Q120" s="37"/>
+      <c r="N120" s="34" t="s">
+        <v>869</v>
+      </c>
+      <c r="O120" s="35">
+        <v>1</v>
+      </c>
+      <c r="P120" s="33"/>
+      <c r="Q120" s="34"/>
       <c r="R120" s="13"/>
       <c r="S120" s="2">
         <f t="shared" si="23"/>
@@ -18028,7 +18030,7 @@
       </c>
       <c r="AE120" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF120" s="2">
         <f t="shared" si="19"/>
@@ -18036,7 +18038,7 @@
       </c>
       <c r="AG120" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH120" s="2">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2083CFC0-C743-48F6-9EAF-CDB9EDD184A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0BDCB4-F262-44F2-B963-A8D794F8C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="924">
   <si>
     <t>Recensore</t>
   </si>
@@ -1843,9 +1843,6 @@
     <t>351/6271679</t>
   </si>
   <si>
-    <t>Via XX Settembre, 17</t>
-  </si>
-  <si>
     <t>Pressato Coffee and Books</t>
   </si>
   <si>
@@ -2888,6 +2885,12 @@
   </si>
   <si>
     <t>4 corse</t>
+  </si>
+  <si>
+    <t>Corso Duca degli Abruzzi, 59</t>
+  </si>
+  <si>
+    <t>45.056982007771495, 7.659341688955742</t>
   </si>
 </sst>
 </file>
@@ -3746,15 +3749,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,18 +3779,18 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3877,7 +3880,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3888,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3898,13 +3901,13 @@
     </row>
     <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>690</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>691</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>692</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>13</v>
@@ -3925,16 +3928,16 @@
         <v>11</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>0</v>
@@ -3946,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="43" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="25">
@@ -4030,22 +4033,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>238</v>
       </c>
       <c r="F8" s="34" t="s">
+        <v>666</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>667</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>668</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J8" s="33">
         <v>99</v>
@@ -4054,13 +4057,13 @@
         <v>302</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4307,10 +4310,10 @@
         <v>130</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4412,7 +4415,7 @@
         <v>238</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>109</v>
@@ -4427,16 +4430,16 @@
         <v>99</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L11" s="36" t="s">
+        <v>687</v>
+      </c>
+      <c r="M11" s="37" t="s">
         <v>688</v>
       </c>
-      <c r="M11" s="37" t="s">
-        <v>689</v>
-      </c>
       <c r="N11" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O11" s="38"/>
       <c r="P11" s="36"/>
@@ -4530,13 +4533,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>280</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G12" s="41" t="s">
         <v>374</v>
@@ -4545,7 +4548,7 @@
         <v>192</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J12" s="40">
         <v>99</v>
@@ -4554,10 +4557,10 @@
         <v>302</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="N12" s="41"/>
       <c r="O12" s="42"/>
@@ -4682,7 +4685,7 @@
         <v>105</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O13" s="35">
         <v>1</v>
@@ -4780,13 +4783,13 @@
         <v>1</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>280</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>90</v>
@@ -4795,7 +4798,7 @@
         <v>192</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J14" s="36">
         <v>2</v>
@@ -4810,7 +4813,7 @@
         <v>197</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4904,20 +4907,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>280</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>192</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
@@ -5020,13 +5023,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>84</v>
@@ -5035,7 +5038,7 @@
         <v>192</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="J16" s="20">
         <v>1</v>
@@ -5142,22 +5145,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G17" s="34" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J17" s="33">
         <v>99</v>
@@ -5169,10 +5172,10 @@
         <v>47</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5268,22 +5271,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>237</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J18" s="36"/>
       <c r="K18" s="36" t="s">
@@ -5293,10 +5296,10 @@
         <v>45</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5539,10 +5542,10 @@
         <v>514</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="N20" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O20" s="35">
         <v>1</v>
@@ -5789,10 +5792,10 @@
         <v>303</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O22" s="35">
         <v>1</v>
@@ -6042,7 +6045,7 @@
         <v>517</v>
       </c>
       <c r="N24" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O24" s="38"/>
       <c r="P24" s="36"/>
@@ -6136,22 +6139,22 @@
         <v>2</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>280</v>
       </c>
       <c r="F25" s="37" t="s">
+        <v>606</v>
+      </c>
+      <c r="G25" s="37" t="s">
         <v>607</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>608</v>
       </c>
       <c r="H25" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J25" s="36">
         <v>99</v>
@@ -6160,13 +6163,13 @@
         <v>292</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M25" s="37" t="s">
         <v>197</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O25" s="38"/>
       <c r="P25" s="36"/>
@@ -6266,10 +6269,10 @@
         <v>237</v>
       </c>
       <c r="F26" s="37" t="s">
+        <v>773</v>
+      </c>
+      <c r="G26" s="37" t="s">
         <v>774</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>775</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>192</v>
@@ -6290,7 +6293,7 @@
         <v>197</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O26" s="38"/>
       <c r="P26" s="36"/>
@@ -6505,13 +6508,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>238</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>139</v>
@@ -6520,7 +6523,7 @@
         <v>192</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J28" s="20">
         <v>6</v>
@@ -6529,7 +6532,7 @@
         <v>388</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>197</v>
@@ -6627,13 +6630,13 @@
         <v>2</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>280</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>90</v>
@@ -6642,7 +6645,7 @@
         <v>192</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J29" s="33">
         <v>2</v>
@@ -6654,10 +6657,10 @@
         <v>514</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6778,10 +6781,10 @@
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="37" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O30" s="38"/>
       <c r="P30" s="36"/>
@@ -6899,18 +6902,18 @@
         <v>302</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O31" s="38"/>
       <c r="P31" s="36"/>
       <c r="Q31" s="37" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="2">
@@ -7031,7 +7034,7 @@
         <v>248</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O32" s="38"/>
       <c r="P32" s="36"/>
@@ -7125,11 +7128,11 @@
         <v>2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>90</v>
@@ -7138,7 +7141,7 @@
         <v>192</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J33" s="33"/>
       <c r="K33" s="33" t="s">
@@ -7147,7 +7150,7 @@
       <c r="L33" s="33"/>
       <c r="M33" s="34"/>
       <c r="N33" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O33" s="35">
         <v>1</v>
@@ -7245,13 +7248,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>280</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>84</v>
@@ -7260,7 +7263,7 @@
         <v>192</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20" t="s">
@@ -7270,7 +7273,7 @@
         <v>75</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N34" s="19"/>
       <c r="O34" s="18"/>
@@ -7392,7 +7395,7 @@
         <v>512</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N35" s="19"/>
       <c r="O35" s="18"/>
@@ -7517,7 +7520,7 @@
         <v>197</v>
       </c>
       <c r="N36" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O36" s="38"/>
       <c r="P36" s="36"/>
@@ -7641,7 +7644,7 @@
         <v>306</v>
       </c>
       <c r="N37" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O37" s="35">
         <v>1</v>
@@ -7739,22 +7742,22 @@
         <v>3</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>236</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G38" s="37" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J38" s="36">
         <v>99</v>
@@ -7766,10 +7769,10 @@
         <v>65</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O38" s="38"/>
       <c r="P38" s="36"/>
@@ -7878,7 +7881,7 @@
         <v>192</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J39" s="20">
         <v>99</v>
@@ -7890,7 +7893,7 @@
         <v>307</v>
       </c>
       <c r="M39" s="19" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N39" s="19"/>
       <c r="O39" s="18"/>
@@ -7985,13 +7988,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>84</v>
@@ -8000,7 +8003,7 @@
         <v>192</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J40" s="36">
         <v>1</v>
@@ -8012,10 +8015,10 @@
         <v>50</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N40" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O40" s="38"/>
       <c r="P40" s="36"/>
@@ -8109,13 +8112,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>236</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G41" s="34" t="s">
         <v>104</v>
@@ -8124,7 +8127,7 @@
         <v>192</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="J41" s="33">
         <v>2</v>
@@ -8136,10 +8139,10 @@
         <v>512</v>
       </c>
       <c r="M41" s="34" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="N41" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O41" s="35">
         <v>1</v>
@@ -8262,7 +8265,7 @@
         <v>40</v>
       </c>
       <c r="M42" s="19" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N42" s="19"/>
       <c r="O42" s="18"/>
@@ -8506,7 +8509,7 @@
         <v>38</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N44" s="19"/>
       <c r="O44" s="18"/>
@@ -8628,7 +8631,7 @@
         <v>25</v>
       </c>
       <c r="M45" s="19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N45" s="19"/>
       <c r="O45" s="18"/>
@@ -8723,13 +8726,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>236</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>84</v>
@@ -8738,7 +8741,7 @@
         <v>192</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J46" s="20">
         <v>1</v>
@@ -8875,7 +8878,7 @@
         <v>520</v>
       </c>
       <c r="N47" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O47" s="35">
         <v>1</v>
@@ -8998,10 +9001,10 @@
         <v>305</v>
       </c>
       <c r="M48" s="37" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="N48" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O48" s="38"/>
       <c r="P48" s="36"/>
@@ -9125,7 +9128,7 @@
         <v>304</v>
       </c>
       <c r="N49" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O49" s="35">
         <v>1</v>
@@ -9251,7 +9254,7 @@
         <v>197</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9347,22 +9350,22 @@
         <v>3</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>236</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H51" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J51" s="36">
         <v>99</v>
@@ -9371,13 +9374,13 @@
         <v>300</v>
       </c>
       <c r="L51" s="36" t="s">
+        <v>681</v>
+      </c>
+      <c r="M51" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="M51" s="37" t="s">
-        <v>683</v>
-      </c>
       <c r="N51" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="36"/>
@@ -9620,7 +9623,7 @@
         <v>304</v>
       </c>
       <c r="N53" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="36"/>
@@ -9704,51 +9707,53 @@
       <c r="AT53" s="13"/>
     </row>
     <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="36">
-        <v>0</v>
-      </c>
-      <c r="B54" s="36">
-        <v>1</v>
-      </c>
-      <c r="C54" s="36">
+      <c r="A54" s="33">
+        <v>0</v>
+      </c>
+      <c r="B54" s="33">
+        <v>1</v>
+      </c>
+      <c r="C54" s="33">
         <v>3</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="34" t="s">
         <v>448</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="E54" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F54" s="37" t="s">
-        <v>902</v>
-      </c>
-      <c r="G54" s="37" t="s">
+      <c r="F54" s="34" t="s">
+        <v>901</v>
+      </c>
+      <c r="G54" s="34" t="s">
         <v>497</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="H54" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I54" s="36" t="s">
+      <c r="I54" s="33" t="s">
         <v>569</v>
       </c>
-      <c r="J54" s="36">
+      <c r="J54" s="33">
         <v>7</v>
       </c>
-      <c r="K54" s="36" t="s">
+      <c r="K54" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L54" s="36" t="s">
+      <c r="L54" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="M54" s="37" t="s">
+      <c r="M54" s="34" t="s">
         <v>267</v>
       </c>
-      <c r="N54" s="37" t="s">
-        <v>862</v>
-      </c>
-      <c r="O54" s="38"/>
-      <c r="P54" s="36"/>
-      <c r="Q54" s="37"/>
+      <c r="N54" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="O54" s="35">
+        <v>1</v>
+      </c>
+      <c r="P54" s="33"/>
+      <c r="Q54" s="34"/>
       <c r="R54" s="13"/>
       <c r="S54" s="2">
         <f t="shared" si="7"/>
@@ -9797,7 +9802,7 @@
       </c>
       <c r="AE54" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" s="2">
         <f t="shared" si="3"/>
@@ -9805,7 +9810,7 @@
       </c>
       <c r="AG54" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH54" s="2">
         <f t="shared" si="5"/>
@@ -9838,13 +9843,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E55" s="41" t="s">
         <v>237</v>
       </c>
       <c r="F55" s="41" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G55" s="41" t="s">
         <v>105</v>
@@ -9853,7 +9858,7 @@
         <v>192</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="J55" s="40">
         <v>99</v>
@@ -9862,16 +9867,16 @@
         <v>294</v>
       </c>
       <c r="L55" s="40" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="M55" s="41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="N55" s="41"/>
       <c r="O55" s="42"/>
       <c r="P55" s="40"/>
       <c r="Q55" s="41" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="R55" s="13"/>
       <c r="S55" s="2">
@@ -9962,13 +9967,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E56" s="34" t="s">
         <v>236</v>
       </c>
       <c r="F56" s="34" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>111</v>
@@ -9977,7 +9982,7 @@
         <v>192</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J56" s="33"/>
       <c r="K56" s="33" t="s">
@@ -9990,7 +9995,7 @@
         <v>197</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O56" s="35">
         <v>1</v>
@@ -10210,13 +10215,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F58" s="34" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>90</v>
@@ -10225,7 +10230,7 @@
         <v>192</v>
       </c>
       <c r="I58" s="33" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J58" s="33">
         <v>2</v>
@@ -10236,7 +10241,7 @@
       <c r="L58" s="33"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O58" s="35">
         <v>1</v>
@@ -10364,7 +10369,7 @@
         <v>249</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O59" s="35">
         <v>1</v>
@@ -10489,7 +10494,7 @@
         <v>307</v>
       </c>
       <c r="M60" s="19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N60" s="19"/>
       <c r="O60" s="18"/>
@@ -10584,13 +10589,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E61" s="34" t="s">
         <v>239</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>72</v>
@@ -10599,7 +10604,7 @@
         <v>192</v>
       </c>
       <c r="I61" s="33" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="J61" s="33">
         <v>4</v>
@@ -10610,7 +10615,7 @@
       <c r="L61" s="33"/>
       <c r="M61" s="34"/>
       <c r="N61" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O61" s="35">
         <v>1</v>
@@ -10830,22 +10835,22 @@
         <v>5</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>239</v>
       </c>
       <c r="F63" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="G63" s="19" t="s">
         <v>741</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>742</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="J63" s="20">
         <v>99</v>
@@ -10857,7 +10862,7 @@
         <v>30</v>
       </c>
       <c r="M63" s="19" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="N63" s="19"/>
       <c r="O63" s="18"/>
@@ -10952,13 +10957,13 @@
         <v>5</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>147</v>
@@ -10967,7 +10972,7 @@
         <v>192</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="J64" s="20">
         <v>99</v>
@@ -10979,7 +10984,7 @@
         <v>40</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="18"/>
@@ -11074,13 +11079,13 @@
         <v>5</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>105</v>
@@ -11089,7 +11094,7 @@
         <v>192</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J65" s="20">
         <v>99</v>
@@ -11101,7 +11106,7 @@
         <v>40</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N65" s="19"/>
       <c r="O65" s="18"/>
@@ -11196,13 +11201,13 @@
         <v>5</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>239</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>84</v>
@@ -11211,7 +11216,7 @@
         <v>192</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J66" s="36">
         <v>1</v>
@@ -11223,10 +11228,10 @@
         <v>514</v>
       </c>
       <c r="M66" s="37" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="N66" s="37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O66" s="38"/>
       <c r="P66" s="36"/>
@@ -11347,10 +11352,10 @@
         <v>31</v>
       </c>
       <c r="M67" s="37" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N67" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="36"/>
@@ -11474,7 +11479,7 @@
         <v>197</v>
       </c>
       <c r="N68" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O68" s="38"/>
       <c r="P68" s="36"/>
@@ -11568,13 +11573,13 @@
         <v>5</v>
       </c>
       <c r="D69" s="19" t="s">
+        <v>918</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>850</v>
+      </c>
+      <c r="F69" s="19" t="s">
         <v>919</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>851</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>920</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>72</v>
@@ -11583,7 +11588,7 @@
         <v>192</v>
       </c>
       <c r="I69" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J69" s="20">
         <v>4</v>
@@ -11595,7 +11600,7 @@
         <v>45</v>
       </c>
       <c r="M69" s="19" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="N69" s="19"/>
       <c r="O69" s="18"/>
@@ -11690,13 +11695,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="34" t="s">
+        <v>825</v>
+      </c>
+      <c r="E70" s="34" t="s">
         <v>826</v>
       </c>
-      <c r="E70" s="34" t="s">
-        <v>827</v>
-      </c>
       <c r="F70" s="34" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G70" s="34" t="s">
         <v>72</v>
@@ -11705,7 +11710,7 @@
         <v>192</v>
       </c>
       <c r="I70" s="33" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J70" s="33"/>
       <c r="K70" s="33" t="s">
@@ -11715,10 +11720,10 @@
         <v>45</v>
       </c>
       <c r="M70" s="34" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N70" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O70" s="35">
         <v>1</v>
@@ -11838,13 +11843,13 @@
         <v>293</v>
       </c>
       <c r="L71" s="36" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="M71" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N71" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="36"/>
@@ -11938,22 +11943,22 @@
         <v>5</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E72" s="34" t="s">
         <v>239</v>
       </c>
       <c r="F72" s="34" t="s">
+        <v>818</v>
+      </c>
+      <c r="G72" s="34" t="s">
         <v>819</v>
-      </c>
-      <c r="G72" s="34" t="s">
-        <v>820</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I72" s="33" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J72" s="33">
         <v>1</v>
@@ -11968,7 +11973,7 @@
         <v>520</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -12064,10 +12069,10 @@
         <v>5</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F73" s="34" t="s">
         <v>68</v>
@@ -12079,7 +12084,7 @@
         <v>192</v>
       </c>
       <c r="I73" s="33" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="J73" s="33">
         <v>2</v>
@@ -12094,7 +12099,7 @@
         <v>520</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O73" s="35">
         <v>1</v>
@@ -12458,13 +12463,13 @@
         <v>294</v>
       </c>
       <c r="L76" s="36" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M76" s="37" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N76" s="37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O76" s="38"/>
       <c r="P76" s="36"/>
@@ -12680,13 +12685,13 @@
         <v>6</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>243</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>90</v>
@@ -12695,7 +12700,7 @@
         <v>192</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J78" s="20">
         <v>2</v>
@@ -12707,7 +12712,7 @@
         <v>303</v>
       </c>
       <c r="M78" s="19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N78" s="19"/>
       <c r="O78" s="18"/>
@@ -12802,13 +12807,13 @@
         <v>6</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>243</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>84</v>
@@ -12817,7 +12822,7 @@
         <v>192</v>
       </c>
       <c r="I79" s="20" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J79" s="20">
         <v>1</v>
@@ -12829,13 +12834,13 @@
         <v>303</v>
       </c>
       <c r="M79" s="19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N79" s="19"/>
       <c r="O79" s="18"/>
       <c r="P79" s="20"/>
       <c r="Q79" s="19" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="R79" s="13"/>
       <c r="S79" s="2">
@@ -12956,7 +12961,7 @@
         <v>515</v>
       </c>
       <c r="N80" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O80" s="35">
         <v>1</v>
@@ -13052,22 +13057,22 @@
         <v>6</v>
       </c>
       <c r="D81" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="E81" s="34" t="s">
         <v>578</v>
       </c>
-      <c r="E81" s="34" t="s">
+      <c r="F81" s="34" t="s">
         <v>579</v>
       </c>
-      <c r="F81" s="34" t="s">
-        <v>580</v>
-      </c>
       <c r="G81" s="34" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H81" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I81" s="33" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J81" s="33">
         <v>1</v>
@@ -13082,7 +13087,7 @@
         <v>105</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13210,7 +13215,7 @@
         <v>250</v>
       </c>
       <c r="N82" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O82" s="35">
         <v>1</v>
@@ -13306,13 +13311,13 @@
         <v>6</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E83" s="34" t="s">
         <v>526</v>
       </c>
       <c r="F83" s="34" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G83" s="34" t="s">
         <v>502</v>
@@ -13321,7 +13326,7 @@
         <v>192</v>
       </c>
       <c r="I83" s="33" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J83" s="33">
         <v>2</v>
@@ -13336,7 +13341,7 @@
         <v>105</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13434,13 +13439,13 @@
         <v>6</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G84" s="34" t="s">
         <v>146</v>
@@ -13449,7 +13454,7 @@
         <v>192</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J84" s="33">
         <v>99</v>
@@ -13461,10 +13466,10 @@
         <v>514</v>
       </c>
       <c r="M84" s="34" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N84" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O84" s="35">
         <v>1</v>
@@ -13560,13 +13565,13 @@
         <v>6</v>
       </c>
       <c r="D85" s="34" t="s">
+        <v>895</v>
+      </c>
+      <c r="E85" s="34" t="s">
         <v>896</v>
       </c>
-      <c r="E85" s="34" t="s">
+      <c r="F85" s="34" t="s">
         <v>897</v>
-      </c>
-      <c r="F85" s="34" t="s">
-        <v>898</v>
       </c>
       <c r="G85" s="34" t="s">
         <v>90</v>
@@ -13575,7 +13580,7 @@
         <v>192</v>
       </c>
       <c r="I85" s="33" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J85" s="33">
         <v>2</v>
@@ -13587,10 +13592,10 @@
         <v>45</v>
       </c>
       <c r="M85" s="34" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N85" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O85" s="35">
         <v>1</v>
@@ -13683,7 +13688,7 @@
         <v>6</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E86" s="37" t="s">
         <v>488</v>
@@ -13713,7 +13718,7 @@
         <v>523</v>
       </c>
       <c r="N86" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O86" s="38"/>
       <c r="P86" s="36"/>
@@ -13804,22 +13809,22 @@
         <v>6</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E87" s="37" t="s">
         <v>488</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H87" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I87" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J87" s="36">
         <v>1</v>
@@ -13834,7 +13839,7 @@
         <v>523</v>
       </c>
       <c r="N87" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O87" s="38"/>
       <c r="P87" s="36"/>
@@ -13958,7 +13963,7 @@
         <v>250</v>
       </c>
       <c r="N88" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -14054,20 +14059,20 @@
         <v>6</v>
       </c>
       <c r="D89" s="34" t="s">
+        <v>872</v>
+      </c>
+      <c r="E89" s="34" t="s">
         <v>873</v>
       </c>
-      <c r="E89" s="34" t="s">
+      <c r="F89" s="34" t="s">
         <v>874</v>
-      </c>
-      <c r="F89" s="34" t="s">
-        <v>875</v>
       </c>
       <c r="G89" s="34"/>
       <c r="H89" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I89" s="33" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J89" s="33"/>
       <c r="K89" s="33" t="s">
@@ -14076,7 +14081,7 @@
       <c r="L89" s="33"/>
       <c r="M89" s="34"/>
       <c r="N89" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O89" s="35">
         <v>1</v>
@@ -14189,7 +14194,7 @@
         <v>192</v>
       </c>
       <c r="I90" s="36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="J90" s="36">
         <v>5</v>
@@ -14204,7 +14209,7 @@
         <v>197</v>
       </c>
       <c r="N90" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O90" s="38"/>
       <c r="P90" s="36"/>
@@ -14298,7 +14303,7 @@
         <v>6</v>
       </c>
       <c r="D91" s="34" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E91" s="34" t="s">
         <v>526</v>
@@ -14325,10 +14330,10 @@
         <v>307</v>
       </c>
       <c r="M91" s="34" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="N91" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O91" s="35">
         <v>1</v>
@@ -14552,7 +14557,7 @@
         <v>40</v>
       </c>
       <c r="F93" s="34" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G93" s="34" t="s">
         <v>105</v>
@@ -14573,10 +14578,10 @@
         <v>307</v>
       </c>
       <c r="M93" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="N93" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O93" s="35">
         <v>1</v>
@@ -14702,7 +14707,7 @@
         <v>311</v>
       </c>
       <c r="N94" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O94" s="35">
         <v>1</v>
@@ -14830,7 +14835,7 @@
         <v>311</v>
       </c>
       <c r="N95" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O95" s="35">
         <v>1</v>
@@ -14958,7 +14963,7 @@
         <v>311</v>
       </c>
       <c r="N96" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O96" s="35">
         <v>1</v>
@@ -14967,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="34" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="R96" s="13"/>
       <c r="S96" s="2">
@@ -15064,7 +15069,7 @@
         <v>40</v>
       </c>
       <c r="F97" s="34" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G97" s="34" t="s">
         <v>139</v>
@@ -15073,7 +15078,7 @@
         <v>192</v>
       </c>
       <c r="I97" s="33" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J97" s="33">
         <v>99</v>
@@ -15088,7 +15093,7 @@
         <v>270</v>
       </c>
       <c r="N97" s="34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O97" s="35">
         <v>1</v>
@@ -15214,7 +15219,7 @@
         <v>270</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15310,13 +15315,13 @@
         <v>7</v>
       </c>
       <c r="D99" s="34" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E99" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F99" s="34" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G99" s="34" t="s">
         <v>72</v>
@@ -15325,7 +15330,7 @@
         <v>192</v>
       </c>
       <c r="I99" s="33" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J99" s="33">
         <v>3</v>
@@ -15337,10 +15342,10 @@
         <v>28</v>
       </c>
       <c r="M99" s="34" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15439,7 +15444,7 @@
         <v>337</v>
       </c>
       <c r="E100" s="34" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F100" s="34" t="s">
         <v>359</v>
@@ -15466,7 +15471,7 @@
         <v>197</v>
       </c>
       <c r="N100" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O100" s="35">
         <v>1</v>
@@ -15562,22 +15567,22 @@
         <v>7</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H101" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I101" s="20" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J101" s="20">
         <v>99</v>
@@ -15589,7 +15594,7 @@
         <v>308</v>
       </c>
       <c r="M101" s="19" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="N101" s="19"/>
       <c r="O101" s="18"/>
@@ -15684,13 +15689,13 @@
         <v>7</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E102" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G102" s="37" t="s">
         <v>72</v>
@@ -15699,7 +15704,7 @@
         <v>192</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="J102" s="36">
         <v>3</v>
@@ -15711,10 +15716,10 @@
         <v>30</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N102" s="37" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="36"/>
@@ -15838,7 +15843,7 @@
         <v>570</v>
       </c>
       <c r="N103" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O103" s="38"/>
       <c r="P103" s="36"/>
@@ -15959,7 +15964,7 @@
         <v>251</v>
       </c>
       <c r="N104" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O104" s="38"/>
       <c r="P104" s="36"/>
@@ -16053,13 +16058,13 @@
         <v>1</v>
       </c>
       <c r="D105" s="34" t="s">
+        <v>694</v>
+      </c>
+      <c r="E105" s="34" t="s">
         <v>695</v>
       </c>
-      <c r="E105" s="34" t="s">
+      <c r="F105" s="34" t="s">
         <v>696</v>
-      </c>
-      <c r="F105" s="34" t="s">
-        <v>697</v>
       </c>
       <c r="G105" s="34" t="s">
         <v>90</v>
@@ -16068,7 +16073,7 @@
         <v>192</v>
       </c>
       <c r="I105" s="33" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J105" s="33">
         <v>2</v>
@@ -16080,10 +16085,10 @@
         <v>7</v>
       </c>
       <c r="M105" s="34" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16181,13 +16186,13 @@
         <v>1</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E106" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G106" s="34" t="s">
         <v>90</v>
@@ -16196,7 +16201,7 @@
         <v>192</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J106" s="33">
         <v>2</v>
@@ -16208,10 +16213,10 @@
         <v>5</v>
       </c>
       <c r="M106" s="34" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N106" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O106" s="35">
         <v>1</v>
@@ -16220,7 +16225,7 @@
         <v>1</v>
       </c>
       <c r="Q106" s="34" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="R106" s="13"/>
       <c r="S106" s="2">
@@ -16311,13 +16316,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E107" s="34" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>84</v>
@@ -16341,7 +16346,7 @@
         <v>195</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O107" s="35">
         <v>1</v>
@@ -16350,7 +16355,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="R107" s="13"/>
       <c r="S107" s="2">
@@ -16441,13 +16446,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G108" s="34" t="s">
         <v>146</v>
@@ -16456,7 +16461,7 @@
         <v>192</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J108" s="33">
         <v>99</v>
@@ -16471,7 +16476,7 @@
         <v>195</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O108" s="35">
         <v>1</v>
@@ -16569,13 +16574,13 @@
         <v>1</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E109" s="34" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F109" s="34" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G109" s="34" t="s">
         <v>105</v>
@@ -16584,7 +16589,7 @@
         <v>192</v>
       </c>
       <c r="I109" s="33" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J109" s="33">
         <v>99</v>
@@ -16596,10 +16601,10 @@
         <v>9</v>
       </c>
       <c r="M109" s="34" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N109" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O109" s="35">
         <v>1</v>
@@ -17066,7 +17071,7 @@
         <v>168</v>
       </c>
       <c r="E113" s="34" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F113" s="34" t="s">
         <v>167</v>
@@ -17093,7 +17098,7 @@
         <v>195</v>
       </c>
       <c r="N113" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O113" s="35">
         <v>1</v>
@@ -17219,7 +17224,7 @@
         <v>195</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O114" s="35">
         <v>1</v>
@@ -17323,16 +17328,16 @@
         <v>61</v>
       </c>
       <c r="F115" s="34" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G115" s="34" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H115" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I115" s="33" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J115" s="33">
         <v>99</v>
@@ -17347,7 +17352,7 @@
         <v>195</v>
       </c>
       <c r="N115" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O115" s="35">
         <v>1</v>
@@ -17597,7 +17602,7 @@
         <v>195</v>
       </c>
       <c r="N117" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O117" s="35">
         <v>1</v>
@@ -17695,13 +17700,13 @@
         <v>1</v>
       </c>
       <c r="D118" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="E118" s="34" t="s">
+        <v>695</v>
+      </c>
+      <c r="F118" s="34" t="s">
         <v>575</v>
-      </c>
-      <c r="E118" s="34" t="s">
-        <v>696</v>
-      </c>
-      <c r="F118" s="34" t="s">
-        <v>576</v>
       </c>
       <c r="G118" s="34" t="s">
         <v>90</v>
@@ -17710,7 +17715,7 @@
         <v>192</v>
       </c>
       <c r="I118" s="33" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J118" s="33">
         <v>2</v>
@@ -17722,10 +17727,10 @@
         <v>9</v>
       </c>
       <c r="M118" s="34" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N118" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O118" s="35">
         <v>1</v>
@@ -17972,10 +17977,10 @@
         <v>305</v>
       </c>
       <c r="M120" s="34" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N120" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O120" s="35">
         <v>1</v>
@@ -18071,22 +18076,22 @@
         <v>2</v>
       </c>
       <c r="D121" s="34" t="s">
+        <v>830</v>
+      </c>
+      <c r="E121" s="34" t="s">
+        <v>762</v>
+      </c>
+      <c r="F121" s="34" t="s">
         <v>831</v>
       </c>
-      <c r="E121" s="34" t="s">
-        <v>763</v>
-      </c>
-      <c r="F121" s="34" t="s">
+      <c r="G121" s="34" t="s">
         <v>832</v>
-      </c>
-      <c r="G121" s="34" t="s">
-        <v>833</v>
       </c>
       <c r="H121" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I121" s="33" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="J121" s="33"/>
       <c r="K121" s="33" t="s">
@@ -18096,10 +18101,10 @@
         <v>30</v>
       </c>
       <c r="M121" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N121" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O121" s="35">
         <v>1</v>
@@ -18222,10 +18227,10 @@
         <v>312</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18323,13 +18328,13 @@
         <v>2</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E123" s="34" t="s">
         <v>243</v>
       </c>
       <c r="F123" s="34" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G123" s="34" t="s">
         <v>162</v>
@@ -18338,7 +18343,7 @@
         <v>192</v>
       </c>
       <c r="I123" s="33" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J123" s="33">
         <v>1</v>
@@ -18347,13 +18352,13 @@
         <v>295</v>
       </c>
       <c r="L123" s="33" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M123" s="34" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="N123" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O123" s="35">
         <v>1</v>
@@ -18699,16 +18704,16 @@
         <v>385</v>
       </c>
       <c r="F126" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="G126" s="19" t="s">
         <v>652</v>
-      </c>
-      <c r="G126" s="19" t="s">
-        <v>653</v>
       </c>
       <c r="H126" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J126" s="20">
         <v>99</v>
@@ -18720,7 +18725,7 @@
         <v>308</v>
       </c>
       <c r="M126" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N126" s="19"/>
       <c r="O126" s="18"/>
@@ -18821,7 +18826,7 @@
         <v>385</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G127" s="19" t="s">
         <v>206</v>
@@ -18842,7 +18847,7 @@
         <v>308</v>
       </c>
       <c r="M127" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N127" s="19"/>
       <c r="O127" s="18"/>
@@ -19303,18 +19308,18 @@
         <v>2</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E131" s="19"/>
       <c r="F131" s="19" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G131" s="19"/>
       <c r="H131" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J131" s="20"/>
       <c r="K131" s="20" t="s">
@@ -19324,7 +19329,7 @@
         <v>22</v>
       </c>
       <c r="M131" s="39" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="N131" s="39"/>
       <c r="O131" s="2"/>
@@ -19446,10 +19451,10 @@
         <v>309</v>
       </c>
       <c r="M132" s="34" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N132" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O132" s="35">
         <v>1</v>
@@ -19562,7 +19567,7 @@
         <v>192</v>
       </c>
       <c r="I133" s="36" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J133" s="36">
         <v>5</v>
@@ -19577,7 +19582,7 @@
         <v>463</v>
       </c>
       <c r="N133" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="36"/>
@@ -19793,13 +19798,13 @@
         <v>2</v>
       </c>
       <c r="D135" s="37" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E135" s="37" t="s">
         <v>281</v>
       </c>
       <c r="F135" s="37" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G135" s="37" t="s">
         <v>147</v>
@@ -19808,7 +19813,7 @@
         <v>192</v>
       </c>
       <c r="I135" s="36" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="J135" s="36">
         <v>99</v>
@@ -19820,10 +19825,10 @@
         <v>512</v>
       </c>
       <c r="M135" s="37" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N135" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O135" s="38"/>
       <c r="P135" s="36"/>
@@ -19941,13 +19946,13 @@
         <v>295</v>
       </c>
       <c r="L136" s="33" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M136" s="34" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="N136" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O136" s="35">
         <v>1</v>
@@ -20169,13 +20174,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G138" s="34" t="s">
         <v>503</v>
@@ -20184,7 +20189,7 @@
         <v>192</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J138" s="33">
         <v>1</v>
@@ -20199,7 +20204,7 @@
         <v>105</v>
       </c>
       <c r="N138" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O138" s="35">
         <v>1</v>
@@ -20327,7 +20332,7 @@
         <v>105</v>
       </c>
       <c r="N139" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O139" s="35">
         <v>1</v>
@@ -20425,13 +20430,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="34" t="s">
+        <v>888</v>
+      </c>
+      <c r="E140" s="34" t="s">
+        <v>887</v>
+      </c>
+      <c r="F140" s="34" t="s">
         <v>889</v>
-      </c>
-      <c r="E140" s="34" t="s">
-        <v>888</v>
-      </c>
-      <c r="F140" s="34" t="s">
-        <v>890</v>
       </c>
       <c r="G140" s="34" t="s">
         <v>139</v>
@@ -20440,7 +20445,7 @@
         <v>192</v>
       </c>
       <c r="I140" s="33" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J140" s="33">
         <v>1</v>
@@ -20451,7 +20456,7 @@
       <c r="L140" s="33"/>
       <c r="M140" s="34"/>
       <c r="N140" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O140" s="35">
         <v>1</v>
@@ -20552,13 +20557,13 @@
         <v>572</v>
       </c>
       <c r="E141" s="34" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F141" s="34" t="s">
-        <v>574</v>
+        <v>922</v>
       </c>
       <c r="G141" s="34" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="H141" s="34" t="s">
         <v>192</v>
@@ -20579,7 +20584,7 @@
         <v>105</v>
       </c>
       <c r="N141" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O141" s="35">
         <v>1</v>
@@ -20587,7 +20592,9 @@
       <c r="P141" s="33">
         <v>1</v>
       </c>
-      <c r="Q141" s="34"/>
+      <c r="Q141" s="34" t="s">
+        <v>923</v>
+      </c>
       <c r="R141" s="13"/>
       <c r="S141" s="2">
         <f t="shared" si="35"/>
@@ -20707,7 +20714,7 @@
         <v>316</v>
       </c>
       <c r="N142" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O142" s="35">
         <v>1</v>
@@ -21057,7 +21064,7 @@
         <v>37</v>
       </c>
       <c r="F145" s="37" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G145" s="37" t="s">
         <v>72</v>
@@ -21078,10 +21085,10 @@
         <v>307</v>
       </c>
       <c r="M145" s="37" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N145" s="37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O145" s="38"/>
       <c r="P145" s="36"/>
@@ -21175,13 +21182,13 @@
         <v>4</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E146" s="19" t="s">
         <v>418</v>
       </c>
       <c r="F146" s="19" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G146" s="19" t="s">
         <v>502</v>
@@ -21202,7 +21209,7 @@
         <v>309</v>
       </c>
       <c r="M146" s="19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N146" s="19"/>
       <c r="O146" s="18"/>
@@ -21419,13 +21426,13 @@
         <v>4</v>
       </c>
       <c r="D148" s="37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E148" s="37" t="s">
         <v>418</v>
       </c>
       <c r="F148" s="37" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G148" s="37" t="s">
         <v>112</v>
@@ -21434,7 +21441,7 @@
         <v>192</v>
       </c>
       <c r="I148" s="36" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J148" s="36">
         <v>3</v>
@@ -21446,10 +21453,10 @@
         <v>307</v>
       </c>
       <c r="M148" s="37" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="N148" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O148" s="38"/>
       <c r="P148" s="36"/>
@@ -21573,7 +21580,7 @@
         <v>521</v>
       </c>
       <c r="N149" s="37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O149" s="38"/>
       <c r="P149" s="36"/>
@@ -21673,7 +21680,7 @@
         <v>30</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G150" s="19" t="s">
         <v>103</v>
@@ -21694,7 +21701,7 @@
         <v>312</v>
       </c>
       <c r="M150" s="19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N150" s="19"/>
       <c r="O150" s="18"/>
@@ -21816,7 +21823,7 @@
         <v>312</v>
       </c>
       <c r="M151" s="19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N151" s="19"/>
       <c r="O151" s="18"/>
@@ -22057,10 +22064,10 @@
         <v>309</v>
       </c>
       <c r="M153" s="41" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N153" s="41" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O153" s="42"/>
       <c r="P153" s="40"/>
@@ -22154,20 +22161,20 @@
         <v>4</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E154" s="19" t="s">
         <v>414</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G154" s="19"/>
       <c r="H154" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I154" s="20" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J154" s="20"/>
       <c r="K154" s="20" t="s">
@@ -22177,7 +22184,7 @@
         <v>20</v>
       </c>
       <c r="M154" s="19" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N154" s="19"/>
       <c r="O154" s="18"/>
@@ -22299,7 +22306,7 @@
         <v>30</v>
       </c>
       <c r="M155" s="19" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="N155" s="19"/>
       <c r="O155" s="18"/>
@@ -22394,13 +22401,13 @@
         <v>5</v>
       </c>
       <c r="D156" s="34" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E156" s="34" t="s">
         <v>539</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G156" s="34" t="s">
         <v>84</v>
@@ -22409,7 +22416,7 @@
         <v>192</v>
       </c>
       <c r="I156" s="33" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="J156" s="33"/>
       <c r="K156" s="33" t="s">
@@ -22419,10 +22426,10 @@
         <v>40</v>
       </c>
       <c r="M156" s="34" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22518,22 +22525,22 @@
         <v>5</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E157" s="34" t="s">
         <v>484</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G157" s="34" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H157" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I157" s="33" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J157" s="33">
         <v>2</v>
@@ -22545,10 +22552,10 @@
         <v>307</v>
       </c>
       <c r="M157" s="34" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="N157" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O157" s="35">
         <v>1</v>
@@ -22766,13 +22773,13 @@
         <v>5</v>
       </c>
       <c r="D159" s="37" t="s">
+        <v>849</v>
+      </c>
+      <c r="E159" s="37" t="s">
         <v>850</v>
       </c>
-      <c r="E159" s="37" t="s">
+      <c r="F159" s="37" t="s">
         <v>851</v>
-      </c>
-      <c r="F159" s="37" t="s">
-        <v>852</v>
       </c>
       <c r="G159" s="37" t="s">
         <v>131</v>
@@ -22781,7 +22788,7 @@
         <v>192</v>
       </c>
       <c r="I159" s="36" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J159" s="36">
         <v>99</v>
@@ -22793,10 +22800,10 @@
         <v>40</v>
       </c>
       <c r="M159" s="37" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N159" s="37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O159" s="38"/>
       <c r="P159" s="36"/>
@@ -22890,20 +22897,20 @@
         <v>5</v>
       </c>
       <c r="D160" s="34" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G160" s="34"/>
       <c r="H160" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I160" s="33" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="J160" s="33"/>
       <c r="K160" s="33" t="s">
@@ -22913,10 +22920,10 @@
         <v>35</v>
       </c>
       <c r="M160" s="34" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -23042,7 +23049,7 @@
         <v>468</v>
       </c>
       <c r="N161" s="34" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="O161" s="35">
         <v>1</v>
@@ -23135,20 +23142,20 @@
         <v>5</v>
       </c>
       <c r="D162" s="37" t="s">
+        <v>876</v>
+      </c>
+      <c r="E162" s="37" t="s">
         <v>877</v>
       </c>
-      <c r="E162" s="37" t="s">
+      <c r="F162" s="37" t="s">
         <v>878</v>
-      </c>
-      <c r="F162" s="37" t="s">
-        <v>879</v>
       </c>
       <c r="G162" s="37"/>
       <c r="H162" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I162" s="36" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J162" s="36"/>
       <c r="K162" s="36" t="s">
@@ -23158,10 +23165,10 @@
         <v>35</v>
       </c>
       <c r="M162" s="37" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N162" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O162" s="38"/>
       <c r="P162" s="36"/>
@@ -23648,10 +23655,10 @@
         <v>307</v>
       </c>
       <c r="M166" s="34" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="N166" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O166" s="35">
         <v>1</v>
@@ -23999,7 +24006,7 @@
         <v>89</v>
       </c>
       <c r="F169" s="19" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G169" s="19" t="s">
         <v>102</v>
@@ -24145,7 +24152,7 @@
         <v>198</v>
       </c>
       <c r="N170" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O170" s="35">
         <v>1</v>
@@ -24249,7 +24256,7 @@
         <v>38</v>
       </c>
       <c r="F171" s="34" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G171" s="34" t="s">
         <v>84</v>
@@ -24273,7 +24280,7 @@
         <v>198</v>
       </c>
       <c r="N171" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O171" s="35">
         <v>1</v>
@@ -24401,7 +24408,7 @@
         <v>198</v>
       </c>
       <c r="N172" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O172" s="35">
         <v>1</v>
@@ -24505,16 +24512,16 @@
         <v>38</v>
       </c>
       <c r="F173" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G173" s="34" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H173" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I173" s="33" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="J173" s="33">
         <v>1</v>
@@ -24529,7 +24536,7 @@
         <v>198</v>
       </c>
       <c r="N173" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O173" s="35">
         <v>1</v>
@@ -24657,7 +24664,7 @@
         <v>198</v>
       </c>
       <c r="N174" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O174" s="35">
         <v>1</v>
@@ -24785,7 +24792,7 @@
         <v>198</v>
       </c>
       <c r="N175" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O175" s="38"/>
       <c r="P175" s="36"/>
@@ -24885,7 +24892,7 @@
         <v>38</v>
       </c>
       <c r="F176" s="37" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G176" s="37" t="s">
         <v>147</v>
@@ -24894,7 +24901,7 @@
         <v>192</v>
       </c>
       <c r="I176" s="36" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J176" s="36">
         <v>99</v>
@@ -24909,7 +24916,7 @@
         <v>198</v>
       </c>
       <c r="N176" s="37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O176" s="38"/>
       <c r="P176" s="36"/>
@@ -25643,7 +25650,7 @@
         <v>198</v>
       </c>
       <c r="N182" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O182" s="35">
         <v>1</v>
@@ -25771,7 +25778,7 @@
         <v>198</v>
       </c>
       <c r="N183" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O183" s="35">
         <v>1</v>
@@ -25899,7 +25906,7 @@
         <v>198</v>
       </c>
       <c r="N184" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O184" s="35">
         <v>1</v>
@@ -26024,7 +26031,7 @@
         <v>198</v>
       </c>
       <c r="N185" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O185" s="38"/>
       <c r="P185" s="36"/>
@@ -26392,7 +26399,7 @@
         <v>105</v>
       </c>
       <c r="N188" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O188" s="35">
         <v>1</v>
@@ -27106,7 +27113,7 @@
         <v>38</v>
       </c>
       <c r="F194" s="34" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G194" s="34" t="s">
         <v>72</v>
@@ -27130,7 +27137,7 @@
         <v>198</v>
       </c>
       <c r="N194" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O194" s="35">
         <v>1</v>
@@ -27258,7 +27265,7 @@
         <v>198</v>
       </c>
       <c r="N195" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O195" s="35">
         <v>1</v>
@@ -27386,7 +27393,7 @@
         <v>198</v>
       </c>
       <c r="N196" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O196" s="35">
         <v>1</v>
@@ -27514,7 +27521,7 @@
         <v>387</v>
       </c>
       <c r="N197" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O197" s="35">
         <v>1</v>
@@ -27618,7 +27625,7 @@
         <v>55</v>
       </c>
       <c r="F198" s="34" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G198" s="34" t="s">
         <v>72</v>
@@ -27627,7 +27634,7 @@
         <v>192</v>
       </c>
       <c r="I198" s="33" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J198" s="33">
         <v>4</v>
@@ -27642,7 +27649,7 @@
         <v>387</v>
       </c>
       <c r="N198" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O198" s="35">
         <v>1</v>
@@ -28106,13 +28113,13 @@
         <v>7</v>
       </c>
       <c r="D202" s="19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E202" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F202" s="19" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G202" s="19" t="s">
         <v>72</v>
@@ -28121,7 +28128,7 @@
         <v>192</v>
       </c>
       <c r="I202" s="20" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="J202" s="20">
         <v>4</v>
@@ -28228,13 +28235,13 @@
         <v>7</v>
       </c>
       <c r="D203" s="19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E203" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F203" s="19" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G203" s="19" t="s">
         <v>102</v>
@@ -28243,7 +28250,7 @@
         <v>192</v>
       </c>
       <c r="I203" s="20" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="J203" s="20">
         <v>99</v>
@@ -28356,7 +28363,7 @@
         <v>38</v>
       </c>
       <c r="F204" s="34" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G204" s="34" t="s">
         <v>84</v>
@@ -28380,7 +28387,7 @@
         <v>198</v>
       </c>
       <c r="N204" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O204" s="35">
         <v>1</v>
@@ -28506,7 +28513,7 @@
         <v>198</v>
       </c>
       <c r="N205" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O205" s="35">
         <v>1</v>
@@ -28739,7 +28746,7 @@
         <v>192</v>
       </c>
       <c r="I207" s="20" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J207" s="20">
         <v>99</v>
@@ -28846,13 +28853,13 @@
         <v>7</v>
       </c>
       <c r="D208" s="34" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E208" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G208" s="34" t="s">
         <v>72</v>
@@ -28861,7 +28868,7 @@
         <v>192</v>
       </c>
       <c r="I208" s="33" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="J208" s="33">
         <v>4</v>
@@ -28876,7 +28883,7 @@
         <v>198</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
@@ -28972,13 +28979,13 @@
         <v>7</v>
       </c>
       <c r="D209" s="34" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E209" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G209" s="34" t="s">
         <v>90</v>
@@ -28987,7 +28994,7 @@
         <v>192</v>
       </c>
       <c r="I209" s="33" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="J209" s="33">
         <v>2</v>
@@ -29002,7 +29009,7 @@
         <v>198</v>
       </c>
       <c r="N209" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="O209" s="35">
         <v>1</v>
@@ -29104,7 +29111,7 @@
         <v>38</v>
       </c>
       <c r="F210" s="34" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G210" s="34" t="s">
         <v>84</v>
@@ -29128,7 +29135,7 @@
         <v>198</v>
       </c>
       <c r="N210" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O210" s="35">
         <v>1</v>
@@ -29256,7 +29263,7 @@
         <v>105</v>
       </c>
       <c r="N211" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O211" s="35">
         <v>1</v>
@@ -29628,7 +29635,7 @@
         <v>105</v>
       </c>
       <c r="N214" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O214" s="35">
         <v>1</v>
@@ -29756,7 +29763,7 @@
         <v>105</v>
       </c>
       <c r="N215" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O215" s="35">
         <v>1</v>
@@ -29884,7 +29891,7 @@
         <v>105</v>
       </c>
       <c r="N216" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O216" s="35">
         <v>1</v>
@@ -29985,7 +29992,7 @@
         <v>55</v>
       </c>
       <c r="F217" s="34" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G217" s="34" t="s">
         <v>147</v>
@@ -29994,7 +30001,7 @@
         <v>192</v>
       </c>
       <c r="I217" s="33" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="J217" s="33">
         <v>99</v>
@@ -30009,7 +30016,7 @@
         <v>105</v>
       </c>
       <c r="N217" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O217" s="35">
         <v>1</v>
@@ -30134,7 +30141,7 @@
         <v>314</v>
       </c>
       <c r="N218" s="37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O218" s="38"/>
       <c r="P218" s="36"/>
@@ -30258,7 +30265,7 @@
         <v>198</v>
       </c>
       <c r="N219" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O219" s="35">
         <v>1</v>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0BDCB4-F262-44F2-B963-A8D794F8C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1759D4-AAF1-4E94-8A6F-C4D324AF305F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="924">
   <si>
     <t>Recensore</t>
   </si>
@@ -3647,47 +3647,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT318"/>
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.140625" style="2"/>
-    <col min="47" max="16384" width="9.140625" style="3"/>
+    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.109375" style="2"/>
+    <col min="47" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3709,7 +3709,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3749,15 +3749,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3769,7 +3769,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3779,15 +3779,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3841,7 +3841,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3899,7 +3899,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>689</v>
       </c>
@@ -4022,7 +4022,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4148,7 +4148,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
         <v>0</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>0</v>
       </c>
@@ -4522,7 +4522,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>0</v>
       </c>
@@ -4644,7 +4644,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5632,7 +5632,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5882,50 +5882,54 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
-        <v>0</v>
-      </c>
-      <c r="B23" s="20">
-        <v>1</v>
-      </c>
-      <c r="C23" s="20">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="33">
+        <v>0</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1</v>
+      </c>
+      <c r="C23" s="33">
         <v>2</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="33">
         <v>99</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="N23" s="19"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="19"/>
+      <c r="N23" s="34" t="s">
+        <v>894</v>
+      </c>
+      <c r="O23" s="35">
+        <v>1</v>
+      </c>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="34"/>
       <c r="R23" s="13"/>
       <c r="S23" s="2">
         <f t="shared" si="7"/>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="AE23" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" s="2">
         <f t="shared" si="3"/>
@@ -5982,7 +5986,7 @@
       </c>
       <c r="AG23" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" s="2">
         <f t="shared" si="5"/>
@@ -6004,7 +6008,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>0</v>
       </c>
@@ -6128,7 +6132,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>0</v>
       </c>
@@ -6252,7 +6256,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>0</v>
       </c>
@@ -6373,7 +6377,7 @@
       <c r="AS26" s="3"/>
       <c r="AT26" s="3"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30">
         <v>0</v>
       </c>
@@ -6497,7 +6501,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6619,7 +6623,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6745,7 +6749,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6867,7 +6871,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -6993,7 +6997,7 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>0</v>
       </c>
@@ -7117,7 +7121,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7237,7 +7241,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7357,7 +7361,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7479,7 +7483,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>0</v>
       </c>
@@ -7603,7 +7607,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>0</v>
       </c>
@@ -7731,7 +7735,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>0</v>
       </c>
@@ -7855,7 +7859,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7977,7 +7981,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>0</v>
       </c>
@@ -8101,7 +8105,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>0</v>
       </c>
@@ -8227,7 +8231,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20">
         <v>0</v>
       </c>
@@ -8349,7 +8353,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8471,7 +8475,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8593,7 +8597,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8715,7 +8719,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8837,7 +8841,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>0</v>
       </c>
@@ -8963,7 +8967,7 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>0</v>
       </c>
@@ -9087,7 +9091,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9213,7 +9217,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9339,7 +9343,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="36">
         <v>0</v>
       </c>
@@ -9460,7 +9464,7 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20">
         <v>0</v>
       </c>
@@ -9582,7 +9586,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="36">
         <v>0</v>
       </c>
@@ -9706,7 +9710,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9832,7 +9836,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
         <v>0</v>
       </c>
@@ -9956,7 +9960,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="33">
         <v>0</v>
       </c>
@@ -10082,7 +10086,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20">
         <v>0</v>
       </c>
@@ -10204,7 +10208,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33">
         <v>0</v>
       </c>
@@ -10328,7 +10332,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10456,7 +10460,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20">
         <v>0</v>
       </c>
@@ -10578,7 +10582,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
         <v>0</v>
       </c>
@@ -10702,7 +10706,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20">
         <v>0</v>
       </c>
@@ -10824,7 +10828,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10946,7 +10950,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11068,7 +11072,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20">
         <v>1</v>
       </c>
@@ -11190,7 +11194,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="36">
         <v>0</v>
       </c>
@@ -11314,7 +11318,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="36">
         <v>0</v>
       </c>
@@ -11438,7 +11442,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11562,7 +11566,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20">
         <v>0</v>
       </c>
@@ -11684,7 +11688,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
         <v>0</v>
       </c>
@@ -11808,7 +11812,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="36">
         <v>0</v>
       </c>
@@ -11932,7 +11936,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
         <v>0</v>
       </c>
@@ -12058,7 +12062,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12184,7 +12188,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>0</v>
       </c>
@@ -12306,7 +12310,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12428,7 +12432,7 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="36">
         <v>0</v>
       </c>
@@ -12552,7 +12556,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20">
         <v>0</v>
       </c>
@@ -12674,7 +12678,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12796,7 +12800,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="20">
         <v>1</v>
       </c>
@@ -12920,7 +12924,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33">
         <v>0</v>
       </c>
@@ -13046,7 +13050,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13174,7 +13178,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13300,7 +13304,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13428,7 +13432,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13554,7 +13558,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13677,7 +13681,7 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="36">
         <v>0</v>
       </c>
@@ -13798,7 +13802,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="36">
         <v>1</v>
       </c>
@@ -13922,7 +13926,7 @@
       <c r="AS87" s="13"/>
       <c r="AT87" s="13"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="33">
         <v>0</v>
       </c>
@@ -14048,7 +14052,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14168,7 +14172,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="36">
         <v>0</v>
       </c>
@@ -14292,7 +14296,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14418,7 +14422,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20">
         <v>0</v>
       </c>
@@ -14540,7 +14544,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="33">
         <v>0</v>
       </c>
@@ -14666,7 +14670,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="33">
         <v>0</v>
       </c>
@@ -14794,7 +14798,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="33">
         <v>1</v>
       </c>
@@ -14922,7 +14926,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15052,7 +15056,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="33">
         <v>0</v>
       </c>
@@ -15178,7 +15182,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33">
         <v>1</v>
       </c>
@@ -15304,7 +15308,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="33">
         <v>0</v>
       </c>
@@ -15430,7 +15434,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15556,7 +15560,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="20">
         <v>0</v>
       </c>
@@ -15678,7 +15682,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="36">
         <v>0</v>
       </c>
@@ -15802,7 +15806,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="36">
         <v>0</v>
       </c>
@@ -15923,7 +15927,7 @@
       <c r="AS103" s="3"/>
       <c r="AT103" s="3"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="36">
         <v>0</v>
       </c>
@@ -16047,7 +16051,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="33">
         <v>0</v>
       </c>
@@ -16175,7 +16179,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16305,7 +16309,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16435,7 +16439,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16563,7 +16567,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16691,7 +16695,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -16813,7 +16817,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="20">
         <v>1</v>
       </c>
@@ -16935,7 +16939,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17057,7 +17061,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="33">
         <v>0</v>
       </c>
@@ -17183,7 +17187,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17311,7 +17315,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="33">
         <v>1</v>
       </c>
@@ -17439,7 +17443,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="20">
         <v>0</v>
       </c>
@@ -17561,7 +17565,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33">
         <v>0</v>
       </c>
@@ -17689,7 +17693,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17817,7 +17821,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="20">
         <v>0</v>
       </c>
@@ -17939,7 +17943,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="33">
         <v>0</v>
       </c>
@@ -18065,7 +18069,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18189,7 +18193,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18317,7 +18321,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18443,7 +18447,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="20">
         <v>0</v>
       </c>
@@ -18565,7 +18569,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18687,7 +18691,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18809,7 +18813,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="20">
         <v>1</v>
       </c>
@@ -18931,7 +18935,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="20">
         <v>0</v>
       </c>
@@ -19053,7 +19057,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19175,7 +19179,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="20">
         <v>1</v>
       </c>
@@ -19297,7 +19301,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="20">
         <v>0</v>
       </c>
@@ -19413,7 +19417,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19541,7 +19545,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="36">
         <v>0</v>
       </c>
@@ -19665,7 +19669,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="20">
         <v>0</v>
       </c>
@@ -19787,7 +19791,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="36">
         <v>0</v>
       </c>
@@ -19911,7 +19915,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="33">
         <v>0</v>
       </c>
@@ -20039,7 +20043,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="30">
         <v>0</v>
       </c>
@@ -20163,7 +20167,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20291,7 +20295,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20419,7 +20423,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20543,7 +20547,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20673,7 +20677,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20801,7 +20805,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="30">
         <v>0</v>
       </c>
@@ -20925,7 +20929,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20">
         <v>0</v>
       </c>
@@ -21047,7 +21051,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="36">
         <v>0</v>
       </c>
@@ -21171,7 +21175,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="20">
         <v>0</v>
       </c>
@@ -21293,7 +21297,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="20">
         <v>0</v>
       </c>
@@ -21415,7 +21419,7 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="36">
         <v>0</v>
       </c>
@@ -21539,7 +21543,7 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="36">
         <v>0</v>
       </c>
@@ -21663,7 +21667,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="20">
         <v>0</v>
       </c>
@@ -21785,7 +21789,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="20">
         <v>1</v>
       </c>
@@ -21907,7 +21911,7 @@
       <c r="AS151" s="13"/>
       <c r="AT151" s="13"/>
     </row>
-    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="20">
         <v>0</v>
       </c>
@@ -22026,7 +22030,7 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="40">
         <v>0</v>
       </c>
@@ -22150,7 +22154,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22268,7 +22272,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="20">
         <v>0</v>
       </c>
@@ -22390,7 +22394,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22514,7 +22518,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="33">
         <v>0</v>
       </c>
@@ -22640,7 +22644,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="20">
         <v>0</v>
       </c>
@@ -22762,7 +22766,7 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="36">
         <v>0</v>
       </c>
@@ -22886,7 +22890,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23008,7 +23012,7 @@
       <c r="AS160" s="13"/>
       <c r="AT160" s="13"/>
     </row>
-    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="33">
         <v>0</v>
       </c>
@@ -23131,7 +23135,7 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="36">
         <v>0</v>
       </c>
@@ -23251,7 +23255,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23373,7 +23377,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23495,7 +23499,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="20">
         <v>0</v>
       </c>
@@ -23617,7 +23621,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="33">
         <v>0</v>
       </c>
@@ -23743,7 +23747,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="20">
         <v>0</v>
       </c>
@@ -23865,7 +23869,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="30">
         <v>0</v>
       </c>
@@ -23989,7 +23993,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="20">
         <v>0</v>
       </c>
@@ -24111,7 +24115,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33">
         <v>0</v>
       </c>
@@ -24239,7 +24243,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24367,7 +24371,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24495,7 +24499,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24623,7 +24627,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="33">
         <v>1</v>
       </c>
@@ -24751,7 +24755,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="36">
         <v>0</v>
       </c>
@@ -24875,7 +24879,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="36">
         <v>1</v>
       </c>
@@ -24999,7 +25003,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25121,7 +25125,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="20">
         <v>0</v>
       </c>
@@ -25243,7 +25247,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="20">
         <v>1</v>
       </c>
@@ -25365,7 +25369,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -25487,7 +25491,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -25609,7 +25613,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25737,7 +25741,7 @@
       <c r="AS182" s="13"/>
       <c r="AT182" s="13"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="33">
         <v>1</v>
       </c>
@@ -25865,7 +25869,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="33">
         <v>0</v>
       </c>
@@ -25990,7 +25994,7 @@
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="36">
         <v>0</v>
       </c>
@@ -26114,7 +26118,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="20">
         <v>0</v>
       </c>
@@ -26236,7 +26240,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26358,7 +26362,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26486,7 +26490,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26608,7 +26612,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="20">
         <v>0</v>
       </c>
@@ -26730,7 +26734,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="20">
         <v>0</v>
       </c>
@@ -26852,7 +26856,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="20">
         <v>1</v>
       </c>
@@ -26974,7 +26978,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="20">
         <v>1</v>
       </c>
@@ -27096,7 +27100,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="33">
         <v>0</v>
       </c>
@@ -27224,7 +27228,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="33">
         <v>1</v>
       </c>
@@ -27352,7 +27356,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27480,7 +27484,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="33">
         <v>0</v>
       </c>
@@ -27608,7 +27612,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="33">
         <v>1</v>
       </c>
@@ -27736,7 +27740,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="20">
         <v>0</v>
       </c>
@@ -27858,7 +27862,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="20">
         <v>1</v>
       </c>
@@ -27980,7 +27984,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="20">
         <v>1</v>
       </c>
@@ -28102,7 +28106,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="20">
         <v>0</v>
       </c>
@@ -28224,7 +28228,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="20">
         <v>1</v>
       </c>
@@ -28346,7 +28350,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28472,7 +28476,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28598,7 +28602,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="20">
         <v>0</v>
       </c>
@@ -28720,7 +28724,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="20">
         <v>1</v>
       </c>
@@ -28842,7 +28846,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -28968,7 +28972,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="33">
         <v>1</v>
       </c>
@@ -29094,7 +29098,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="33">
         <v>0</v>
       </c>
@@ -29222,7 +29226,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="33">
         <v>0</v>
       </c>
@@ -29350,7 +29354,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="20">
         <v>0</v>
       </c>
@@ -29472,7 +29476,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="20">
         <v>0</v>
       </c>
@@ -29594,7 +29598,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29722,7 +29726,7 @@
       <c r="AS214" s="13"/>
       <c r="AT214" s="13"/>
     </row>
-    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29850,7 +29854,7 @@
       <c r="AS215" s="13"/>
       <c r="AT215" s="13"/>
     </row>
-    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="33">
         <v>0</v>
       </c>
@@ -29975,7 +29979,7 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="33">
         <v>1</v>
       </c>
@@ -30100,7 +30104,7 @@
       <c r="AS217" s="3"/>
       <c r="AT217" s="3"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="36">
         <v>0</v>
       </c>
@@ -30224,7 +30228,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="33">
         <v>0</v>
       </c>
@@ -30352,7 +30356,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30400,7 +30404,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30448,7 +30452,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30496,7 +30500,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30544,7 +30548,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30592,7 +30596,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30640,7 +30644,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30688,7 +30692,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30736,7 +30740,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30784,7 +30788,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30832,7 +30836,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30880,7 +30884,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30928,7 +30932,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30976,7 +30980,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -31024,7 +31028,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -31072,7 +31076,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31120,7 +31124,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31168,7 +31172,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31216,7 +31220,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31264,7 +31268,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31312,7 +31316,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31360,7 +31364,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31408,7 +31412,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31456,7 +31460,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31504,7 +31508,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31552,7 +31556,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31600,7 +31604,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31648,7 +31652,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31696,7 +31700,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31744,7 +31748,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31792,7 +31796,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31840,7 +31844,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31888,7 +31892,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31936,7 +31940,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -31984,7 +31988,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -32032,7 +32036,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32080,7 +32084,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32128,7 +32132,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32176,7 +32180,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32224,7 +32228,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32272,7 +32276,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32320,7 +32324,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32368,7 +32372,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32416,7 +32420,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32464,7 +32468,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32512,7 +32516,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32560,7 +32564,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32608,7 +32612,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32656,7 +32660,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32704,7 +32708,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32752,7 +32756,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32800,7 +32804,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32848,7 +32852,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32896,7 +32900,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32944,7 +32948,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -32992,7 +32996,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -33040,7 +33044,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33088,7 +33092,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33136,7 +33140,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33184,7 +33188,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33232,7 +33236,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33280,7 +33284,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33328,7 +33332,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33376,7 +33380,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33424,7 +33428,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33472,7 +33476,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33520,7 +33524,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33568,7 +33572,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33616,7 +33620,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33664,7 +33668,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33712,7 +33716,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33760,7 +33764,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33808,7 +33812,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33856,7 +33860,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33904,7 +33908,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33952,7 +33956,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -34000,7 +34004,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -34048,7 +34052,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34096,7 +34100,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34144,7 +34148,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34192,7 +34196,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34240,7 +34244,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34288,7 +34292,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34336,7 +34340,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34384,7 +34388,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34432,7 +34436,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34480,7 +34484,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34528,7 +34532,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34576,7 +34580,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34624,7 +34628,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34672,7 +34676,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34720,7 +34724,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34768,7 +34772,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34816,7 +34820,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34864,7 +34868,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34912,7 +34916,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34960,7 +34964,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -35008,7 +35012,7 @@
       <c r="AS316" s="13"/>
       <c r="AT316" s="13"/>
     </row>
-    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -35056,7 +35060,7 @@
       <c r="AS317" s="13"/>
       <c r="AT317" s="13"/>
     </row>
-    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1759D4-AAF1-4E94-8A6F-C4D324AF305F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB317BB0-D2FD-47D4-9DAC-A9702F4FE1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3647,47 +3647,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT318"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.109375" style="2"/>
-    <col min="47" max="16384" width="9.109375" style="3"/>
+    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.140625" style="2"/>
+    <col min="47" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3709,7 +3709,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3749,15 +3749,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3769,7 +3769,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3779,15 +3779,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3841,7 +3841,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3899,7 +3899,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>689</v>
       </c>
@@ -4022,7 +4022,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4148,7 +4148,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>0</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>0</v>
       </c>
@@ -4522,7 +4522,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <v>0</v>
       </c>
@@ -4644,7 +4644,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4896,7 +4896,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -5012,7 +5012,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5260,7 +5260,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5632,7 +5632,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>0</v>
       </c>
@@ -6008,7 +6008,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>0</v>
       </c>
@@ -6132,7 +6132,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <v>0</v>
       </c>
@@ -6256,7 +6256,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>0</v>
       </c>
@@ -6377,7 +6377,7 @@
       <c r="AS26" s="3"/>
       <c r="AT26" s="3"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>0</v>
       </c>
@@ -6501,7 +6501,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6623,7 +6623,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6749,7 +6749,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6871,7 +6871,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -6997,52 +6997,54 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="36">
-        <v>0</v>
-      </c>
-      <c r="B32" s="36">
-        <v>1</v>
-      </c>
-      <c r="C32" s="36">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33">
+        <v>0</v>
+      </c>
+      <c r="B32" s="33">
+        <v>1</v>
+      </c>
+      <c r="C32" s="33">
         <v>2</v>
       </c>
-      <c r="D32" s="37" t="s">
+      <c r="D32" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="G32" s="37" t="s">
+      <c r="G32" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="37" t="s">
+      <c r="H32" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="I32" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="33">
         <v>3</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L32" s="36" t="s">
+      <c r="L32" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M32" s="37" t="s">
+      <c r="M32" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="N32" s="37" t="s">
-        <v>859</v>
-      </c>
-      <c r="O32" s="38"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="37"/>
+      <c r="N32" s="34" t="s">
+        <v>867</v>
+      </c>
+      <c r="O32" s="35">
+        <v>1</v>
+      </c>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="34"/>
       <c r="R32" s="13"/>
       <c r="S32" s="2">
         <f t="shared" si="7"/>
@@ -7091,7 +7093,7 @@
       </c>
       <c r="AE32" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" s="2">
         <f t="shared" si="3"/>
@@ -7099,7 +7101,7 @@
       </c>
       <c r="AG32" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" s="2">
         <f t="shared" si="5"/>
@@ -7121,7 +7123,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7241,7 +7243,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7361,7 +7363,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7483,7 +7485,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
         <v>0</v>
       </c>
@@ -7607,7 +7609,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>0</v>
       </c>
@@ -7735,7 +7737,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="36">
         <v>0</v>
       </c>
@@ -7859,7 +7861,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7981,7 +7983,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="36">
         <v>0</v>
       </c>
@@ -8105,7 +8107,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>0</v>
       </c>
@@ -8231,7 +8233,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>0</v>
       </c>
@@ -8353,7 +8355,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8475,7 +8477,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8597,7 +8599,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8719,7 +8721,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8841,7 +8843,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>0</v>
       </c>
@@ -8967,7 +8969,7 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="36">
         <v>0</v>
       </c>
@@ -9091,7 +9093,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9217,7 +9219,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9343,7 +9345,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="36">
         <v>0</v>
       </c>
@@ -9464,7 +9466,7 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>0</v>
       </c>
@@ -9586,7 +9588,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="36">
         <v>0</v>
       </c>
@@ -9710,7 +9712,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9836,7 +9838,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>0</v>
       </c>
@@ -9960,7 +9962,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>0</v>
       </c>
@@ -10086,7 +10088,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20">
         <v>0</v>
       </c>
@@ -10208,7 +10210,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>0</v>
       </c>
@@ -10332,7 +10334,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10460,7 +10462,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>0</v>
       </c>
@@ -10582,7 +10584,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>0</v>
       </c>
@@ -10706,7 +10708,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>0</v>
       </c>
@@ -10828,7 +10830,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10950,7 +10952,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11072,7 +11074,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>1</v>
       </c>
@@ -11194,7 +11196,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="36">
         <v>0</v>
       </c>
@@ -11318,7 +11320,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="36">
         <v>0</v>
       </c>
@@ -11442,7 +11444,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11566,7 +11568,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="20">
         <v>0</v>
       </c>
@@ -11688,7 +11690,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>0</v>
       </c>
@@ -11812,7 +11814,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="36">
         <v>0</v>
       </c>
@@ -11936,7 +11938,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <v>0</v>
       </c>
@@ -12062,7 +12064,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12188,7 +12190,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20">
         <v>0</v>
       </c>
@@ -12310,7 +12312,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12432,7 +12434,7 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="36">
         <v>0</v>
       </c>
@@ -12556,7 +12558,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20">
         <v>0</v>
       </c>
@@ -12678,7 +12680,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12800,7 +12802,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20">
         <v>1</v>
       </c>
@@ -12924,7 +12926,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="33">
         <v>0</v>
       </c>
@@ -13050,7 +13052,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13178,7 +13180,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13304,7 +13306,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13432,7 +13434,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13558,7 +13560,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13681,7 +13683,7 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="36">
         <v>0</v>
       </c>
@@ -13802,7 +13804,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="36">
         <v>1</v>
       </c>
@@ -13926,7 +13928,7 @@
       <c r="AS87" s="13"/>
       <c r="AT87" s="13"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
         <v>0</v>
       </c>
@@ -14052,7 +14054,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14172,7 +14174,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="36">
         <v>0</v>
       </c>
@@ -14296,7 +14298,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14422,7 +14424,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20">
         <v>0</v>
       </c>
@@ -14544,7 +14546,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33">
         <v>0</v>
       </c>
@@ -14670,7 +14672,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="33">
         <v>0</v>
       </c>
@@ -14798,7 +14800,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33">
         <v>1</v>
       </c>
@@ -14926,7 +14928,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15056,7 +15058,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33">
         <v>0</v>
       </c>
@@ -15182,7 +15184,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33">
         <v>1</v>
       </c>
@@ -15308,7 +15310,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33">
         <v>0</v>
       </c>
@@ -15434,7 +15436,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15560,7 +15562,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20">
         <v>0</v>
       </c>
@@ -15682,7 +15684,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="36">
         <v>0</v>
       </c>
@@ -15806,7 +15808,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="36">
         <v>0</v>
       </c>
@@ -15927,7 +15929,7 @@
       <c r="AS103" s="3"/>
       <c r="AT103" s="3"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="36">
         <v>0</v>
       </c>
@@ -16051,7 +16053,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33">
         <v>0</v>
       </c>
@@ -16179,7 +16181,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16309,7 +16311,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16439,7 +16441,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16567,7 +16569,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16695,7 +16697,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -16817,7 +16819,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20">
         <v>1</v>
       </c>
@@ -16939,7 +16941,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17061,7 +17063,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33">
         <v>0</v>
       </c>
@@ -17187,7 +17189,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17315,7 +17317,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
         <v>1</v>
       </c>
@@ -17443,7 +17445,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20">
         <v>0</v>
       </c>
@@ -17565,7 +17567,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33">
         <v>0</v>
       </c>
@@ -17693,7 +17695,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17821,7 +17823,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20">
         <v>0</v>
       </c>
@@ -17943,7 +17945,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33">
         <v>0</v>
       </c>
@@ -18069,7 +18071,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18193,7 +18195,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18321,7 +18323,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18447,7 +18449,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="20">
         <v>0</v>
       </c>
@@ -18569,7 +18571,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18691,7 +18693,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18813,7 +18815,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20">
         <v>1</v>
       </c>
@@ -18935,7 +18937,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20">
         <v>0</v>
       </c>
@@ -19057,7 +19059,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19179,7 +19181,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>1</v>
       </c>
@@ -19301,7 +19303,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20">
         <v>0</v>
       </c>
@@ -19417,7 +19419,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19545,7 +19547,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="36">
         <v>0</v>
       </c>
@@ -19669,7 +19671,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="20">
         <v>0</v>
       </c>
@@ -19791,7 +19793,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="36">
         <v>0</v>
       </c>
@@ -19915,7 +19917,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="33">
         <v>0</v>
       </c>
@@ -20043,7 +20045,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="30">
         <v>0</v>
       </c>
@@ -20167,7 +20169,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20295,7 +20297,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20423,7 +20425,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20547,7 +20549,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20677,7 +20679,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20805,7 +20807,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="30">
         <v>0</v>
       </c>
@@ -20929,7 +20931,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20">
         <v>0</v>
       </c>
@@ -21051,7 +21053,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="36">
         <v>0</v>
       </c>
@@ -21175,7 +21177,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20">
         <v>0</v>
       </c>
@@ -21297,7 +21299,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="20">
         <v>0</v>
       </c>
@@ -21419,52 +21421,54 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="36">
-        <v>0</v>
-      </c>
-      <c r="B148" s="36">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="33">
+        <v>0</v>
+      </c>
+      <c r="B148" s="33">
         <v>2</v>
       </c>
-      <c r="C148" s="36">
+      <c r="C148" s="33">
         <v>4</v>
       </c>
-      <c r="D148" s="37" t="s">
+      <c r="D148" s="34" t="s">
         <v>646</v>
       </c>
-      <c r="E148" s="37" t="s">
+      <c r="E148" s="34" t="s">
         <v>418</v>
       </c>
-      <c r="F148" s="37" t="s">
+      <c r="F148" s="34" t="s">
         <v>658</v>
       </c>
-      <c r="G148" s="37" t="s">
+      <c r="G148" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H148" s="37" t="s">
+      <c r="H148" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I148" s="36" t="s">
+      <c r="I148" s="33" t="s">
         <v>604</v>
       </c>
-      <c r="J148" s="36">
+      <c r="J148" s="33">
         <v>3</v>
       </c>
-      <c r="K148" s="36" t="s">
+      <c r="K148" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L148" s="36" t="s">
+      <c r="L148" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="M148" s="37" t="s">
+      <c r="M148" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="N148" s="37" t="s">
-        <v>860</v>
-      </c>
-      <c r="O148" s="38"/>
-      <c r="P148" s="36"/>
-      <c r="Q148" s="37"/>
+      <c r="N148" s="34" t="s">
+        <v>868</v>
+      </c>
+      <c r="O148" s="35">
+        <v>1</v>
+      </c>
+      <c r="P148" s="33"/>
+      <c r="Q148" s="34"/>
       <c r="R148" s="13"/>
       <c r="S148" s="2">
         <f t="shared" si="35"/>
@@ -21513,7 +21517,7 @@
       </c>
       <c r="AE148" s="2">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF148" s="2">
         <f t="shared" si="47"/>
@@ -21521,7 +21525,7 @@
       </c>
       <c r="AG148" s="2">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH148" s="2">
         <f t="shared" si="49"/>
@@ -21543,7 +21547,7 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="36">
         <v>0</v>
       </c>
@@ -21667,7 +21671,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="20">
         <v>0</v>
       </c>
@@ -21789,7 +21793,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="20">
         <v>1</v>
       </c>
@@ -21911,7 +21915,7 @@
       <c r="AS151" s="13"/>
       <c r="AT151" s="13"/>
     </row>
-    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20">
         <v>0</v>
       </c>
@@ -22030,7 +22034,7 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="40">
         <v>0</v>
       </c>
@@ -22154,7 +22158,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22272,7 +22276,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="20">
         <v>0</v>
       </c>
@@ -22394,7 +22398,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22518,7 +22522,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33">
         <v>0</v>
       </c>
@@ -22644,7 +22648,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20">
         <v>0</v>
       </c>
@@ -22766,7 +22770,7 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="36">
         <v>0</v>
       </c>
@@ -22890,7 +22894,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23012,7 +23016,7 @@
       <c r="AS160" s="13"/>
       <c r="AT160" s="13"/>
     </row>
-    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="33">
         <v>0</v>
       </c>
@@ -23135,7 +23139,7 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="36">
         <v>0</v>
       </c>
@@ -23255,7 +23259,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23377,7 +23381,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23499,7 +23503,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="20">
         <v>0</v>
       </c>
@@ -23621,7 +23625,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="33">
         <v>0</v>
       </c>
@@ -23747,7 +23751,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="20">
         <v>0</v>
       </c>
@@ -23869,7 +23873,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="30">
         <v>0</v>
       </c>
@@ -23993,7 +23997,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="20">
         <v>0</v>
       </c>
@@ -24115,7 +24119,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33">
         <v>0</v>
       </c>
@@ -24243,7 +24247,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24371,7 +24375,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24499,7 +24503,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24627,7 +24631,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="33">
         <v>1</v>
       </c>
@@ -24755,7 +24759,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="36">
         <v>0</v>
       </c>
@@ -24879,7 +24883,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="36">
         <v>1</v>
       </c>
@@ -25003,7 +25007,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25125,7 +25129,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>0</v>
       </c>
@@ -25247,7 +25251,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>1</v>
       </c>
@@ -25369,7 +25373,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -25491,7 +25495,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -25613,7 +25617,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25741,7 +25745,7 @@
       <c r="AS182" s="13"/>
       <c r="AT182" s="13"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="33">
         <v>1</v>
       </c>
@@ -25869,7 +25873,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="33">
         <v>0</v>
       </c>
@@ -25994,7 +25998,7 @@
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="36">
         <v>0</v>
       </c>
@@ -26118,7 +26122,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="20">
         <v>0</v>
       </c>
@@ -26240,7 +26244,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26362,7 +26366,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26490,7 +26494,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26612,7 +26616,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20">
         <v>0</v>
       </c>
@@ -26734,7 +26738,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="20">
         <v>0</v>
       </c>
@@ -26856,7 +26860,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="20">
         <v>1</v>
       </c>
@@ -26978,7 +26982,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="20">
         <v>1</v>
       </c>
@@ -27100,7 +27104,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33">
         <v>0</v>
       </c>
@@ -27228,7 +27232,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33">
         <v>1</v>
       </c>
@@ -27356,7 +27360,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27484,7 +27488,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="33">
         <v>0</v>
       </c>
@@ -27612,7 +27616,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="33">
         <v>1</v>
       </c>
@@ -27740,7 +27744,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="20">
         <v>0</v>
       </c>
@@ -27862,7 +27866,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20">
         <v>1</v>
       </c>
@@ -27984,7 +27988,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="20">
         <v>1</v>
       </c>
@@ -28106,7 +28110,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="20">
         <v>0</v>
       </c>
@@ -28228,7 +28232,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="20">
         <v>1</v>
       </c>
@@ -28350,7 +28354,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28476,7 +28480,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28602,7 +28606,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="20">
         <v>0</v>
       </c>
@@ -28724,7 +28728,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="20">
         <v>1</v>
       </c>
@@ -28846,7 +28850,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -28972,7 +28976,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33">
         <v>1</v>
       </c>
@@ -29098,7 +29102,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="33">
         <v>0</v>
       </c>
@@ -29226,7 +29230,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="33">
         <v>0</v>
       </c>
@@ -29354,7 +29358,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="20">
         <v>0</v>
       </c>
@@ -29476,7 +29480,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="20">
         <v>0</v>
       </c>
@@ -29598,7 +29602,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29726,7 +29730,7 @@
       <c r="AS214" s="13"/>
       <c r="AT214" s="13"/>
     </row>
-    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29854,7 +29858,7 @@
       <c r="AS215" s="13"/>
       <c r="AT215" s="13"/>
     </row>
-    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="33">
         <v>0</v>
       </c>
@@ -29979,7 +29983,7 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33">
         <v>1</v>
       </c>
@@ -30104,7 +30108,7 @@
       <c r="AS217" s="3"/>
       <c r="AT217" s="3"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="36">
         <v>0</v>
       </c>
@@ -30228,7 +30232,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="33">
         <v>0</v>
       </c>
@@ -30356,7 +30360,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30404,7 +30408,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30452,7 +30456,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30500,7 +30504,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30548,7 +30552,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30596,7 +30600,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30644,7 +30648,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30692,7 +30696,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30740,7 +30744,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30788,7 +30792,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30836,7 +30840,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30884,7 +30888,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30932,7 +30936,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30980,7 +30984,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -31028,7 +31032,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -31076,7 +31080,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31124,7 +31128,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31172,7 +31176,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31220,7 +31224,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31268,7 +31272,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31316,7 +31320,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31364,7 +31368,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31412,7 +31416,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31460,7 +31464,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31508,7 +31512,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31556,7 +31560,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31604,7 +31608,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31652,7 +31656,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31700,7 +31704,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31748,7 +31752,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31796,7 +31800,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31844,7 +31848,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31892,7 +31896,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31940,7 +31944,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -31988,7 +31992,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -32036,7 +32040,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32084,7 +32088,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32132,7 +32136,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32180,7 +32184,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32228,7 +32232,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32276,7 +32280,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32324,7 +32328,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32372,7 +32376,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32420,7 +32424,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32468,7 +32472,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32516,7 +32520,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32564,7 +32568,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32612,7 +32616,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32660,7 +32664,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32708,7 +32712,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32756,7 +32760,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32804,7 +32808,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32852,7 +32856,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32900,7 +32904,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32948,7 +32952,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -32996,7 +33000,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -33044,7 +33048,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33092,7 +33096,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33140,7 +33144,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33188,7 +33192,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33236,7 +33240,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33284,7 +33288,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33332,7 +33336,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33380,7 +33384,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33428,7 +33432,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33476,7 +33480,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33524,7 +33528,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33572,7 +33576,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33620,7 +33624,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33668,7 +33672,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33716,7 +33720,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33764,7 +33768,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33812,7 +33816,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33860,7 +33864,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33908,7 +33912,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33956,7 +33960,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -34004,7 +34008,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -34052,7 +34056,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34100,7 +34104,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34148,7 +34152,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34196,7 +34200,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34244,7 +34248,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34292,7 +34296,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34340,7 +34344,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34388,7 +34392,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34436,7 +34440,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34484,7 +34488,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34532,7 +34536,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34580,7 +34584,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34628,7 +34632,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34676,7 +34680,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34724,7 +34728,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34772,7 +34776,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34820,7 +34824,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34868,7 +34872,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34916,7 +34920,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34964,7 +34968,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -35012,7 +35016,7 @@
       <c r="AS316" s="13"/>
       <c r="AT316" s="13"/>
     </row>
-    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -35060,7 +35064,7 @@
       <c r="AS317" s="13"/>
       <c r="AT317" s="13"/>
     </row>
-    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB317BB0-D2FD-47D4-9DAC-A9702F4FE1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBA7294-D755-4E86-A8D1-3374FB11FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3749,15 +3749,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3779,15 +3779,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -4399,51 +4399,53 @@
       <c r="AT10" s="13"/>
     </row>
     <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36">
-        <v>0</v>
-      </c>
-      <c r="B11" s="36">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36">
-        <v>1</v>
-      </c>
-      <c r="D11" s="37" t="s">
+      <c r="A11" s="33">
+        <v>0</v>
+      </c>
+      <c r="B11" s="33">
+        <v>1</v>
+      </c>
+      <c r="C11" s="33">
+        <v>1</v>
+      </c>
+      <c r="D11" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="34" t="s">
         <v>908</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="I11" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="33">
         <v>99</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="33" t="s">
         <v>794</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="33" t="s">
         <v>687</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="34" t="s">
         <v>688</v>
       </c>
-      <c r="N11" s="37" t="s">
-        <v>859</v>
-      </c>
-      <c r="O11" s="38"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="37"/>
+      <c r="N11" s="34" t="s">
+        <v>867</v>
+      </c>
+      <c r="O11" s="35">
+        <v>1</v>
+      </c>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="34"/>
       <c r="R11" s="13"/>
       <c r="S11" s="2">
         <f t="shared" ref="S11:S72" si="7">IF(J11=$S$7,1,0)</f>
@@ -4492,7 +4494,7 @@
       </c>
       <c r="AE11" s="2">
         <f t="shared" ref="AE11:AE72" si="18">O11*(1-P11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="2">
         <f t="shared" si="3"/>
@@ -4500,7 +4502,7 @@
       </c>
       <c r="AG11" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="2">
         <f t="shared" si="5"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBA7294-D755-4E86-A8D1-3374FB11FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A27AC5-F4FA-4D31-B587-E3EE9568D59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="923">
   <si>
     <t>Recensore</t>
   </si>
@@ -2257,9 +2257,6 @@
     <t>menù della sinoira</t>
   </si>
   <si>
-    <t>menù degustazione Chakana</t>
-  </si>
-  <si>
     <t>1 antipasto (no verdure),1 piatto di riso o noodles, 1 secondo (o carne o pesce), 1 dolce</t>
   </si>
   <si>
@@ -2506,9 +2503,6 @@
     <t>9½</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -2891,6 +2885,9 @@
   </si>
   <si>
     <t>45.056982007771495, 7.659341688955742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menù 6 corse Matriz </t>
   </si>
 </sst>
 </file>
@@ -3931,7 +3928,7 @@
         <v>692</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>19</v>
@@ -3949,7 +3946,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="43" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="25">
@@ -4057,13 +4054,13 @@
         <v>302</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4313,7 +4310,7 @@
         <v>708</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4415,7 +4412,7 @@
         <v>238</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>109</v>
@@ -4430,7 +4427,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L11" s="33" t="s">
         <v>687</v>
@@ -4439,7 +4436,7 @@
         <v>688</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O11" s="35">
         <v>1</v>
@@ -4559,10 +4556,10 @@
         <v>302</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="N12" s="41"/>
       <c r="O12" s="42"/>
@@ -4687,7 +4684,7 @@
         <v>105</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O13" s="35">
         <v>1</v>
@@ -4815,7 +4812,7 @@
         <v>197</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4909,20 +4906,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>280</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>192</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
@@ -5025,13 +5022,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>84</v>
@@ -5040,7 +5037,7 @@
         <v>192</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="J16" s="20">
         <v>1</v>
@@ -5177,7 +5174,7 @@
         <v>707</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5273,13 +5270,13 @@
         <v>2</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>237</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>664</v>
@@ -5288,7 +5285,7 @@
         <v>192</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="J18" s="36"/>
       <c r="K18" s="36" t="s">
@@ -5298,10 +5295,10 @@
         <v>45</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5544,10 +5541,10 @@
         <v>514</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="N20" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O20" s="35">
         <v>1</v>
@@ -5797,7 +5794,7 @@
         <v>684</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O22" s="35">
         <v>1</v>
@@ -5925,7 +5922,7 @@
         <v>248</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="O23" s="35">
         <v>1</v>
@@ -6051,7 +6048,7 @@
         <v>517</v>
       </c>
       <c r="N24" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O24" s="38"/>
       <c r="P24" s="36"/>
@@ -6169,13 +6166,13 @@
         <v>292</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="M25" s="37" t="s">
         <v>197</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O25" s="38"/>
       <c r="P25" s="36"/>
@@ -6275,10 +6272,10 @@
         <v>237</v>
       </c>
       <c r="F26" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="G26" s="37" t="s">
         <v>773</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>774</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>192</v>
@@ -6299,7 +6296,7 @@
         <v>197</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O26" s="38"/>
       <c r="P26" s="36"/>
@@ -6666,7 +6663,7 @@
         <v>709</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6787,10 +6784,10 @@
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O30" s="38"/>
       <c r="P30" s="36"/>
@@ -6908,18 +6905,18 @@
         <v>302</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="M31" s="37" t="s">
         <v>710</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O31" s="38"/>
       <c r="P31" s="36"/>
       <c r="Q31" s="37" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="2">
@@ -7040,7 +7037,7 @@
         <v>248</v>
       </c>
       <c r="N32" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O32" s="35">
         <v>1</v>
@@ -7136,11 +7133,11 @@
         <v>2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>90</v>
@@ -7149,7 +7146,7 @@
         <v>192</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="J33" s="33"/>
       <c r="K33" s="33" t="s">
@@ -7158,7 +7155,7 @@
       <c r="L33" s="33"/>
       <c r="M33" s="34"/>
       <c r="N33" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O33" s="35">
         <v>1</v>
@@ -7256,13 +7253,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>280</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>84</v>
@@ -7271,7 +7268,7 @@
         <v>192</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20" t="s">
@@ -7281,7 +7278,7 @@
         <v>75</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="N34" s="19"/>
       <c r="O34" s="18"/>
@@ -7403,7 +7400,7 @@
         <v>512</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N35" s="19"/>
       <c r="O35" s="18"/>
@@ -7528,7 +7525,7 @@
         <v>197</v>
       </c>
       <c r="N36" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O36" s="38"/>
       <c r="P36" s="36"/>
@@ -7652,7 +7649,7 @@
         <v>306</v>
       </c>
       <c r="N37" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O37" s="35">
         <v>1</v>
@@ -7777,10 +7774,10 @@
         <v>65</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O38" s="38"/>
       <c r="P38" s="36"/>
@@ -7996,13 +7993,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>84</v>
@@ -8011,7 +8008,7 @@
         <v>192</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="J40" s="36">
         <v>1</v>
@@ -8023,10 +8020,10 @@
         <v>50</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="N40" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O40" s="38"/>
       <c r="P40" s="36"/>
@@ -8150,7 +8147,7 @@
         <v>702</v>
       </c>
       <c r="N41" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O41" s="35">
         <v>1</v>
@@ -8886,7 +8883,7 @@
         <v>520</v>
       </c>
       <c r="N47" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O47" s="35">
         <v>1</v>
@@ -9012,7 +9009,7 @@
         <v>686</v>
       </c>
       <c r="N48" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O48" s="38"/>
       <c r="P48" s="36"/>
@@ -9136,7 +9133,7 @@
         <v>304</v>
       </c>
       <c r="N49" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O49" s="35">
         <v>1</v>
@@ -9262,7 +9259,7 @@
         <v>197</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9388,7 +9385,7 @@
         <v>682</v>
       </c>
       <c r="N51" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="36"/>
@@ -9631,7 +9628,7 @@
         <v>304</v>
       </c>
       <c r="N53" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="36"/>
@@ -9731,7 +9728,7 @@
         <v>237</v>
       </c>
       <c r="F54" s="34" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G54" s="34" t="s">
         <v>497</v>
@@ -9755,7 +9752,7 @@
         <v>267</v>
       </c>
       <c r="N54" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O54" s="35">
         <v>1</v>
@@ -9884,7 +9881,7 @@
       <c r="O55" s="42"/>
       <c r="P55" s="40"/>
       <c r="Q55" s="41" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="R55" s="13"/>
       <c r="S55" s="2">
@@ -9975,13 +9972,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E56" s="34" t="s">
         <v>236</v>
       </c>
       <c r="F56" s="34" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>111</v>
@@ -9990,7 +9987,7 @@
         <v>192</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="J56" s="33"/>
       <c r="K56" s="33" t="s">
@@ -10003,7 +10000,7 @@
         <v>197</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O56" s="35">
         <v>1</v>
@@ -10223,13 +10220,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F58" s="34" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>90</v>
@@ -10238,7 +10235,7 @@
         <v>192</v>
       </c>
       <c r="I58" s="33" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="J58" s="33">
         <v>2</v>
@@ -10249,7 +10246,7 @@
       <c r="L58" s="33"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O58" s="35">
         <v>1</v>
@@ -10377,7 +10374,7 @@
         <v>249</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O59" s="35">
         <v>1</v>
@@ -10597,13 +10594,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E61" s="34" t="s">
         <v>239</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>72</v>
@@ -10612,7 +10609,7 @@
         <v>192</v>
       </c>
       <c r="I61" s="33" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="J61" s="33">
         <v>4</v>
@@ -10623,7 +10620,7 @@
       <c r="L61" s="33"/>
       <c r="M61" s="34"/>
       <c r="N61" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O61" s="35">
         <v>1</v>
@@ -10843,22 +10840,22 @@
         <v>5</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>239</v>
       </c>
       <c r="F63" s="19" t="s">
+        <v>739</v>
+      </c>
+      <c r="G63" s="19" t="s">
         <v>740</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>741</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J63" s="20">
         <v>99</v>
@@ -10870,7 +10867,7 @@
         <v>30</v>
       </c>
       <c r="M63" s="19" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="N63" s="19"/>
       <c r="O63" s="18"/>
@@ -10965,13 +10962,13 @@
         <v>5</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>147</v>
@@ -10980,7 +10977,7 @@
         <v>192</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="J64" s="20">
         <v>99</v>
@@ -10992,7 +10989,7 @@
         <v>40</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="18"/>
@@ -11087,13 +11084,13 @@
         <v>5</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>105</v>
@@ -11102,7 +11099,7 @@
         <v>192</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="J65" s="20">
         <v>99</v>
@@ -11114,7 +11111,7 @@
         <v>40</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="N65" s="19"/>
       <c r="O65" s="18"/>
@@ -11239,7 +11236,7 @@
         <v>685</v>
       </c>
       <c r="N66" s="37" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O66" s="38"/>
       <c r="P66" s="36"/>
@@ -11363,7 +11360,7 @@
         <v>711</v>
       </c>
       <c r="N67" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="36"/>
@@ -11487,7 +11484,7 @@
         <v>197</v>
       </c>
       <c r="N68" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O68" s="38"/>
       <c r="P68" s="36"/>
@@ -11581,13 +11578,13 @@
         <v>5</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>72</v>
@@ -11596,7 +11593,7 @@
         <v>192</v>
       </c>
       <c r="I69" s="20" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J69" s="20">
         <v>4</v>
@@ -11608,7 +11605,7 @@
         <v>45</v>
       </c>
       <c r="M69" s="19" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="N69" s="19"/>
       <c r="O69" s="18"/>
@@ -11703,13 +11700,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G70" s="34" t="s">
         <v>72</v>
@@ -11718,7 +11715,7 @@
         <v>192</v>
       </c>
       <c r="I70" s="33" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="J70" s="33"/>
       <c r="K70" s="33" t="s">
@@ -11728,10 +11725,10 @@
         <v>45</v>
       </c>
       <c r="M70" s="34" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="N70" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O70" s="35">
         <v>1</v>
@@ -11854,10 +11851,10 @@
         <v>681</v>
       </c>
       <c r="M71" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N71" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="36"/>
@@ -11951,22 +11948,22 @@
         <v>5</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E72" s="34" t="s">
         <v>239</v>
       </c>
       <c r="F72" s="34" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I72" s="33" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="J72" s="33">
         <v>1</v>
@@ -11981,7 +11978,7 @@
         <v>520</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -12077,10 +12074,10 @@
         <v>5</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F73" s="34" t="s">
         <v>68</v>
@@ -12092,7 +12089,7 @@
         <v>192</v>
       </c>
       <c r="I73" s="33" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="J73" s="33">
         <v>2</v>
@@ -12107,7 +12104,7 @@
         <v>520</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O73" s="35">
         <v>1</v>
@@ -12470,14 +12467,14 @@
       <c r="K76" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="L76" s="36" t="s">
-        <v>795</v>
+      <c r="L76" s="36">
+        <v>70</v>
       </c>
       <c r="M76" s="37" t="s">
-        <v>712</v>
+        <v>922</v>
       </c>
       <c r="N76" s="37" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O76" s="38"/>
       <c r="P76" s="36"/>
@@ -12708,7 +12705,7 @@
         <v>192</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J78" s="20">
         <v>2</v>
@@ -12830,7 +12827,7 @@
         <v>192</v>
       </c>
       <c r="I79" s="20" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J79" s="20">
         <v>1</v>
@@ -12848,7 +12845,7 @@
       <c r="O79" s="18"/>
       <c r="P79" s="20"/>
       <c r="Q79" s="19" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="R79" s="13"/>
       <c r="S79" s="2">
@@ -12969,7 +12966,7 @@
         <v>515</v>
       </c>
       <c r="N80" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O80" s="35">
         <v>1</v>
@@ -13095,7 +13092,7 @@
         <v>105</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13223,7 +13220,7 @@
         <v>250</v>
       </c>
       <c r="N82" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O82" s="35">
         <v>1</v>
@@ -13349,7 +13346,7 @@
         <v>105</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13447,13 +13444,13 @@
         <v>6</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G84" s="34" t="s">
         <v>146</v>
@@ -13462,7 +13459,7 @@
         <v>192</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J84" s="33">
         <v>99</v>
@@ -13474,10 +13471,10 @@
         <v>514</v>
       </c>
       <c r="M84" s="34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N84" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O84" s="35">
         <v>1</v>
@@ -13573,13 +13570,13 @@
         <v>6</v>
       </c>
       <c r="D85" s="34" t="s">
+        <v>893</v>
+      </c>
+      <c r="E85" s="34" t="s">
+        <v>894</v>
+      </c>
+      <c r="F85" s="34" t="s">
         <v>895</v>
-      </c>
-      <c r="E85" s="34" t="s">
-        <v>896</v>
-      </c>
-      <c r="F85" s="34" t="s">
-        <v>897</v>
       </c>
       <c r="G85" s="34" t="s">
         <v>90</v>
@@ -13588,7 +13585,7 @@
         <v>192</v>
       </c>
       <c r="I85" s="33" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="J85" s="33">
         <v>2</v>
@@ -13600,10 +13597,10 @@
         <v>45</v>
       </c>
       <c r="M85" s="34" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="N85" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O85" s="35">
         <v>1</v>
@@ -13726,7 +13723,7 @@
         <v>523</v>
       </c>
       <c r="N86" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O86" s="38"/>
       <c r="P86" s="36"/>
@@ -13847,7 +13844,7 @@
         <v>523</v>
       </c>
       <c r="N87" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O87" s="38"/>
       <c r="P87" s="36"/>
@@ -13971,7 +13968,7 @@
         <v>250</v>
       </c>
       <c r="N88" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -14067,20 +14064,20 @@
         <v>6</v>
       </c>
       <c r="D89" s="34" t="s">
+        <v>870</v>
+      </c>
+      <c r="E89" s="34" t="s">
+        <v>871</v>
+      </c>
+      <c r="F89" s="34" t="s">
         <v>872</v>
-      </c>
-      <c r="E89" s="34" t="s">
-        <v>873</v>
-      </c>
-      <c r="F89" s="34" t="s">
-        <v>874</v>
       </c>
       <c r="G89" s="34"/>
       <c r="H89" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I89" s="33" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J89" s="33"/>
       <c r="K89" s="33" t="s">
@@ -14089,7 +14086,7 @@
       <c r="L89" s="33"/>
       <c r="M89" s="34"/>
       <c r="N89" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O89" s="35">
         <v>1</v>
@@ -14217,7 +14214,7 @@
         <v>197</v>
       </c>
       <c r="N90" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O90" s="38"/>
       <c r="P90" s="36"/>
@@ -14338,10 +14335,10 @@
         <v>307</v>
       </c>
       <c r="M91" s="34" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N91" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O91" s="35">
         <v>1</v>
@@ -14589,7 +14586,7 @@
         <v>635</v>
       </c>
       <c r="N93" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O93" s="35">
         <v>1</v>
@@ -14715,7 +14712,7 @@
         <v>311</v>
       </c>
       <c r="N94" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O94" s="35">
         <v>1</v>
@@ -14843,7 +14840,7 @@
         <v>311</v>
       </c>
       <c r="N95" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O95" s="35">
         <v>1</v>
@@ -14971,7 +14968,7 @@
         <v>311</v>
       </c>
       <c r="N96" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O96" s="35">
         <v>1</v>
@@ -14980,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="34" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="R96" s="13"/>
       <c r="S96" s="2">
@@ -15101,7 +15098,7 @@
         <v>270</v>
       </c>
       <c r="N97" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="O97" s="35">
         <v>1</v>
@@ -15227,7 +15224,7 @@
         <v>270</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15323,13 +15320,13 @@
         <v>7</v>
       </c>
       <c r="D99" s="34" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E99" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F99" s="34" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G99" s="34" t="s">
         <v>72</v>
@@ -15338,7 +15335,7 @@
         <v>192</v>
       </c>
       <c r="I99" s="33" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="J99" s="33">
         <v>3</v>
@@ -15350,10 +15347,10 @@
         <v>28</v>
       </c>
       <c r="M99" s="34" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15479,7 +15476,7 @@
         <v>197</v>
       </c>
       <c r="N100" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O100" s="35">
         <v>1</v>
@@ -15602,7 +15599,7 @@
         <v>308</v>
       </c>
       <c r="M101" s="19" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="N101" s="19"/>
       <c r="O101" s="18"/>
@@ -15697,13 +15694,13 @@
         <v>7</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E102" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G102" s="37" t="s">
         <v>72</v>
@@ -15712,7 +15709,7 @@
         <v>192</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="J102" s="36">
         <v>3</v>
@@ -15724,10 +15721,10 @@
         <v>30</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="N102" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="36"/>
@@ -15851,7 +15848,7 @@
         <v>570</v>
       </c>
       <c r="N103" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O103" s="38"/>
       <c r="P103" s="36"/>
@@ -15972,7 +15969,7 @@
         <v>251</v>
       </c>
       <c r="N104" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O104" s="38"/>
       <c r="P104" s="36"/>
@@ -16081,7 +16078,7 @@
         <v>192</v>
       </c>
       <c r="I105" s="33" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J105" s="33">
         <v>2</v>
@@ -16096,7 +16093,7 @@
         <v>698</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16194,13 +16191,13 @@
         <v>1</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E106" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G106" s="34" t="s">
         <v>90</v>
@@ -16209,7 +16206,7 @@
         <v>192</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="J106" s="33">
         <v>2</v>
@@ -16221,10 +16218,10 @@
         <v>5</v>
       </c>
       <c r="M106" s="34" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="N106" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O106" s="35">
         <v>1</v>
@@ -16233,7 +16230,7 @@
         <v>1</v>
       </c>
       <c r="Q106" s="34" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="R106" s="13"/>
       <c r="S106" s="2">
@@ -16354,7 +16351,7 @@
         <v>195</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O107" s="35">
         <v>1</v>
@@ -16363,7 +16360,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="34" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="R107" s="13"/>
       <c r="S107" s="2">
@@ -16454,13 +16451,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G108" s="34" t="s">
         <v>146</v>
@@ -16469,7 +16466,7 @@
         <v>192</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J108" s="33">
         <v>99</v>
@@ -16484,7 +16481,7 @@
         <v>195</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O108" s="35">
         <v>1</v>
@@ -16582,13 +16579,13 @@
         <v>1</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E109" s="34" t="s">
         <v>695</v>
       </c>
       <c r="F109" s="34" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G109" s="34" t="s">
         <v>105</v>
@@ -16609,10 +16606,10 @@
         <v>9</v>
       </c>
       <c r="M109" s="34" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N109" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O109" s="35">
         <v>1</v>
@@ -17106,7 +17103,7 @@
         <v>195</v>
       </c>
       <c r="N113" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O113" s="35">
         <v>1</v>
@@ -17232,7 +17229,7 @@
         <v>195</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O114" s="35">
         <v>1</v>
@@ -17336,10 +17333,10 @@
         <v>61</v>
       </c>
       <c r="F115" s="34" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G115" s="34" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H115" s="34" t="s">
         <v>192</v>
@@ -17360,7 +17357,7 @@
         <v>195</v>
       </c>
       <c r="N115" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O115" s="35">
         <v>1</v>
@@ -17610,7 +17607,7 @@
         <v>195</v>
       </c>
       <c r="N117" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O117" s="35">
         <v>1</v>
@@ -17735,10 +17732,10 @@
         <v>9</v>
       </c>
       <c r="M118" s="34" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N118" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O118" s="35">
         <v>1</v>
@@ -17985,10 +17982,10 @@
         <v>305</v>
       </c>
       <c r="M120" s="34" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="N120" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O120" s="35">
         <v>1</v>
@@ -18084,22 +18081,22 @@
         <v>2</v>
       </c>
       <c r="D121" s="34" t="s">
+        <v>828</v>
+      </c>
+      <c r="E121" s="34" t="s">
+        <v>761</v>
+      </c>
+      <c r="F121" s="34" t="s">
+        <v>829</v>
+      </c>
+      <c r="G121" s="34" t="s">
         <v>830</v>
-      </c>
-      <c r="E121" s="34" t="s">
-        <v>762</v>
-      </c>
-      <c r="F121" s="34" t="s">
-        <v>831</v>
-      </c>
-      <c r="G121" s="34" t="s">
-        <v>832</v>
       </c>
       <c r="H121" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I121" s="33" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J121" s="33"/>
       <c r="K121" s="33" t="s">
@@ -18109,10 +18106,10 @@
         <v>30</v>
       </c>
       <c r="M121" s="34" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="N121" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O121" s="35">
         <v>1</v>
@@ -18235,10 +18232,10 @@
         <v>312</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18336,13 +18333,13 @@
         <v>2</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E123" s="34" t="s">
         <v>243</v>
       </c>
       <c r="F123" s="34" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G123" s="34" t="s">
         <v>162</v>
@@ -18351,7 +18348,7 @@
         <v>192</v>
       </c>
       <c r="I123" s="33" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J123" s="33">
         <v>1</v>
@@ -18360,13 +18357,13 @@
         <v>295</v>
       </c>
       <c r="L123" s="33" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="M123" s="34" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N123" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O123" s="35">
         <v>1</v>
@@ -18834,7 +18831,7 @@
         <v>385</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G127" s="19" t="s">
         <v>206</v>
@@ -19316,18 +19313,18 @@
         <v>2</v>
       </c>
       <c r="D131" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E131" s="19"/>
       <c r="F131" s="19" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G131" s="19"/>
       <c r="H131" s="19" t="s">
         <v>192</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="J131" s="20"/>
       <c r="K131" s="20" t="s">
@@ -19337,7 +19334,7 @@
         <v>22</v>
       </c>
       <c r="M131" s="39" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="N131" s="39"/>
       <c r="O131" s="2"/>
@@ -19462,7 +19459,7 @@
         <v>598</v>
       </c>
       <c r="N132" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O132" s="35">
         <v>1</v>
@@ -19590,7 +19587,7 @@
         <v>463</v>
       </c>
       <c r="N133" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="36"/>
@@ -19821,7 +19818,7 @@
         <v>192</v>
       </c>
       <c r="I135" s="36" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="J135" s="36">
         <v>99</v>
@@ -19836,7 +19833,7 @@
         <v>675</v>
       </c>
       <c r="N135" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O135" s="38"/>
       <c r="P135" s="36"/>
@@ -19954,13 +19951,13 @@
         <v>295</v>
       </c>
       <c r="L136" s="33" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="M136" s="34" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N136" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O136" s="35">
         <v>1</v>
@@ -20212,7 +20209,7 @@
         <v>105</v>
       </c>
       <c r="N138" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O138" s="35">
         <v>1</v>
@@ -20340,7 +20337,7 @@
         <v>105</v>
       </c>
       <c r="N139" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O139" s="35">
         <v>1</v>
@@ -20438,13 +20435,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="34" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E140" s="34" t="s">
+        <v>885</v>
+      </c>
+      <c r="F140" s="34" t="s">
         <v>887</v>
-      </c>
-      <c r="F140" s="34" t="s">
-        <v>889</v>
       </c>
       <c r="G140" s="34" t="s">
         <v>139</v>
@@ -20464,7 +20461,7 @@
       <c r="L140" s="33"/>
       <c r="M140" s="34"/>
       <c r="N140" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O140" s="35">
         <v>1</v>
@@ -20568,7 +20565,7 @@
         <v>643</v>
       </c>
       <c r="F141" s="34" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G141" s="34" t="s">
         <v>85</v>
@@ -20592,7 +20589,7 @@
         <v>105</v>
       </c>
       <c r="N141" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O141" s="35">
         <v>1</v>
@@ -20601,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="Q141" s="34" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="R141" s="13"/>
       <c r="S141" s="2">
@@ -20722,7 +20719,7 @@
         <v>316</v>
       </c>
       <c r="N142" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O142" s="35">
         <v>1</v>
@@ -21096,7 +21093,7 @@
         <v>676</v>
       </c>
       <c r="N145" s="37" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O145" s="38"/>
       <c r="P145" s="36"/>
@@ -21196,7 +21193,7 @@
         <v>418</v>
       </c>
       <c r="F146" s="19" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G146" s="19" t="s">
         <v>502</v>
@@ -21217,7 +21214,7 @@
         <v>309</v>
       </c>
       <c r="M146" s="19" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N146" s="19"/>
       <c r="O146" s="18"/>
@@ -21464,7 +21461,7 @@
         <v>630</v>
       </c>
       <c r="N148" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O148" s="35">
         <v>1</v>
@@ -21590,7 +21587,7 @@
         <v>521</v>
       </c>
       <c r="N149" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="O149" s="38"/>
       <c r="P149" s="36"/>
@@ -21690,7 +21687,7 @@
         <v>30</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G150" s="19" t="s">
         <v>103</v>
@@ -22077,7 +22074,7 @@
         <v>677</v>
       </c>
       <c r="N153" s="41" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O153" s="42"/>
       <c r="P153" s="40"/>
@@ -22316,7 +22313,7 @@
         <v>30</v>
       </c>
       <c r="M155" s="19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N155" s="19"/>
       <c r="O155" s="18"/>
@@ -22411,13 +22408,13 @@
         <v>5</v>
       </c>
       <c r="D156" s="34" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E156" s="34" t="s">
         <v>539</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G156" s="34" t="s">
         <v>84</v>
@@ -22426,7 +22423,7 @@
         <v>192</v>
       </c>
       <c r="I156" s="33" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J156" s="33"/>
       <c r="K156" s="33" t="s">
@@ -22436,10 +22433,10 @@
         <v>40</v>
       </c>
       <c r="M156" s="34" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22535,22 +22532,22 @@
         <v>5</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E157" s="34" t="s">
         <v>484</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G157" s="34" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H157" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I157" s="33" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J157" s="33">
         <v>2</v>
@@ -22562,10 +22559,10 @@
         <v>307</v>
       </c>
       <c r="M157" s="34" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="N157" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O157" s="35">
         <v>1</v>
@@ -22783,13 +22780,13 @@
         <v>5</v>
       </c>
       <c r="D159" s="37" t="s">
+        <v>847</v>
+      </c>
+      <c r="E159" s="37" t="s">
+        <v>848</v>
+      </c>
+      <c r="F159" s="37" t="s">
         <v>849</v>
-      </c>
-      <c r="E159" s="37" t="s">
-        <v>850</v>
-      </c>
-      <c r="F159" s="37" t="s">
-        <v>851</v>
       </c>
       <c r="G159" s="37" t="s">
         <v>131</v>
@@ -22798,7 +22795,7 @@
         <v>192</v>
       </c>
       <c r="I159" s="36" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="J159" s="36">
         <v>99</v>
@@ -22810,10 +22807,10 @@
         <v>40</v>
       </c>
       <c r="M159" s="37" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="N159" s="37" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O159" s="38"/>
       <c r="P159" s="36"/>
@@ -22907,20 +22904,20 @@
         <v>5</v>
       </c>
       <c r="D160" s="34" t="s">
+        <v>835</v>
+      </c>
+      <c r="E160" s="34" t="s">
+        <v>839</v>
+      </c>
+      <c r="F160" s="34" t="s">
         <v>837</v>
-      </c>
-      <c r="E160" s="34" t="s">
-        <v>841</v>
-      </c>
-      <c r="F160" s="34" t="s">
-        <v>839</v>
       </c>
       <c r="G160" s="34"/>
       <c r="H160" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I160" s="33" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="J160" s="33"/>
       <c r="K160" s="33" t="s">
@@ -22930,10 +22927,10 @@
         <v>35</v>
       </c>
       <c r="M160" s="34" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -23059,7 +23056,7 @@
         <v>468</v>
       </c>
       <c r="N161" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="O161" s="35">
         <v>1</v>
@@ -23152,20 +23149,20 @@
         <v>5</v>
       </c>
       <c r="D162" s="37" t="s">
+        <v>874</v>
+      </c>
+      <c r="E162" s="37" t="s">
+        <v>875</v>
+      </c>
+      <c r="F162" s="37" t="s">
         <v>876</v>
-      </c>
-      <c r="E162" s="37" t="s">
-        <v>877</v>
-      </c>
-      <c r="F162" s="37" t="s">
-        <v>878</v>
       </c>
       <c r="G162" s="37"/>
       <c r="H162" s="37" t="s">
         <v>192</v>
       </c>
       <c r="I162" s="36" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="J162" s="36"/>
       <c r="K162" s="36" t="s">
@@ -23175,10 +23172,10 @@
         <v>35</v>
       </c>
       <c r="M162" s="37" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="N162" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O162" s="38"/>
       <c r="P162" s="36"/>
@@ -23665,10 +23662,10 @@
         <v>307</v>
       </c>
       <c r="M166" s="34" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="N166" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O166" s="35">
         <v>1</v>
@@ -24016,7 +24013,7 @@
         <v>89</v>
       </c>
       <c r="F169" s="19" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G169" s="19" t="s">
         <v>102</v>
@@ -24162,7 +24159,7 @@
         <v>198</v>
       </c>
       <c r="N170" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O170" s="35">
         <v>1</v>
@@ -24266,7 +24263,7 @@
         <v>38</v>
       </c>
       <c r="F171" s="34" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G171" s="34" t="s">
         <v>84</v>
@@ -24290,7 +24287,7 @@
         <v>198</v>
       </c>
       <c r="N171" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O171" s="35">
         <v>1</v>
@@ -24418,7 +24415,7 @@
         <v>198</v>
       </c>
       <c r="N172" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O172" s="35">
         <v>1</v>
@@ -24522,16 +24519,16 @@
         <v>38</v>
       </c>
       <c r="F173" s="34" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G173" s="34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H173" s="34" t="s">
         <v>192</v>
       </c>
       <c r="I173" s="33" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="J173" s="33">
         <v>1</v>
@@ -24546,7 +24543,7 @@
         <v>198</v>
       </c>
       <c r="N173" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O173" s="35">
         <v>1</v>
@@ -24674,7 +24671,7 @@
         <v>198</v>
       </c>
       <c r="N174" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O174" s="35">
         <v>1</v>
@@ -24802,7 +24799,7 @@
         <v>198</v>
       </c>
       <c r="N175" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O175" s="38"/>
       <c r="P175" s="36"/>
@@ -24902,7 +24899,7 @@
         <v>38</v>
       </c>
       <c r="F176" s="37" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G176" s="37" t="s">
         <v>147</v>
@@ -24926,7 +24923,7 @@
         <v>198</v>
       </c>
       <c r="N176" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O176" s="38"/>
       <c r="P176" s="36"/>
@@ -25660,7 +25657,7 @@
         <v>198</v>
       </c>
       <c r="N182" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O182" s="35">
         <v>1</v>
@@ -25788,7 +25785,7 @@
         <v>198</v>
       </c>
       <c r="N183" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O183" s="35">
         <v>1</v>
@@ -25916,7 +25913,7 @@
         <v>198</v>
       </c>
       <c r="N184" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O184" s="35">
         <v>1</v>
@@ -26041,7 +26038,7 @@
         <v>198</v>
       </c>
       <c r="N185" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O185" s="38"/>
       <c r="P185" s="36"/>
@@ -26409,7 +26406,7 @@
         <v>105</v>
       </c>
       <c r="N188" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O188" s="35">
         <v>1</v>
@@ -27147,7 +27144,7 @@
         <v>198</v>
       </c>
       <c r="N194" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O194" s="35">
         <v>1</v>
@@ -27275,7 +27272,7 @@
         <v>198</v>
       </c>
       <c r="N195" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O195" s="35">
         <v>1</v>
@@ -27403,7 +27400,7 @@
         <v>198</v>
       </c>
       <c r="N196" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O196" s="35">
         <v>1</v>
@@ -27531,7 +27528,7 @@
         <v>387</v>
       </c>
       <c r="N197" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O197" s="35">
         <v>1</v>
@@ -27635,7 +27632,7 @@
         <v>55</v>
       </c>
       <c r="F198" s="34" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G198" s="34" t="s">
         <v>72</v>
@@ -27644,7 +27641,7 @@
         <v>192</v>
       </c>
       <c r="I198" s="33" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="J198" s="33">
         <v>4</v>
@@ -27659,7 +27656,7 @@
         <v>387</v>
       </c>
       <c r="N198" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O198" s="35">
         <v>1</v>
@@ -28123,13 +28120,13 @@
         <v>7</v>
       </c>
       <c r="D202" s="19" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E202" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F202" s="19" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G202" s="19" t="s">
         <v>72</v>
@@ -28138,7 +28135,7 @@
         <v>192</v>
       </c>
       <c r="I202" s="20" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="J202" s="20">
         <v>4</v>
@@ -28245,13 +28242,13 @@
         <v>7</v>
       </c>
       <c r="D203" s="19" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E203" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F203" s="19" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G203" s="19" t="s">
         <v>102</v>
@@ -28260,7 +28257,7 @@
         <v>192</v>
       </c>
       <c r="I203" s="20" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="J203" s="20">
         <v>99</v>
@@ -28373,7 +28370,7 @@
         <v>38</v>
       </c>
       <c r="F204" s="34" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G204" s="34" t="s">
         <v>84</v>
@@ -28397,7 +28394,7 @@
         <v>198</v>
       </c>
       <c r="N204" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O204" s="35">
         <v>1</v>
@@ -28523,7 +28520,7 @@
         <v>198</v>
       </c>
       <c r="N205" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O205" s="35">
         <v>1</v>
@@ -28756,7 +28753,7 @@
         <v>192</v>
       </c>
       <c r="I207" s="20" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J207" s="20">
         <v>99</v>
@@ -28863,13 +28860,13 @@
         <v>7</v>
       </c>
       <c r="D208" s="34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E208" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G208" s="34" t="s">
         <v>72</v>
@@ -28878,7 +28875,7 @@
         <v>192</v>
       </c>
       <c r="I208" s="33" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J208" s="33">
         <v>4</v>
@@ -28893,7 +28890,7 @@
         <v>198</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
@@ -28989,13 +28986,13 @@
         <v>7</v>
       </c>
       <c r="D209" s="34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E209" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G209" s="34" t="s">
         <v>90</v>
@@ -29004,7 +29001,7 @@
         <v>192</v>
       </c>
       <c r="I209" s="33" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J209" s="33">
         <v>2</v>
@@ -29019,7 +29016,7 @@
         <v>198</v>
       </c>
       <c r="N209" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="O209" s="35">
         <v>1</v>
@@ -29121,7 +29118,7 @@
         <v>38</v>
       </c>
       <c r="F210" s="34" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G210" s="34" t="s">
         <v>84</v>
@@ -29145,7 +29142,7 @@
         <v>198</v>
       </c>
       <c r="N210" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O210" s="35">
         <v>1</v>
@@ -29273,7 +29270,7 @@
         <v>105</v>
       </c>
       <c r="N211" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O211" s="35">
         <v>1</v>
@@ -29645,7 +29642,7 @@
         <v>105</v>
       </c>
       <c r="N214" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O214" s="35">
         <v>1</v>
@@ -29773,7 +29770,7 @@
         <v>105</v>
       </c>
       <c r="N215" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O215" s="35">
         <v>1</v>
@@ -29901,7 +29898,7 @@
         <v>105</v>
       </c>
       <c r="N216" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O216" s="35">
         <v>1</v>
@@ -30002,7 +29999,7 @@
         <v>55</v>
       </c>
       <c r="F217" s="34" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G217" s="34" t="s">
         <v>147</v>
@@ -30011,7 +30008,7 @@
         <v>192</v>
       </c>
       <c r="I217" s="33" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="J217" s="33">
         <v>99</v>
@@ -30026,7 +30023,7 @@
         <v>105</v>
       </c>
       <c r="N217" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O217" s="35">
         <v>1</v>
@@ -30151,7 +30148,7 @@
         <v>314</v>
       </c>
       <c r="N218" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="O218" s="38"/>
       <c r="P218" s="36"/>
@@ -30275,7 +30272,7 @@
         <v>198</v>
       </c>
       <c r="N219" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="O219" s="35">
         <v>1</v>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A27AC5-F4FA-4D31-B587-E3EE9568D59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3353F0B8-9BF7-44E9-BE4F-66910D9573EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -6008,51 +6008,53 @@
       <c r="AT23" s="13"/>
     </row>
     <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
-        <v>0</v>
-      </c>
-      <c r="B24" s="36">
-        <v>1</v>
-      </c>
-      <c r="C24" s="36">
+      <c r="A24" s="33">
+        <v>0</v>
+      </c>
+      <c r="B24" s="33">
+        <v>1</v>
+      </c>
+      <c r="C24" s="33">
         <v>2</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="G24" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="37" t="s">
+      <c r="H24" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I24" s="36" t="s">
+      <c r="I24" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="J24" s="36">
-        <v>1</v>
-      </c>
-      <c r="K24" s="36" t="s">
+      <c r="J24" s="33">
+        <v>1</v>
+      </c>
+      <c r="K24" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="L24" s="36" t="s">
+      <c r="L24" s="33" t="s">
         <v>516</v>
       </c>
-      <c r="M24" s="37" t="s">
+      <c r="M24" s="34" t="s">
         <v>517</v>
       </c>
-      <c r="N24" s="37" t="s">
-        <v>858</v>
-      </c>
-      <c r="O24" s="38"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="37"/>
+      <c r="N24" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="O24" s="35">
+        <v>1</v>
+      </c>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="34"/>
       <c r="R24" s="13"/>
       <c r="S24" s="2">
         <f t="shared" si="7"/>
@@ -6101,7 +6103,7 @@
       </c>
       <c r="AE24" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" s="2">
         <f t="shared" si="3"/>
@@ -6109,7 +6111,7 @@
       </c>
       <c r="AG24" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="2">
         <f t="shared" si="5"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3353F0B8-9BF7-44E9-BE4F-66910D9573EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E35E12-C00A-4845-BC8C-8447907ADB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -11198,51 +11198,53 @@
       <c r="AT65" s="13"/>
     </row>
     <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="36">
-        <v>0</v>
-      </c>
-      <c r="B66" s="36">
-        <v>1</v>
-      </c>
-      <c r="C66" s="36">
+      <c r="A66" s="33">
+        <v>0</v>
+      </c>
+      <c r="B66" s="33">
+        <v>1</v>
+      </c>
+      <c r="C66" s="33">
         <v>5</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="D66" s="34" t="s">
         <v>647</v>
       </c>
-      <c r="E66" s="37" t="s">
+      <c r="E66" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="F66" s="37" t="s">
+      <c r="F66" s="34" t="s">
         <v>661</v>
       </c>
-      <c r="G66" s="37" t="s">
+      <c r="G66" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H66" s="37" t="s">
+      <c r="H66" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I66" s="36" t="s">
+      <c r="I66" s="33" t="s">
         <v>613</v>
       </c>
-      <c r="J66" s="36">
-        <v>1</v>
-      </c>
-      <c r="K66" s="36" t="s">
+      <c r="J66" s="33">
+        <v>1</v>
+      </c>
+      <c r="K66" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L66" s="36" t="s">
+      <c r="L66" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="M66" s="37" t="s">
+      <c r="M66" s="34" t="s">
         <v>685</v>
       </c>
-      <c r="N66" s="37" t="s">
-        <v>860</v>
-      </c>
-      <c r="O66" s="38"/>
-      <c r="P66" s="36"/>
-      <c r="Q66" s="37"/>
+      <c r="N66" s="34" t="s">
+        <v>898</v>
+      </c>
+      <c r="O66" s="35">
+        <v>1</v>
+      </c>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="34"/>
       <c r="R66" s="13"/>
       <c r="S66" s="2">
         <f t="shared" si="7"/>
@@ -11291,7 +11293,7 @@
       </c>
       <c r="AE66" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF66" s="2">
         <f t="shared" si="3"/>
@@ -11299,7 +11301,7 @@
       </c>
       <c r="AG66" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH66" s="2">
         <f t="shared" si="5"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E35E12-C00A-4845-BC8C-8447907ADB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BECA170-DE02-469F-8E43-5327F7A2FE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -14178,51 +14178,53 @@
       <c r="AT89" s="13"/>
     </row>
     <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="36">
-        <v>0</v>
-      </c>
-      <c r="B90" s="36">
-        <v>1</v>
-      </c>
-      <c r="C90" s="36">
+      <c r="A90" s="33">
+        <v>0</v>
+      </c>
+      <c r="B90" s="33">
+        <v>1</v>
+      </c>
+      <c r="C90" s="33">
         <v>6</v>
       </c>
-      <c r="D90" s="37" t="s">
+      <c r="D90" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="E90" s="37" t="s">
+      <c r="E90" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="F90" s="37" t="s">
+      <c r="F90" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="G90" s="37" t="s">
+      <c r="G90" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H90" s="37" t="s">
+      <c r="H90" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I90" s="36" t="s">
+      <c r="I90" s="33" t="s">
         <v>673</v>
       </c>
-      <c r="J90" s="36">
+      <c r="J90" s="33">
         <v>5</v>
       </c>
-      <c r="K90" s="36" t="s">
+      <c r="K90" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="L90" s="36" t="s">
+      <c r="L90" s="33" t="s">
         <v>512</v>
       </c>
-      <c r="M90" s="37" t="s">
+      <c r="M90" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="N90" s="37" t="s">
-        <v>857</v>
-      </c>
-      <c r="O90" s="38"/>
-      <c r="P90" s="36"/>
-      <c r="Q90" s="37"/>
+      <c r="N90" s="34" t="s">
+        <v>865</v>
+      </c>
+      <c r="O90" s="35">
+        <v>1</v>
+      </c>
+      <c r="P90" s="33"/>
+      <c r="Q90" s="34"/>
       <c r="R90" s="13"/>
       <c r="S90" s="2">
         <f t="shared" si="23"/>
@@ -14271,7 +14273,7 @@
       </c>
       <c r="AE90" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF90" s="2">
         <f t="shared" si="19"/>
@@ -14279,7 +14281,7 @@
       </c>
       <c r="AG90" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="2">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BECA170-DE02-469F-8E43-5327F7A2FE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45270F6B-D868-45F6-9D38-CDF5C734C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -6257,52 +6257,55 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36">
-        <v>0</v>
-      </c>
-      <c r="B26" s="36">
-        <v>1</v>
-      </c>
-      <c r="C26" s="36">
+    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="33">
+        <v>0</v>
+      </c>
+      <c r="B26" s="33">
+        <v>1</v>
+      </c>
+      <c r="C26" s="33">
         <v>2</v>
       </c>
-      <c r="D26" s="37" t="s">
+      <c r="D26" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="E26" s="37" t="s">
+      <c r="E26" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="34" t="s">
         <v>772</v>
       </c>
-      <c r="G26" s="37" t="s">
+      <c r="G26" s="34" t="s">
         <v>773</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="H26" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I26" s="36" t="s">
+      <c r="I26" s="33" t="s">
         <v>450</v>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="33">
         <v>7</v>
       </c>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L26" s="36" t="s">
+      <c r="L26" s="33" t="s">
         <v>516</v>
       </c>
-      <c r="M26" s="37" t="s">
+      <c r="M26" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="N26" s="37" t="s">
-        <v>891</v>
-      </c>
-      <c r="O26" s="38"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="37"/>
+      <c r="N26" s="34" t="s">
+        <v>892</v>
+      </c>
+      <c r="O26" s="35">
+        <v>1</v>
+      </c>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="13"/>
       <c r="S26" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6343,13 +6346,14 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" s="2">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE26" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" s="2">
         <f t="shared" si="3"/>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="AG26" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="2">
         <f t="shared" si="5"/>
@@ -6367,16 +6371,17 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-      <c r="AM26" s="3"/>
-      <c r="AN26" s="3"/>
-      <c r="AO26" s="3"/>
-      <c r="AP26" s="3"/>
-      <c r="AQ26" s="3"/>
-      <c r="AR26" s="3"/>
-      <c r="AS26" s="3"/>
-      <c r="AT26" s="3"/>
+      <c r="AJ26" s="13"/>
+      <c r="AK26" s="13"/>
+      <c r="AL26" s="13"/>
+      <c r="AM26" s="13"/>
+      <c r="AN26" s="13"/>
+      <c r="AO26" s="13"/>
+      <c r="AP26" s="13"/>
+      <c r="AQ26" s="13"/>
+      <c r="AR26" s="13"/>
+      <c r="AS26" s="13"/>
+      <c r="AT26" s="13"/>
     </row>
     <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30">

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45270F6B-D868-45F6-9D38-CDF5C734C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795B318-C00A-478B-AA07-4EC54BCFC5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -9595,51 +9595,53 @@
       <c r="AT52" s="13"/>
     </row>
     <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="36">
-        <v>0</v>
-      </c>
-      <c r="B53" s="36">
-        <v>1</v>
-      </c>
-      <c r="C53" s="36">
+      <c r="A53" s="33">
+        <v>0</v>
+      </c>
+      <c r="B53" s="33">
+        <v>1</v>
+      </c>
+      <c r="C53" s="33">
         <v>3</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="37" t="s">
+      <c r="E53" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="F53" s="37" t="s">
+      <c r="F53" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="G53" s="37" t="s">
+      <c r="G53" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H53" s="37" t="s">
+      <c r="H53" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I53" s="36" t="s">
+      <c r="I53" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J53" s="36">
+      <c r="J53" s="33">
         <v>4</v>
       </c>
-      <c r="K53" s="36" t="s">
+      <c r="K53" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L53" s="36" t="s">
+      <c r="L53" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M53" s="37" t="s">
+      <c r="M53" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="N53" s="37" t="s">
-        <v>859</v>
-      </c>
-      <c r="O53" s="38"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="37"/>
+      <c r="N53" s="34" t="s">
+        <v>864</v>
+      </c>
+      <c r="O53" s="35">
+        <v>1</v>
+      </c>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="34"/>
       <c r="R53" s="13"/>
       <c r="S53" s="2">
         <f t="shared" si="7"/>
@@ -9688,7 +9690,7 @@
       </c>
       <c r="AE53" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF53" s="2">
         <f t="shared" si="3"/>
@@ -9696,7 +9698,7 @@
       </c>
       <c r="AG53" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" s="2">
         <f t="shared" si="5"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2795B318-C00A-478B-AA07-4EC54BCFC5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F88574A-B3BC-4FFC-B65D-D834EE965808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3644,47 +3644,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT318"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.140625" style="2"/>
-    <col min="47" max="16384" width="9.140625" style="3"/>
+    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.109375" style="2"/>
+    <col min="47" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3706,7 +3706,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3766,7 +3766,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3838,7 +3838,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3896,7 +3896,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>689</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4145,7 +4145,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
         <v>0</v>
       </c>
@@ -4269,7 +4269,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>0</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>0</v>
       </c>
@@ -4643,7 +4643,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -5011,7 +5011,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5133,7 +5133,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5259,7 +5259,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5381,7 +5381,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5503,7 +5503,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5631,7 +5631,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5881,7 +5881,7 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>0</v>
       </c>
@@ -6007,7 +6007,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="33">
         <v>0</v>
       </c>
@@ -6133,7 +6133,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>0</v>
       </c>
@@ -6257,7 +6257,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>0</v>
       </c>
@@ -6383,7 +6383,7 @@
       <c r="AS26" s="13"/>
       <c r="AT26" s="13"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30">
         <v>0</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6629,7 +6629,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6755,7 +6755,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -7003,7 +7003,7 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>0</v>
       </c>
@@ -7129,7 +7129,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7369,7 +7369,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7491,7 +7491,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>0</v>
       </c>
@@ -7615,7 +7615,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>0</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>0</v>
       </c>
@@ -7867,7 +7867,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7989,7 +7989,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>0</v>
       </c>
@@ -8113,7 +8113,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>0</v>
       </c>
@@ -8239,7 +8239,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20">
         <v>0</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8483,7 +8483,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8605,7 +8605,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8727,7 +8727,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8849,7 +8849,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>0</v>
       </c>
@@ -8975,7 +8975,7 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>0</v>
       </c>
@@ -9099,7 +9099,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9351,7 +9351,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="36">
         <v>0</v>
       </c>
@@ -9472,7 +9472,7 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20">
         <v>0</v>
       </c>
@@ -9594,7 +9594,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="33">
         <v>0</v>
       </c>
@@ -9720,7 +9720,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9846,7 +9846,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
         <v>0</v>
       </c>
@@ -9970,7 +9970,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="33">
         <v>0</v>
       </c>
@@ -10096,7 +10096,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20">
         <v>0</v>
       </c>
@@ -10218,7 +10218,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33">
         <v>0</v>
       </c>
@@ -10342,7 +10342,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10470,7 +10470,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20">
         <v>0</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
         <v>0</v>
       </c>
@@ -10716,7 +10716,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20">
         <v>0</v>
       </c>
@@ -10838,7 +10838,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20">
         <v>1</v>
       </c>
@@ -11204,7 +11204,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="33">
         <v>0</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="36">
         <v>0</v>
       </c>
@@ -11454,7 +11454,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20">
         <v>0</v>
       </c>
@@ -11700,7 +11700,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
         <v>0</v>
       </c>
@@ -11824,7 +11824,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="36">
         <v>0</v>
       </c>
@@ -11948,7 +11948,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
         <v>0</v>
       </c>
@@ -12074,7 +12074,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12200,7 +12200,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>0</v>
       </c>
@@ -12322,7 +12322,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12444,52 +12444,54 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="36">
-        <v>0</v>
-      </c>
-      <c r="B76" s="36">
-        <v>1</v>
-      </c>
-      <c r="C76" s="36">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="33">
+        <v>0</v>
+      </c>
+      <c r="B76" s="33">
+        <v>1</v>
+      </c>
+      <c r="C76" s="33">
         <v>6</v>
       </c>
-      <c r="D76" s="37" t="s">
+      <c r="D76" s="34" t="s">
         <v>438</v>
       </c>
-      <c r="E76" s="37" t="s">
+      <c r="E76" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="F76" s="37" t="s">
+      <c r="F76" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="G76" s="37" t="s">
+      <c r="G76" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="H76" s="37" t="s">
+      <c r="H76" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I76" s="36" t="s">
+      <c r="I76" s="33" t="s">
         <v>437</v>
       </c>
-      <c r="J76" s="36">
-        <v>1</v>
-      </c>
-      <c r="K76" s="36" t="s">
+      <c r="J76" s="33">
+        <v>1</v>
+      </c>
+      <c r="K76" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L76" s="36">
+      <c r="L76" s="33">
         <v>70</v>
       </c>
-      <c r="M76" s="37" t="s">
+      <c r="M76" s="34" t="s">
         <v>922</v>
       </c>
-      <c r="N76" s="37" t="s">
-        <v>860</v>
-      </c>
-      <c r="O76" s="38"/>
-      <c r="P76" s="36"/>
-      <c r="Q76" s="37"/>
+      <c r="N76" s="34" t="s">
+        <v>898</v>
+      </c>
+      <c r="O76" s="35">
+        <v>1</v>
+      </c>
+      <c r="P76" s="33"/>
+      <c r="Q76" s="34"/>
       <c r="R76" s="13"/>
       <c r="S76" s="2">
         <f t="shared" si="23"/>
@@ -12538,7 +12540,7 @@
       </c>
       <c r="AE76" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF76" s="2">
         <f t="shared" si="19"/>
@@ -12546,7 +12548,7 @@
       </c>
       <c r="AG76" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH76" s="2">
         <f t="shared" si="21"/>
@@ -12568,7 +12570,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20">
         <v>0</v>
       </c>
@@ -12690,7 +12692,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12812,7 +12814,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="20">
         <v>1</v>
       </c>
@@ -12936,7 +12938,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33">
         <v>0</v>
       </c>
@@ -13062,7 +13064,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13190,7 +13192,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13316,7 +13318,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13444,7 +13446,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13570,7 +13572,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13693,7 +13695,7 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="36">
         <v>0</v>
       </c>
@@ -13814,7 +13816,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="36">
         <v>1</v>
       </c>
@@ -13938,7 +13940,7 @@
       <c r="AS87" s="13"/>
       <c r="AT87" s="13"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="33">
         <v>0</v>
       </c>
@@ -14064,7 +14066,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14184,7 +14186,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="33">
         <v>0</v>
       </c>
@@ -14310,7 +14312,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14436,7 +14438,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20">
         <v>0</v>
       </c>
@@ -14558,7 +14560,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="33">
         <v>0</v>
       </c>
@@ -14684,7 +14686,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="33">
         <v>0</v>
       </c>
@@ -14812,7 +14814,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="33">
         <v>1</v>
       </c>
@@ -14940,7 +14942,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15070,7 +15072,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="33">
         <v>0</v>
       </c>
@@ -15196,7 +15198,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33">
         <v>1</v>
       </c>
@@ -15322,7 +15324,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="33">
         <v>0</v>
       </c>
@@ -15448,7 +15450,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15574,7 +15576,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="20">
         <v>0</v>
       </c>
@@ -15696,7 +15698,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="36">
         <v>0</v>
       </c>
@@ -15820,7 +15822,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="36">
         <v>0</v>
       </c>
@@ -15941,7 +15943,7 @@
       <c r="AS103" s="3"/>
       <c r="AT103" s="3"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="36">
         <v>0</v>
       </c>
@@ -16065,7 +16067,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="33">
         <v>0</v>
       </c>
@@ -16193,7 +16195,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16323,7 +16325,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16453,7 +16455,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16581,7 +16583,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16709,7 +16711,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -16831,7 +16833,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="20">
         <v>1</v>
       </c>
@@ -16953,7 +16955,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17075,7 +17077,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="33">
         <v>0</v>
       </c>
@@ -17201,7 +17203,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17329,7 +17331,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="33">
         <v>1</v>
       </c>
@@ -17457,7 +17459,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="20">
         <v>0</v>
       </c>
@@ -17579,7 +17581,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33">
         <v>0</v>
       </c>
@@ -17707,7 +17709,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17835,7 +17837,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="20">
         <v>0</v>
       </c>
@@ -17957,7 +17959,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="33">
         <v>0</v>
       </c>
@@ -18083,7 +18085,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18207,7 +18209,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18335,7 +18337,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18461,7 +18463,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="20">
         <v>0</v>
       </c>
@@ -18583,7 +18585,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18705,7 +18707,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18827,7 +18829,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="20">
         <v>1</v>
       </c>
@@ -18949,7 +18951,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="20">
         <v>0</v>
       </c>
@@ -19071,7 +19073,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19193,7 +19195,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="20">
         <v>1</v>
       </c>
@@ -19315,7 +19317,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="20">
         <v>0</v>
       </c>
@@ -19431,7 +19433,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19559,7 +19561,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="36">
         <v>0</v>
       </c>
@@ -19683,7 +19685,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="20">
         <v>0</v>
       </c>
@@ -19805,7 +19807,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="36">
         <v>0</v>
       </c>
@@ -19929,7 +19931,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="33">
         <v>0</v>
       </c>
@@ -20057,7 +20059,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="30">
         <v>0</v>
       </c>
@@ -20181,7 +20183,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20309,7 +20311,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20437,7 +20439,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20561,7 +20563,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20691,7 +20693,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20819,7 +20821,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="30">
         <v>0</v>
       </c>
@@ -20943,7 +20945,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20">
         <v>0</v>
       </c>
@@ -21065,7 +21067,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="36">
         <v>0</v>
       </c>
@@ -21189,7 +21191,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="20">
         <v>0</v>
       </c>
@@ -21311,7 +21313,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="20">
         <v>0</v>
       </c>
@@ -21433,7 +21435,7 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="33">
         <v>0</v>
       </c>
@@ -21559,7 +21561,7 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="36">
         <v>0</v>
       </c>
@@ -21683,7 +21685,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="20">
         <v>0</v>
       </c>
@@ -21805,7 +21807,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="20">
         <v>1</v>
       </c>
@@ -21927,7 +21929,7 @@
       <c r="AS151" s="13"/>
       <c r="AT151" s="13"/>
     </row>
-    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="20">
         <v>0</v>
       </c>
@@ -22046,7 +22048,7 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="40">
         <v>0</v>
       </c>
@@ -22170,7 +22172,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22288,7 +22290,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="20">
         <v>0</v>
       </c>
@@ -22410,7 +22412,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22534,7 +22536,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="33">
         <v>0</v>
       </c>
@@ -22660,7 +22662,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="20">
         <v>0</v>
       </c>
@@ -22782,7 +22784,7 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="36">
         <v>0</v>
       </c>
@@ -22906,7 +22908,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23028,7 +23030,7 @@
       <c r="AS160" s="13"/>
       <c r="AT160" s="13"/>
     </row>
-    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="33">
         <v>0</v>
       </c>
@@ -23151,7 +23153,7 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="36">
         <v>0</v>
       </c>
@@ -23271,7 +23273,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23393,7 +23395,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23515,7 +23517,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="20">
         <v>0</v>
       </c>
@@ -23637,7 +23639,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="33">
         <v>0</v>
       </c>
@@ -23763,7 +23765,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="20">
         <v>0</v>
       </c>
@@ -23885,7 +23887,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="30">
         <v>0</v>
       </c>
@@ -24009,7 +24011,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="20">
         <v>0</v>
       </c>
@@ -24131,7 +24133,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33">
         <v>0</v>
       </c>
@@ -24259,7 +24261,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24387,7 +24389,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24515,7 +24517,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24643,7 +24645,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="33">
         <v>1</v>
       </c>
@@ -24771,7 +24773,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="36">
         <v>0</v>
       </c>
@@ -24895,7 +24897,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="36">
         <v>1</v>
       </c>
@@ -25019,7 +25021,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25141,7 +25143,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="20">
         <v>0</v>
       </c>
@@ -25263,7 +25265,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="20">
         <v>1</v>
       </c>
@@ -25385,7 +25387,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -25507,7 +25509,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -25629,7 +25631,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25757,7 +25759,7 @@
       <c r="AS182" s="13"/>
       <c r="AT182" s="13"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="33">
         <v>1</v>
       </c>
@@ -25885,7 +25887,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="33">
         <v>0</v>
       </c>
@@ -26010,7 +26012,7 @@
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="36">
         <v>0</v>
       </c>
@@ -26134,7 +26136,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="20">
         <v>0</v>
       </c>
@@ -26256,7 +26258,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26378,7 +26380,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26506,7 +26508,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26628,7 +26630,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="20">
         <v>0</v>
       </c>
@@ -26750,7 +26752,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="20">
         <v>0</v>
       </c>
@@ -26872,7 +26874,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="20">
         <v>1</v>
       </c>
@@ -26994,7 +26996,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="20">
         <v>1</v>
       </c>
@@ -27116,7 +27118,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="33">
         <v>0</v>
       </c>
@@ -27244,7 +27246,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="33">
         <v>1</v>
       </c>
@@ -27372,7 +27374,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27500,7 +27502,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="33">
         <v>0</v>
       </c>
@@ -27628,7 +27630,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="33">
         <v>1</v>
       </c>
@@ -27756,7 +27758,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="20">
         <v>0</v>
       </c>
@@ -27878,7 +27880,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="20">
         <v>1</v>
       </c>
@@ -28000,7 +28002,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="20">
         <v>1</v>
       </c>
@@ -28122,7 +28124,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="20">
         <v>0</v>
       </c>
@@ -28244,7 +28246,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="20">
         <v>1</v>
       </c>
@@ -28366,7 +28368,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28492,7 +28494,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28618,7 +28620,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="20">
         <v>0</v>
       </c>
@@ -28740,7 +28742,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="20">
         <v>1</v>
       </c>
@@ -28862,7 +28864,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -28988,7 +28990,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="33">
         <v>1</v>
       </c>
@@ -29114,7 +29116,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="33">
         <v>0</v>
       </c>
@@ -29242,7 +29244,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="33">
         <v>0</v>
       </c>
@@ -29370,7 +29372,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="20">
         <v>0</v>
       </c>
@@ -29492,7 +29494,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="20">
         <v>0</v>
       </c>
@@ -29614,7 +29616,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29742,7 +29744,7 @@
       <c r="AS214" s="13"/>
       <c r="AT214" s="13"/>
     </row>
-    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29870,7 +29872,7 @@
       <c r="AS215" s="13"/>
       <c r="AT215" s="13"/>
     </row>
-    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="33">
         <v>0</v>
       </c>
@@ -29995,7 +29997,7 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="33">
         <v>1</v>
       </c>
@@ -30120,7 +30122,7 @@
       <c r="AS217" s="3"/>
       <c r="AT217" s="3"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="36">
         <v>0</v>
       </c>
@@ -30244,7 +30246,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="33">
         <v>0</v>
       </c>
@@ -30372,7 +30374,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30420,7 +30422,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30468,7 +30470,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30516,7 +30518,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30564,7 +30566,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30612,7 +30614,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30660,7 +30662,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30708,7 +30710,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30756,7 +30758,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30804,7 +30806,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30852,7 +30854,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30900,7 +30902,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30948,7 +30950,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30996,7 +30998,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -31044,7 +31046,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -31092,7 +31094,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31140,7 +31142,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31188,7 +31190,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31236,7 +31238,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31284,7 +31286,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31332,7 +31334,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31380,7 +31382,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31428,7 +31430,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31476,7 +31478,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31524,7 +31526,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31572,7 +31574,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31620,7 +31622,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31668,7 +31670,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31716,7 +31718,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31764,7 +31766,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31812,7 +31814,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31860,7 +31862,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31908,7 +31910,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31956,7 +31958,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -32004,7 +32006,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -32052,7 +32054,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32100,7 +32102,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32148,7 +32150,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32196,7 +32198,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32244,7 +32246,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32292,7 +32294,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32340,7 +32342,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32388,7 +32390,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32436,7 +32438,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32484,7 +32486,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32532,7 +32534,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32580,7 +32582,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32628,7 +32630,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32676,7 +32678,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32724,7 +32726,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32772,7 +32774,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32820,7 +32822,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32868,7 +32870,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32916,7 +32918,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32964,7 +32966,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -33012,7 +33014,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -33060,7 +33062,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33108,7 +33110,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33156,7 +33158,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33204,7 +33206,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33252,7 +33254,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33300,7 +33302,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33348,7 +33350,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33396,7 +33398,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33444,7 +33446,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33492,7 +33494,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33540,7 +33542,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33588,7 +33590,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33636,7 +33638,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33684,7 +33686,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33732,7 +33734,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33780,7 +33782,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33828,7 +33830,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33876,7 +33878,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33924,7 +33926,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33972,7 +33974,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -34020,7 +34022,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -34068,7 +34070,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34116,7 +34118,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34164,7 +34166,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34212,7 +34214,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34260,7 +34262,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34308,7 +34310,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34356,7 +34358,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34404,7 +34406,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34452,7 +34454,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34500,7 +34502,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34548,7 +34550,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34596,7 +34598,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34644,7 +34646,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34692,7 +34694,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34740,7 +34742,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34788,7 +34790,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34836,7 +34838,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34884,7 +34886,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34932,7 +34934,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34980,7 +34982,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -35028,7 +35030,7 @@
       <c r="AS316" s="13"/>
       <c r="AT316" s="13"/>
     </row>
-    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -35076,7 +35078,7 @@
       <c r="AS317" s="13"/>
       <c r="AT317" s="13"/>
     </row>
-    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F88574A-B3BC-4FFC-B65D-D834EE965808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFACA27-E9A2-4570-A49C-8FE62420D7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3644,47 +3644,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT318"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.109375" style="2"/>
-    <col min="47" max="16384" width="9.109375" style="3"/>
+    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.140625" style="2"/>
+    <col min="47" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3706,7 +3706,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3766,7 +3766,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3838,7 +3838,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3896,7 +3896,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>689</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4145,7 +4145,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>0</v>
       </c>
@@ -4269,7 +4269,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>0</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <v>0</v>
       </c>
@@ -4643,7 +4643,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4895,7 +4895,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -5011,7 +5011,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5133,7 +5133,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5259,7 +5259,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5381,7 +5381,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5503,7 +5503,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5631,7 +5631,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5881,7 +5881,7 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>0</v>
       </c>
@@ -6007,7 +6007,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>0</v>
       </c>
@@ -6133,7 +6133,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <v>0</v>
       </c>
@@ -6257,7 +6257,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>0</v>
       </c>
@@ -6383,7 +6383,7 @@
       <c r="AS26" s="13"/>
       <c r="AT26" s="13"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>0</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6629,7 +6629,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6755,7 +6755,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -7003,7 +7003,7 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>0</v>
       </c>
@@ -7129,7 +7129,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7369,7 +7369,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7491,7 +7491,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
         <v>0</v>
       </c>
@@ -7615,7 +7615,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>0</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="36">
         <v>0</v>
       </c>
@@ -7867,7 +7867,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7989,7 +7989,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="36">
         <v>0</v>
       </c>
@@ -8113,7 +8113,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>0</v>
       </c>
@@ -8239,7 +8239,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>0</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8483,7 +8483,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8605,7 +8605,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8727,7 +8727,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8849,7 +8849,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>0</v>
       </c>
@@ -8975,7 +8975,7 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="36">
         <v>0</v>
       </c>
@@ -9099,7 +9099,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9351,7 +9351,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="36">
         <v>0</v>
       </c>
@@ -9472,7 +9472,7 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>0</v>
       </c>
@@ -9594,7 +9594,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>0</v>
       </c>
@@ -9720,7 +9720,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9846,7 +9846,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>0</v>
       </c>
@@ -9970,7 +9970,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>0</v>
       </c>
@@ -10096,7 +10096,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20">
         <v>0</v>
       </c>
@@ -10218,7 +10218,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>0</v>
       </c>
@@ -10342,7 +10342,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10470,7 +10470,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>0</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>0</v>
       </c>
@@ -10716,7 +10716,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>0</v>
       </c>
@@ -10838,7 +10838,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>1</v>
       </c>
@@ -11204,7 +11204,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>0</v>
       </c>
@@ -11330,7 +11330,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="36">
         <v>0</v>
       </c>
@@ -11454,7 +11454,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="20">
         <v>0</v>
       </c>
@@ -11700,7 +11700,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>0</v>
       </c>
@@ -11824,7 +11824,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="36">
         <v>0</v>
       </c>
@@ -11948,7 +11948,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <v>0</v>
       </c>
@@ -12074,7 +12074,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12200,7 +12200,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20">
         <v>0</v>
       </c>
@@ -12322,7 +12322,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12444,7 +12444,7 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33">
         <v>0</v>
       </c>
@@ -12570,7 +12570,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20">
         <v>0</v>
       </c>
@@ -12692,7 +12692,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12814,7 +12814,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20">
         <v>1</v>
       </c>
@@ -12938,7 +12938,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="33">
         <v>0</v>
       </c>
@@ -13064,7 +13064,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13192,7 +13192,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13318,7 +13318,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13446,7 +13446,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13572,7 +13572,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13695,7 +13695,7 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="36">
         <v>0</v>
       </c>
@@ -13816,7 +13816,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="36">
         <v>1</v>
       </c>
@@ -13940,7 +13940,7 @@
       <c r="AS87" s="13"/>
       <c r="AT87" s="13"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
         <v>0</v>
       </c>
@@ -14066,7 +14066,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14186,7 +14186,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33">
         <v>0</v>
       </c>
@@ -14312,7 +14312,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14438,7 +14438,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20">
         <v>0</v>
       </c>
@@ -14560,7 +14560,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33">
         <v>0</v>
       </c>
@@ -14686,7 +14686,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="33">
         <v>0</v>
       </c>
@@ -14814,7 +14814,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33">
         <v>1</v>
       </c>
@@ -14942,7 +14942,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15072,7 +15072,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33">
         <v>0</v>
       </c>
@@ -15198,7 +15198,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33">
         <v>1</v>
       </c>
@@ -15324,7 +15324,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33">
         <v>0</v>
       </c>
@@ -15450,7 +15450,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15576,7 +15576,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20">
         <v>0</v>
       </c>
@@ -15698,7 +15698,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="36">
         <v>0</v>
       </c>
@@ -15822,7 +15822,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="36">
         <v>0</v>
       </c>
@@ -15943,7 +15943,7 @@
       <c r="AS103" s="3"/>
       <c r="AT103" s="3"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="36">
         <v>0</v>
       </c>
@@ -16067,7 +16067,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33">
         <v>0</v>
       </c>
@@ -16195,7 +16195,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16325,7 +16325,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16455,7 +16455,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16583,7 +16583,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16711,7 +16711,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -16833,7 +16833,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20">
         <v>1</v>
       </c>
@@ -16955,7 +16955,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17077,7 +17077,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33">
         <v>0</v>
       </c>
@@ -17203,7 +17203,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17331,7 +17331,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
         <v>1</v>
       </c>
@@ -17459,7 +17459,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20">
         <v>0</v>
       </c>
@@ -17581,7 +17581,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33">
         <v>0</v>
       </c>
@@ -17709,7 +17709,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17837,7 +17837,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20">
         <v>0</v>
       </c>
@@ -17959,7 +17959,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33">
         <v>0</v>
       </c>
@@ -18085,7 +18085,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18209,7 +18209,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18337,7 +18337,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18463,7 +18463,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="20">
         <v>0</v>
       </c>
@@ -18585,7 +18585,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18707,7 +18707,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18829,7 +18829,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20">
         <v>1</v>
       </c>
@@ -18951,7 +18951,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20">
         <v>0</v>
       </c>
@@ -19073,7 +19073,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19195,7 +19195,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>1</v>
       </c>
@@ -19317,7 +19317,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20">
         <v>0</v>
       </c>
@@ -19433,7 +19433,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19561,7 +19561,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="36">
         <v>0</v>
       </c>
@@ -19685,7 +19685,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="20">
         <v>0</v>
       </c>
@@ -19807,7 +19807,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="36">
         <v>0</v>
       </c>
@@ -19931,7 +19931,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="33">
         <v>0</v>
       </c>
@@ -20059,7 +20059,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="30">
         <v>0</v>
       </c>
@@ -20183,7 +20183,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20311,7 +20311,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20439,7 +20439,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20563,7 +20563,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20693,7 +20693,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20821,7 +20821,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="30">
         <v>0</v>
       </c>
@@ -20945,7 +20945,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20">
         <v>0</v>
       </c>
@@ -21067,7 +21067,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="36">
         <v>0</v>
       </c>
@@ -21191,7 +21191,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20">
         <v>0</v>
       </c>
@@ -21313,7 +21313,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="20">
         <v>0</v>
       </c>
@@ -21435,7 +21435,7 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="33">
         <v>0</v>
       </c>
@@ -21561,52 +21561,54 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="36">
-        <v>0</v>
-      </c>
-      <c r="B149" s="36">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="33">
+        <v>0</v>
+      </c>
+      <c r="B149" s="33">
         <v>2</v>
       </c>
-      <c r="C149" s="36">
+      <c r="C149" s="33">
         <v>4</v>
       </c>
-      <c r="D149" s="37" t="s">
+      <c r="D149" s="34" t="s">
         <v>473</v>
       </c>
-      <c r="E149" s="37" t="s">
+      <c r="E149" s="34" t="s">
         <v>418</v>
       </c>
-      <c r="F149" s="37" t="s">
+      <c r="F149" s="34" t="s">
         <v>474</v>
       </c>
-      <c r="G149" s="37" t="s">
+      <c r="G149" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H149" s="37" t="s">
+      <c r="H149" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I149" s="36" t="s">
+      <c r="I149" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="J149" s="36">
-        <v>1</v>
-      </c>
-      <c r="K149" s="36" t="s">
+      <c r="J149" s="33">
+        <v>1</v>
+      </c>
+      <c r="K149" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L149" s="36" t="s">
+      <c r="L149" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="M149" s="37" t="s">
+      <c r="M149" s="34" t="s">
         <v>521</v>
       </c>
-      <c r="N149" s="37" t="s">
-        <v>858</v>
-      </c>
-      <c r="O149" s="38"/>
-      <c r="P149" s="36"/>
-      <c r="Q149" s="37"/>
+      <c r="N149" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="O149" s="35">
+        <v>1</v>
+      </c>
+      <c r="P149" s="33"/>
+      <c r="Q149" s="34"/>
       <c r="R149" s="13"/>
       <c r="S149" s="2">
         <f t="shared" si="35"/>
@@ -21655,7 +21657,7 @@
       </c>
       <c r="AE149" s="2">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF149" s="2">
         <f t="shared" si="47"/>
@@ -21663,7 +21665,7 @@
       </c>
       <c r="AG149" s="2">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH149" s="2">
         <f t="shared" si="49"/>
@@ -21685,7 +21687,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="20">
         <v>0</v>
       </c>
@@ -21807,7 +21809,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="20">
         <v>1</v>
       </c>
@@ -21929,7 +21931,7 @@
       <c r="AS151" s="13"/>
       <c r="AT151" s="13"/>
     </row>
-    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20">
         <v>0</v>
       </c>
@@ -22048,7 +22050,7 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="40">
         <v>0</v>
       </c>
@@ -22172,7 +22174,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22290,7 +22292,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="20">
         <v>0</v>
       </c>
@@ -22412,7 +22414,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22536,7 +22538,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33">
         <v>0</v>
       </c>
@@ -22662,7 +22664,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20">
         <v>0</v>
       </c>
@@ -22784,7 +22786,7 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="36">
         <v>0</v>
       </c>
@@ -22908,7 +22910,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23030,7 +23032,7 @@
       <c r="AS160" s="13"/>
       <c r="AT160" s="13"/>
     </row>
-    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="33">
         <v>0</v>
       </c>
@@ -23153,7 +23155,7 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="36">
         <v>0</v>
       </c>
@@ -23273,7 +23275,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23395,7 +23397,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23517,7 +23519,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="20">
         <v>0</v>
       </c>
@@ -23639,7 +23641,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="33">
         <v>0</v>
       </c>
@@ -23765,7 +23767,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="20">
         <v>0</v>
       </c>
@@ -23887,7 +23889,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="30">
         <v>0</v>
       </c>
@@ -24011,7 +24013,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="20">
         <v>0</v>
       </c>
@@ -24133,7 +24135,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33">
         <v>0</v>
       </c>
@@ -24261,7 +24263,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24389,7 +24391,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24517,7 +24519,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24645,7 +24647,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="33">
         <v>1</v>
       </c>
@@ -24773,7 +24775,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="36">
         <v>0</v>
       </c>
@@ -24897,7 +24899,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="36">
         <v>1</v>
       </c>
@@ -25021,7 +25023,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25143,7 +25145,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>0</v>
       </c>
@@ -25265,7 +25267,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>1</v>
       </c>
@@ -25387,7 +25389,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="20">
         <v>0</v>
       </c>
@@ -25509,7 +25511,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="20">
         <v>0</v>
       </c>
@@ -25631,7 +25633,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25759,7 +25761,7 @@
       <c r="AS182" s="13"/>
       <c r="AT182" s="13"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="33">
         <v>1</v>
       </c>
@@ -25887,7 +25889,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="33">
         <v>0</v>
       </c>
@@ -26012,7 +26014,7 @@
       <c r="AS184" s="3"/>
       <c r="AT184" s="3"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="36">
         <v>0</v>
       </c>
@@ -26136,7 +26138,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="20">
         <v>0</v>
       </c>
@@ -26258,7 +26260,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26380,7 +26382,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26508,7 +26510,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26630,7 +26632,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20">
         <v>0</v>
       </c>
@@ -26752,7 +26754,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="20">
         <v>0</v>
       </c>
@@ -26874,7 +26876,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="20">
         <v>1</v>
       </c>
@@ -26996,7 +26998,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="20">
         <v>1</v>
       </c>
@@ -27118,7 +27120,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33">
         <v>0</v>
       </c>
@@ -27246,7 +27248,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33">
         <v>1</v>
       </c>
@@ -27374,7 +27376,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27502,7 +27504,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="33">
         <v>0</v>
       </c>
@@ -27630,7 +27632,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="33">
         <v>1</v>
       </c>
@@ -27758,7 +27760,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="20">
         <v>0</v>
       </c>
@@ -27880,7 +27882,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="20">
         <v>1</v>
       </c>
@@ -28002,7 +28004,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="20">
         <v>1</v>
       </c>
@@ -28124,7 +28126,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="20">
         <v>0</v>
       </c>
@@ -28246,7 +28248,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="20">
         <v>1</v>
       </c>
@@ -28368,7 +28370,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28494,7 +28496,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28620,7 +28622,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="20">
         <v>0</v>
       </c>
@@ -28742,7 +28744,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="20">
         <v>1</v>
       </c>
@@ -28864,7 +28866,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -28990,7 +28992,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33">
         <v>1</v>
       </c>
@@ -29116,7 +29118,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="33">
         <v>0</v>
       </c>
@@ -29244,7 +29246,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="33">
         <v>0</v>
       </c>
@@ -29372,7 +29374,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="20">
         <v>0</v>
       </c>
@@ -29494,7 +29496,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="20">
         <v>0</v>
       </c>
@@ -29616,7 +29618,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29744,7 +29746,7 @@
       <c r="AS214" s="13"/>
       <c r="AT214" s="13"/>
     </row>
-    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29872,7 +29874,7 @@
       <c r="AS215" s="13"/>
       <c r="AT215" s="13"/>
     </row>
-    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="33">
         <v>0</v>
       </c>
@@ -29997,7 +29999,7 @@
       <c r="AS216" s="3"/>
       <c r="AT216" s="3"/>
     </row>
-    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33">
         <v>1</v>
       </c>
@@ -30122,7 +30124,7 @@
       <c r="AS217" s="3"/>
       <c r="AT217" s="3"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="36">
         <v>0</v>
       </c>
@@ -30246,7 +30248,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="33">
         <v>0</v>
       </c>
@@ -30374,7 +30376,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30422,7 +30424,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30470,7 +30472,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30518,7 +30520,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30566,7 +30568,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30614,7 +30616,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30662,7 +30664,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30710,7 +30712,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30758,7 +30760,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30806,7 +30808,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30854,7 +30856,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30902,7 +30904,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30950,7 +30952,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30998,7 +31000,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -31046,7 +31048,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -31094,7 +31096,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31142,7 +31144,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31190,7 +31192,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31238,7 +31240,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31286,7 +31288,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31334,7 +31336,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31382,7 +31384,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31430,7 +31432,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31478,7 +31480,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31526,7 +31528,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31574,7 +31576,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31622,7 +31624,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31670,7 +31672,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31718,7 +31720,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31766,7 +31768,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31814,7 +31816,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31862,7 +31864,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31910,7 +31912,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31958,7 +31960,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -32006,7 +32008,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -32054,7 +32056,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32102,7 +32104,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32150,7 +32152,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32198,7 +32200,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32246,7 +32248,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32294,7 +32296,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32342,7 +32344,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32390,7 +32392,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32438,7 +32440,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32486,7 +32488,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32534,7 +32536,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32582,7 +32584,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32630,7 +32632,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32678,7 +32680,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32726,7 +32728,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32774,7 +32776,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32822,7 +32824,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32870,7 +32872,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32918,7 +32920,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32966,7 +32968,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -33014,7 +33016,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -33062,7 +33064,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33110,7 +33112,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33158,7 +33160,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33206,7 +33208,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33254,7 +33256,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33302,7 +33304,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33350,7 +33352,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33398,7 +33400,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33446,7 +33448,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33494,7 +33496,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33542,7 +33544,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33590,7 +33592,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33638,7 +33640,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33686,7 +33688,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33734,7 +33736,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33782,7 +33784,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33830,7 +33832,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33878,7 +33880,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33926,7 +33928,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33974,7 +33976,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -34022,7 +34024,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -34070,7 +34072,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34118,7 +34120,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34166,7 +34168,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34214,7 +34216,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34262,7 +34264,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34310,7 +34312,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34358,7 +34360,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34406,7 +34408,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34454,7 +34456,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34502,7 +34504,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34550,7 +34552,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34598,7 +34600,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34646,7 +34648,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34694,7 +34696,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34742,7 +34744,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34790,7 +34792,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34838,7 +34840,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34886,7 +34888,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34934,7 +34936,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34982,7 +34984,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
@@ -35030,7 +35032,7 @@
       <c r="AS316" s="13"/>
       <c r="AT316" s="13"/>
     </row>
-    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="20"/>
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
@@ -35078,7 +35080,7 @@
       <c r="AS317" s="13"/>
       <c r="AT317" s="13"/>
     </row>
-    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="20"/>
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFACA27-E9A2-4570-A49C-8FE62420D7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1986A4-C4CF-4398-82C7-4CDFD6B94686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -19562,51 +19562,53 @@
       <c r="AT132" s="13"/>
     </row>
     <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="36">
-        <v>0</v>
-      </c>
-      <c r="B133" s="36">
+      <c r="A133" s="33">
+        <v>0</v>
+      </c>
+      <c r="B133" s="33">
         <v>2</v>
       </c>
-      <c r="C133" s="36">
+      <c r="C133" s="33">
         <v>2</v>
       </c>
-      <c r="D133" s="37" t="s">
+      <c r="D133" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="E133" s="37" t="s">
+      <c r="E133" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="F133" s="37" t="s">
+      <c r="F133" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="G133" s="37" t="s">
+      <c r="G133" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H133" s="37" t="s">
+      <c r="H133" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I133" s="36" t="s">
+      <c r="I133" s="33" t="s">
         <v>670</v>
       </c>
-      <c r="J133" s="36">
+      <c r="J133" s="33">
         <v>5</v>
       </c>
-      <c r="K133" s="36" t="s">
+      <c r="K133" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="L133" s="36" t="s">
+      <c r="L133" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="M133" s="37" t="s">
+      <c r="M133" s="34" t="s">
         <v>463</v>
       </c>
-      <c r="N133" s="37" t="s">
-        <v>858</v>
-      </c>
-      <c r="O133" s="38"/>
-      <c r="P133" s="36"/>
-      <c r="Q133" s="37"/>
+      <c r="N133" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="O133" s="35">
+        <v>1</v>
+      </c>
+      <c r="P133" s="33"/>
+      <c r="Q133" s="34"/>
       <c r="R133" s="13"/>
       <c r="S133" s="2">
         <f t="shared" si="35"/>
@@ -19655,7 +19657,7 @@
       </c>
       <c r="AE133" s="2">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF133" s="2">
         <f t="shared" si="19"/>
@@ -19663,7 +19665,7 @@
       </c>
       <c r="AG133" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH133" s="2">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1986A4-C4CF-4398-82C7-4CDFD6B94686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CFA33C-3ECC-42E1-A4B6-7E194A79D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3776,15 +3776,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>623</v>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -15699,51 +15699,53 @@
       <c r="AT101" s="13"/>
     </row>
     <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="36">
-        <v>0</v>
-      </c>
-      <c r="B102" s="36">
-        <v>1</v>
-      </c>
-      <c r="C102" s="36">
+      <c r="A102" s="33">
+        <v>0</v>
+      </c>
+      <c r="B102" s="33">
+        <v>1</v>
+      </c>
+      <c r="C102" s="33">
         <v>7</v>
       </c>
-      <c r="D102" s="37" t="s">
+      <c r="D102" s="34" t="s">
         <v>744</v>
       </c>
-      <c r="E102" s="37" t="s">
+      <c r="E102" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="37" t="s">
+      <c r="F102" s="34" t="s">
         <v>745</v>
       </c>
-      <c r="G102" s="37" t="s">
+      <c r="G102" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H102" s="37" t="s">
+      <c r="H102" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="I102" s="36" t="s">
+      <c r="I102" s="33" t="s">
         <v>746</v>
       </c>
-      <c r="J102" s="36">
+      <c r="J102" s="33">
         <v>3</v>
       </c>
-      <c r="K102" s="36" t="s">
+      <c r="K102" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L102" s="36">
+      <c r="L102" s="33">
         <v>30</v>
       </c>
-      <c r="M102" s="37" t="s">
+      <c r="M102" s="34" t="s">
         <v>812</v>
       </c>
-      <c r="N102" s="37" t="s">
-        <v>859</v>
-      </c>
-      <c r="O102" s="38"/>
-      <c r="P102" s="36"/>
-      <c r="Q102" s="37"/>
+      <c r="N102" s="34" t="s">
+        <v>864</v>
+      </c>
+      <c r="O102" s="35">
+        <v>1</v>
+      </c>
+      <c r="P102" s="33"/>
+      <c r="Q102" s="34"/>
       <c r="R102" s="13"/>
       <c r="S102" s="2">
         <f t="shared" si="23"/>
@@ -15792,7 +15794,7 @@
       </c>
       <c r="AE102" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF102" s="2">
         <f t="shared" si="19"/>
@@ -15800,7 +15802,7 @@
       </c>
       <c r="AG102" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH102" s="2">
         <f t="shared" si="21"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D82E10E-F737-45C2-8C5B-9F5B0AB98F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050A65A3-9344-4648-8849-47412F757322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3722,15 +3722,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3752,15 +3752,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>616</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -15810,52 +15810,55 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="36">
-        <v>0</v>
-      </c>
-      <c r="B103" s="36">
-        <v>1</v>
-      </c>
-      <c r="C103" s="36">
+    <row r="103" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="33">
+        <v>0</v>
+      </c>
+      <c r="B103" s="33">
+        <v>1</v>
+      </c>
+      <c r="C103" s="33">
         <v>7</v>
       </c>
-      <c r="D103" s="37" t="s">
+      <c r="D103" s="34" t="s">
         <v>522</v>
       </c>
-      <c r="E103" s="37" t="s">
+      <c r="E103" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F103" s="37" t="s">
+      <c r="F103" s="34" t="s">
         <v>555</v>
       </c>
-      <c r="G103" s="37" t="s">
+      <c r="G103" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="H103" s="37" t="s">
+      <c r="H103" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I103" s="36" t="s">
+      <c r="I103" s="33" t="s">
         <v>523</v>
       </c>
-      <c r="J103" s="36">
+      <c r="J103" s="33">
         <v>99</v>
       </c>
-      <c r="K103" s="36" t="s">
+      <c r="K103" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L103" s="36" t="s">
+      <c r="L103" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M103" s="37" t="s">
+      <c r="M103" s="34" t="s">
         <v>563</v>
       </c>
-      <c r="N103" s="37" t="s">
-        <v>851</v>
-      </c>
-      <c r="O103" s="38"/>
-      <c r="P103" s="36"/>
-      <c r="Q103" s="37"/>
+      <c r="N103" s="34" t="s">
+        <v>859</v>
+      </c>
+      <c r="O103" s="35">
+        <v>1</v>
+      </c>
+      <c r="P103" s="33"/>
+      <c r="Q103" s="34"/>
+      <c r="R103" s="13"/>
       <c r="S103" s="2">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -15896,13 +15899,14 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" s="2">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE103" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF103" s="2">
         <f t="shared" si="19"/>
@@ -15910,7 +15914,7 @@
       </c>
       <c r="AG103" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH103" s="2">
         <f t="shared" si="21"/>
@@ -15920,16 +15924,17 @@
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="AK103" s="3"/>
-      <c r="AL103" s="3"/>
-      <c r="AM103" s="3"/>
-      <c r="AN103" s="3"/>
-      <c r="AO103" s="3"/>
-      <c r="AP103" s="3"/>
-      <c r="AQ103" s="3"/>
-      <c r="AR103" s="3"/>
-      <c r="AS103" s="3"/>
-      <c r="AT103" s="3"/>
+      <c r="AJ103" s="13"/>
+      <c r="AK103" s="13"/>
+      <c r="AL103" s="13"/>
+      <c r="AM103" s="13"/>
+      <c r="AN103" s="13"/>
+      <c r="AO103" s="13"/>
+      <c r="AP103" s="13"/>
+      <c r="AQ103" s="13"/>
+      <c r="AR103" s="13"/>
+      <c r="AS103" s="13"/>
+      <c r="AT103" s="13"/>
     </row>
     <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="36">

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050A65A3-9344-4648-8849-47412F757322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FED82D-C4EC-423C-9F2B-D7FC3430D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3620,47 +3620,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT316"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.109375" style="2"/>
-    <col min="47" max="16384" width="9.109375" style="3"/>
+    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.140625" style="2"/>
+    <col min="47" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3722,15 +3722,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3742,7 +3742,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3752,15 +3752,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>616</v>
@@ -3814,7 +3814,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3872,7 +3872,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>682</v>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4121,7 +4121,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>0</v>
       </c>
@@ -4249,7 +4249,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4375,7 +4375,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>0</v>
       </c>
@@ -4501,7 +4501,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>0</v>
       </c>
@@ -4623,7 +4623,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4751,7 +4751,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4875,7 +4875,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -4991,7 +4991,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5113,7 +5113,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5239,7 +5239,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5483,7 +5483,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5733,7 +5733,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5861,7 +5861,7 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>0</v>
       </c>
@@ -5987,7 +5987,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>0</v>
       </c>
@@ -6113,7 +6113,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>0</v>
       </c>
@@ -6239,7 +6239,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>0</v>
       </c>
@@ -6365,7 +6365,7 @@
       <c r="AS26" s="13"/>
       <c r="AT26" s="13"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>0</v>
       </c>
@@ -6493,7 +6493,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6615,7 +6615,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6741,7 +6741,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -6989,7 +6989,7 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>0</v>
       </c>
@@ -7115,7 +7115,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7235,7 +7235,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7355,7 +7355,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7477,7 +7477,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
         <v>0</v>
       </c>
@@ -7601,7 +7601,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>0</v>
       </c>
@@ -7729,7 +7729,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="36">
         <v>0</v>
       </c>
@@ -7853,7 +7853,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>0</v>
       </c>
@@ -7975,7 +7975,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="36">
         <v>0</v>
       </c>
@@ -8099,7 +8099,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>0</v>
       </c>
@@ -8225,7 +8225,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>0</v>
       </c>
@@ -8347,7 +8347,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8469,7 +8469,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8591,7 +8591,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8713,7 +8713,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8835,7 +8835,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>0</v>
       </c>
@@ -8961,52 +8961,54 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36">
-        <v>0</v>
-      </c>
-      <c r="B48" s="36">
-        <v>1</v>
-      </c>
-      <c r="C48" s="36">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="33">
+        <v>0</v>
+      </c>
+      <c r="B48" s="33">
+        <v>1</v>
+      </c>
+      <c r="C48" s="33">
         <v>3</v>
       </c>
-      <c r="D48" s="37" t="s">
+      <c r="D48" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E48" s="37" t="s">
+      <c r="E48" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="F48" s="37" t="s">
+      <c r="F48" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="G48" s="37" t="s">
+      <c r="G48" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="37" t="s">
+      <c r="H48" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I48" s="36" t="s">
+      <c r="I48" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="J48" s="36">
+      <c r="J48" s="33">
         <v>2</v>
       </c>
-      <c r="K48" s="36" t="s">
+      <c r="K48" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="L48" s="36" t="s">
+      <c r="L48" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="M48" s="37" t="s">
+      <c r="M48" s="34" t="s">
         <v>679</v>
       </c>
-      <c r="N48" s="37" t="s">
-        <v>851</v>
-      </c>
-      <c r="O48" s="38"/>
-      <c r="P48" s="36"/>
-      <c r="Q48" s="37"/>
+      <c r="N48" s="34" t="s">
+        <v>859</v>
+      </c>
+      <c r="O48" s="35">
+        <v>1</v>
+      </c>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="34"/>
       <c r="R48" s="13"/>
       <c r="S48" s="2">
         <f t="shared" si="7"/>
@@ -9055,7 +9057,7 @@
       </c>
       <c r="AE48" s="2">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF48" s="2">
         <f t="shared" si="3"/>
@@ -9063,7 +9065,7 @@
       </c>
       <c r="AG48" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" s="2">
         <f t="shared" si="5"/>
@@ -9085,7 +9087,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9211,7 +9213,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9337,7 +9339,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="36">
         <v>0</v>
       </c>
@@ -9458,7 +9460,7 @@
       <c r="AS51" s="3"/>
       <c r="AT51" s="3"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>0</v>
       </c>
@@ -9580,7 +9582,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>0</v>
       </c>
@@ -9706,7 +9708,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9832,7 +9834,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>0</v>
       </c>
@@ -9956,7 +9958,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>0</v>
       </c>
@@ -10082,7 +10084,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20">
         <v>0</v>
       </c>
@@ -10204,7 +10206,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>0</v>
       </c>
@@ -10328,7 +10330,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10456,7 +10458,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>0</v>
       </c>
@@ -10578,7 +10580,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>0</v>
       </c>
@@ -10702,7 +10704,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20">
         <v>0</v>
       </c>
@@ -10824,7 +10826,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10946,7 +10948,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11068,7 +11070,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>1</v>
       </c>
@@ -11190,7 +11192,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>0</v>
       </c>
@@ -11316,7 +11318,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="36">
         <v>0</v>
       </c>
@@ -11440,7 +11442,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11564,7 +11566,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="20">
         <v>0</v>
       </c>
@@ -11686,7 +11688,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <v>0</v>
       </c>
@@ -11810,7 +11812,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="36">
         <v>0</v>
       </c>
@@ -11934,7 +11936,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <v>0</v>
       </c>
@@ -12060,7 +12062,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12186,7 +12188,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20">
         <v>0</v>
       </c>
@@ -12308,7 +12310,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12430,7 +12432,7 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33">
         <v>0</v>
       </c>
@@ -12556,7 +12558,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20">
         <v>0</v>
       </c>
@@ -12678,7 +12680,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12800,7 +12802,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20">
         <v>1</v>
       </c>
@@ -12924,7 +12926,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="33">
         <v>0</v>
       </c>
@@ -13050,7 +13052,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13178,7 +13180,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13304,7 +13306,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13432,7 +13434,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13558,7 +13560,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13681,7 +13683,7 @@
       <c r="AS85" s="3"/>
       <c r="AT85" s="3"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="36">
         <v>0</v>
       </c>
@@ -13802,7 +13804,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="36">
         <v>1</v>
       </c>
@@ -13926,7 +13928,7 @@
       <c r="AS87" s="13"/>
       <c r="AT87" s="13"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
         <v>0</v>
       </c>
@@ -14052,7 +14054,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14172,7 +14174,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33">
         <v>0</v>
       </c>
@@ -14298,7 +14300,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14424,7 +14426,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20">
         <v>0</v>
       </c>
@@ -14546,7 +14548,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33">
         <v>0</v>
       </c>
@@ -14672,7 +14674,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="33">
         <v>0</v>
       </c>
@@ -14800,7 +14802,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33">
         <v>1</v>
       </c>
@@ -14928,7 +14930,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15058,7 +15060,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33">
         <v>0</v>
       </c>
@@ -15184,7 +15186,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33">
         <v>1</v>
       </c>
@@ -15310,7 +15312,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33">
         <v>0</v>
       </c>
@@ -15436,7 +15438,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15562,7 +15564,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20">
         <v>0</v>
       </c>
@@ -15684,7 +15686,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="33">
         <v>0</v>
       </c>
@@ -15810,7 +15812,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33">
         <v>0</v>
       </c>
@@ -15936,7 +15938,7 @@
       <c r="AS103" s="13"/>
       <c r="AT103" s="13"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="36">
         <v>0</v>
       </c>
@@ -16060,7 +16062,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33">
         <v>0</v>
       </c>
@@ -16188,7 +16190,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16318,7 +16320,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16448,7 +16450,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16576,7 +16578,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16704,7 +16706,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20">
         <v>0</v>
       </c>
@@ -16826,7 +16828,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20">
         <v>1</v>
       </c>
@@ -16948,7 +16950,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17070,7 +17072,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33">
         <v>0</v>
       </c>
@@ -17196,7 +17198,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17324,7 +17326,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
         <v>1</v>
       </c>
@@ -17452,7 +17454,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20">
         <v>0</v>
       </c>
@@ -17574,7 +17576,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33">
         <v>0</v>
       </c>
@@ -17702,7 +17704,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17830,7 +17832,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20">
         <v>0</v>
       </c>
@@ -17952,7 +17954,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33">
         <v>0</v>
       </c>
@@ -18078,7 +18080,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18202,7 +18204,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18330,7 +18332,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18456,7 +18458,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="20">
         <v>0</v>
       </c>
@@ -18578,7 +18580,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18700,7 +18702,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18822,7 +18824,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20">
         <v>1</v>
       </c>
@@ -18944,7 +18946,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20">
         <v>0</v>
       </c>
@@ -19066,7 +19068,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19188,7 +19190,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>1</v>
       </c>
@@ -19310,7 +19312,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="33">
         <v>0</v>
       </c>
@@ -19432,7 +19434,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19560,7 +19562,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="33">
         <v>0</v>
       </c>
@@ -19686,7 +19688,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="20">
         <v>0</v>
       </c>
@@ -19808,7 +19810,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="36">
         <v>0</v>
       </c>
@@ -19932,7 +19934,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="33">
         <v>0</v>
       </c>
@@ -20060,7 +20062,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="33">
         <v>0</v>
       </c>
@@ -20188,7 +20190,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20316,7 +20318,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20444,7 +20446,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20568,7 +20570,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20698,7 +20700,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20826,7 +20828,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="30">
         <v>0</v>
       </c>
@@ -20950,7 +20952,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20">
         <v>0</v>
       </c>
@@ -21072,7 +21074,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="36">
         <v>0</v>
       </c>
@@ -21196,7 +21198,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20">
         <v>0</v>
       </c>
@@ -21318,7 +21320,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="33">
         <v>0</v>
       </c>
@@ -21444,7 +21446,7 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="33">
         <v>0</v>
       </c>
@@ -21570,7 +21572,7 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="33">
         <v>0</v>
       </c>
@@ -21698,7 +21700,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33">
         <v>1</v>
       </c>
@@ -21826,7 +21828,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="20">
         <v>0</v>
       </c>
@@ -21945,7 +21947,7 @@
       <c r="AS151" s="3"/>
       <c r="AT151" s="3"/>
     </row>
-    <row r="152" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="39">
         <v>0</v>
       </c>
@@ -22069,7 +22071,7 @@
       <c r="AS152" s="13"/>
       <c r="AT152" s="13"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="20">
         <v>0</v>
       </c>
@@ -22187,7 +22189,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22309,7 +22311,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="33">
         <v>0</v>
       </c>
@@ -22433,7 +22435,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22559,7 +22561,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="20">
         <v>0</v>
       </c>
@@ -22681,7 +22683,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="36">
         <v>0</v>
       </c>
@@ -22805,7 +22807,7 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="33">
         <v>0</v>
       </c>
@@ -22927,7 +22929,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23050,7 +23052,7 @@
       <c r="AS160" s="3"/>
       <c r="AT160" s="3"/>
     </row>
-    <row r="161" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="36">
         <v>0</v>
       </c>
@@ -23170,7 +23172,7 @@
       <c r="AS161" s="13"/>
       <c r="AT161" s="13"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20">
         <v>0</v>
       </c>
@@ -23292,7 +23294,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23414,7 +23416,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23536,7 +23538,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="33">
         <v>0</v>
       </c>
@@ -23662,7 +23664,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="20">
         <v>0</v>
       </c>
@@ -23784,7 +23786,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33">
         <v>0</v>
       </c>
@@ -23912,7 +23914,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20">
         <v>0</v>
       </c>
@@ -24034,7 +24036,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="33">
         <v>0</v>
       </c>
@@ -24162,7 +24164,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33">
         <v>1</v>
       </c>
@@ -24290,7 +24292,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24418,7 +24420,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24546,7 +24548,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24674,7 +24676,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="36">
         <v>0</v>
       </c>
@@ -24798,7 +24800,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="36">
         <v>1</v>
       </c>
@@ -24922,7 +24924,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20">
         <v>0</v>
       </c>
@@ -25044,7 +25046,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25166,7 +25168,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>1</v>
       </c>
@@ -25288,7 +25290,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>0</v>
       </c>
@@ -25410,7 +25412,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="33">
         <v>0</v>
       </c>
@@ -25538,7 +25540,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33">
         <v>1</v>
       </c>
@@ -25666,7 +25668,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25791,7 +25793,7 @@
       <c r="AS182" s="3"/>
       <c r="AT182" s="3"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="36">
         <v>0</v>
       </c>
@@ -25915,7 +25917,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20">
         <v>0</v>
       </c>
@@ -26037,7 +26039,7 @@
       <c r="AS184" s="13"/>
       <c r="AT184" s="13"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="20">
         <v>0</v>
       </c>
@@ -26159,7 +26161,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33">
         <v>0</v>
       </c>
@@ -26287,7 +26289,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26409,7 +26411,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26537,7 +26539,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26659,7 +26661,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20">
         <v>1</v>
       </c>
@@ -26781,7 +26783,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="20">
         <v>1</v>
       </c>
@@ -26903,7 +26905,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="33">
         <v>0</v>
       </c>
@@ -27031,7 +27033,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="33">
         <v>1</v>
       </c>
@@ -27159,7 +27161,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33">
         <v>1</v>
       </c>
@@ -27287,7 +27289,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33">
         <v>0</v>
       </c>
@@ -27415,7 +27417,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27543,7 +27545,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="20">
         <v>0</v>
       </c>
@@ -27665,7 +27667,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20">
         <v>1</v>
       </c>
@@ -27787,7 +27789,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="20">
         <v>1</v>
       </c>
@@ -27909,7 +27911,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="33">
         <v>0</v>
       </c>
@@ -28037,7 +28039,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="33">
         <v>1</v>
       </c>
@@ -28165,7 +28167,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="33">
         <v>0</v>
       </c>
@@ -28291,7 +28293,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="33">
         <v>1</v>
       </c>
@@ -28417,7 +28419,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28545,7 +28547,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28673,7 +28675,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="33">
         <v>0</v>
       </c>
@@ -28799,7 +28801,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="33">
         <v>1</v>
       </c>
@@ -28925,7 +28927,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -29053,7 +29055,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33">
         <v>0</v>
       </c>
@@ -29181,7 +29183,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="20">
         <v>0</v>
       </c>
@@ -29303,7 +29305,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="20">
         <v>0</v>
       </c>
@@ -29425,7 +29427,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="33">
         <v>0</v>
       </c>
@@ -29553,7 +29555,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="33">
         <v>1</v>
       </c>
@@ -29681,7 +29683,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29806,7 +29808,7 @@
       <c r="AS214" s="3"/>
       <c r="AT214" s="3"/>
     </row>
-    <row r="215" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29931,7 +29933,7 @@
       <c r="AS215" s="3"/>
       <c r="AT215" s="3"/>
     </row>
-    <row r="216" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="36">
         <v>0</v>
       </c>
@@ -30055,7 +30057,7 @@
       <c r="AS216" s="13"/>
       <c r="AT216" s="13"/>
     </row>
-    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33">
         <v>0</v>
       </c>
@@ -30183,7 +30185,7 @@
       <c r="AS217" s="13"/>
       <c r="AT217" s="13"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20"/>
       <c r="B218" s="20"/>
       <c r="C218" s="20"/>
@@ -30231,7 +30233,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="20"/>
       <c r="B219" s="20"/>
       <c r="C219" s="20"/>
@@ -30279,7 +30281,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30327,7 +30329,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30375,7 +30377,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30423,7 +30425,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30471,7 +30473,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30519,7 +30521,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30567,7 +30569,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30615,7 +30617,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30663,7 +30665,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30711,7 +30713,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30759,7 +30761,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30807,7 +30809,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30855,7 +30857,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30903,7 +30905,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -30951,7 +30953,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -30999,7 +31001,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31047,7 +31049,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31095,7 +31097,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31143,7 +31145,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31191,7 +31193,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31239,7 +31241,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31287,7 +31289,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31335,7 +31337,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31383,7 +31385,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31431,7 +31433,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31479,7 +31481,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31527,7 +31529,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31575,7 +31577,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31623,7 +31625,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31671,7 +31673,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31719,7 +31721,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31767,7 +31769,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31815,7 +31817,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31863,7 +31865,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -31911,7 +31913,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -31959,7 +31961,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32007,7 +32009,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32055,7 +32057,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32103,7 +32105,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32151,7 +32153,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32199,7 +32201,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32247,7 +32249,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32295,7 +32297,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32343,7 +32345,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32391,7 +32393,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32439,7 +32441,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32487,7 +32489,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32535,7 +32537,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32583,7 +32585,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32631,7 +32633,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32679,7 +32681,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32727,7 +32729,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32775,7 +32777,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32823,7 +32825,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32871,7 +32873,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -32919,7 +32921,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -32967,7 +32969,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33015,7 +33017,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33063,7 +33065,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33111,7 +33113,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33159,7 +33161,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33207,7 +33209,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33255,7 +33257,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33303,7 +33305,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33351,7 +33353,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33399,7 +33401,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33447,7 +33449,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33495,7 +33497,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33543,7 +33545,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33591,7 +33593,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33639,7 +33641,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33687,7 +33689,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33735,7 +33737,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33783,7 +33785,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33831,7 +33833,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33879,7 +33881,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -33927,7 +33929,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -33975,7 +33977,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34023,7 +34025,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34071,7 +34073,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34119,7 +34121,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34167,7 +34169,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34215,7 +34217,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34263,7 +34265,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34311,7 +34313,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34359,7 +34361,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34407,7 +34409,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34455,7 +34457,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34503,7 +34505,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34551,7 +34553,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34599,7 +34601,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34647,7 +34649,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34695,7 +34697,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34743,7 +34745,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34791,7 +34793,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34839,7 +34841,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34887,7 +34889,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB34BB01-DD21-4E34-A63F-DAB5CFCF7DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED3CB36-F8E6-449A-9541-A160541FB8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
   <sheets>
     <sheet name="Tavole e pause golose" sheetId="6" r:id="rId1"/>
@@ -3623,47 +3623,47 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT316"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.88671875" style="15" customWidth="1"/>
-    <col min="13" max="13" width="28.5546875" style="16" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="16" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="15" customWidth="1"/>
+    <col min="13" max="13" width="28.5703125" style="16" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" style="16" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="7" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" customWidth="1"/>
-    <col min="22" max="27" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" style="2" customWidth="1"/>
+    <col min="22" max="27" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="2" customWidth="1"/>
-    <col min="30" max="30" width="21.88671875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="27.33203125" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="19.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="15.109375" style="2" customWidth="1"/>
-    <col min="35" max="35" width="18.109375" style="2" customWidth="1"/>
-    <col min="36" max="46" width="9.109375" style="2"/>
-    <col min="47" max="16384" width="9.109375" style="3"/>
+    <col min="30" max="30" width="21.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="27.28515625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" style="2" customWidth="1"/>
+    <col min="36" max="46" width="9.140625" style="2"/>
+    <col min="47" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
@@ -3685,7 +3685,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
@@ -3725,15 +3725,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3745,7 +3745,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="12" t="s">
         <v>12</v>
       </c>
@@ -3755,15 +3755,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>616</v>
@@ -3817,7 +3817,7 @@
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
     </row>
-    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="2"/>
       <c r="F6" s="2"/>
       <c r="S6" s="2" t="s">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3875,7 +3875,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>682</v>
       </c>
@@ -3998,7 +3998,7 @@
       <c r="AS7" s="25"/>
       <c r="AT7" s="25"/>
     </row>
-    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>0</v>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
     </row>
-    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>0</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
     </row>
-    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>0</v>
       </c>
@@ -4378,7 +4378,7 @@
       <c r="AS10" s="13"/>
       <c r="AT10" s="13"/>
     </row>
-    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>0</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="AS11" s="13"/>
       <c r="AT11" s="13"/>
     </row>
-    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>0</v>
       </c>
@@ -4626,7 +4626,7 @@
       <c r="AS12" s="13"/>
       <c r="AT12" s="13"/>
     </row>
-    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>0</v>
       </c>
@@ -4754,7 +4754,7 @@
       <c r="AS13" s="13"/>
       <c r="AT13" s="13"/>
     </row>
-    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>0</v>
       </c>
@@ -4878,7 +4878,7 @@
       <c r="AS14" s="13"/>
       <c r="AT14" s="13"/>
     </row>
-    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>0</v>
       </c>
@@ -4994,7 +4994,7 @@
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
     </row>
-    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>0</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="AS16" s="13"/>
       <c r="AT16" s="13"/>
     </row>
-    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>0</v>
       </c>
@@ -5242,7 +5242,7 @@
       <c r="AS17" s="13"/>
       <c r="AT17" s="13"/>
     </row>
-    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>0</v>
       </c>
@@ -5364,7 +5364,7 @@
       <c r="AS18" s="13"/>
       <c r="AT18" s="13"/>
     </row>
-    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>0</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="AS19" s="13"/>
       <c r="AT19" s="13"/>
     </row>
-    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>0</v>
       </c>
@@ -5614,7 +5614,7 @@
       <c r="AS20" s="13"/>
       <c r="AT20" s="13"/>
     </row>
-    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>0</v>
       </c>
@@ -5736,7 +5736,7 @@
       <c r="AS21" s="13"/>
       <c r="AT21" s="13"/>
     </row>
-    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>0</v>
       </c>
@@ -5864,7 +5864,7 @@
       <c r="AS22" s="13"/>
       <c r="AT22" s="13"/>
     </row>
-    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>0</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="AS23" s="13"/>
       <c r="AT23" s="13"/>
     </row>
-    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>0</v>
       </c>
@@ -6116,7 +6116,7 @@
       <c r="AS24" s="13"/>
       <c r="AT24" s="13"/>
     </row>
-    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>0</v>
       </c>
@@ -6242,7 +6242,7 @@
       <c r="AS25" s="13"/>
       <c r="AT25" s="13"/>
     </row>
-    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>0</v>
       </c>
@@ -6368,7 +6368,7 @@
       <c r="AS26" s="13"/>
       <c r="AT26" s="13"/>
     </row>
-    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>0</v>
       </c>
@@ -6496,7 +6496,7 @@
       <c r="AS27" s="13"/>
       <c r="AT27" s="13"/>
     </row>
-    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>0</v>
       </c>
@@ -6618,7 +6618,7 @@
       <c r="AS28" s="13"/>
       <c r="AT28" s="13"/>
     </row>
-    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>0</v>
       </c>
@@ -6744,7 +6744,7 @@
       <c r="AS29" s="13"/>
       <c r="AT29" s="13"/>
     </row>
-    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>0</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="AS30" s="13"/>
       <c r="AT30" s="13"/>
     </row>
-    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>0</v>
       </c>
@@ -6992,7 +6992,7 @@
       <c r="AS31" s="13"/>
       <c r="AT31" s="13"/>
     </row>
-    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>0</v>
       </c>
@@ -7118,7 +7118,7 @@
       <c r="AS32" s="13"/>
       <c r="AT32" s="13"/>
     </row>
-    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>0</v>
       </c>
@@ -7238,7 +7238,7 @@
       <c r="AS33" s="13"/>
       <c r="AT33" s="13"/>
     </row>
-    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>0</v>
       </c>
@@ -7358,7 +7358,7 @@
       <c r="AS34" s="13"/>
       <c r="AT34" s="13"/>
     </row>
-    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>0</v>
       </c>
@@ -7480,7 +7480,7 @@
       <c r="AS35" s="13"/>
       <c r="AT35" s="13"/>
     </row>
-    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>0</v>
       </c>
@@ -7606,7 +7606,7 @@
       <c r="AS36" s="13"/>
       <c r="AT36" s="13"/>
     </row>
-    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="36">
         <v>0</v>
       </c>
@@ -7730,7 +7730,7 @@
       <c r="AS37" s="13"/>
       <c r="AT37" s="13"/>
     </row>
-    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>0</v>
       </c>
@@ -7858,7 +7858,7 @@
       <c r="AS38" s="13"/>
       <c r="AT38" s="13"/>
     </row>
-    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="36">
         <v>0</v>
       </c>
@@ -7982,7 +7982,7 @@
       <c r="AS39" s="13"/>
       <c r="AT39" s="13"/>
     </row>
-    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>0</v>
       </c>
@@ -8104,7 +8104,7 @@
       <c r="AS40" s="13"/>
       <c r="AT40" s="13"/>
     </row>
-    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="36">
         <v>0</v>
       </c>
@@ -8228,7 +8228,7 @@
       <c r="AS41" s="13"/>
       <c r="AT41" s="13"/>
     </row>
-    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>0</v>
       </c>
@@ -8354,7 +8354,7 @@
       <c r="AS42" s="13"/>
       <c r="AT42" s="13"/>
     </row>
-    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>0</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="AS43" s="13"/>
       <c r="AT43" s="13"/>
     </row>
-    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>0</v>
       </c>
@@ -8598,7 +8598,7 @@
       <c r="AS44" s="13"/>
       <c r="AT44" s="13"/>
     </row>
-    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20">
         <v>0</v>
       </c>
@@ -8720,7 +8720,7 @@
       <c r="AS45" s="13"/>
       <c r="AT45" s="13"/>
     </row>
-    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>0</v>
       </c>
@@ -8842,7 +8842,7 @@
       <c r="AS46" s="13"/>
       <c r="AT46" s="13"/>
     </row>
-    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20">
         <v>0</v>
       </c>
@@ -8964,7 +8964,7 @@
       <c r="AS47" s="13"/>
       <c r="AT47" s="13"/>
     </row>
-    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>0</v>
       </c>
@@ -9090,7 +9090,7 @@
       <c r="AS48" s="13"/>
       <c r="AT48" s="13"/>
     </row>
-    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>0</v>
       </c>
@@ -9216,7 +9216,7 @@
       <c r="AS49" s="13"/>
       <c r="AT49" s="13"/>
     </row>
-    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>0</v>
       </c>
@@ -9342,7 +9342,7 @@
       <c r="AS50" s="13"/>
       <c r="AT50" s="13"/>
     </row>
-    <row r="51" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="33">
         <v>0</v>
       </c>
@@ -9468,7 +9468,7 @@
       <c r="AS51" s="13"/>
       <c r="AT51" s="13"/>
     </row>
-    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
         <v>0</v>
       </c>
@@ -9594,7 +9594,7 @@
       <c r="AS52" s="13"/>
       <c r="AT52" s="13"/>
     </row>
-    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20">
         <v>0</v>
       </c>
@@ -9716,7 +9716,7 @@
       <c r="AS53" s="13"/>
       <c r="AT53" s="13"/>
     </row>
-    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>0</v>
       </c>
@@ -9842,7 +9842,7 @@
       <c r="AS54" s="13"/>
       <c r="AT54" s="13"/>
     </row>
-    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>0</v>
       </c>
@@ -9968,7 +9968,7 @@
       <c r="AS55" s="13"/>
       <c r="AT55" s="13"/>
     </row>
-    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>0</v>
       </c>
@@ -10092,7 +10092,7 @@
       <c r="AS56" s="13"/>
       <c r="AT56" s="13"/>
     </row>
-    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
         <v>0</v>
       </c>
@@ -10218,7 +10218,7 @@
       <c r="AS57" s="13"/>
       <c r="AT57" s="13"/>
     </row>
-    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>0</v>
       </c>
@@ -10340,7 +10340,7 @@
       <c r="AS58" s="13"/>
       <c r="AT58" s="13"/>
     </row>
-    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>0</v>
       </c>
@@ -10464,7 +10464,7 @@
       <c r="AS59" s="13"/>
       <c r="AT59" s="13"/>
     </row>
-    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="33">
         <v>0</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="AS60" s="13"/>
       <c r="AT60" s="13"/>
     </row>
-    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20">
         <v>0</v>
       </c>
@@ -10714,7 +10714,7 @@
       <c r="AS61" s="13"/>
       <c r="AT61" s="13"/>
     </row>
-    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="33">
         <v>0</v>
       </c>
@@ -10838,7 +10838,7 @@
       <c r="AS62" s="13"/>
       <c r="AT62" s="13"/>
     </row>
-    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
         <v>0</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="AS63" s="13"/>
       <c r="AT63" s="13"/>
     </row>
-    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>0</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="AS64" s="13"/>
       <c r="AT64" s="13"/>
     </row>
-    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>0</v>
       </c>
@@ -11204,7 +11204,7 @@
       <c r="AS65" s="13"/>
       <c r="AT65" s="13"/>
     </row>
-    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="20">
         <v>1</v>
       </c>
@@ -11326,7 +11326,7 @@
       <c r="AS66" s="13"/>
       <c r="AT66" s="13"/>
     </row>
-    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="33">
         <v>0</v>
       </c>
@@ -11452,7 +11452,7 @@
       <c r="AS67" s="13"/>
       <c r="AT67" s="13"/>
     </row>
-    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="36">
         <v>0</v>
       </c>
@@ -11576,7 +11576,7 @@
       <c r="AS68" s="13"/>
       <c r="AT68" s="13"/>
     </row>
-    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="36">
         <v>0</v>
       </c>
@@ -11700,7 +11700,7 @@
       <c r="AS69" s="13"/>
       <c r="AT69" s="13"/>
     </row>
-    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="20">
         <v>0</v>
       </c>
@@ -11822,7 +11822,7 @@
       <c r="AS70" s="13"/>
       <c r="AT70" s="13"/>
     </row>
-    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="33">
         <v>0</v>
       </c>
@@ -11946,7 +11946,7 @@
       <c r="AS71" s="13"/>
       <c r="AT71" s="13"/>
     </row>
-    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="36">
         <v>0</v>
       </c>
@@ -12070,7 +12070,7 @@
       <c r="AS72" s="13"/>
       <c r="AT72" s="13"/>
     </row>
-    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <v>0</v>
       </c>
@@ -12196,7 +12196,7 @@
       <c r="AS73" s="13"/>
       <c r="AT73" s="13"/>
     </row>
-    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="33">
         <v>0</v>
       </c>
@@ -12322,7 +12322,7 @@
       <c r="AS74" s="13"/>
       <c r="AT74" s="13"/>
     </row>
-    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20">
         <v>0</v>
       </c>
@@ -12444,7 +12444,7 @@
       <c r="AS75" s="13"/>
       <c r="AT75" s="13"/>
     </row>
-    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="20">
         <v>0</v>
       </c>
@@ -12566,7 +12566,7 @@
       <c r="AS76" s="13"/>
       <c r="AT76" s="13"/>
     </row>
-    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33">
         <v>0</v>
       </c>
@@ -12692,7 +12692,7 @@
       <c r="AS77" s="13"/>
       <c r="AT77" s="13"/>
     </row>
-    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>0</v>
       </c>
@@ -12814,7 +12814,7 @@
       <c r="AS78" s="13"/>
       <c r="AT78" s="13"/>
     </row>
-    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20">
         <v>0</v>
       </c>
@@ -12936,7 +12936,7 @@
       <c r="AS79" s="13"/>
       <c r="AT79" s="13"/>
     </row>
-    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="20">
         <v>1</v>
       </c>
@@ -13060,7 +13060,7 @@
       <c r="AS80" s="13"/>
       <c r="AT80" s="13"/>
     </row>
-    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <v>0</v>
       </c>
@@ -13186,7 +13186,7 @@
       <c r="AS81" s="13"/>
       <c r="AT81" s="13"/>
     </row>
-    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <v>0</v>
       </c>
@@ -13314,7 +13314,7 @@
       <c r="AS82" s="13"/>
       <c r="AT82" s="13"/>
     </row>
-    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <v>0</v>
       </c>
@@ -13440,7 +13440,7 @@
       <c r="AS83" s="13"/>
       <c r="AT83" s="13"/>
     </row>
-    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <v>0</v>
       </c>
@@ -13568,7 +13568,7 @@
       <c r="AS84" s="13"/>
       <c r="AT84" s="13"/>
     </row>
-    <row r="85" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <v>0</v>
       </c>
@@ -13694,7 +13694,7 @@
       <c r="AS85" s="13"/>
       <c r="AT85" s="13"/>
     </row>
-    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33">
         <v>0</v>
       </c>
@@ -13817,7 +13817,7 @@
       <c r="AS86" s="3"/>
       <c r="AT86" s="3"/>
     </row>
-    <row r="87" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="36">
         <v>0</v>
       </c>
@@ -13938,7 +13938,7 @@
       <c r="AS87" s="3"/>
       <c r="AT87" s="3"/>
     </row>
-    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="36">
         <v>1</v>
       </c>
@@ -14062,7 +14062,7 @@
       <c r="AS88" s="13"/>
       <c r="AT88" s="13"/>
     </row>
-    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33">
         <v>0</v>
       </c>
@@ -14188,7 +14188,7 @@
       <c r="AS89" s="13"/>
       <c r="AT89" s="13"/>
     </row>
-    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33">
         <v>0</v>
       </c>
@@ -14308,7 +14308,7 @@
       <c r="AS90" s="13"/>
       <c r="AT90" s="13"/>
     </row>
-    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>0</v>
       </c>
@@ -14434,7 +14434,7 @@
       <c r="AS91" s="13"/>
       <c r="AT91" s="13"/>
     </row>
-    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="33">
         <v>0</v>
       </c>
@@ -14560,7 +14560,7 @@
       <c r="AS92" s="13"/>
       <c r="AT92" s="13"/>
     </row>
-    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="20">
         <v>0</v>
       </c>
@@ -14682,7 +14682,7 @@
       <c r="AS93" s="13"/>
       <c r="AT93" s="13"/>
     </row>
-    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="39">
         <v>0</v>
       </c>
@@ -14808,7 +14808,7 @@
       <c r="AS94" s="13"/>
       <c r="AT94" s="13"/>
     </row>
-    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33">
         <v>0</v>
       </c>
@@ -14936,7 +14936,7 @@
       <c r="AS95" s="13"/>
       <c r="AT95" s="13"/>
     </row>
-    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33">
         <v>1</v>
       </c>
@@ -15064,7 +15064,7 @@
       <c r="AS96" s="13"/>
       <c r="AT96" s="13"/>
     </row>
-    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33">
         <v>1</v>
       </c>
@@ -15194,7 +15194,7 @@
       <c r="AS97" s="13"/>
       <c r="AT97" s="13"/>
     </row>
-    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33">
         <v>0</v>
       </c>
@@ -15320,7 +15320,7 @@
       <c r="AS98" s="13"/>
       <c r="AT98" s="13"/>
     </row>
-    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33">
         <v>1</v>
       </c>
@@ -15446,7 +15446,7 @@
       <c r="AS99" s="13"/>
       <c r="AT99" s="13"/>
     </row>
-    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33">
         <v>0</v>
       </c>
@@ -15572,7 +15572,7 @@
       <c r="AS100" s="13"/>
       <c r="AT100" s="13"/>
     </row>
-    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="33">
         <v>0</v>
       </c>
@@ -15698,7 +15698,7 @@
       <c r="AS101" s="13"/>
       <c r="AT101" s="13"/>
     </row>
-    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="20">
         <v>0</v>
       </c>
@@ -15820,7 +15820,7 @@
       <c r="AS102" s="13"/>
       <c r="AT102" s="13"/>
     </row>
-    <row r="103" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33">
         <v>0</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="AS103" s="13"/>
       <c r="AT103" s="13"/>
     </row>
-    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="33">
         <v>0</v>
       </c>
@@ -16072,7 +16072,7 @@
       <c r="AS104" s="13"/>
       <c r="AT104" s="13"/>
     </row>
-    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="36">
         <v>0</v>
       </c>
@@ -16196,7 +16196,7 @@
       <c r="AS105" s="13"/>
       <c r="AT105" s="13"/>
     </row>
-    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33">
         <v>0</v>
       </c>
@@ -16324,7 +16324,7 @@
       <c r="AS106" s="13"/>
       <c r="AT106" s="13"/>
     </row>
-    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33">
         <v>0</v>
       </c>
@@ -16454,7 +16454,7 @@
       <c r="AS107" s="13"/>
       <c r="AT107" s="13"/>
     </row>
-    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33">
         <v>0</v>
       </c>
@@ -16584,7 +16584,7 @@
       <c r="AS108" s="13"/>
       <c r="AT108" s="13"/>
     </row>
-    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33">
         <v>0</v>
       </c>
@@ -16712,7 +16712,7 @@
       <c r="AS109" s="13"/>
       <c r="AT109" s="13"/>
     </row>
-    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33">
         <v>0</v>
       </c>
@@ -16840,7 +16840,7 @@
       <c r="AS110" s="13"/>
       <c r="AT110" s="13"/>
     </row>
-    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20">
         <v>0</v>
       </c>
@@ -16962,7 +16962,7 @@
       <c r="AS111" s="13"/>
       <c r="AT111" s="13"/>
     </row>
-    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20">
         <v>1</v>
       </c>
@@ -17084,7 +17084,7 @@
       <c r="AS112" s="13"/>
       <c r="AT112" s="13"/>
     </row>
-    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="20">
         <v>1</v>
       </c>
@@ -17206,7 +17206,7 @@
       <c r="AS113" s="13"/>
       <c r="AT113" s="13"/>
     </row>
-    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33">
         <v>0</v>
       </c>
@@ -17332,7 +17332,7 @@
       <c r="AS114" s="13"/>
       <c r="AT114" s="13"/>
     </row>
-    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33">
         <v>0</v>
       </c>
@@ -17460,7 +17460,7 @@
       <c r="AS115" s="13"/>
       <c r="AT115" s="13"/>
     </row>
-    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="33">
         <v>1</v>
       </c>
@@ -17588,7 +17588,7 @@
       <c r="AS116" s="13"/>
       <c r="AT116" s="13"/>
     </row>
-    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="20">
         <v>0</v>
       </c>
@@ -17710,7 +17710,7 @@
       <c r="AS117" s="13"/>
       <c r="AT117" s="13"/>
     </row>
-    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33">
         <v>0</v>
       </c>
@@ -17838,7 +17838,7 @@
       <c r="AS118" s="13"/>
       <c r="AT118" s="13"/>
     </row>
-    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="33">
         <v>0</v>
       </c>
@@ -17966,7 +17966,7 @@
       <c r="AS119" s="13"/>
       <c r="AT119" s="13"/>
     </row>
-    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="20">
         <v>0</v>
       </c>
@@ -18088,7 +18088,7 @@
       <c r="AS120" s="13"/>
       <c r="AT120" s="13"/>
     </row>
-    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33">
         <v>0</v>
       </c>
@@ -18214,7 +18214,7 @@
       <c r="AS121" s="13"/>
       <c r="AT121" s="13"/>
     </row>
-    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33">
         <v>0</v>
       </c>
@@ -18338,7 +18338,7 @@
       <c r="AS122" s="13"/>
       <c r="AT122" s="13"/>
     </row>
-    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33">
         <v>0</v>
       </c>
@@ -18466,7 +18466,7 @@
       <c r="AS123" s="13"/>
       <c r="AT123" s="13"/>
     </row>
-    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="33">
         <v>0</v>
       </c>
@@ -18592,7 +18592,7 @@
       <c r="AS124" s="13"/>
       <c r="AT124" s="13"/>
     </row>
-    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20">
         <v>0</v>
       </c>
@@ -18714,7 +18714,7 @@
       <c r="AS125" s="13"/>
       <c r="AT125" s="13"/>
     </row>
-    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20">
         <v>0</v>
       </c>
@@ -18836,7 +18836,7 @@
       <c r="AS126" s="13"/>
       <c r="AT126" s="13"/>
     </row>
-    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20">
         <v>0</v>
       </c>
@@ -18958,7 +18958,7 @@
       <c r="AS127" s="13"/>
       <c r="AT127" s="13"/>
     </row>
-    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20">
         <v>1</v>
       </c>
@@ -19080,7 +19080,7 @@
       <c r="AS128" s="13"/>
       <c r="AT128" s="13"/>
     </row>
-    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20">
         <v>0</v>
       </c>
@@ -19202,7 +19202,7 @@
       <c r="AS129" s="13"/>
       <c r="AT129" s="13"/>
     </row>
-    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20">
         <v>0</v>
       </c>
@@ -19324,7 +19324,7 @@
       <c r="AS130" s="13"/>
       <c r="AT130" s="13"/>
     </row>
-    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20">
         <v>1</v>
       </c>
@@ -19446,7 +19446,7 @@
       <c r="AS131" s="13"/>
       <c r="AT131" s="13"/>
     </row>
-    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33">
         <v>0</v>
       </c>
@@ -19568,7 +19568,7 @@
       <c r="AS132" s="13"/>
       <c r="AT132" s="13"/>
     </row>
-    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="33">
         <v>0</v>
       </c>
@@ -19696,7 +19696,7 @@
       <c r="AS133" s="13"/>
       <c r="AT133" s="13"/>
     </row>
-    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="33">
         <v>0</v>
       </c>
@@ -19822,7 +19822,7 @@
       <c r="AS134" s="13"/>
       <c r="AT134" s="13"/>
     </row>
-    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="20">
         <v>0</v>
       </c>
@@ -19944,7 +19944,7 @@
       <c r="AS135" s="13"/>
       <c r="AT135" s="13"/>
     </row>
-    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="36">
         <v>0</v>
       </c>
@@ -20068,7 +20068,7 @@
       <c r="AS136" s="13"/>
       <c r="AT136" s="13"/>
     </row>
-    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="33">
         <v>0</v>
       </c>
@@ -20196,7 +20196,7 @@
       <c r="AS137" s="13"/>
       <c r="AT137" s="13"/>
     </row>
-    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33">
         <v>0</v>
       </c>
@@ -20324,7 +20324,7 @@
       <c r="AS138" s="13"/>
       <c r="AT138" s="13"/>
     </row>
-    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33">
         <v>0</v>
       </c>
@@ -20452,7 +20452,7 @@
       <c r="AS139" s="13"/>
       <c r="AT139" s="13"/>
     </row>
-    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33">
         <v>0</v>
       </c>
@@ -20580,7 +20580,7 @@
       <c r="AS140" s="13"/>
       <c r="AT140" s="13"/>
     </row>
-    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33">
         <v>0</v>
       </c>
@@ -20704,7 +20704,7 @@
       <c r="AS141" s="13"/>
       <c r="AT141" s="13"/>
     </row>
-    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33">
         <v>0</v>
       </c>
@@ -20834,7 +20834,7 @@
       <c r="AS142" s="13"/>
       <c r="AT142" s="13"/>
     </row>
-    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="33">
         <v>0</v>
       </c>
@@ -20962,7 +20962,7 @@
       <c r="AS143" s="13"/>
       <c r="AT143" s="13"/>
     </row>
-    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="30">
         <v>0</v>
       </c>
@@ -21086,7 +21086,7 @@
       <c r="AS144" s="13"/>
       <c r="AT144" s="13"/>
     </row>
-    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="20">
         <v>0</v>
       </c>
@@ -21208,7 +21208,7 @@
       <c r="AS145" s="13"/>
       <c r="AT145" s="13"/>
     </row>
-    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="36">
         <v>0</v>
       </c>
@@ -21332,7 +21332,7 @@
       <c r="AS146" s="13"/>
       <c r="AT146" s="13"/>
     </row>
-    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="20">
         <v>0</v>
       </c>
@@ -21454,7 +21454,7 @@
       <c r="AS147" s="13"/>
       <c r="AT147" s="13"/>
     </row>
-    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="33">
         <v>0</v>
       </c>
@@ -21580,7 +21580,7 @@
       <c r="AS148" s="13"/>
       <c r="AT148" s="13"/>
     </row>
-    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="33">
         <v>0</v>
       </c>
@@ -21706,7 +21706,7 @@
       <c r="AS149" s="13"/>
       <c r="AT149" s="13"/>
     </row>
-    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33">
         <v>0</v>
       </c>
@@ -21834,7 +21834,7 @@
       <c r="AS150" s="13"/>
       <c r="AT150" s="13"/>
     </row>
-    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="33">
         <v>1</v>
       </c>
@@ -21962,7 +21962,7 @@
       <c r="AS151" s="13"/>
       <c r="AT151" s="13"/>
     </row>
-    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="20">
         <v>0</v>
       </c>
@@ -22081,7 +22081,7 @@
       <c r="AS152" s="3"/>
       <c r="AT152" s="3"/>
     </row>
-    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="39">
         <v>0</v>
       </c>
@@ -22205,7 +22205,7 @@
       <c r="AS153" s="13"/>
       <c r="AT153" s="13"/>
     </row>
-    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="20">
         <v>0</v>
       </c>
@@ -22323,7 +22323,7 @@
       <c r="AS154" s="13"/>
       <c r="AT154" s="13"/>
     </row>
-    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="20">
         <v>0</v>
       </c>
@@ -22445,7 +22445,7 @@
       <c r="AS155" s="13"/>
       <c r="AT155" s="13"/>
     </row>
-    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33">
         <v>0</v>
       </c>
@@ -22569,7 +22569,7 @@
       <c r="AS156" s="13"/>
       <c r="AT156" s="13"/>
     </row>
-    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33">
         <v>0</v>
       </c>
@@ -22695,7 +22695,7 @@
       <c r="AS157" s="13"/>
       <c r="AT157" s="13"/>
     </row>
-    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="20">
         <v>0</v>
       </c>
@@ -22817,52 +22817,54 @@
       <c r="AS158" s="13"/>
       <c r="AT158" s="13"/>
     </row>
-    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="36">
-        <v>0</v>
-      </c>
-      <c r="B159" s="36">
+    <row r="159" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="33">
+        <v>0</v>
+      </c>
+      <c r="B159" s="33">
         <v>2</v>
       </c>
-      <c r="C159" s="36">
+      <c r="C159" s="33">
         <v>5</v>
       </c>
-      <c r="D159" s="37" t="s">
+      <c r="D159" s="34" t="s">
         <v>840</v>
       </c>
-      <c r="E159" s="37" t="s">
+      <c r="E159" s="34" t="s">
         <v>841</v>
       </c>
-      <c r="F159" s="37" t="s">
+      <c r="F159" s="34" t="s">
         <v>842</v>
       </c>
-      <c r="G159" s="37" t="s">
+      <c r="G159" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="H159" s="37" t="s">
+      <c r="H159" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I159" s="36" t="s">
+      <c r="I159" s="33" t="s">
         <v>843</v>
       </c>
-      <c r="J159" s="36">
+      <c r="J159" s="33">
         <v>99</v>
       </c>
-      <c r="K159" s="36" t="s">
+      <c r="K159" s="33" t="s">
         <v>385</v>
       </c>
-      <c r="L159" s="36">
+      <c r="L159" s="33">
         <v>40</v>
       </c>
-      <c r="M159" s="37" t="s">
+      <c r="M159" s="34" t="s">
         <v>844</v>
       </c>
-      <c r="N159" s="37" t="s">
-        <v>853</v>
-      </c>
-      <c r="O159" s="38"/>
-      <c r="P159" s="36"/>
-      <c r="Q159" s="37"/>
+      <c r="N159" s="34" t="s">
+        <v>886</v>
+      </c>
+      <c r="O159" s="35">
+        <v>1</v>
+      </c>
+      <c r="P159" s="33"/>
+      <c r="Q159" s="34"/>
       <c r="R159" s="13"/>
       <c r="S159" s="2">
         <f t="shared" si="51"/>
@@ -22911,7 +22913,7 @@
       </c>
       <c r="AE159" s="2">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF159" s="2">
         <f t="shared" si="63"/>
@@ -22919,7 +22921,7 @@
       </c>
       <c r="AG159" s="2">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH159" s="2">
         <f t="shared" si="65"/>
@@ -22941,7 +22943,7 @@
       <c r="AS159" s="13"/>
       <c r="AT159" s="13"/>
     </row>
-    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33">
         <v>0</v>
       </c>
@@ -23063,7 +23065,7 @@
       <c r="AS160" s="13"/>
       <c r="AT160" s="13"/>
     </row>
-    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="33">
         <v>0</v>
       </c>
@@ -23186,7 +23188,7 @@
       <c r="AS161" s="3"/>
       <c r="AT161" s="3"/>
     </row>
-    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20">
         <v>0</v>
       </c>
@@ -23308,7 +23310,7 @@
       <c r="AS162" s="13"/>
       <c r="AT162" s="13"/>
     </row>
-    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="20">
         <v>0</v>
       </c>
@@ -23430,7 +23432,7 @@
       <c r="AS163" s="13"/>
       <c r="AT163" s="13"/>
     </row>
-    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20">
         <v>0</v>
       </c>
@@ -23552,7 +23554,7 @@
       <c r="AS164" s="13"/>
       <c r="AT164" s="13"/>
     </row>
-    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="33">
         <v>0</v>
       </c>
@@ -23678,7 +23680,7 @@
       <c r="AS165" s="13"/>
       <c r="AT165" s="13"/>
     </row>
-    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="20">
         <v>0</v>
       </c>
@@ -23800,7 +23802,7 @@
       <c r="AS166" s="13"/>
       <c r="AT166" s="13"/>
     </row>
-    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33">
         <v>0</v>
       </c>
@@ -23928,7 +23930,7 @@
       <c r="AS167" s="13"/>
       <c r="AT167" s="13"/>
     </row>
-    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20">
         <v>0</v>
       </c>
@@ -24050,7 +24052,7 @@
       <c r="AS168" s="13"/>
       <c r="AT168" s="13"/>
     </row>
-    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="33">
         <v>0</v>
       </c>
@@ -24178,7 +24180,7 @@
       <c r="AS169" s="13"/>
       <c r="AT169" s="13"/>
     </row>
-    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33">
         <v>1</v>
       </c>
@@ -24306,7 +24308,7 @@
       <c r="AS170" s="13"/>
       <c r="AT170" s="13"/>
     </row>
-    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33">
         <v>1</v>
       </c>
@@ -24434,7 +24436,7 @@
       <c r="AS171" s="13"/>
       <c r="AT171" s="13"/>
     </row>
-    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33">
         <v>1</v>
       </c>
@@ -24562,7 +24564,7 @@
       <c r="AS172" s="13"/>
       <c r="AT172" s="13"/>
     </row>
-    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33">
         <v>1</v>
       </c>
@@ -24690,7 +24692,7 @@
       <c r="AS173" s="13"/>
       <c r="AT173" s="13"/>
     </row>
-    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="36">
         <v>0</v>
       </c>
@@ -24814,7 +24816,7 @@
       <c r="AS174" s="13"/>
       <c r="AT174" s="13"/>
     </row>
-    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="36">
         <v>1</v>
       </c>
@@ -24938,7 +24940,7 @@
       <c r="AS175" s="13"/>
       <c r="AT175" s="13"/>
     </row>
-    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="20">
         <v>0</v>
       </c>
@@ -25060,7 +25062,7 @@
       <c r="AS176" s="13"/>
       <c r="AT176" s="13"/>
     </row>
-    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="20">
         <v>0</v>
       </c>
@@ -25182,7 +25184,7 @@
       <c r="AS177" s="13"/>
       <c r="AT177" s="13"/>
     </row>
-    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="20">
         <v>1</v>
       </c>
@@ -25304,7 +25306,7 @@
       <c r="AS178" s="13"/>
       <c r="AT178" s="13"/>
     </row>
-    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="20">
         <v>0</v>
       </c>
@@ -25426,7 +25428,7 @@
       <c r="AS179" s="13"/>
       <c r="AT179" s="13"/>
     </row>
-    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="33">
         <v>0</v>
       </c>
@@ -25554,7 +25556,7 @@
       <c r="AS180" s="13"/>
       <c r="AT180" s="13"/>
     </row>
-    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33">
         <v>1</v>
       </c>
@@ -25682,7 +25684,7 @@
       <c r="AS181" s="13"/>
       <c r="AT181" s="13"/>
     </row>
-    <row r="182" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33">
         <v>0</v>
       </c>
@@ -25807,7 +25809,7 @@
       <c r="AS182" s="3"/>
       <c r="AT182" s="3"/>
     </row>
-    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="36">
         <v>0</v>
       </c>
@@ -25931,7 +25933,7 @@
       <c r="AS183" s="13"/>
       <c r="AT183" s="13"/>
     </row>
-    <row r="184" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="20">
         <v>0</v>
       </c>
@@ -26053,7 +26055,7 @@
       <c r="AS184" s="13"/>
       <c r="AT184" s="13"/>
     </row>
-    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="20">
         <v>0</v>
       </c>
@@ -26175,7 +26177,7 @@
       <c r="AS185" s="13"/>
       <c r="AT185" s="13"/>
     </row>
-    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33">
         <v>0</v>
       </c>
@@ -26303,7 +26305,7 @@
       <c r="AS186" s="13"/>
       <c r="AT186" s="13"/>
     </row>
-    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="20">
         <v>0</v>
       </c>
@@ -26425,7 +26427,7 @@
       <c r="AS187" s="13"/>
       <c r="AT187" s="13"/>
     </row>
-    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33">
         <v>0</v>
       </c>
@@ -26553,7 +26555,7 @@
       <c r="AS188" s="13"/>
       <c r="AT188" s="13"/>
     </row>
-    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="20">
         <v>0</v>
       </c>
@@ -26675,7 +26677,7 @@
       <c r="AS189" s="13"/>
       <c r="AT189" s="13"/>
     </row>
-    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="20">
         <v>1</v>
       </c>
@@ -26797,7 +26799,7 @@
       <c r="AS190" s="13"/>
       <c r="AT190" s="13"/>
     </row>
-    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="20">
         <v>1</v>
       </c>
@@ -26919,7 +26921,7 @@
       <c r="AS191" s="13"/>
       <c r="AT191" s="13"/>
     </row>
-    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="33">
         <v>0</v>
       </c>
@@ -27047,7 +27049,7 @@
       <c r="AS192" s="13"/>
       <c r="AT192" s="13"/>
     </row>
-    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="33">
         <v>1</v>
       </c>
@@ -27175,7 +27177,7 @@
       <c r="AS193" s="13"/>
       <c r="AT193" s="13"/>
     </row>
-    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33">
         <v>1</v>
       </c>
@@ -27303,7 +27305,7 @@
       <c r="AS194" s="13"/>
       <c r="AT194" s="13"/>
     </row>
-    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33">
         <v>0</v>
       </c>
@@ -27431,7 +27433,7 @@
       <c r="AS195" s="13"/>
       <c r="AT195" s="13"/>
     </row>
-    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33">
         <v>1</v>
       </c>
@@ -27559,7 +27561,7 @@
       <c r="AS196" s="13"/>
       <c r="AT196" s="13"/>
     </row>
-    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="20">
         <v>0</v>
       </c>
@@ -27681,7 +27683,7 @@
       <c r="AS197" s="13"/>
       <c r="AT197" s="13"/>
     </row>
-    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="20">
         <v>1</v>
       </c>
@@ -27803,7 +27805,7 @@
       <c r="AS198" s="13"/>
       <c r="AT198" s="13"/>
     </row>
-    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="20">
         <v>1</v>
       </c>
@@ -27925,7 +27927,7 @@
       <c r="AS199" s="13"/>
       <c r="AT199" s="13"/>
     </row>
-    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="33">
         <v>0</v>
       </c>
@@ -28053,7 +28055,7 @@
       <c r="AS200" s="13"/>
       <c r="AT200" s="13"/>
     </row>
-    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="33">
         <v>1</v>
       </c>
@@ -28181,7 +28183,7 @@
       <c r="AS201" s="13"/>
       <c r="AT201" s="13"/>
     </row>
-    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="33">
         <v>0</v>
       </c>
@@ -28307,7 +28309,7 @@
       <c r="AS202" s="13"/>
       <c r="AT202" s="13"/>
     </row>
-    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="33">
         <v>1</v>
       </c>
@@ -28433,7 +28435,7 @@
       <c r="AS203" s="13"/>
       <c r="AT203" s="13"/>
     </row>
-    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33">
         <v>0</v>
       </c>
@@ -28561,7 +28563,7 @@
       <c r="AS204" s="13"/>
       <c r="AT204" s="13"/>
     </row>
-    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33">
         <v>1</v>
       </c>
@@ -28689,7 +28691,7 @@
       <c r="AS205" s="13"/>
       <c r="AT205" s="13"/>
     </row>
-    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="33">
         <v>0</v>
       </c>
@@ -28815,7 +28817,7 @@
       <c r="AS206" s="13"/>
       <c r="AT206" s="13"/>
     </row>
-    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="33">
         <v>1</v>
       </c>
@@ -28941,7 +28943,7 @@
       <c r="AS207" s="13"/>
       <c r="AT207" s="13"/>
     </row>
-    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33">
         <v>0</v>
       </c>
@@ -29069,7 +29071,7 @@
       <c r="AS208" s="13"/>
       <c r="AT208" s="13"/>
     </row>
-    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33">
         <v>0</v>
       </c>
@@ -29197,7 +29199,7 @@
       <c r="AS209" s="13"/>
       <c r="AT209" s="13"/>
     </row>
-    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="20">
         <v>0</v>
       </c>
@@ -29319,7 +29321,7 @@
       <c r="AS210" s="13"/>
       <c r="AT210" s="13"/>
     </row>
-    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="20">
         <v>0</v>
       </c>
@@ -29441,7 +29443,7 @@
       <c r="AS211" s="13"/>
       <c r="AT211" s="13"/>
     </row>
-    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="33">
         <v>0</v>
       </c>
@@ -29569,7 +29571,7 @@
       <c r="AS212" s="13"/>
       <c r="AT212" s="13"/>
     </row>
-    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="33">
         <v>1</v>
       </c>
@@ -29697,7 +29699,7 @@
       <c r="AS213" s="13"/>
       <c r="AT213" s="13"/>
     </row>
-    <row r="214" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33">
         <v>0</v>
       </c>
@@ -29822,7 +29824,7 @@
       <c r="AS214" s="3"/>
       <c r="AT214" s="3"/>
     </row>
-    <row r="215" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33">
         <v>1</v>
       </c>
@@ -29947,7 +29949,7 @@
       <c r="AS215" s="3"/>
       <c r="AT215" s="3"/>
     </row>
-    <row r="216" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="36">
         <v>0</v>
       </c>
@@ -30071,7 +30073,7 @@
       <c r="AS216" s="13"/>
       <c r="AT216" s="13"/>
     </row>
-    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33">
         <v>0</v>
       </c>
@@ -30199,7 +30201,7 @@
       <c r="AS217" s="13"/>
       <c r="AT217" s="13"/>
     </row>
-    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="20"/>
       <c r="B218" s="20"/>
       <c r="C218" s="20"/>
@@ -30247,7 +30249,7 @@
       <c r="AS218" s="13"/>
       <c r="AT218" s="13"/>
     </row>
-    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="20"/>
       <c r="B219" s="20"/>
       <c r="C219" s="20"/>
@@ -30295,7 +30297,7 @@
       <c r="AS219" s="13"/>
       <c r="AT219" s="13"/>
     </row>
-    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="20"/>
       <c r="B220" s="20"/>
       <c r="C220" s="20"/>
@@ -30343,7 +30345,7 @@
       <c r="AS220" s="13"/>
       <c r="AT220" s="13"/>
     </row>
-    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="20"/>
       <c r="B221" s="20"/>
       <c r="C221" s="20"/>
@@ -30391,7 +30393,7 @@
       <c r="AS221" s="13"/>
       <c r="AT221" s="13"/>
     </row>
-    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="20"/>
       <c r="B222" s="20"/>
       <c r="C222" s="20"/>
@@ -30439,7 +30441,7 @@
       <c r="AS222" s="13"/>
       <c r="AT222" s="13"/>
     </row>
-    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="20"/>
       <c r="B223" s="20"/>
       <c r="C223" s="20"/>
@@ -30487,7 +30489,7 @@
       <c r="AS223" s="13"/>
       <c r="AT223" s="13"/>
     </row>
-    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="20"/>
       <c r="B224" s="20"/>
       <c r="C224" s="20"/>
@@ -30535,7 +30537,7 @@
       <c r="AS224" s="13"/>
       <c r="AT224" s="13"/>
     </row>
-    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="20"/>
       <c r="B225" s="20"/>
       <c r="C225" s="20"/>
@@ -30583,7 +30585,7 @@
       <c r="AS225" s="13"/>
       <c r="AT225" s="13"/>
     </row>
-    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="20"/>
       <c r="B226" s="20"/>
       <c r="C226" s="20"/>
@@ -30631,7 +30633,7 @@
       <c r="AS226" s="13"/>
       <c r="AT226" s="13"/>
     </row>
-    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="20"/>
       <c r="B227" s="20"/>
       <c r="C227" s="20"/>
@@ -30679,7 +30681,7 @@
       <c r="AS227" s="13"/>
       <c r="AT227" s="13"/>
     </row>
-    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="20"/>
       <c r="B228" s="20"/>
       <c r="C228" s="20"/>
@@ -30727,7 +30729,7 @@
       <c r="AS228" s="13"/>
       <c r="AT228" s="13"/>
     </row>
-    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="20"/>
       <c r="B229" s="20"/>
       <c r="C229" s="20"/>
@@ -30775,7 +30777,7 @@
       <c r="AS229" s="13"/>
       <c r="AT229" s="13"/>
     </row>
-    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="20"/>
       <c r="B230" s="20"/>
       <c r="C230" s="20"/>
@@ -30823,7 +30825,7 @@
       <c r="AS230" s="13"/>
       <c r="AT230" s="13"/>
     </row>
-    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="20"/>
       <c r="B231" s="20"/>
       <c r="C231" s="20"/>
@@ -30871,7 +30873,7 @@
       <c r="AS231" s="13"/>
       <c r="AT231" s="13"/>
     </row>
-    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="20"/>
       <c r="B232" s="20"/>
       <c r="C232" s="20"/>
@@ -30919,7 +30921,7 @@
       <c r="AS232" s="13"/>
       <c r="AT232" s="13"/>
     </row>
-    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="20"/>
       <c r="B233" s="20"/>
       <c r="C233" s="20"/>
@@ -30967,7 +30969,7 @@
       <c r="AS233" s="13"/>
       <c r="AT233" s="13"/>
     </row>
-    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="20"/>
       <c r="B234" s="20"/>
       <c r="C234" s="20"/>
@@ -31015,7 +31017,7 @@
       <c r="AS234" s="13"/>
       <c r="AT234" s="13"/>
     </row>
-    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="20"/>
       <c r="B235" s="20"/>
       <c r="C235" s="20"/>
@@ -31063,7 +31065,7 @@
       <c r="AS235" s="13"/>
       <c r="AT235" s="13"/>
     </row>
-    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="20"/>
       <c r="B236" s="20"/>
       <c r="C236" s="20"/>
@@ -31111,7 +31113,7 @@
       <c r="AS236" s="13"/>
       <c r="AT236" s="13"/>
     </row>
-    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="20"/>
       <c r="B237" s="20"/>
       <c r="C237" s="20"/>
@@ -31159,7 +31161,7 @@
       <c r="AS237" s="13"/>
       <c r="AT237" s="13"/>
     </row>
-    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="20"/>
       <c r="B238" s="20"/>
       <c r="C238" s="20"/>
@@ -31207,7 +31209,7 @@
       <c r="AS238" s="13"/>
       <c r="AT238" s="13"/>
     </row>
-    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="20"/>
       <c r="B239" s="20"/>
       <c r="C239" s="20"/>
@@ -31255,7 +31257,7 @@
       <c r="AS239" s="13"/>
       <c r="AT239" s="13"/>
     </row>
-    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="20"/>
@@ -31303,7 +31305,7 @@
       <c r="AS240" s="13"/>
       <c r="AT240" s="13"/>
     </row>
-    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="20"/>
       <c r="B241" s="20"/>
       <c r="C241" s="20"/>
@@ -31351,7 +31353,7 @@
       <c r="AS241" s="13"/>
       <c r="AT241" s="13"/>
     </row>
-    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="20"/>
       <c r="B242" s="20"/>
       <c r="C242" s="20"/>
@@ -31399,7 +31401,7 @@
       <c r="AS242" s="13"/>
       <c r="AT242" s="13"/>
     </row>
-    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="20"/>
       <c r="B243" s="20"/>
       <c r="C243" s="20"/>
@@ -31447,7 +31449,7 @@
       <c r="AS243" s="13"/>
       <c r="AT243" s="13"/>
     </row>
-    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="20"/>
       <c r="B244" s="20"/>
       <c r="C244" s="20"/>
@@ -31495,7 +31497,7 @@
       <c r="AS244" s="13"/>
       <c r="AT244" s="13"/>
     </row>
-    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="20"/>
       <c r="B245" s="20"/>
       <c r="C245" s="20"/>
@@ -31543,7 +31545,7 @@
       <c r="AS245" s="13"/>
       <c r="AT245" s="13"/>
     </row>
-    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="20"/>
       <c r="B246" s="20"/>
       <c r="C246" s="20"/>
@@ -31591,7 +31593,7 @@
       <c r="AS246" s="13"/>
       <c r="AT246" s="13"/>
     </row>
-    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="20"/>
       <c r="B247" s="20"/>
       <c r="C247" s="20"/>
@@ -31639,7 +31641,7 @@
       <c r="AS247" s="13"/>
       <c r="AT247" s="13"/>
     </row>
-    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="20"/>
       <c r="B248" s="20"/>
       <c r="C248" s="20"/>
@@ -31687,7 +31689,7 @@
       <c r="AS248" s="13"/>
       <c r="AT248" s="13"/>
     </row>
-    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="20"/>
       <c r="B249" s="20"/>
       <c r="C249" s="20"/>
@@ -31735,7 +31737,7 @@
       <c r="AS249" s="13"/>
       <c r="AT249" s="13"/>
     </row>
-    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="20"/>
       <c r="B250" s="20"/>
       <c r="C250" s="20"/>
@@ -31783,7 +31785,7 @@
       <c r="AS250" s="13"/>
       <c r="AT250" s="13"/>
     </row>
-    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="20"/>
       <c r="B251" s="20"/>
       <c r="C251" s="20"/>
@@ -31831,7 +31833,7 @@
       <c r="AS251" s="13"/>
       <c r="AT251" s="13"/>
     </row>
-    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="20"/>
       <c r="B252" s="20"/>
       <c r="C252" s="20"/>
@@ -31879,7 +31881,7 @@
       <c r="AS252" s="13"/>
       <c r="AT252" s="13"/>
     </row>
-    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="20"/>
       <c r="B253" s="20"/>
       <c r="C253" s="20"/>
@@ -31927,7 +31929,7 @@
       <c r="AS253" s="13"/>
       <c r="AT253" s="13"/>
     </row>
-    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="20"/>
       <c r="B254" s="20"/>
       <c r="C254" s="20"/>
@@ -31975,7 +31977,7 @@
       <c r="AS254" s="13"/>
       <c r="AT254" s="13"/>
     </row>
-    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="20"/>
       <c r="B255" s="20"/>
       <c r="C255" s="20"/>
@@ -32023,7 +32025,7 @@
       <c r="AS255" s="13"/>
       <c r="AT255" s="13"/>
     </row>
-    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="20"/>
       <c r="B256" s="20"/>
       <c r="C256" s="20"/>
@@ -32071,7 +32073,7 @@
       <c r="AS256" s="13"/>
       <c r="AT256" s="13"/>
     </row>
-    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="20"/>
       <c r="B257" s="20"/>
       <c r="C257" s="20"/>
@@ -32119,7 +32121,7 @@
       <c r="AS257" s="13"/>
       <c r="AT257" s="13"/>
     </row>
-    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="20"/>
       <c r="B258" s="20"/>
       <c r="C258" s="20"/>
@@ -32167,7 +32169,7 @@
       <c r="AS258" s="13"/>
       <c r="AT258" s="13"/>
     </row>
-    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="20"/>
       <c r="B259" s="20"/>
       <c r="C259" s="20"/>
@@ -32215,7 +32217,7 @@
       <c r="AS259" s="13"/>
       <c r="AT259" s="13"/>
     </row>
-    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="20"/>
       <c r="B260" s="20"/>
       <c r="C260" s="20"/>
@@ -32263,7 +32265,7 @@
       <c r="AS260" s="13"/>
       <c r="AT260" s="13"/>
     </row>
-    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="20"/>
       <c r="B261" s="20"/>
       <c r="C261" s="20"/>
@@ -32311,7 +32313,7 @@
       <c r="AS261" s="13"/>
       <c r="AT261" s="13"/>
     </row>
-    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="20"/>
       <c r="B262" s="20"/>
       <c r="C262" s="20"/>
@@ -32359,7 +32361,7 @@
       <c r="AS262" s="13"/>
       <c r="AT262" s="13"/>
     </row>
-    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="20"/>
       <c r="B263" s="20"/>
       <c r="C263" s="20"/>
@@ -32407,7 +32409,7 @@
       <c r="AS263" s="13"/>
       <c r="AT263" s="13"/>
     </row>
-    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="20"/>
       <c r="B264" s="20"/>
       <c r="C264" s="20"/>
@@ -32455,7 +32457,7 @@
       <c r="AS264" s="13"/>
       <c r="AT264" s="13"/>
     </row>
-    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="20"/>
       <c r="B265" s="20"/>
       <c r="C265" s="20"/>
@@ -32503,7 +32505,7 @@
       <c r="AS265" s="13"/>
       <c r="AT265" s="13"/>
     </row>
-    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="20"/>
       <c r="B266" s="20"/>
       <c r="C266" s="20"/>
@@ -32551,7 +32553,7 @@
       <c r="AS266" s="13"/>
       <c r="AT266" s="13"/>
     </row>
-    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="20"/>
       <c r="B267" s="20"/>
       <c r="C267" s="20"/>
@@ -32599,7 +32601,7 @@
       <c r="AS267" s="13"/>
       <c r="AT267" s="13"/>
     </row>
-    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="20"/>
       <c r="B268" s="20"/>
       <c r="C268" s="20"/>
@@ -32647,7 +32649,7 @@
       <c r="AS268" s="13"/>
       <c r="AT268" s="13"/>
     </row>
-    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="20"/>
@@ -32695,7 +32697,7 @@
       <c r="AS269" s="13"/>
       <c r="AT269" s="13"/>
     </row>
-    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="20"/>
       <c r="B270" s="20"/>
       <c r="C270" s="20"/>
@@ -32743,7 +32745,7 @@
       <c r="AS270" s="13"/>
       <c r="AT270" s="13"/>
     </row>
-    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="20"/>
       <c r="B271" s="20"/>
       <c r="C271" s="20"/>
@@ -32791,7 +32793,7 @@
       <c r="AS271" s="13"/>
       <c r="AT271" s="13"/>
     </row>
-    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="20"/>
       <c r="B272" s="20"/>
       <c r="C272" s="20"/>
@@ -32839,7 +32841,7 @@
       <c r="AS272" s="13"/>
       <c r="AT272" s="13"/>
     </row>
-    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="20"/>
       <c r="B273" s="20"/>
       <c r="C273" s="20"/>
@@ -32887,7 +32889,7 @@
       <c r="AS273" s="13"/>
       <c r="AT273" s="13"/>
     </row>
-    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="20"/>
       <c r="B274" s="20"/>
       <c r="C274" s="20"/>
@@ -32935,7 +32937,7 @@
       <c r="AS274" s="13"/>
       <c r="AT274" s="13"/>
     </row>
-    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="20"/>
       <c r="B275" s="20"/>
       <c r="C275" s="20"/>
@@ -32983,7 +32985,7 @@
       <c r="AS275" s="13"/>
       <c r="AT275" s="13"/>
     </row>
-    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="20"/>
       <c r="B276" s="20"/>
       <c r="C276" s="20"/>
@@ -33031,7 +33033,7 @@
       <c r="AS276" s="13"/>
       <c r="AT276" s="13"/>
     </row>
-    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="20"/>
       <c r="B277" s="20"/>
       <c r="C277" s="20"/>
@@ -33079,7 +33081,7 @@
       <c r="AS277" s="13"/>
       <c r="AT277" s="13"/>
     </row>
-    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="20"/>
       <c r="B278" s="20"/>
       <c r="C278" s="20"/>
@@ -33127,7 +33129,7 @@
       <c r="AS278" s="13"/>
       <c r="AT278" s="13"/>
     </row>
-    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="20"/>
       <c r="B279" s="20"/>
       <c r="C279" s="20"/>
@@ -33175,7 +33177,7 @@
       <c r="AS279" s="13"/>
       <c r="AT279" s="13"/>
     </row>
-    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="20"/>
       <c r="B280" s="20"/>
       <c r="C280" s="20"/>
@@ -33223,7 +33225,7 @@
       <c r="AS280" s="13"/>
       <c r="AT280" s="13"/>
     </row>
-    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="20"/>
       <c r="B281" s="20"/>
       <c r="C281" s="20"/>
@@ -33271,7 +33273,7 @@
       <c r="AS281" s="13"/>
       <c r="AT281" s="13"/>
     </row>
-    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="20"/>
       <c r="B282" s="20"/>
       <c r="C282" s="20"/>
@@ -33319,7 +33321,7 @@
       <c r="AS282" s="13"/>
       <c r="AT282" s="13"/>
     </row>
-    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="20"/>
       <c r="B283" s="20"/>
       <c r="C283" s="20"/>
@@ -33367,7 +33369,7 @@
       <c r="AS283" s="13"/>
       <c r="AT283" s="13"/>
     </row>
-    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="20"/>
       <c r="B284" s="20"/>
       <c r="C284" s="20"/>
@@ -33415,7 +33417,7 @@
       <c r="AS284" s="13"/>
       <c r="AT284" s="13"/>
     </row>
-    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="20"/>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
@@ -33463,7 +33465,7 @@
       <c r="AS285" s="13"/>
       <c r="AT285" s="13"/>
     </row>
-    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="20"/>
       <c r="B286" s="20"/>
       <c r="C286" s="20"/>
@@ -33511,7 +33513,7 @@
       <c r="AS286" s="13"/>
       <c r="AT286" s="13"/>
     </row>
-    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="20"/>
       <c r="B287" s="20"/>
       <c r="C287" s="20"/>
@@ -33559,7 +33561,7 @@
       <c r="AS287" s="13"/>
       <c r="AT287" s="13"/>
     </row>
-    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="20"/>
       <c r="B288" s="20"/>
       <c r="C288" s="20"/>
@@ -33607,7 +33609,7 @@
       <c r="AS288" s="13"/>
       <c r="AT288" s="13"/>
     </row>
-    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="20"/>
       <c r="B289" s="20"/>
       <c r="C289" s="20"/>
@@ -33655,7 +33657,7 @@
       <c r="AS289" s="13"/>
       <c r="AT289" s="13"/>
     </row>
-    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="20"/>
       <c r="B290" s="20"/>
       <c r="C290" s="20"/>
@@ -33703,7 +33705,7 @@
       <c r="AS290" s="13"/>
       <c r="AT290" s="13"/>
     </row>
-    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="20"/>
       <c r="B291" s="20"/>
       <c r="C291" s="20"/>
@@ -33751,7 +33753,7 @@
       <c r="AS291" s="13"/>
       <c r="AT291" s="13"/>
     </row>
-    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="20"/>
       <c r="B292" s="20"/>
       <c r="C292" s="20"/>
@@ -33799,7 +33801,7 @@
       <c r="AS292" s="13"/>
       <c r="AT292" s="13"/>
     </row>
-    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="20"/>
       <c r="B293" s="20"/>
       <c r="C293" s="20"/>
@@ -33847,7 +33849,7 @@
       <c r="AS293" s="13"/>
       <c r="AT293" s="13"/>
     </row>
-    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="20"/>
       <c r="B294" s="20"/>
       <c r="C294" s="20"/>
@@ -33895,7 +33897,7 @@
       <c r="AS294" s="13"/>
       <c r="AT294" s="13"/>
     </row>
-    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="20"/>
       <c r="B295" s="20"/>
       <c r="C295" s="20"/>
@@ -33943,7 +33945,7 @@
       <c r="AS295" s="13"/>
       <c r="AT295" s="13"/>
     </row>
-    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="20"/>
       <c r="B296" s="20"/>
       <c r="C296" s="20"/>
@@ -33991,7 +33993,7 @@
       <c r="AS296" s="13"/>
       <c r="AT296" s="13"/>
     </row>
-    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="20"/>
       <c r="B297" s="20"/>
       <c r="C297" s="20"/>
@@ -34039,7 +34041,7 @@
       <c r="AS297" s="13"/>
       <c r="AT297" s="13"/>
     </row>
-    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="20"/>
       <c r="B298" s="20"/>
       <c r="C298" s="20"/>
@@ -34087,7 +34089,7 @@
       <c r="AS298" s="13"/>
       <c r="AT298" s="13"/>
     </row>
-    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="20"/>
       <c r="B299" s="20"/>
       <c r="C299" s="20"/>
@@ -34135,7 +34137,7 @@
       <c r="AS299" s="13"/>
       <c r="AT299" s="13"/>
     </row>
-    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="20"/>
       <c r="B300" s="20"/>
       <c r="C300" s="20"/>
@@ -34183,7 +34185,7 @@
       <c r="AS300" s="13"/>
       <c r="AT300" s="13"/>
     </row>
-    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="20"/>
       <c r="B301" s="20"/>
       <c r="C301" s="20"/>
@@ -34231,7 +34233,7 @@
       <c r="AS301" s="13"/>
       <c r="AT301" s="13"/>
     </row>
-    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="20"/>
       <c r="B302" s="20"/>
       <c r="C302" s="20"/>
@@ -34279,7 +34281,7 @@
       <c r="AS302" s="13"/>
       <c r="AT302" s="13"/>
     </row>
-    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="20"/>
       <c r="B303" s="20"/>
       <c r="C303" s="20"/>
@@ -34327,7 +34329,7 @@
       <c r="AS303" s="13"/>
       <c r="AT303" s="13"/>
     </row>
-    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="20"/>
       <c r="B304" s="20"/>
       <c r="C304" s="20"/>
@@ -34375,7 +34377,7 @@
       <c r="AS304" s="13"/>
       <c r="AT304" s="13"/>
     </row>
-    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="20"/>
       <c r="B305" s="20"/>
       <c r="C305" s="20"/>
@@ -34423,7 +34425,7 @@
       <c r="AS305" s="13"/>
       <c r="AT305" s="13"/>
     </row>
-    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="20"/>
       <c r="B306" s="20"/>
       <c r="C306" s="20"/>
@@ -34471,7 +34473,7 @@
       <c r="AS306" s="13"/>
       <c r="AT306" s="13"/>
     </row>
-    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="20"/>
       <c r="B307" s="20"/>
       <c r="C307" s="20"/>
@@ -34519,7 +34521,7 @@
       <c r="AS307" s="13"/>
       <c r="AT307" s="13"/>
     </row>
-    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="20"/>
       <c r="B308" s="20"/>
       <c r="C308" s="20"/>
@@ -34567,7 +34569,7 @@
       <c r="AS308" s="13"/>
       <c r="AT308" s="13"/>
     </row>
-    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="20"/>
       <c r="B309" s="20"/>
       <c r="C309" s="20"/>
@@ -34615,7 +34617,7 @@
       <c r="AS309" s="13"/>
       <c r="AT309" s="13"/>
     </row>
-    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="20"/>
       <c r="B310" s="20"/>
       <c r="C310" s="20"/>
@@ -34663,7 +34665,7 @@
       <c r="AS310" s="13"/>
       <c r="AT310" s="13"/>
     </row>
-    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="20"/>
       <c r="B311" s="20"/>
       <c r="C311" s="20"/>
@@ -34711,7 +34713,7 @@
       <c r="AS311" s="13"/>
       <c r="AT311" s="13"/>
     </row>
-    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="20"/>
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
@@ -34759,7 +34761,7 @@
       <c r="AS312" s="13"/>
       <c r="AT312" s="13"/>
     </row>
-    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="20"/>
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
@@ -34807,7 +34809,7 @@
       <c r="AS313" s="13"/>
       <c r="AT313" s="13"/>
     </row>
-    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="20"/>
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
@@ -34855,7 +34857,7 @@
       <c r="AS314" s="13"/>
       <c r="AT314" s="13"/>
     </row>
-    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="20"/>
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
@@ -34903,7 +34905,7 @@
       <c r="AS315" s="13"/>
       <c r="AT315" s="13"/>
     </row>
-    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="20"/>
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE95411C-E039-4517-933C-0557EFE41367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2852C06-0609-4CC7-9701-157B5D09DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3725,15 +3725,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3755,15 +3755,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>616</v>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -4097,19 +4097,19 @@
         <v>1</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" ref="AF8:AF72" si="3">+O8*P8*(1-A8)</f>
+        <f t="shared" ref="AF8:AF12" si="3">+O8*P8*(1-A8)</f>
         <v>0</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" ref="AG8:AG72" si="4">O8*(1-P8)*(1-A8)</f>
+        <f t="shared" ref="AG8:AG12" si="4">O8*(1-P8)*(1-A8)</f>
         <v>1</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" ref="AH8:AH72" si="5">+P8*(1-A8)</f>
+        <f t="shared" ref="AH8:AH12" si="5">+P8*(1-A8)</f>
         <v>0</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" ref="AI8:AI72" si="6">+(1-A8)*(1-P8)</f>
+        <f t="shared" ref="AI8:AI12" si="6">+(1-A8)*(1-P8)</f>
         <v>1</v>
       </c>
       <c r="AJ8" s="13"/>
@@ -4428,52 +4428,52 @@
       <c r="Q11" s="34"/>
       <c r="R11" s="13"/>
       <c r="S11" s="2">
-        <f t="shared" ref="S11:S73" si="7">IF(J11=$S$7,1,0)</f>
+        <f t="shared" ref="S11:S15" si="7">IF(J11=$S$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="T11" s="2">
-        <f t="shared" ref="T11:T73" si="8">IF(J11=$T$7,1,0)</f>
+        <f t="shared" ref="T11:T15" si="8">IF(J11=$T$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" ref="U11:U73" si="9">IF(J11=$U$7,1,0)</f>
+        <f t="shared" ref="U11:U15" si="9">IF(J11=$U$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" ref="V11:V73" si="10">IF(J11=$V$7,1,0)</f>
+        <f t="shared" ref="V11:V15" si="10">IF(J11=$V$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="W11" s="2">
-        <f t="shared" ref="W11:W73" si="11">IF(J11=$W$7,1,0)</f>
+        <f t="shared" ref="W11:W15" si="11">IF(J11=$W$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="X11" s="2">
-        <f t="shared" ref="X11:X73" si="12">IF(J11=$X$7,1,0)</f>
+        <f t="shared" ref="X11:X15" si="12">IF(J11=$X$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Y11" s="2">
-        <f t="shared" ref="Y11:Y73" si="13">IF(J11=$Y$7,1,0)</f>
+        <f t="shared" ref="Y11:Y15" si="13">IF(J11=$Y$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" ref="Z11:Z73" si="14">IF(J11=$Z$7,1,0)</f>
+        <f t="shared" ref="Z11:Z15" si="14">IF(J11=$Z$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" ref="AA11:AA73" si="15">IF(J11=$AA$7,1,0)</f>
+        <f t="shared" ref="AA11:AA15" si="15">IF(J11=$AA$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB11" s="2">
-        <f t="shared" ref="AB11:AB73" si="16">IF(J11=$AB$7,1,0)</f>
+        <f t="shared" ref="AB11:AB15" si="16">IF(J11=$AB$7,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2">
-        <f t="shared" ref="AD11:AD73" si="17">+O11*P11</f>
+        <f t="shared" ref="AD11:AD15" si="17">+O11*P11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" ref="AE11:AE73" si="18">O11*(1-P11)</f>
+        <f t="shared" ref="AE11:AE15" si="18">O11*(1-P11)</f>
         <v>1</v>
       </c>
       <c r="AF11" s="2">
@@ -11453,13 +11453,13 @@
       <c r="AT67" s="13"/>
     </row>
     <row r="68" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="36">
-        <v>0</v>
-      </c>
-      <c r="B68" s="36">
-        <v>1</v>
-      </c>
-      <c r="C68" s="36">
+      <c r="A68" s="33">
+        <v>0</v>
+      </c>
+      <c r="B68" s="33">
+        <v>1</v>
+      </c>
+      <c r="C68" s="33">
         <v>5</v>
       </c>
       <c r="D68" s="34" t="s">
@@ -13820,54 +13820,56 @@
       <c r="AT86" s="3"/>
     </row>
     <row r="87" spans="1:46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="36">
-        <v>0</v>
-      </c>
-      <c r="B87" s="36">
-        <v>1</v>
-      </c>
-      <c r="C87" s="36">
+      <c r="A87" s="33">
+        <v>0</v>
+      </c>
+      <c r="B87" s="33">
+        <v>1</v>
+      </c>
+      <c r="C87" s="33">
         <v>6</v>
       </c>
-      <c r="D87" s="37" t="s">
+      <c r="D87" s="34" t="s">
         <v>641</v>
       </c>
-      <c r="E87" s="37" t="s">
+      <c r="E87" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="F87" s="37" t="s">
-        <v>439</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H87" s="37" t="s">
+      <c r="F87" s="34" t="s">
+        <v>618</v>
+      </c>
+      <c r="G87" s="34" t="s">
+        <v>655</v>
+      </c>
+      <c r="H87" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I87" s="36" t="s">
-        <v>440</v>
-      </c>
-      <c r="J87" s="36">
-        <v>4</v>
-      </c>
-      <c r="K87" s="36" t="s">
+      <c r="I87" s="33" t="s">
+        <v>619</v>
+      </c>
+      <c r="J87" s="33">
+        <v>1</v>
+      </c>
+      <c r="K87" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L87" s="36" t="s">
+      <c r="L87" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="M87" s="37" t="s">
+      <c r="M87" s="34" t="s">
         <v>516</v>
       </c>
-      <c r="N87" s="37" t="s">
-        <v>879</v>
-      </c>
-      <c r="O87" s="38"/>
-      <c r="P87" s="36"/>
-      <c r="Q87" s="37"/>
+      <c r="N87" s="34" t="s">
+        <v>880</v>
+      </c>
+      <c r="O87" s="35">
+        <v>1</v>
+      </c>
+      <c r="P87" s="33"/>
+      <c r="Q87" s="34"/>
       <c r="S87" s="2">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="2">
         <f t="shared" si="40"/>
@@ -13879,7 +13881,7 @@
       </c>
       <c r="V87" s="2">
         <f t="shared" si="42"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" s="2">
         <f t="shared" si="43"/>
@@ -13911,7 +13913,7 @@
       </c>
       <c r="AE87" s="2">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF87" s="2">
         <f t="shared" si="35"/>
@@ -13919,7 +13921,7 @@
       </c>
       <c r="AG87" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH87" s="2">
         <f t="shared" si="37"/>
@@ -13941,55 +13943,57 @@
       <c r="AT87" s="3"/>
     </row>
     <row r="88" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="36">
-        <v>1</v>
-      </c>
-      <c r="B88" s="36">
-        <v>1</v>
-      </c>
-      <c r="C88" s="36">
+      <c r="A88" s="33">
+        <v>1</v>
+      </c>
+      <c r="B88" s="33">
+        <v>1</v>
+      </c>
+      <c r="C88" s="33">
         <v>6</v>
       </c>
-      <c r="D88" s="37" t="s">
+      <c r="D88" s="34" t="s">
         <v>641</v>
       </c>
-      <c r="E88" s="37" t="s">
+      <c r="E88" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="F88" s="37" t="s">
-        <v>618</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>655</v>
-      </c>
-      <c r="H88" s="37" t="s">
+      <c r="F88" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="G88" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H88" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I88" s="36" t="s">
-        <v>619</v>
-      </c>
-      <c r="J88" s="36">
-        <v>1</v>
-      </c>
-      <c r="K88" s="36" t="s">
+      <c r="I88" s="33" t="s">
+        <v>440</v>
+      </c>
+      <c r="J88" s="33">
+        <v>4</v>
+      </c>
+      <c r="K88" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L88" s="36" t="s">
+      <c r="L88" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="M88" s="37" t="s">
+      <c r="M88" s="34" t="s">
         <v>516</v>
       </c>
-      <c r="N88" s="37" t="s">
-        <v>879</v>
-      </c>
-      <c r="O88" s="38"/>
-      <c r="P88" s="36"/>
-      <c r="Q88" s="37"/>
+      <c r="N88" s="34" t="s">
+        <v>880</v>
+      </c>
+      <c r="O88" s="35">
+        <v>1</v>
+      </c>
+      <c r="P88" s="33"/>
+      <c r="Q88" s="34"/>
       <c r="R88" s="13"/>
       <c r="S88" s="2">
         <f t="shared" si="39"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" s="2">
         <f t="shared" si="40"/>
@@ -14001,7 +14005,7 @@
       </c>
       <c r="V88" s="2">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="2">
         <f t="shared" si="43"/>
@@ -14034,7 +14038,7 @@
       </c>
       <c r="AE88" s="2">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF88" s="2">
         <f t="shared" si="35"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2852C06-0609-4CC7-9701-157B5D09DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0933A056-CA54-427D-9894-CF5803C0F911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="917">
   <si>
     <t>Recensore</t>
   </si>
@@ -13853,8 +13853,8 @@
       <c r="K87" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L87" s="33" t="s">
-        <v>306</v>
+      <c r="L87" s="33">
+        <v>30</v>
       </c>
       <c r="M87" s="34" t="s">
         <v>516</v>
@@ -13976,8 +13976,8 @@
       <c r="K88" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L88" s="33" t="s">
-        <v>306</v>
+      <c r="L88" s="33">
+        <v>30</v>
       </c>
       <c r="M88" s="34" t="s">
         <v>516</v>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0933A056-CA54-427D-9894-CF5803C0F911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA60B790-70E9-4F01-B69B-847B14EF757C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="916">
   <si>
     <t>Recensore</t>
   </si>
@@ -1811,9 +1811,6 @@
   </si>
   <si>
     <t>1 nuvola, 1 focaccia o pizza crunch, 1 pizza contemporanea</t>
-  </si>
-  <si>
-    <t>33</t>
   </si>
   <si>
     <t>Tartatea Torteria</t>
@@ -3725,15 +3722,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3755,18 +3752,18 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3856,7 +3853,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3864,7 +3861,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -3877,13 +3874,13 @@
     </row>
     <row r="7" spans="1:46" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
+        <v>681</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>682</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>683</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>684</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>13</v>
@@ -3904,16 +3901,16 @@
         <v>11</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>0</v>
@@ -3925,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R7" s="25"/>
       <c r="S7" s="25">
@@ -4009,22 +4006,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>236</v>
       </c>
       <c r="F8" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>659</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>660</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J8" s="33">
         <v>99</v>
@@ -4033,13 +4030,13 @@
         <v>300</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4165,7 +4162,7 @@
         <v>103</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O9" s="35">
         <v>1</v>
@@ -4290,10 +4287,10 @@
         <v>130</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4395,7 +4392,7 @@
         <v>236</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>107</v>
@@ -4410,16 +4407,16 @@
         <v>99</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L11" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="M11" s="34" t="s">
         <v>680</v>
       </c>
-      <c r="M11" s="34" t="s">
-        <v>681</v>
-      </c>
       <c r="N11" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O11" s="35">
         <v>1</v>
@@ -4515,13 +4512,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>278</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G12" s="40" t="s">
         <v>371</v>
@@ -4530,7 +4527,7 @@
         <v>190</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J12" s="39">
         <v>99</v>
@@ -4539,10 +4536,10 @@
         <v>300</v>
       </c>
       <c r="L12" s="39" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="N12" s="40"/>
       <c r="O12" s="41"/>
@@ -4667,7 +4664,7 @@
         <v>103</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O13" s="35">
         <v>1</v>
@@ -4765,13 +4762,13 @@
         <v>1</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>278</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>88</v>
@@ -4780,7 +4777,7 @@
         <v>190</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J14" s="36">
         <v>2</v>
@@ -4795,7 +4792,7 @@
         <v>195</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4889,20 +4886,20 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>278</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>190</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
@@ -5005,13 +5002,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>82</v>
@@ -5020,7 +5017,7 @@
         <v>190</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="J16" s="20">
         <v>1</v>
@@ -5127,22 +5124,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>235</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G17" s="34" t="s">
         <v>103</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J17" s="33">
         <v>99</v>
@@ -5154,10 +5151,10 @@
         <v>47</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5253,22 +5250,22 @@
         <v>2</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>235</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>190</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J18" s="36"/>
       <c r="K18" s="36" t="s">
@@ -5278,10 +5275,10 @@
         <v>45</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5524,10 +5521,10 @@
         <v>507</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N20" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O20" s="35">
         <v>1</v>
@@ -5774,10 +5771,10 @@
         <v>301</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O22" s="35">
         <v>1</v>
@@ -5905,7 +5902,7 @@
         <v>246</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O23" s="35">
         <v>1</v>
@@ -6031,7 +6028,7 @@
         <v>510</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O24" s="35">
         <v>1</v>
@@ -6127,22 +6124,22 @@
         <v>2</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E25" s="34" t="s">
         <v>278</v>
       </c>
       <c r="F25" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="G25" s="34" t="s">
         <v>599</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>600</v>
       </c>
       <c r="H25" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J25" s="33">
         <v>99</v>
@@ -6151,13 +6148,13 @@
         <v>290</v>
       </c>
       <c r="L25" s="33" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="M25" s="34" t="s">
         <v>195</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O25" s="35">
         <v>1</v>
@@ -6259,10 +6256,10 @@
         <v>235</v>
       </c>
       <c r="F26" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="G26" s="34" t="s">
         <v>765</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>766</v>
       </c>
       <c r="H26" s="34" t="s">
         <v>190</v>
@@ -6283,7 +6280,7 @@
         <v>195</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O26" s="35">
         <v>1</v>
@@ -6409,7 +6406,7 @@
         <v>103</v>
       </c>
       <c r="N27" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O27" s="35">
         <v>1</v>
@@ -6507,13 +6504,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>236</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>137</v>
@@ -6522,7 +6519,7 @@
         <v>190</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J28" s="20">
         <v>6</v>
@@ -6531,7 +6528,7 @@
         <v>385</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>195</v>
@@ -6629,13 +6626,13 @@
         <v>2</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>278</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>88</v>
@@ -6644,7 +6641,7 @@
         <v>190</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J29" s="33">
         <v>2</v>
@@ -6656,10 +6653,10 @@
         <v>507</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6780,10 +6777,10 @@
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="37" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O30" s="38"/>
       <c r="P30" s="36"/>
@@ -6901,18 +6898,18 @@
         <v>300</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O31" s="38"/>
       <c r="P31" s="36"/>
       <c r="Q31" s="37" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="R31" s="13"/>
       <c r="S31" s="2">
@@ -7033,7 +7030,7 @@
         <v>246</v>
       </c>
       <c r="N32" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O32" s="35">
         <v>1</v>
@@ -7129,11 +7126,11 @@
         <v>2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>88</v>
@@ -7142,7 +7139,7 @@
         <v>190</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J33" s="33"/>
       <c r="K33" s="33" t="s">
@@ -7151,7 +7148,7 @@
       <c r="L33" s="33"/>
       <c r="M33" s="34"/>
       <c r="N33" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O33" s="35">
         <v>1</v>
@@ -7249,13 +7246,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>278</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>82</v>
@@ -7264,7 +7261,7 @@
         <v>190</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20" t="s">
@@ -7274,7 +7271,7 @@
         <v>75</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="N34" s="19"/>
       <c r="O34" s="18"/>
@@ -7396,7 +7393,7 @@
         <v>505</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="N35" s="19"/>
       <c r="O35" s="18"/>
@@ -7491,22 +7488,22 @@
         <v>3</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E36" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="J36" s="33"/>
       <c r="K36" s="33" t="s">
@@ -7516,17 +7513,17 @@
         <v>55</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N36" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O36" s="35">
         <v>1</v>
       </c>
       <c r="P36" s="33"/>
       <c r="Q36" s="34" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="2">
@@ -7647,7 +7644,7 @@
         <v>195</v>
       </c>
       <c r="N37" s="37" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O37" s="38"/>
       <c r="P37" s="36"/>
@@ -7771,7 +7768,7 @@
         <v>304</v>
       </c>
       <c r="N38" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O38" s="35">
         <v>1</v>
@@ -7869,22 +7866,22 @@
         <v>3</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>234</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G39" s="37" t="s">
         <v>103</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J39" s="36">
         <v>99</v>
@@ -7896,10 +7893,10 @@
         <v>65</v>
       </c>
       <c r="M39" s="37" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="N39" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O39" s="38"/>
       <c r="P39" s="36"/>
@@ -8008,7 +8005,7 @@
         <v>190</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J40" s="20">
         <v>99</v>
@@ -8020,7 +8017,7 @@
         <v>305</v>
       </c>
       <c r="M40" s="19" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N40" s="19"/>
       <c r="O40" s="18"/>
@@ -8115,13 +8112,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>82</v>
@@ -8130,7 +8127,7 @@
         <v>190</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="J41" s="36">
         <v>1</v>
@@ -8142,10 +8139,10 @@
         <v>50</v>
       </c>
       <c r="M41" s="37" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N41" s="37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="36"/>
@@ -8239,13 +8236,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E42" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F42" s="34" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G42" s="34" t="s">
         <v>102</v>
@@ -8254,7 +8251,7 @@
         <v>190</v>
       </c>
       <c r="I42" s="33" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J42" s="33">
         <v>2</v>
@@ -8266,10 +8263,10 @@
         <v>505</v>
       </c>
       <c r="M42" s="34" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="N42" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O42" s="35">
         <v>1</v>
@@ -8392,7 +8389,7 @@
         <v>40</v>
       </c>
       <c r="M43" s="19" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N43" s="19"/>
       <c r="O43" s="18"/>
@@ -8636,7 +8633,7 @@
         <v>38</v>
       </c>
       <c r="M45" s="19" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N45" s="19"/>
       <c r="O45" s="18"/>
@@ -8758,7 +8755,7 @@
         <v>25</v>
       </c>
       <c r="M46" s="19" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="N46" s="19"/>
       <c r="O46" s="18"/>
@@ -8853,13 +8850,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>234</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>82</v>
@@ -8868,7 +8865,7 @@
         <v>190</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J47" s="20">
         <v>1</v>
@@ -9005,7 +9002,7 @@
         <v>513</v>
       </c>
       <c r="N48" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O48" s="35">
         <v>1</v>
@@ -9128,10 +9125,10 @@
         <v>303</v>
       </c>
       <c r="M49" s="34" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N49" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O49" s="35">
         <v>1</v>
@@ -9257,7 +9254,7 @@
         <v>302</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9383,7 +9380,7 @@
         <v>195</v>
       </c>
       <c r="N51" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O51" s="35">
         <v>1</v>
@@ -9479,22 +9476,22 @@
         <v>3</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E52" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H52" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I52" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J52" s="33">
         <v>99</v>
@@ -9503,13 +9500,13 @@
         <v>298</v>
       </c>
       <c r="L52" s="33" t="s">
+        <v>673</v>
+      </c>
+      <c r="M52" s="34" t="s">
         <v>674</v>
       </c>
-      <c r="M52" s="34" t="s">
-        <v>675</v>
-      </c>
       <c r="N52" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O52" s="35">
         <v>1</v>
@@ -9757,7 +9754,7 @@
         <v>302</v>
       </c>
       <c r="N54" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O54" s="35">
         <v>1</v>
@@ -9859,7 +9856,7 @@
         <v>235</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G55" s="34" t="s">
         <v>490</v>
@@ -9883,7 +9880,7 @@
         <v>265</v>
       </c>
       <c r="N55" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O55" s="35">
         <v>1</v>
@@ -9979,13 +9976,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E56" s="40" t="s">
         <v>235</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G56" s="40" t="s">
         <v>103</v>
@@ -9994,7 +9991,7 @@
         <v>190</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J56" s="39">
         <v>99</v>
@@ -10003,16 +10000,16 @@
         <v>292</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="M56" s="40" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="N56" s="40"/>
       <c r="O56" s="41"/>
       <c r="P56" s="39"/>
       <c r="Q56" s="40" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R56" s="13"/>
       <c r="S56" s="2">
@@ -10103,13 +10100,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E57" s="34" t="s">
         <v>234</v>
       </c>
       <c r="F57" s="34" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G57" s="34" t="s">
         <v>109</v>
@@ -10118,7 +10115,7 @@
         <v>190</v>
       </c>
       <c r="I57" s="33" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="J57" s="33"/>
       <c r="K57" s="33" t="s">
@@ -10131,7 +10128,7 @@
         <v>195</v>
       </c>
       <c r="N57" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O57" s="35">
         <v>1</v>
@@ -10351,13 +10348,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E59" s="34" t="s">
         <v>235</v>
       </c>
       <c r="F59" s="34" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G59" s="34" t="s">
         <v>88</v>
@@ -10366,7 +10363,7 @@
         <v>190</v>
       </c>
       <c r="I59" s="33" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J59" s="33">
         <v>2</v>
@@ -10377,7 +10374,7 @@
       <c r="L59" s="33"/>
       <c r="M59" s="34"/>
       <c r="N59" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O59" s="35">
         <v>1</v>
@@ -10505,7 +10502,7 @@
         <v>247</v>
       </c>
       <c r="N60" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O60" s="35">
         <v>1</v>
@@ -10630,7 +10627,7 @@
         <v>305</v>
       </c>
       <c r="M61" s="19" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N61" s="19"/>
       <c r="O61" s="18"/>
@@ -10725,13 +10722,13 @@
         <v>5</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E62" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F62" s="34" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G62" s="34" t="s">
         <v>72</v>
@@ -10740,7 +10737,7 @@
         <v>190</v>
       </c>
       <c r="I62" s="33" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="J62" s="33">
         <v>4</v>
@@ -10751,7 +10748,7 @@
       <c r="L62" s="33"/>
       <c r="M62" s="34"/>
       <c r="N62" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O62" s="35">
         <v>1</v>
@@ -10971,22 +10968,22 @@
         <v>5</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>237</v>
       </c>
       <c r="F64" s="19" t="s">
+        <v>731</v>
+      </c>
+      <c r="G64" s="19" t="s">
         <v>732</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>733</v>
       </c>
       <c r="H64" s="19" t="s">
         <v>190</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J64" s="20">
         <v>99</v>
@@ -10998,7 +10995,7 @@
         <v>30</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="18"/>
@@ -11093,13 +11090,13 @@
         <v>5</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>145</v>
@@ -11108,7 +11105,7 @@
         <v>190</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J65" s="20">
         <v>99</v>
@@ -11120,7 +11117,7 @@
         <v>40</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="N65" s="19"/>
       <c r="O65" s="18"/>
@@ -11215,13 +11212,13 @@
         <v>5</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G66" s="19" t="s">
         <v>103</v>
@@ -11230,7 +11227,7 @@
         <v>190</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="J66" s="20">
         <v>99</v>
@@ -11242,7 +11239,7 @@
         <v>40</v>
       </c>
       <c r="M66" s="19" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="N66" s="19"/>
       <c r="O66" s="18"/>
@@ -11337,13 +11334,13 @@
         <v>5</v>
       </c>
       <c r="D67" s="34" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F67" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G67" s="34" t="s">
         <v>82</v>
@@ -11352,7 +11349,7 @@
         <v>190</v>
       </c>
       <c r="I67" s="33" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J67" s="33">
         <v>1</v>
@@ -11364,10 +11361,10 @@
         <v>507</v>
       </c>
       <c r="M67" s="34" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N67" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O67" s="35">
         <v>1</v>
@@ -11490,10 +11487,10 @@
         <v>31</v>
       </c>
       <c r="M68" s="34" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N68" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O68" s="35">
         <v>1</v>
@@ -11579,51 +11576,53 @@
       <c r="AT68" s="13"/>
     </row>
     <row r="69" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
-        <v>0</v>
-      </c>
-      <c r="B69" s="36">
-        <v>1</v>
-      </c>
-      <c r="C69" s="36">
+      <c r="A69" s="33">
+        <v>0</v>
+      </c>
+      <c r="B69" s="33">
+        <v>1</v>
+      </c>
+      <c r="C69" s="33">
         <v>5</v>
       </c>
-      <c r="D69" s="37" t="s">
+      <c r="D69" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="E69" s="37" t="s">
+      <c r="E69" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F69" s="37" t="s">
+      <c r="F69" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="G69" s="37" t="s">
+      <c r="G69" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="H69" s="37" t="s">
+      <c r="H69" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I69" s="36" t="s">
+      <c r="I69" s="33" t="s">
         <v>561</v>
       </c>
-      <c r="J69" s="36">
+      <c r="J69" s="33">
         <v>5</v>
       </c>
-      <c r="K69" s="36" t="s">
+      <c r="K69" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="L69" s="36" t="s">
-        <v>564</v>
-      </c>
-      <c r="M69" s="37" t="s">
+      <c r="L69" s="33">
+        <v>36</v>
+      </c>
+      <c r="M69" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="N69" s="37" t="s">
-        <v>850</v>
-      </c>
-      <c r="O69" s="38"/>
-      <c r="P69" s="36"/>
-      <c r="Q69" s="37"/>
+      <c r="N69" s="34" t="s">
+        <v>857</v>
+      </c>
+      <c r="O69" s="35">
+        <v>1</v>
+      </c>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="34"/>
       <c r="R69" s="13"/>
       <c r="S69" s="2">
         <f t="shared" si="23"/>
@@ -11672,7 +11671,7 @@
       </c>
       <c r="AE69" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF69" s="2">
         <f t="shared" si="19"/>
@@ -11680,7 +11679,7 @@
       </c>
       <c r="AG69" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH69" s="2">
         <f t="shared" si="21"/>
@@ -11713,13 +11712,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="19" t="s">
+        <v>903</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="F70" s="19" t="s">
         <v>904</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>841</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>905</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>72</v>
@@ -11728,7 +11727,7 @@
         <v>190</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J70" s="20">
         <v>4</v>
@@ -11740,7 +11739,7 @@
         <v>45</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N70" s="19"/>
       <c r="O70" s="18"/>
@@ -11835,13 +11834,13 @@
         <v>5</v>
       </c>
       <c r="D71" s="34" t="s">
+        <v>815</v>
+      </c>
+      <c r="E71" s="34" t="s">
         <v>816</v>
       </c>
-      <c r="E71" s="34" t="s">
-        <v>817</v>
-      </c>
       <c r="F71" s="34" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G71" s="34" t="s">
         <v>72</v>
@@ -11850,7 +11849,7 @@
         <v>190</v>
       </c>
       <c r="I71" s="33" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J71" s="33"/>
       <c r="K71" s="33" t="s">
@@ -11860,10 +11859,10 @@
         <v>45</v>
       </c>
       <c r="M71" s="34" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O71" s="35">
         <v>1</v>
@@ -11983,13 +11982,13 @@
         <v>291</v>
       </c>
       <c r="L72" s="36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="M72" s="37" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N72" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O72" s="38"/>
       <c r="P72" s="36"/>
@@ -12083,22 +12082,22 @@
         <v>5</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E73" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F73" s="34" t="s">
+        <v>808</v>
+      </c>
+      <c r="G73" s="34" t="s">
         <v>809</v>
-      </c>
-      <c r="G73" s="34" t="s">
-        <v>810</v>
       </c>
       <c r="H73" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I73" s="33" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="J73" s="33">
         <v>1</v>
@@ -12113,7 +12112,7 @@
         <v>513</v>
       </c>
       <c r="N73" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O73" s="35">
         <v>1</v>
@@ -12209,10 +12208,10 @@
         <v>5</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F74" s="34" t="s">
         <v>68</v>
@@ -12224,7 +12223,7 @@
         <v>190</v>
       </c>
       <c r="I74" s="33" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J74" s="33">
         <v>2</v>
@@ -12239,7 +12238,7 @@
         <v>513</v>
       </c>
       <c r="N74" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O74" s="35">
         <v>1</v>
@@ -12606,10 +12605,10 @@
         <v>70</v>
       </c>
       <c r="M77" s="34" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N77" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O77" s="35">
         <v>1</v>
@@ -12827,13 +12826,13 @@
         <v>6</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>241</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>88</v>
@@ -12842,7 +12841,7 @@
         <v>190</v>
       </c>
       <c r="I79" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="J79" s="20">
         <v>2</v>
@@ -12854,7 +12853,7 @@
         <v>301</v>
       </c>
       <c r="M79" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N79" s="19"/>
       <c r="O79" s="18"/>
@@ -12949,13 +12948,13 @@
         <v>6</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E80" s="19" t="s">
         <v>241</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>82</v>
@@ -12964,7 +12963,7 @@
         <v>190</v>
       </c>
       <c r="I80" s="20" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J80" s="20">
         <v>1</v>
@@ -12976,13 +12975,13 @@
         <v>301</v>
       </c>
       <c r="M80" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N80" s="19"/>
       <c r="O80" s="18"/>
       <c r="P80" s="20"/>
       <c r="Q80" s="19" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="R80" s="13"/>
       <c r="S80" s="2">
@@ -13103,7 +13102,7 @@
         <v>508</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13199,22 +13198,22 @@
         <v>6</v>
       </c>
       <c r="D82" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="E82" s="34" t="s">
         <v>570</v>
       </c>
-      <c r="E82" s="34" t="s">
+      <c r="F82" s="34" t="s">
         <v>571</v>
       </c>
-      <c r="F82" s="34" t="s">
-        <v>572</v>
-      </c>
       <c r="G82" s="34" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H82" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I82" s="33" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J82" s="33">
         <v>1</v>
@@ -13229,7 +13228,7 @@
         <v>103</v>
       </c>
       <c r="N82" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O82" s="35">
         <v>1</v>
@@ -13357,7 +13356,7 @@
         <v>248</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13453,13 +13452,13 @@
         <v>6</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E84" s="34" t="s">
         <v>519</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G84" s="34" t="s">
         <v>495</v>
@@ -13468,7 +13467,7 @@
         <v>190</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J84" s="33">
         <v>2</v>
@@ -13483,7 +13482,7 @@
         <v>103</v>
       </c>
       <c r="N84" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O84" s="35">
         <v>1</v>
@@ -13581,13 +13580,13 @@
         <v>6</v>
       </c>
       <c r="D85" s="34" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E85" s="34" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F85" s="34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G85" s="34" t="s">
         <v>144</v>
@@ -13596,7 +13595,7 @@
         <v>190</v>
       </c>
       <c r="I85" s="33" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J85" s="33">
         <v>99</v>
@@ -13608,10 +13607,10 @@
         <v>507</v>
       </c>
       <c r="M85" s="34" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N85" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O85" s="35">
         <v>1</v>
@@ -13707,13 +13706,13 @@
         <v>6</v>
       </c>
       <c r="D86" s="34" t="s">
+        <v>880</v>
+      </c>
+      <c r="E86" s="34" t="s">
         <v>881</v>
       </c>
-      <c r="E86" s="34" t="s">
+      <c r="F86" s="34" t="s">
         <v>882</v>
-      </c>
-      <c r="F86" s="34" t="s">
-        <v>883</v>
       </c>
       <c r="G86" s="34" t="s">
         <v>88</v>
@@ -13722,7 +13721,7 @@
         <v>190</v>
       </c>
       <c r="I86" s="33" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J86" s="33">
         <v>2</v>
@@ -13734,10 +13733,10 @@
         <v>45</v>
       </c>
       <c r="M86" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="N86" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O86" s="35">
         <v>1</v>
@@ -13830,22 +13829,22 @@
         <v>6</v>
       </c>
       <c r="D87" s="34" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E87" s="34" t="s">
         <v>481</v>
       </c>
       <c r="F87" s="34" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I87" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J87" s="33">
         <v>1</v>
@@ -13860,7 +13859,7 @@
         <v>516</v>
       </c>
       <c r="N87" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O87" s="35">
         <v>1</v>
@@ -13953,7 +13952,7 @@
         <v>6</v>
       </c>
       <c r="D88" s="34" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E88" s="34" t="s">
         <v>481</v>
@@ -13983,7 +13982,7 @@
         <v>516</v>
       </c>
       <c r="N88" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -14109,7 +14108,7 @@
         <v>248</v>
       </c>
       <c r="N89" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O89" s="35">
         <v>1</v>
@@ -14205,20 +14204,20 @@
         <v>6</v>
       </c>
       <c r="D90" s="34" t="s">
+        <v>862</v>
+      </c>
+      <c r="E90" s="34" t="s">
         <v>863</v>
       </c>
-      <c r="E90" s="34" t="s">
+      <c r="F90" s="34" t="s">
         <v>864</v>
-      </c>
-      <c r="F90" s="34" t="s">
-        <v>865</v>
       </c>
       <c r="G90" s="34"/>
       <c r="H90" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I90" s="33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J90" s="33"/>
       <c r="K90" s="33" t="s">
@@ -14227,7 +14226,7 @@
       <c r="L90" s="33"/>
       <c r="M90" s="34"/>
       <c r="N90" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O90" s="35">
         <v>1</v>
@@ -14340,7 +14339,7 @@
         <v>190</v>
       </c>
       <c r="I91" s="33" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J91" s="33">
         <v>5</v>
@@ -14355,7 +14354,7 @@
         <v>195</v>
       </c>
       <c r="N91" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O91" s="35">
         <v>1</v>
@@ -14451,7 +14450,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E92" s="34" t="s">
         <v>519</v>
@@ -14478,10 +14477,10 @@
         <v>305</v>
       </c>
       <c r="M92" s="34" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N92" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O92" s="35">
         <v>1</v>
@@ -14705,7 +14704,7 @@
         <v>40</v>
       </c>
       <c r="F94" s="40" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G94" s="40" t="s">
         <v>103</v>
@@ -14726,10 +14725,10 @@
         <v>305</v>
       </c>
       <c r="M94" s="40" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N94" s="40" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O94" s="41">
         <v>1</v>
@@ -14855,7 +14854,7 @@
         <v>309</v>
       </c>
       <c r="N95" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O95" s="35">
         <v>1</v>
@@ -14983,7 +14982,7 @@
         <v>309</v>
       </c>
       <c r="N96" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O96" s="35">
         <v>1</v>
@@ -15111,7 +15110,7 @@
         <v>309</v>
       </c>
       <c r="N97" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O97" s="35">
         <v>1</v>
@@ -15120,7 +15119,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="R97" s="13"/>
       <c r="S97" s="2">
@@ -15217,7 +15216,7 @@
         <v>40</v>
       </c>
       <c r="F98" s="34" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G98" s="34" t="s">
         <v>137</v>
@@ -15226,7 +15225,7 @@
         <v>190</v>
       </c>
       <c r="I98" s="33" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J98" s="33">
         <v>99</v>
@@ -15241,7 +15240,7 @@
         <v>268</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15367,7 +15366,7 @@
         <v>268</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15463,13 +15462,13 @@
         <v>7</v>
       </c>
       <c r="D100" s="34" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E100" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F100" s="34" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G100" s="34" t="s">
         <v>72</v>
@@ -15478,7 +15477,7 @@
         <v>190</v>
       </c>
       <c r="I100" s="33" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J100" s="33">
         <v>3</v>
@@ -15490,10 +15489,10 @@
         <v>28</v>
       </c>
       <c r="M100" s="34" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N100" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O100" s="35">
         <v>1</v>
@@ -15592,7 +15591,7 @@
         <v>335</v>
       </c>
       <c r="E101" s="34" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F101" s="34" t="s">
         <v>356</v>
@@ -15619,7 +15618,7 @@
         <v>195</v>
       </c>
       <c r="N101" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O101" s="35">
         <v>1</v>
@@ -15715,22 +15714,22 @@
         <v>7</v>
       </c>
       <c r="D102" s="19" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E102" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H102" s="19" t="s">
         <v>190</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J102" s="20">
         <v>99</v>
@@ -15742,7 +15741,7 @@
         <v>306</v>
       </c>
       <c r="M102" s="19" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="N102" s="19"/>
       <c r="O102" s="18"/>
@@ -15837,13 +15836,13 @@
         <v>7</v>
       </c>
       <c r="D103" s="34" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E103" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G103" s="34" t="s">
         <v>72</v>
@@ -15852,7 +15851,7 @@
         <v>190</v>
       </c>
       <c r="I103" s="33" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J103" s="33">
         <v>3</v>
@@ -15864,10 +15863,10 @@
         <v>30</v>
       </c>
       <c r="M103" s="34" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N103" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O103" s="35">
         <v>1</v>
@@ -15993,7 +15992,7 @@
         <v>563</v>
       </c>
       <c r="N104" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O104" s="35">
         <v>1</v>
@@ -16079,51 +16078,53 @@
       <c r="AT104" s="13"/>
     </row>
     <row r="105" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="36">
-        <v>0</v>
-      </c>
-      <c r="B105" s="36">
-        <v>1</v>
-      </c>
-      <c r="C105" s="36">
+      <c r="A105" s="33">
+        <v>0</v>
+      </c>
+      <c r="B105" s="33">
+        <v>1</v>
+      </c>
+      <c r="C105" s="33">
         <v>7</v>
       </c>
-      <c r="D105" s="37" t="s">
+      <c r="D105" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="E105" s="37" t="s">
+      <c r="E105" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F105" s="37" t="s">
+      <c r="F105" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="G105" s="37" t="s">
+      <c r="G105" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H105" s="37" t="s">
+      <c r="H105" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I105" s="36" t="s">
+      <c r="I105" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="J105" s="36">
-        <v>1</v>
-      </c>
-      <c r="K105" s="36" t="s">
+      <c r="J105" s="33">
+        <v>1</v>
+      </c>
+      <c r="K105" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="L105" s="36" t="s">
+      <c r="L105" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="M105" s="37" t="s">
+      <c r="M105" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="N105" s="37" t="s">
+      <c r="N105" s="34" t="s">
         <v>879</v>
       </c>
-      <c r="O105" s="38"/>
-      <c r="P105" s="36"/>
-      <c r="Q105" s="37"/>
+      <c r="O105" s="35">
+        <v>1</v>
+      </c>
+      <c r="P105" s="33"/>
+      <c r="Q105" s="34"/>
       <c r="R105" s="13"/>
       <c r="S105" s="2">
         <f t="shared" si="39"/>
@@ -16172,7 +16173,7 @@
       </c>
       <c r="AE105" s="2">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF105" s="2">
         <f t="shared" si="35"/>
@@ -16180,7 +16181,7 @@
       </c>
       <c r="AG105" s="2">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH105" s="2">
         <f t="shared" si="37"/>
@@ -16213,13 +16214,13 @@
         <v>1</v>
       </c>
       <c r="D106" s="34" t="s">
+        <v>686</v>
+      </c>
+      <c r="E106" s="34" t="s">
         <v>687</v>
       </c>
-      <c r="E106" s="34" t="s">
+      <c r="F106" s="34" t="s">
         <v>688</v>
-      </c>
-      <c r="F106" s="34" t="s">
-        <v>689</v>
       </c>
       <c r="G106" s="34" t="s">
         <v>88</v>
@@ -16228,7 +16229,7 @@
         <v>190</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="J106" s="33">
         <v>2</v>
@@ -16240,10 +16241,10 @@
         <v>7</v>
       </c>
       <c r="M106" s="34" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="N106" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O106" s="35">
         <v>1</v>
@@ -16341,13 +16342,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E107" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>88</v>
@@ -16356,7 +16357,7 @@
         <v>190</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J107" s="33">
         <v>2</v>
@@ -16368,10 +16369,10 @@
         <v>5</v>
       </c>
       <c r="M107" s="34" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O107" s="35">
         <v>1</v>
@@ -16380,7 +16381,7 @@
         <v>1</v>
       </c>
       <c r="Q107" s="34" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="R107" s="13"/>
       <c r="S107" s="2">
@@ -16471,13 +16472,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G108" s="34" t="s">
         <v>82</v>
@@ -16501,7 +16502,7 @@
         <v>193</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O108" s="35">
         <v>1</v>
@@ -16510,7 +16511,7 @@
         <v>1</v>
       </c>
       <c r="Q108" s="34" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R108" s="13"/>
       <c r="S108" s="2">
@@ -16601,13 +16602,13 @@
         <v>1</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E109" s="34" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F109" s="34" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G109" s="34" t="s">
         <v>144</v>
@@ -16616,7 +16617,7 @@
         <v>190</v>
       </c>
       <c r="I109" s="33" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J109" s="33">
         <v>99</v>
@@ -16631,7 +16632,7 @@
         <v>193</v>
       </c>
       <c r="N109" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O109" s="35">
         <v>1</v>
@@ -16729,13 +16730,13 @@
         <v>1</v>
       </c>
       <c r="D110" s="34" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E110" s="34" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F110" s="34" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G110" s="34" t="s">
         <v>103</v>
@@ -16744,7 +16745,7 @@
         <v>190</v>
       </c>
       <c r="I110" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J110" s="33">
         <v>99</v>
@@ -16756,10 +16757,10 @@
         <v>9</v>
       </c>
       <c r="M110" s="34" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N110" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O110" s="35">
         <v>1</v>
@@ -17226,7 +17227,7 @@
         <v>166</v>
       </c>
       <c r="E114" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F114" s="34" t="s">
         <v>165</v>
@@ -17253,7 +17254,7 @@
         <v>193</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O114" s="35">
         <v>1</v>
@@ -17379,7 +17380,7 @@
         <v>193</v>
       </c>
       <c r="N115" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O115" s="35">
         <v>1</v>
@@ -17483,16 +17484,16 @@
         <v>61</v>
       </c>
       <c r="F116" s="34" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G116" s="34" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H116" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I116" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J116" s="33">
         <v>99</v>
@@ -17507,7 +17508,7 @@
         <v>193</v>
       </c>
       <c r="N116" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O116" s="35">
         <v>1</v>
@@ -17757,7 +17758,7 @@
         <v>193</v>
       </c>
       <c r="N118" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O118" s="35">
         <v>1</v>
@@ -17855,13 +17856,13 @@
         <v>1</v>
       </c>
       <c r="D119" s="34" t="s">
+        <v>566</v>
+      </c>
+      <c r="E119" s="34" t="s">
+        <v>687</v>
+      </c>
+      <c r="F119" s="34" t="s">
         <v>567</v>
-      </c>
-      <c r="E119" s="34" t="s">
-        <v>688</v>
-      </c>
-      <c r="F119" s="34" t="s">
-        <v>568</v>
       </c>
       <c r="G119" s="34" t="s">
         <v>88</v>
@@ -17870,7 +17871,7 @@
         <v>190</v>
       </c>
       <c r="I119" s="33" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J119" s="33">
         <v>2</v>
@@ -17882,10 +17883,10 @@
         <v>9</v>
       </c>
       <c r="M119" s="34" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="N119" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O119" s="35">
         <v>1</v>
@@ -18132,10 +18133,10 @@
         <v>303</v>
       </c>
       <c r="M121" s="34" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="N121" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O121" s="35">
         <v>1</v>
@@ -18231,22 +18232,22 @@
         <v>2</v>
       </c>
       <c r="D122" s="34" t="s">
+        <v>820</v>
+      </c>
+      <c r="E122" s="34" t="s">
+        <v>753</v>
+      </c>
+      <c r="F122" s="34" t="s">
         <v>821</v>
       </c>
-      <c r="E122" s="34" t="s">
-        <v>754</v>
-      </c>
-      <c r="F122" s="34" t="s">
+      <c r="G122" s="34" t="s">
         <v>822</v>
-      </c>
-      <c r="G122" s="34" t="s">
-        <v>823</v>
       </c>
       <c r="H122" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I122" s="33" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J122" s="33"/>
       <c r="K122" s="33" t="s">
@@ -18256,10 +18257,10 @@
         <v>30</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18382,10 +18383,10 @@
         <v>310</v>
       </c>
       <c r="M123" s="34" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N123" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O123" s="35">
         <v>1</v>
@@ -18483,13 +18484,13 @@
         <v>2</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E124" s="34" t="s">
         <v>241</v>
       </c>
       <c r="F124" s="34" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G124" s="34" t="s">
         <v>160</v>
@@ -18498,7 +18499,7 @@
         <v>190</v>
       </c>
       <c r="I124" s="33" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J124" s="33">
         <v>1</v>
@@ -18507,13 +18508,13 @@
         <v>293</v>
       </c>
       <c r="L124" s="33" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M124" s="34" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="N124" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O124" s="35">
         <v>1</v>
@@ -18859,16 +18860,16 @@
         <v>382</v>
       </c>
       <c r="F127" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="G127" s="19" t="s">
         <v>644</v>
-      </c>
-      <c r="G127" s="19" t="s">
-        <v>645</v>
       </c>
       <c r="H127" s="19" t="s">
         <v>190</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J127" s="20">
         <v>99</v>
@@ -18880,7 +18881,7 @@
         <v>306</v>
       </c>
       <c r="M127" s="19" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N127" s="19"/>
       <c r="O127" s="18"/>
@@ -18981,7 +18982,7 @@
         <v>382</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>204</v>
@@ -19002,7 +19003,7 @@
         <v>306</v>
       </c>
       <c r="M128" s="19" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N128" s="19"/>
       <c r="O128" s="18"/>
@@ -19463,18 +19464,18 @@
         <v>2</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E132" s="34"/>
       <c r="F132" s="34" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G132" s="34"/>
       <c r="H132" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I132" s="33" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="J132" s="33"/>
       <c r="K132" s="33" t="s">
@@ -19484,10 +19485,10 @@
         <v>22</v>
       </c>
       <c r="M132" s="34" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="N132" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O132" s="35">
         <v>1</v>
@@ -19612,10 +19613,10 @@
         <v>307</v>
       </c>
       <c r="M133" s="34" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="N133" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O133" s="35">
         <v>1</v>
@@ -19728,7 +19729,7 @@
         <v>190</v>
       </c>
       <c r="I134" s="33" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J134" s="33">
         <v>5</v>
@@ -19743,7 +19744,7 @@
         <v>456</v>
       </c>
       <c r="N134" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O134" s="35">
         <v>1</v>
@@ -19961,13 +19962,13 @@
         <v>2</v>
       </c>
       <c r="D136" s="37" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E136" s="37" t="s">
         <v>279</v>
       </c>
       <c r="F136" s="37" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G136" s="37" t="s">
         <v>145</v>
@@ -19976,7 +19977,7 @@
         <v>190</v>
       </c>
       <c r="I136" s="36" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J136" s="36">
         <v>99</v>
@@ -19988,10 +19989,10 @@
         <v>505</v>
       </c>
       <c r="M136" s="37" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N136" s="37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O136" s="38"/>
       <c r="P136" s="36"/>
@@ -20109,13 +20110,13 @@
         <v>293</v>
       </c>
       <c r="L137" s="33" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M137" s="34" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="N137" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O137" s="35">
         <v>1</v>
@@ -20243,7 +20244,7 @@
         <v>103</v>
       </c>
       <c r="N138" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O138" s="35">
         <v>1</v>
@@ -20341,13 +20342,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="34" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E139" s="34" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G139" s="34" t="s">
         <v>496</v>
@@ -20356,7 +20357,7 @@
         <v>190</v>
       </c>
       <c r="I139" s="33" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J139" s="33">
         <v>1</v>
@@ -20371,7 +20372,7 @@
         <v>103</v>
       </c>
       <c r="N139" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O139" s="35">
         <v>1</v>
@@ -20499,7 +20500,7 @@
         <v>103</v>
       </c>
       <c r="N140" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O140" s="35">
         <v>1</v>
@@ -20597,13 +20598,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="34" t="s">
+        <v>873</v>
+      </c>
+      <c r="E141" s="34" t="s">
+        <v>872</v>
+      </c>
+      <c r="F141" s="34" t="s">
         <v>874</v>
-      </c>
-      <c r="E141" s="34" t="s">
-        <v>873</v>
-      </c>
-      <c r="F141" s="34" t="s">
-        <v>875</v>
       </c>
       <c r="G141" s="34" t="s">
         <v>137</v>
@@ -20612,7 +20613,7 @@
         <v>190</v>
       </c>
       <c r="I141" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J141" s="33">
         <v>1</v>
@@ -20623,7 +20624,7 @@
       <c r="L141" s="33"/>
       <c r="M141" s="34"/>
       <c r="N141" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O141" s="35">
         <v>1</v>
@@ -20721,13 +20722,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="34" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E142" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G142" s="34" t="s">
         <v>83</v>
@@ -20736,7 +20737,7 @@
         <v>190</v>
       </c>
       <c r="I142" s="33" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J142" s="33">
         <v>1</v>
@@ -20751,7 +20752,7 @@
         <v>103</v>
       </c>
       <c r="N142" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O142" s="35">
         <v>1</v>
@@ -20760,7 +20761,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="34" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="R142" s="13"/>
       <c r="S142" s="2">
@@ -20881,7 +20882,7 @@
         <v>314</v>
       </c>
       <c r="N143" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O143" s="35">
         <v>1</v>
@@ -21231,7 +21232,7 @@
         <v>37</v>
       </c>
       <c r="F146" s="37" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G146" s="37" t="s">
         <v>72</v>
@@ -21252,10 +21253,10 @@
         <v>305</v>
       </c>
       <c r="M146" s="37" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N146" s="37" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O146" s="38"/>
       <c r="P146" s="36"/>
@@ -21349,13 +21350,13 @@
         <v>4</v>
       </c>
       <c r="D147" s="19" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E147" s="19" t="s">
         <v>411</v>
       </c>
       <c r="F147" s="19" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G147" s="19" t="s">
         <v>495</v>
@@ -21376,7 +21377,7 @@
         <v>307</v>
       </c>
       <c r="M147" s="19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N147" s="19"/>
       <c r="O147" s="18"/>
@@ -21471,13 +21472,13 @@
         <v>4</v>
       </c>
       <c r="D148" s="34" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E148" s="34" t="s">
         <v>411</v>
       </c>
       <c r="F148" s="34" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G148" s="34" t="s">
         <v>110</v>
@@ -21486,7 +21487,7 @@
         <v>190</v>
       </c>
       <c r="I148" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J148" s="33">
         <v>3</v>
@@ -21498,10 +21499,10 @@
         <v>305</v>
       </c>
       <c r="M148" s="34" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="N148" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O148" s="35">
         <v>1</v>
@@ -21627,7 +21628,7 @@
         <v>514</v>
       </c>
       <c r="N149" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O149" s="35">
         <v>1</v>
@@ -21729,7 +21730,7 @@
         <v>30</v>
       </c>
       <c r="F150" s="34" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G150" s="34" t="s">
         <v>101</v>
@@ -21750,10 +21751,10 @@
         <v>310</v>
       </c>
       <c r="M150" s="34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N150" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O150" s="35">
         <v>1</v>
@@ -21878,10 +21879,10 @@
         <v>310</v>
       </c>
       <c r="M151" s="34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N151" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O151" s="35">
         <v>1</v>
@@ -22125,10 +22126,10 @@
         <v>307</v>
       </c>
       <c r="M153" s="40" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="N153" s="40" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O153" s="41"/>
       <c r="P153" s="39"/>
@@ -22222,20 +22223,20 @@
         <v>4</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E154" s="19" t="s">
         <v>410</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G154" s="19"/>
       <c r="H154" s="19" t="s">
         <v>190</v>
       </c>
       <c r="I154" s="20" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J154" s="20"/>
       <c r="K154" s="20" t="s">
@@ -22245,7 +22246,7 @@
         <v>20</v>
       </c>
       <c r="M154" s="19" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N154" s="19"/>
       <c r="O154" s="18"/>
@@ -22367,7 +22368,7 @@
         <v>30</v>
       </c>
       <c r="M155" s="19" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="N155" s="19"/>
       <c r="O155" s="18"/>
@@ -22462,13 +22463,13 @@
         <v>5</v>
       </c>
       <c r="D156" s="34" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E156" s="34" t="s">
         <v>532</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G156" s="34" t="s">
         <v>82</v>
@@ -22477,7 +22478,7 @@
         <v>190</v>
       </c>
       <c r="I156" s="33" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J156" s="33"/>
       <c r="K156" s="33" t="s">
@@ -22487,10 +22488,10 @@
         <v>40</v>
       </c>
       <c r="M156" s="34" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22586,22 +22587,22 @@
         <v>5</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E157" s="34" t="s">
         <v>477</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G157" s="34" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H157" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I157" s="33" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J157" s="33">
         <v>2</v>
@@ -22613,10 +22614,10 @@
         <v>305</v>
       </c>
       <c r="M157" s="34" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N157" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O157" s="35">
         <v>1</v>
@@ -22834,13 +22835,13 @@
         <v>5</v>
       </c>
       <c r="D159" s="34" t="s">
+        <v>839</v>
+      </c>
+      <c r="E159" s="34" t="s">
         <v>840</v>
       </c>
-      <c r="E159" s="34" t="s">
+      <c r="F159" s="34" t="s">
         <v>841</v>
-      </c>
-      <c r="F159" s="34" t="s">
-        <v>842</v>
       </c>
       <c r="G159" s="34" t="s">
         <v>129</v>
@@ -22849,7 +22850,7 @@
         <v>190</v>
       </c>
       <c r="I159" s="33" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="J159" s="33">
         <v>99</v>
@@ -22861,10 +22862,10 @@
         <v>40</v>
       </c>
       <c r="M159" s="34" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="N159" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="O159" s="35">
         <v>1</v>
@@ -22960,20 +22961,20 @@
         <v>5</v>
       </c>
       <c r="D160" s="34" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G160" s="34"/>
       <c r="H160" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I160" s="33" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J160" s="33"/>
       <c r="K160" s="33" t="s">
@@ -22983,10 +22984,10 @@
         <v>35</v>
       </c>
       <c r="M160" s="34" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -23112,7 +23113,7 @@
         <v>461</v>
       </c>
       <c r="N161" s="34" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O161" s="35">
         <v>1</v>
@@ -23598,10 +23599,10 @@
         <v>305</v>
       </c>
       <c r="M165" s="34" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="N165" s="34" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O165" s="35">
         <v>1</v>
@@ -23849,7 +23850,7 @@
         <v>103</v>
       </c>
       <c r="N167" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O167" s="35">
         <v>1</v>
@@ -23953,7 +23954,7 @@
         <v>87</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>100</v>
@@ -24099,7 +24100,7 @@
         <v>196</v>
       </c>
       <c r="N169" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O169" s="35">
         <v>1</v>
@@ -24203,7 +24204,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G170" s="34" t="s">
         <v>82</v>
@@ -24227,7 +24228,7 @@
         <v>196</v>
       </c>
       <c r="N170" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O170" s="35">
         <v>1</v>
@@ -24355,7 +24356,7 @@
         <v>196</v>
       </c>
       <c r="N171" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O171" s="35">
         <v>1</v>
@@ -24459,16 +24460,16 @@
         <v>38</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G172" s="34" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H172" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I172" s="33" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J172" s="33">
         <v>1</v>
@@ -24483,7 +24484,7 @@
         <v>196</v>
       </c>
       <c r="N172" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O172" s="35">
         <v>1</v>
@@ -24611,7 +24612,7 @@
         <v>196</v>
       </c>
       <c r="N173" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O173" s="35">
         <v>1</v>
@@ -24739,7 +24740,7 @@
         <v>196</v>
       </c>
       <c r="N174" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O174" s="35">
         <v>1</v>
@@ -24841,7 +24842,7 @@
         <v>38</v>
       </c>
       <c r="F175" s="34" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G175" s="34" t="s">
         <v>145</v>
@@ -24850,7 +24851,7 @@
         <v>190</v>
       </c>
       <c r="I175" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J175" s="33">
         <v>99</v>
@@ -24865,7 +24866,7 @@
         <v>196</v>
       </c>
       <c r="N175" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O175" s="35">
         <v>1</v>
@@ -25479,7 +25480,7 @@
         <v>196</v>
       </c>
       <c r="N180" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O180" s="35">
         <v>1</v>
@@ -25607,7 +25608,7 @@
         <v>196</v>
       </c>
       <c r="N181" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O181" s="35">
         <v>1</v>
@@ -25735,7 +25736,7 @@
         <v>196</v>
       </c>
       <c r="N182" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O182" s="35">
         <v>1</v>
@@ -25860,7 +25861,7 @@
         <v>196</v>
       </c>
       <c r="N183" s="37" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O183" s="38"/>
       <c r="P183" s="36"/>
@@ -26228,7 +26229,7 @@
         <v>103</v>
       </c>
       <c r="N186" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O186" s="35">
         <v>1</v>
@@ -26478,7 +26479,7 @@
         <v>196</v>
       </c>
       <c r="N188" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O188" s="35">
         <v>1</v>
@@ -26948,7 +26949,7 @@
         <v>38</v>
       </c>
       <c r="F192" s="34" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G192" s="34" t="s">
         <v>72</v>
@@ -26972,7 +26973,7 @@
         <v>196</v>
       </c>
       <c r="N192" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O192" s="35">
         <v>1</v>
@@ -27100,7 +27101,7 @@
         <v>196</v>
       </c>
       <c r="N193" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O193" s="35">
         <v>1</v>
@@ -27228,7 +27229,7 @@
         <v>196</v>
       </c>
       <c r="N194" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O194" s="35">
         <v>1</v>
@@ -27356,7 +27357,7 @@
         <v>384</v>
       </c>
       <c r="N195" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O195" s="35">
         <v>1</v>
@@ -27460,7 +27461,7 @@
         <v>55</v>
       </c>
       <c r="F196" s="34" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G196" s="34" t="s">
         <v>72</v>
@@ -27469,7 +27470,7 @@
         <v>190</v>
       </c>
       <c r="I196" s="33" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="J196" s="33">
         <v>4</v>
@@ -27484,7 +27485,7 @@
         <v>384</v>
       </c>
       <c r="N196" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O196" s="35">
         <v>1</v>
@@ -27948,13 +27949,13 @@
         <v>7</v>
       </c>
       <c r="D200" s="34" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E200" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F200" s="34" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G200" s="34" t="s">
         <v>72</v>
@@ -27963,7 +27964,7 @@
         <v>190</v>
       </c>
       <c r="I200" s="33" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="J200" s="33">
         <v>4</v>
@@ -27978,7 +27979,7 @@
         <v>103</v>
       </c>
       <c r="N200" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O200" s="35">
         <v>1</v>
@@ -28076,13 +28077,13 @@
         <v>7</v>
       </c>
       <c r="D201" s="34" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E201" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F201" s="34" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G201" s="34" t="s">
         <v>100</v>
@@ -28091,7 +28092,7 @@
         <v>190</v>
       </c>
       <c r="I201" s="33" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J201" s="33">
         <v>99</v>
@@ -28106,7 +28107,7 @@
         <v>103</v>
       </c>
       <c r="N201" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O201" s="35">
         <v>1</v>
@@ -28210,7 +28211,7 @@
         <v>38</v>
       </c>
       <c r="F202" s="34" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G202" s="34" t="s">
         <v>82</v>
@@ -28234,7 +28235,7 @@
         <v>196</v>
       </c>
       <c r="N202" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O202" s="35">
         <v>1</v>
@@ -28360,7 +28361,7 @@
         <v>196</v>
       </c>
       <c r="N203" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O203" s="35">
         <v>1</v>
@@ -28486,7 +28487,7 @@
         <v>196</v>
       </c>
       <c r="N204" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O204" s="35">
         <v>1</v>
@@ -28599,7 +28600,7 @@
         <v>190</v>
       </c>
       <c r="I205" s="33" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="J205" s="33">
         <v>99</v>
@@ -28614,7 +28615,7 @@
         <v>196</v>
       </c>
       <c r="N205" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O205" s="35">
         <v>1</v>
@@ -28712,13 +28713,13 @@
         <v>7</v>
       </c>
       <c r="D206" s="34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E206" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G206" s="34" t="s">
         <v>72</v>
@@ -28727,7 +28728,7 @@
         <v>190</v>
       </c>
       <c r="I206" s="33" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J206" s="33">
         <v>4</v>
@@ -28742,7 +28743,7 @@
         <v>196</v>
       </c>
       <c r="N206" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O206" s="35">
         <v>1</v>
@@ -28838,13 +28839,13 @@
         <v>7</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E207" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G207" s="34" t="s">
         <v>88</v>
@@ -28853,7 +28854,7 @@
         <v>190</v>
       </c>
       <c r="I207" s="33" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="J207" s="33">
         <v>2</v>
@@ -28868,7 +28869,7 @@
         <v>196</v>
       </c>
       <c r="N207" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O207" s="35">
         <v>1</v>
@@ -28970,7 +28971,7 @@
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G208" s="34" t="s">
         <v>82</v>
@@ -28994,7 +28995,7 @@
         <v>196</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
@@ -29122,7 +29123,7 @@
         <v>103</v>
       </c>
       <c r="N209" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O209" s="35">
         <v>1</v>
@@ -29494,7 +29495,7 @@
         <v>103</v>
       </c>
       <c r="N212" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O212" s="35">
         <v>1</v>
@@ -29622,7 +29623,7 @@
         <v>103</v>
       </c>
       <c r="N213" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O213" s="35">
         <v>1</v>
@@ -29750,7 +29751,7 @@
         <v>103</v>
       </c>
       <c r="N214" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O214" s="35">
         <v>1</v>
@@ -29851,7 +29852,7 @@
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G215" s="34" t="s">
         <v>145</v>
@@ -29860,7 +29861,7 @@
         <v>190</v>
       </c>
       <c r="I215" s="33" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="J215" s="33">
         <v>99</v>
@@ -29875,7 +29876,7 @@
         <v>103</v>
       </c>
       <c r="N215" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O215" s="35">
         <v>1</v>
@@ -30000,7 +30001,7 @@
         <v>312</v>
       </c>
       <c r="N216" s="37" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O216" s="38"/>
       <c r="P216" s="36"/>
@@ -30124,7 +30125,7 @@
         <v>196</v>
       </c>
       <c r="N217" s="34" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="O217" s="35">
         <v>1</v>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA60B790-70E9-4F01-B69B-847B14EF757C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1069DE4B-8219-4A82-9E45-2F99584F873E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="916">
   <si>
     <t>Recensore</t>
   </si>
@@ -10590,49 +10590,51 @@
       <c r="AT60" s="13"/>
     </row>
     <row r="61" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20">
-        <v>0</v>
-      </c>
-      <c r="B61" s="20">
-        <v>1</v>
-      </c>
-      <c r="C61" s="20">
+      <c r="A61" s="36">
+        <v>0</v>
+      </c>
+      <c r="B61" s="36">
+        <v>1</v>
+      </c>
+      <c r="C61" s="36">
         <v>5</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="37" t="s">
         <v>390</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="F61" s="37" t="s">
         <v>391</v>
       </c>
-      <c r="G61" s="19" t="s">
+      <c r="G61" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="36" t="s">
         <v>392</v>
       </c>
-      <c r="J61" s="20">
+      <c r="J61" s="36">
         <v>5</v>
       </c>
-      <c r="K61" s="20" t="s">
+      <c r="K61" s="36" t="s">
         <v>298</v>
       </c>
-      <c r="L61" s="20" t="s">
+      <c r="L61" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="M61" s="19" t="s">
+      <c r="M61" s="37" t="s">
         <v>675</v>
       </c>
-      <c r="N61" s="19"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="20"/>
-      <c r="Q61" s="19"/>
+      <c r="N61" s="37" t="s">
+        <v>850</v>
+      </c>
+      <c r="O61" s="38"/>
+      <c r="P61" s="36"/>
+      <c r="Q61" s="37"/>
       <c r="R61" s="13"/>
       <c r="S61" s="2">
         <f t="shared" si="23"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1069DE4B-8219-4A82-9E45-2F99584F873E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0F5224-3B75-494E-A0DA-63986F3B745B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -3722,15 +3722,15 @@
       </c>
       <c r="F4" s="10">
         <f>+AE6</f>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" s="10">
         <f>+AG6</f>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H4" s="7">
         <f>+E4-G4</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>16</v>
@@ -3752,15 +3752,15 @@
       </c>
       <c r="F5" s="12">
         <f>+F3+F4</f>
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G5" s="12">
         <f>+G3+G4</f>
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H5" s="12">
         <f>+H3+H4</f>
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>615</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="1"/>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="1"/>
@@ -6742,49 +6742,51 @@
       <c r="AT29" s="13"/>
     </row>
     <row r="30" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36">
-        <v>0</v>
-      </c>
-      <c r="B30" s="36">
-        <v>1</v>
-      </c>
-      <c r="C30" s="36">
+      <c r="A30" s="33">
+        <v>0</v>
+      </c>
+      <c r="B30" s="33">
+        <v>1</v>
+      </c>
+      <c r="C30" s="33">
         <v>2</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="G30" s="37" t="s">
+      <c r="G30" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H30" s="37" t="s">
+      <c r="H30" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I30" s="36" t="s">
+      <c r="I30" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="J30" s="36">
-        <v>1</v>
-      </c>
-      <c r="K30" s="36" t="s">
+      <c r="J30" s="33">
+        <v>1</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="L30" s="36"/>
-      <c r="M30" s="37" t="s">
+      <c r="L30" s="33"/>
+      <c r="M30" s="34" t="s">
         <v>793</v>
       </c>
-      <c r="N30" s="37" t="s">
-        <v>851</v>
-      </c>
-      <c r="O30" s="38"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="37"/>
+      <c r="N30" s="34" t="s">
+        <v>856</v>
+      </c>
+      <c r="O30" s="35">
+        <v>1</v>
+      </c>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="34"/>
       <c r="R30" s="13"/>
       <c r="S30" s="2">
         <f t="shared" si="23"/>
@@ -6833,7 +6835,7 @@
       </c>
       <c r="AE30" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" s="2">
         <f t="shared" si="19"/>
@@ -6841,7 +6843,7 @@
       </c>
       <c r="AG30" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" s="2">
         <f t="shared" si="21"/>
@@ -6864,51 +6866,53 @@
       <c r="AT30" s="13"/>
     </row>
     <row r="31" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36">
-        <v>0</v>
-      </c>
-      <c r="B31" s="36">
-        <v>1</v>
-      </c>
-      <c r="C31" s="36">
+      <c r="A31" s="33">
+        <v>0</v>
+      </c>
+      <c r="B31" s="33">
+        <v>1</v>
+      </c>
+      <c r="C31" s="33">
         <v>2</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="34" t="s">
         <v>556</v>
       </c>
-      <c r="G31" s="37" t="s">
+      <c r="G31" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H31" s="37" t="s">
+      <c r="H31" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="I31" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="J31" s="36">
-        <v>1</v>
-      </c>
-      <c r="K31" s="36" t="s">
+      <c r="J31" s="33">
+        <v>1</v>
+      </c>
+      <c r="K31" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="L31" s="36" t="s">
+      <c r="L31" s="33" t="s">
         <v>791</v>
       </c>
-      <c r="M31" s="37" t="s">
+      <c r="M31" s="34" t="s">
         <v>702</v>
       </c>
-      <c r="N31" s="37" t="s">
-        <v>850</v>
-      </c>
-      <c r="O31" s="38"/>
-      <c r="P31" s="36"/>
-      <c r="Q31" s="37" t="s">
+      <c r="N31" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="O31" s="35">
+        <v>1</v>
+      </c>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="34" t="s">
         <v>896</v>
       </c>
       <c r="R31" s="13"/>
@@ -6959,7 +6963,7 @@
       </c>
       <c r="AE31" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" s="2">
         <f t="shared" si="19"/>
@@ -6967,7 +6971,7 @@
       </c>
       <c r="AG31" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" s="2">
         <f t="shared" si="21"/>
@@ -11950,51 +11954,53 @@
       <c r="AT71" s="13"/>
     </row>
     <row r="72" spans="1:46" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="36">
-        <v>0</v>
-      </c>
-      <c r="B72" s="36">
-        <v>1</v>
-      </c>
-      <c r="C72" s="36">
+      <c r="A72" s="33">
+        <v>0</v>
+      </c>
+      <c r="B72" s="33">
+        <v>1</v>
+      </c>
+      <c r="C72" s="33">
         <v>5</v>
       </c>
-      <c r="D72" s="37" t="s">
+      <c r="D72" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="E72" s="37" t="s">
+      <c r="E72" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="F72" s="37" t="s">
+      <c r="F72" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="G72" s="37" t="s">
+      <c r="G72" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="H72" s="37" t="s">
+      <c r="H72" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I72" s="36" t="s">
+      <c r="I72" s="33" t="s">
         <v>438</v>
       </c>
-      <c r="J72" s="36">
-        <v>1</v>
-      </c>
-      <c r="K72" s="36" t="s">
+      <c r="J72" s="33">
+        <v>1</v>
+      </c>
+      <c r="K72" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="L72" s="36" t="s">
+      <c r="L72" s="33" t="s">
         <v>673</v>
       </c>
-      <c r="M72" s="37" t="s">
+      <c r="M72" s="34" t="s">
         <v>712</v>
       </c>
-      <c r="N72" s="37" t="s">
-        <v>850</v>
-      </c>
-      <c r="O72" s="38"/>
-      <c r="P72" s="36"/>
-      <c r="Q72" s="37"/>
+      <c r="N72" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="O72" s="35">
+        <v>1</v>
+      </c>
+      <c r="P72" s="33"/>
+      <c r="Q72" s="34"/>
       <c r="R72" s="13"/>
       <c r="S72" s="2">
         <f t="shared" si="23"/>
@@ -12043,7 +12049,7 @@
       </c>
       <c r="AE72" s="2">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" s="2">
         <f t="shared" si="19"/>
@@ -12051,7 +12057,7 @@
       </c>
       <c r="AG72" s="2">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH72" s="2">
         <f t="shared" si="21"/>
